--- a/arena_enrichment/output/arena_leaderboard_enriched.xlsx
+++ b/arena_enrichment/output/arena_leaderboard_enriched.xlsx
@@ -671,29 +671,29 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>glm-5.3-max</t>
+          <t>kimi-k3-max</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1485.592204205781</v>
+        <v>1484.765988463367</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1479.072789706068</v>
+        <v>1479.540297028585</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1492.111618705495</v>
+        <v>1489.991679898149</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>10559</v>
+        <v>20987</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Z.ai</t>
+          <t>Moonshot</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Kimi K3 license</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -742,29 +742,29 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>kimi-k3-max</t>
+          <t>glm-5.3-max</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1484.54350958167</v>
+        <v>1483.017935544073</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1479.310617028643</v>
+        <v>1476.577518950137</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1489.776402134697</v>
+        <v>1489.458352138009</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>20911</v>
+        <v>10960</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Moonshot</t>
+          <t>Z.ai</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Kimi K3 license</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -817,16 +817,16 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1475.028268889917</v>
+        <v>1475.404453561832</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1468.338279101925</v>
+        <v>1468.843465489025</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1481.718258677909</v>
+        <v>1481.965441634638</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>9479</v>
+        <v>10038</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -888,16 +888,16 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1472.320217907826</v>
+        <v>1472.096810454114</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1467.697714737121</v>
+        <v>1467.481222561827</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1476.942721078532</v>
+        <v>1476.712398346403</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>36471</v>
+        <v>36798</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -959,16 +959,16 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1467.530400231424</v>
+        <v>1467.419793477693</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1463.684585917028</v>
+        <v>1463.587186905816</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1471.37621454582</v>
+        <v>1471.25240004957</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>60523</v>
+        <v>60919</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -1030,16 +1030,16 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1465.43906786557</v>
+        <v>1465.51269490208</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1461.55408581988</v>
+        <v>1461.641443689336</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1469.324049911259</v>
+        <v>1469.383946114824</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>48503</v>
+        <v>48901</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -1101,16 +1101,16 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1462.107397204858</v>
+        <v>1463.361459504057</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1455.182524200707</v>
+        <v>1456.524582790941</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1469.032270209008</v>
+        <v>1470.198336217174</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>8623</v>
+        <v>9008</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -1172,16 +1172,16 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1460.506478160575</v>
+        <v>1460.444505965357</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1455.972590570844</v>
+        <v>1455.912819531686</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1465.040365750306</v>
+        <v>1464.976192399029</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>37497</v>
+        <v>37502</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -1323,16 +1323,16 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1457.576258526869</v>
+        <v>1457.642588383018</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1453.229189509882</v>
+        <v>1453.295826191549</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1461.923327543856</v>
+        <v>1461.989350574488</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>27600</v>
+        <v>27605</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
@@ -1474,16 +1474,16 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1457.495497680818</v>
+        <v>1457.340187662021</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1453.489812596973</v>
+        <v>1453.335577934442</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1461.501182764662</v>
+        <v>1461.344797389601</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>54142</v>
+        <v>54130</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
@@ -1625,16 +1625,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1455.884222628109</v>
+        <v>1455.778960201683</v>
       </c>
       <c r="D12" t="n">
-        <v>1448.658857930336</v>
+        <v>1448.566799127387</v>
       </c>
       <c r="E12" t="n">
-        <v>1463.109587325882</v>
+        <v>1462.991121275978</v>
       </c>
       <c r="F12" t="n">
-        <v>8023</v>
+        <v>8047</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1776,16 +1776,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1454.915210070168</v>
+        <v>1454.710248662347</v>
       </c>
       <c r="D13" t="n">
-        <v>1450.83715974268</v>
+        <v>1450.634324562247</v>
       </c>
       <c r="E13" t="n">
-        <v>1458.993260397656</v>
+        <v>1458.786172762447</v>
       </c>
       <c r="F13" t="n">
-        <v>51494</v>
+        <v>51485</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1847,16 +1847,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1451.099041300087</v>
+        <v>1451.085822407218</v>
       </c>
       <c r="D14" t="n">
-        <v>1443.514016780242</v>
+        <v>1443.504845041369</v>
       </c>
       <c r="E14" t="n">
-        <v>1458.684065819933</v>
+        <v>1458.666799773066</v>
       </c>
       <c r="F14" t="n">
-        <v>5891</v>
+        <v>5894</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1998,13 +1998,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1450.313754662983</v>
+        <v>1450.350469230902</v>
       </c>
       <c r="D15" t="n">
-        <v>1446.953341569618</v>
+        <v>1446.990868477258</v>
       </c>
       <c r="E15" t="n">
-        <v>1453.674167756348</v>
+        <v>1453.710069984546</v>
       </c>
       <c r="F15" t="n">
         <v>70513</v>
@@ -2149,16 +2149,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1442.141651162135</v>
+        <v>1441.829384488417</v>
       </c>
       <c r="D16" t="n">
-        <v>1438.819732429533</v>
+        <v>1438.518502155283</v>
       </c>
       <c r="E16" t="n">
-        <v>1445.463569894736</v>
+        <v>1445.140266821551</v>
       </c>
       <c r="F16" t="n">
-        <v>76643</v>
+        <v>77007</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -2296,148 +2296,68 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>minimax-m3</t>
+          <t>glm-4.7</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1441.830134812853</v>
+        <v>1441.733453705634</v>
       </c>
       <c r="D17" t="n">
-        <v>1437.607140858492</v>
+        <v>1435.606959826073</v>
       </c>
       <c r="E17" t="n">
-        <v>1446.053128767215</v>
+        <v>1447.859947585195</v>
       </c>
       <c r="F17" t="n">
-        <v>48130</v>
+        <v>11893</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>MiniMax</t>
+          <t>Z.ai</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>MiniMax Community License</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>428</v>
-      </c>
-      <c r="J17" t="n">
-        <v>23</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>aa_single_scrape</t>
-        </is>
-      </c>
-      <c r="M17" t="n">
-        <v>856</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1070</v>
-      </c>
-      <c r="O17" t="n">
-        <v>428</v>
-      </c>
-      <c r="P17" t="n">
-        <v>535</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>214</v>
-      </c>
-      <c r="R17" t="n">
-        <v>267.5</v>
-      </c>
-      <c r="S17" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T17" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U17" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V17" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W17" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y17" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z17" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA17" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB17" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC17" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD17" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AE17" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF17" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG17" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -2447,68 +2367,148 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>glm-4.7</t>
+          <t>minimax-m3</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1441.726649784012</v>
+        <v>1441.250343150466</v>
       </c>
       <c r="D18" t="n">
-        <v>1435.599186312459</v>
+        <v>1437.038559496921</v>
       </c>
       <c r="E18" t="n">
-        <v>1447.854113255565</v>
+        <v>1445.46212680401</v>
       </c>
       <c r="F18" t="n">
-        <v>11892</v>
+        <v>48540</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Z.ai</t>
+          <t>MiniMax</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+          <t>MiniMax Community License</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>428</v>
+      </c>
+      <c r="J18" t="n">
+        <v>23</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr"/>
-      <c r="AB18" t="inlineStr"/>
-      <c r="AC18" t="inlineStr"/>
-      <c r="AD18" t="inlineStr"/>
-      <c r="AE18" t="inlineStr"/>
-      <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="inlineStr"/>
+          <t>aa_single_scrape</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>856</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1070</v>
+      </c>
+      <c r="O18" t="n">
+        <v>428</v>
+      </c>
+      <c r="P18" t="n">
+        <v>535</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>214</v>
+      </c>
+      <c r="R18" t="n">
+        <v>267.5</v>
+      </c>
+      <c r="S18" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T18" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U18" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V18" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W18" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X18" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y18" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z18" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA18" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB18" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC18" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD18" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE18" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF18" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG18" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -2522,16 +2522,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1439.242277025689</v>
+        <v>1440.121967405652</v>
       </c>
       <c r="D19" t="n">
-        <v>1434.286150188</v>
+        <v>1435.193566134788</v>
       </c>
       <c r="E19" t="n">
-        <v>1444.198403863378</v>
+        <v>1445.050368676516</v>
       </c>
       <c r="F19" t="n">
-        <v>25509</v>
+        <v>25922</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -2673,16 +2673,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1438.108275587755</v>
+        <v>1437.93628921571</v>
       </c>
       <c r="D20" t="n">
-        <v>1433.900959802821</v>
+        <v>1433.730016729036</v>
       </c>
       <c r="E20" t="n">
-        <v>1442.315591372689</v>
+        <v>1442.142561702384</v>
       </c>
       <c r="F20" t="n">
-        <v>48595</v>
+        <v>48597</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -2744,13 +2744,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1437.991139131659</v>
+        <v>1437.909567630927</v>
       </c>
       <c r="D21" t="n">
-        <v>1430.371045037949</v>
+        <v>1430.289453726562</v>
       </c>
       <c r="E21" t="n">
-        <v>1445.611233225369</v>
+        <v>1445.529681535292</v>
       </c>
       <c r="F21" t="n">
         <v>5804</v>
@@ -2895,16 +2895,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1437.779711749466</v>
+        <v>1437.095473920987</v>
       </c>
       <c r="D22" t="n">
-        <v>1431.240527700039</v>
+        <v>1430.634874461472</v>
       </c>
       <c r="E22" t="n">
-        <v>1444.318895798893</v>
+        <v>1443.556073380502</v>
       </c>
       <c r="F22" t="n">
-        <v>10256</v>
+        <v>10697</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -3046,16 +3046,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1435.575319161382</v>
+        <v>1435.565287041955</v>
       </c>
       <c r="D23" t="n">
-        <v>1431.430049922282</v>
+        <v>1431.422564808053</v>
       </c>
       <c r="E23" t="n">
-        <v>1439.720588400482</v>
+        <v>1439.708009275857</v>
       </c>
       <c r="F23" t="n">
-        <v>48890</v>
+        <v>48887</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -3197,16 +3197,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1433.453709917578</v>
+        <v>1433.614497741101</v>
       </c>
       <c r="D24" t="n">
-        <v>1429.113297231956</v>
+        <v>1429.277550530529</v>
       </c>
       <c r="E24" t="n">
-        <v>1437.7941226032</v>
+        <v>1437.951444951674</v>
       </c>
       <c r="F24" t="n">
-        <v>44446</v>
+        <v>44466</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -3268,16 +3268,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1431.025564971653</v>
+        <v>1430.911202794813</v>
       </c>
       <c r="D25" t="n">
-        <v>1424.382502971281</v>
+        <v>1424.268016783441</v>
       </c>
       <c r="E25" t="n">
-        <v>1437.668626972026</v>
+        <v>1437.554388806185</v>
       </c>
       <c r="F25" t="n">
-        <v>7990</v>
+        <v>7987</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -3419,16 +3419,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1430.191397667885</v>
+        <v>1430.133075454599</v>
       </c>
       <c r="D26" t="n">
-        <v>1427.043639141294</v>
+        <v>1426.986598791947</v>
       </c>
       <c r="E26" t="n">
-        <v>1433.339156194477</v>
+        <v>1433.279552117251</v>
       </c>
       <c r="F26" t="n">
-        <v>61079</v>
+        <v>61088</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -3570,16 +3570,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1427.028272402935</v>
+        <v>1427.15574799922</v>
       </c>
       <c r="D27" t="n">
-        <v>1417.05169042692</v>
+        <v>1417.179519776562</v>
       </c>
       <c r="E27" t="n">
-        <v>1437.004854378949</v>
+        <v>1437.131976221878</v>
       </c>
       <c r="F27" t="n">
-        <v>3665</v>
+        <v>3666</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -3721,16 +3721,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1426.484996878381</v>
+        <v>1426.346545099959</v>
       </c>
       <c r="D28" t="n">
-        <v>1419.927860458745</v>
+        <v>1419.788672295837</v>
       </c>
       <c r="E28" t="n">
-        <v>1433.042133298018</v>
+        <v>1432.904417904082</v>
       </c>
       <c r="F28" t="n">
-        <v>10998</v>
+        <v>10996</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -3792,16 +3792,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1425.578631429396</v>
+        <v>1425.587865203899</v>
       </c>
       <c r="D29" t="n">
-        <v>1418.569331066932</v>
+        <v>1418.580723400662</v>
       </c>
       <c r="E29" t="n">
-        <v>1432.587931791859</v>
+        <v>1432.595007007136</v>
       </c>
       <c r="F29" t="n">
-        <v>10691</v>
+        <v>10693</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -3943,16 +3943,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1425.298226946014</v>
+        <v>1425.279766308678</v>
       </c>
       <c r="D30" t="n">
-        <v>1418.70811660703</v>
+        <v>1418.688135327046</v>
       </c>
       <c r="E30" t="n">
-        <v>1431.888337284998</v>
+        <v>1431.87139729031</v>
       </c>
       <c r="F30" t="n">
-        <v>8908</v>
+        <v>8905</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -4014,16 +4014,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1425.171305943913</v>
+        <v>1425.180109239172</v>
       </c>
       <c r="D31" t="n">
-        <v>1421.61906082825</v>
+        <v>1421.628721498453</v>
       </c>
       <c r="E31" t="n">
-        <v>1428.723551059577</v>
+        <v>1428.73149697989</v>
       </c>
       <c r="F31" t="n">
-        <v>46464</v>
+        <v>46458</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -4085,16 +4085,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1424.792031822342</v>
+        <v>1424.743961543189</v>
       </c>
       <c r="D32" t="n">
-        <v>1420.857034421803</v>
+        <v>1420.809728877601</v>
       </c>
       <c r="E32" t="n">
-        <v>1428.727029222881</v>
+        <v>1428.678194208778</v>
       </c>
       <c r="F32" t="n">
-        <v>35065</v>
+        <v>35061</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1423.074290775332</v>
+        <v>1423.029368299067</v>
       </c>
       <c r="D33" t="n">
-        <v>1420.486349473</v>
+        <v>1420.442626324724</v>
       </c>
       <c r="E33" t="n">
-        <v>1425.662232077665</v>
+        <v>1425.616110273411</v>
       </c>
       <c r="F33" t="n">
-        <v>95656</v>
+        <v>95670</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -4307,16 +4307,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1422.498089088644</v>
+        <v>1422.425311214995</v>
       </c>
       <c r="D34" t="n">
-        <v>1418.854573998914</v>
+        <v>1418.782637805199</v>
       </c>
       <c r="E34" t="n">
-        <v>1426.141604178374</v>
+        <v>1426.067984624792</v>
       </c>
       <c r="F34" t="n">
-        <v>40496</v>
+        <v>40499</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -4378,16 +4378,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1422.131067183415</v>
+        <v>1422.305320425359</v>
       </c>
       <c r="D35" t="n">
-        <v>1415.701107269259</v>
+        <v>1415.876050283005</v>
       </c>
       <c r="E35" t="n">
-        <v>1428.561027097571</v>
+        <v>1428.734590567712</v>
       </c>
       <c r="F35" t="n">
-        <v>11756</v>
+        <v>11760</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -4449,16 +4449,16 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1421.422553519575</v>
+        <v>1421.368693662487</v>
       </c>
       <c r="D36" t="n">
-        <v>1415.731477270505</v>
+        <v>1415.679522566481</v>
       </c>
       <c r="E36" t="n">
-        <v>1427.113629768644</v>
+        <v>1427.057864758492</v>
       </c>
       <c r="F36" t="n">
-        <v>18089</v>
+        <v>18091</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -4520,16 +4520,16 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1418.045844290529</v>
+        <v>1418.055969275088</v>
       </c>
       <c r="D37" t="n">
-        <v>1411.513000675953</v>
+        <v>1411.523099908822</v>
       </c>
       <c r="E37" t="n">
-        <v>1424.578687905105</v>
+        <v>1424.588838641355</v>
       </c>
       <c r="F37" t="n">
-        <v>11566</v>
+        <v>11568</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -4671,16 +4671,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1417.765840674333</v>
+        <v>1417.768634531463</v>
       </c>
       <c r="D38" t="n">
-        <v>1412.859598171272</v>
+        <v>1412.86153925468</v>
       </c>
       <c r="E38" t="n">
-        <v>1422.672083177393</v>
+        <v>1422.675729808247</v>
       </c>
       <c r="F38" t="n">
-        <v>27027</v>
+        <v>27029</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -4822,13 +4822,13 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1417.451376075758</v>
+        <v>1417.433459097317</v>
       </c>
       <c r="D39" t="n">
-        <v>1407.339240109267</v>
+        <v>1407.321300350448</v>
       </c>
       <c r="E39" t="n">
-        <v>1427.563512042249</v>
+        <v>1427.545617844187</v>
       </c>
       <c r="F39" t="n">
         <v>3369</v>
@@ -4893,16 +4893,16 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1417.331730155427</v>
+        <v>1417.307825843851</v>
       </c>
       <c r="D40" t="n">
-        <v>1411.270334927559</v>
+        <v>1411.246573315888</v>
       </c>
       <c r="E40" t="n">
-        <v>1423.393125383295</v>
+        <v>1423.369078371813</v>
       </c>
       <c r="F40" t="n">
-        <v>14604</v>
+        <v>14607</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -4964,16 +4964,16 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1416.929095405213</v>
+        <v>1416.777978713208</v>
       </c>
       <c r="D41" t="n">
-        <v>1412.551429158421</v>
+        <v>1412.401427628401</v>
       </c>
       <c r="E41" t="n">
-        <v>1421.306761652006</v>
+        <v>1421.154529798016</v>
       </c>
       <c r="F41" t="n">
-        <v>28349</v>
+        <v>28359</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -5115,16 +5115,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1415.978433896952</v>
+        <v>1415.981023438076</v>
       </c>
       <c r="D42" t="n">
-        <v>1409.303874158684</v>
+        <v>1409.306581411861</v>
       </c>
       <c r="E42" t="n">
-        <v>1422.65299363522</v>
+        <v>1422.655465464291</v>
       </c>
       <c r="F42" t="n">
-        <v>11462</v>
+        <v>11460</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -5182,29 +5182,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-terminus</t>
+          <t>minimax-m2.7</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1414.766720368171</v>
+        <v>1415.173845342476</v>
       </c>
       <c r="D43" t="n">
-        <v>1405.052665883166</v>
+        <v>1411.56784970984</v>
       </c>
       <c r="E43" t="n">
-        <v>1424.480774853177</v>
+        <v>1418.779840975111</v>
       </c>
       <c r="F43" t="n">
-        <v>3611</v>
+        <v>69169</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>MiniMax</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Modified MIT</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5253,29 +5253,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>minimax-m2.7</t>
+          <t>deepseek-v3.1-terminus</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1414.74217885247</v>
+        <v>1414.748273479899</v>
       </c>
       <c r="D44" t="n">
-        <v>1411.118404347036</v>
+        <v>1405.034252730385</v>
       </c>
       <c r="E44" t="n">
-        <v>1418.365953357903</v>
+        <v>1424.462294229412</v>
       </c>
       <c r="F44" t="n">
-        <v>68700</v>
+        <v>3611</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>MiniMax</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Modified MIT</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5328,13 +5328,13 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1413.939681602459</v>
+        <v>1414.068430473983</v>
       </c>
       <c r="D45" t="n">
-        <v>1407.37435294747</v>
+        <v>1407.502891386036</v>
       </c>
       <c r="E45" t="n">
-        <v>1420.505010257448</v>
+        <v>1420.63396956193</v>
       </c>
       <c r="F45" t="n">
         <v>11219</v>
@@ -5479,16 +5479,16 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1413.302588967827</v>
+        <v>1412.993950097514</v>
       </c>
       <c r="D46" t="n">
-        <v>1410.269521624133</v>
+        <v>1409.967952098212</v>
       </c>
       <c r="E46" t="n">
-        <v>1416.335656311521</v>
+        <v>1416.019948096815</v>
       </c>
       <c r="F46" t="n">
-        <v>68591</v>
+        <v>69028</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -5630,16 +5630,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1412.526462982839</v>
+        <v>1412.692710389082</v>
       </c>
       <c r="D47" t="n">
-        <v>1404.982616481045</v>
+        <v>1405.152381365332</v>
       </c>
       <c r="E47" t="n">
-        <v>1420.070309484634</v>
+        <v>1420.233039412831</v>
       </c>
       <c r="F47" t="n">
-        <v>6606</v>
+        <v>6614</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -5701,16 +5701,16 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1411.346318567627</v>
+        <v>1411.302867511255</v>
       </c>
       <c r="D48" t="n">
-        <v>1406.408447682047</v>
+        <v>1406.364740470774</v>
       </c>
       <c r="E48" t="n">
-        <v>1416.284189453207</v>
+        <v>1416.240994551737</v>
       </c>
       <c r="F48" t="n">
-        <v>23707</v>
+        <v>23712</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1407.915410528693</v>
+        <v>1407.880961593894</v>
       </c>
       <c r="D49" t="n">
-        <v>1403.514866485021</v>
+        <v>1403.481564510898</v>
       </c>
       <c r="E49" t="n">
-        <v>1412.315954572364</v>
+        <v>1412.28035867689</v>
       </c>
       <c r="F49" t="n">
-        <v>27228</v>
+        <v>27227</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -6003,16 +6003,16 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1404.285038751059</v>
+        <v>1404.608375964015</v>
       </c>
       <c r="D50" t="n">
-        <v>1398.785402944343</v>
+        <v>1399.146286110081</v>
       </c>
       <c r="E50" t="n">
-        <v>1409.784674557774</v>
+        <v>1410.070465817949</v>
       </c>
       <c r="F50" t="n">
-        <v>18408</v>
+        <v>18844</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -6154,16 +6154,16 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1402.497472953545</v>
+        <v>1402.520988354147</v>
       </c>
       <c r="D51" t="n">
-        <v>1397.962532089559</v>
+        <v>1397.985353398939</v>
       </c>
       <c r="E51" t="n">
-        <v>1407.03241381753</v>
+        <v>1407.056623309356</v>
       </c>
       <c r="F51" t="n">
-        <v>37381</v>
+        <v>37389</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -6305,16 +6305,16 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1401.393088804601</v>
+        <v>1401.33714249126</v>
       </c>
       <c r="D52" t="n">
-        <v>1394.973207726857</v>
+        <v>1394.915265437951</v>
       </c>
       <c r="E52" t="n">
-        <v>1407.812969882345</v>
+        <v>1407.759019544569</v>
       </c>
       <c r="F52" t="n">
-        <v>11162</v>
+        <v>11154</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -6456,16 +6456,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1400.030440375623</v>
+        <v>1400.055426959004</v>
       </c>
       <c r="D53" t="n">
-        <v>1393.445798961224</v>
+        <v>1393.470452142837</v>
       </c>
       <c r="E53" t="n">
-        <v>1406.615081790022</v>
+        <v>1406.64040177517</v>
       </c>
       <c r="F53" t="n">
-        <v>8797</v>
+        <v>8796</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -6607,16 +6607,16 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1399.408596798159</v>
+        <v>1399.32825767228</v>
       </c>
       <c r="D54" t="n">
-        <v>1394.608594097324</v>
+        <v>1394.529723068331</v>
       </c>
       <c r="E54" t="n">
-        <v>1404.208599498994</v>
+        <v>1404.126792276229</v>
       </c>
       <c r="F54" t="n">
-        <v>22527</v>
+        <v>22529</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -6758,13 +6758,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1398.035047670959</v>
+        <v>1398.035776349719</v>
       </c>
       <c r="D55" t="n">
-        <v>1393.141977360099</v>
+        <v>1393.142221084037</v>
       </c>
       <c r="E55" t="n">
-        <v>1402.92811798182</v>
+        <v>1402.929331615401</v>
       </c>
       <c r="F55" t="n">
         <v>18524</v>
@@ -6909,16 +6909,16 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1395.761102374601</v>
+        <v>1395.728783805527</v>
       </c>
       <c r="D56" t="n">
-        <v>1391.858678395953</v>
+        <v>1391.826423628811</v>
       </c>
       <c r="E56" t="n">
-        <v>1399.66352635325</v>
+        <v>1399.631143982243</v>
       </c>
       <c r="F56" t="n">
-        <v>44781</v>
+        <v>44787</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -7060,13 +7060,13 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1395.238560964129</v>
+        <v>1395.150210247945</v>
       </c>
       <c r="D57" t="n">
-        <v>1388.382215684954</v>
+        <v>1388.294816650495</v>
       </c>
       <c r="E57" t="n">
-        <v>1402.094906243305</v>
+        <v>1402.005603845395</v>
       </c>
       <c r="F57" t="n">
         <v>7780</v>
@@ -7211,16 +7211,16 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1395.072795392223</v>
+        <v>1394.966280676535</v>
       </c>
       <c r="D58" t="n">
-        <v>1390.748210857904</v>
+        <v>1390.643539003625</v>
       </c>
       <c r="E58" t="n">
-        <v>1399.397379926542</v>
+        <v>1399.289022349446</v>
       </c>
       <c r="F58" t="n">
-        <v>29033</v>
+        <v>29043</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -7362,16 +7362,16 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1394.232158080758</v>
+        <v>1394.134297560689</v>
       </c>
       <c r="D59" t="n">
-        <v>1390.592256023663</v>
+        <v>1390.496349252427</v>
       </c>
       <c r="E59" t="n">
-        <v>1397.872060137854</v>
+        <v>1397.772245868952</v>
       </c>
       <c r="F59" t="n">
-        <v>57129</v>
+        <v>57137</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -7433,16 +7433,16 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1391.955902669925</v>
+        <v>1391.869035413959</v>
       </c>
       <c r="D60" t="n">
-        <v>1388.399726369188</v>
+        <v>1388.31459451962</v>
       </c>
       <c r="E60" t="n">
-        <v>1395.512078970662</v>
+        <v>1395.423476308299</v>
       </c>
       <c r="F60" t="n">
-        <v>46110</v>
+        <v>46116</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -7504,16 +7504,16 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1390.332605033225</v>
+        <v>1390.322201308044</v>
       </c>
       <c r="D61" t="n">
-        <v>1386.352882012253</v>
+        <v>1386.342790722012</v>
       </c>
       <c r="E61" t="n">
-        <v>1394.312328054196</v>
+        <v>1394.301611894075</v>
       </c>
       <c r="F61" t="n">
-        <v>40852</v>
+        <v>40843</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -7575,16 +7575,16 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1387.486274147753</v>
+        <v>1387.505295091868</v>
       </c>
       <c r="D62" t="n">
-        <v>1382.496605274336</v>
+        <v>1382.515924439447</v>
       </c>
       <c r="E62" t="n">
-        <v>1392.475943021171</v>
+        <v>1392.494665744289</v>
       </c>
       <c r="F62" t="n">
-        <v>25091</v>
+        <v>25089</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -7726,16 +7726,16 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1385.998342411834</v>
+        <v>1386.138757395958</v>
       </c>
       <c r="D63" t="n">
-        <v>1379.717494411719</v>
+        <v>1379.859174075734</v>
       </c>
       <c r="E63" t="n">
-        <v>1392.279190411949</v>
+        <v>1392.418340716182</v>
       </c>
       <c r="F63" t="n">
-        <v>10742</v>
+        <v>10739</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -7797,16 +7797,16 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1383.921072390575</v>
+        <v>1383.788625927177</v>
       </c>
       <c r="D64" t="n">
-        <v>1378.657840113151</v>
+        <v>1378.52595620125</v>
       </c>
       <c r="E64" t="n">
-        <v>1389.184304667998</v>
+        <v>1389.051295653104</v>
       </c>
       <c r="F64" t="n">
-        <v>16623</v>
+        <v>16622</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -7868,16 +7868,16 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1382.387172178531</v>
+        <v>1382.343474230352</v>
       </c>
       <c r="D65" t="n">
-        <v>1377.466706030237</v>
+        <v>1377.422213355228</v>
       </c>
       <c r="E65" t="n">
-        <v>1387.307638326826</v>
+        <v>1387.264735105476</v>
       </c>
       <c r="F65" t="n">
-        <v>23220</v>
+        <v>23222</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -8015,144 +8015,68 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>trinity-large-preview</t>
+          <t>glm-4.6v</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1378.457989809332</v>
+        <v>1378.458596606527</v>
       </c>
       <c r="D66" t="n">
-        <v>1374.099337323238</v>
+        <v>1367.129778731687</v>
       </c>
       <c r="E66" t="n">
-        <v>1382.816642295425</v>
+        <v>1389.787414481368</v>
       </c>
       <c r="F66" t="n">
-        <v>29739</v>
-      </c>
-      <c r="G66" t="inlineStr"/>
+        <v>2762</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Z.ai</t>
+        </is>
+      </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
-        </is>
-      </c>
-      <c r="I66" t="n">
-        <v>70</v>
-      </c>
-      <c r="J66" t="n">
-        <v>70</v>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>dense</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
-          <t>override</t>
-        </is>
-      </c>
-      <c r="M66" t="n">
-        <v>140</v>
-      </c>
-      <c r="N66" t="n">
-        <v>175</v>
-      </c>
-      <c r="O66" t="n">
-        <v>70</v>
-      </c>
-      <c r="P66" t="n">
-        <v>87.5</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>35</v>
-      </c>
-      <c r="R66" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="S66" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T66" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U66" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V66" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W66" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X66" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y66" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z66" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA66" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB66" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC66" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD66" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE66" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF66" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG66" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="inlineStr"/>
+      <c r="X66" t="inlineStr"/>
+      <c r="Y66" t="inlineStr"/>
+      <c r="Z66" t="inlineStr"/>
+      <c r="AA66" t="inlineStr"/>
+      <c r="AB66" t="inlineStr"/>
+      <c r="AC66" t="inlineStr"/>
+      <c r="AD66" t="inlineStr"/>
+      <c r="AE66" t="inlineStr"/>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="inlineStr"/>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>B200 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>RTX PRO 6000</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -8162,68 +8086,144 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>glm-4.6v</t>
+          <t>trinity-large-preview</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1378.414748557498</v>
+        <v>1378.44414722243</v>
       </c>
       <c r="D67" t="n">
-        <v>1367.082711380527</v>
+        <v>1374.086796399941</v>
       </c>
       <c r="E67" t="n">
-        <v>1389.746785734468</v>
+        <v>1382.801498044918</v>
       </c>
       <c r="F67" t="n">
-        <v>2761</v>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Z.ai</t>
-        </is>
-      </c>
+        <v>29742</v>
+      </c>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>70</v>
+      </c>
+      <c r="J67" t="n">
+        <v>70</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>dense</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr"/>
-      <c r="S67" t="inlineStr"/>
-      <c r="T67" t="inlineStr"/>
-      <c r="U67" t="inlineStr"/>
-      <c r="V67" t="inlineStr"/>
-      <c r="W67" t="inlineStr"/>
-      <c r="X67" t="inlineStr"/>
-      <c r="Y67" t="inlineStr"/>
-      <c r="Z67" t="inlineStr"/>
-      <c r="AA67" t="inlineStr"/>
-      <c r="AB67" t="inlineStr"/>
-      <c r="AC67" t="inlineStr"/>
-      <c r="AD67" t="inlineStr"/>
-      <c r="AE67" t="inlineStr"/>
-      <c r="AF67" t="inlineStr"/>
-      <c r="AG67" t="inlineStr"/>
+          <t>override</t>
+        </is>
+      </c>
+      <c r="M67" t="n">
+        <v>140</v>
+      </c>
+      <c r="N67" t="n">
+        <v>175</v>
+      </c>
+      <c r="O67" t="n">
+        <v>70</v>
+      </c>
+      <c r="P67" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>35</v>
+      </c>
+      <c r="R67" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="S67" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T67" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U67" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V67" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W67" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X67" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y67" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z67" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA67" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB67" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC67" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD67" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE67" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF67" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG67" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>B200 SXM</t>
         </is>
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>RTX PRO 6000</t>
         </is>
       </c>
     </row>
@@ -8237,16 +8237,16 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1374.932465911331</v>
+        <v>1374.892893901962</v>
       </c>
       <c r="D68" t="n">
-        <v>1370.220890895177</v>
+        <v>1370.180559070101</v>
       </c>
       <c r="E68" t="n">
-        <v>1379.644040927485</v>
+        <v>1379.605228733823</v>
       </c>
       <c r="F68" t="n">
-        <v>25861</v>
+        <v>25865</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -8388,13 +8388,13 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1373.196483307733</v>
+        <v>1373.207299476924</v>
       </c>
       <c r="D69" t="n">
-        <v>1368.9208168924</v>
+        <v>1368.931968920771</v>
       </c>
       <c r="E69" t="n">
-        <v>1377.472149723066</v>
+        <v>1377.482630033077</v>
       </c>
       <c r="F69" t="n">
         <v>30367</v>
@@ -8455,69 +8455,73 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>trinity-large-thinking</t>
+          <t>qwen3-next-80b-a3b-thinking</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1369.037440411232</v>
+        <v>1368.961836972322</v>
       </c>
       <c r="D70" t="n">
-        <v>1364.359181725455</v>
+        <v>1363.078785435144</v>
       </c>
       <c r="E70" t="n">
-        <v>1373.71569909701</v>
+        <v>1374.844888509499</v>
       </c>
       <c r="F70" t="n">
-        <v>28956</v>
-      </c>
-      <c r="G70" t="inlineStr"/>
+        <v>13380</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Alibaba</t>
+        </is>
+      </c>
       <c r="H70" t="inlineStr">
         <is>
           <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="J70" t="n">
-        <v>70</v>
+        <v>3</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>name_parsing</t>
         </is>
       </c>
       <c r="M70" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="N70" t="n">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="O70" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="P70" t="n">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="Q70" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="R70" t="n">
-        <v>43.8</v>
+        <v>50</v>
       </c>
       <c r="S70" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="T70" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="T70" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="U70" s="6" t="inlineStr">
@@ -8555,9 +8559,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB70" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AB70" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AC70" s="6" t="inlineStr">
@@ -8587,12 +8591,12 @@
       </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>B200 SXM</t>
+          <t>B300 SXM</t>
         </is>
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>RTX PRO 6000</t>
+          <t>H200 SXM</t>
         </is>
       </c>
     </row>
@@ -8602,73 +8606,69 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>qwen3-next-80b-a3b-thinking</t>
+          <t>trinity-large-thinking</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1368.946601369613</v>
+        <v>1368.961288649815</v>
       </c>
       <c r="D71" t="n">
-        <v>1363.062843720067</v>
+        <v>1364.285003693916</v>
       </c>
       <c r="E71" t="n">
-        <v>1374.830359019158</v>
+        <v>1373.637573605714</v>
       </c>
       <c r="F71" t="n">
-        <v>13379</v>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Alibaba</t>
-        </is>
-      </c>
+        <v>28967</v>
+      </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
           <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="J71" t="n">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>override</t>
         </is>
       </c>
       <c r="M71" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="N71" t="n">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="O71" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="P71" t="n">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="Q71" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="R71" t="n">
-        <v>50</v>
+        <v>43.8</v>
       </c>
       <c r="S71" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="T71" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="T71" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="U71" s="6" t="inlineStr">
@@ -8706,9 +8706,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB71" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AB71" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AC71" s="6" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>B300 SXM</t>
+          <t>B200 SXM</t>
         </is>
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>H200 SXM</t>
+          <t>RTX PRO 6000</t>
         </is>
       </c>
     </row>
@@ -8757,16 +8757,16 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1366.227782533648</v>
+        <v>1366.264649011693</v>
       </c>
       <c r="D72" t="n">
-        <v>1360.404396929105</v>
+        <v>1360.441828840396</v>
       </c>
       <c r="E72" t="n">
-        <v>1372.051168138192</v>
+        <v>1372.08746918299</v>
       </c>
       <c r="F72" t="n">
-        <v>11495</v>
+        <v>11491</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -8828,16 +8828,16 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1365.159988648556</v>
+        <v>1365.187389953344</v>
       </c>
       <c r="D73" t="n">
-        <v>1361.447561914797</v>
+        <v>1361.474592562229</v>
       </c>
       <c r="E73" t="n">
-        <v>1368.872415382316</v>
+        <v>1368.900187344459</v>
       </c>
       <c r="F73" t="n">
-        <v>46418</v>
+        <v>46422</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -8979,16 +8979,16 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1363.865352077129</v>
+        <v>1363.915208905732</v>
       </c>
       <c r="D74" t="n">
-        <v>1359.551699528068</v>
+        <v>1359.601679931117</v>
       </c>
       <c r="E74" t="n">
-        <v>1368.17900462619</v>
+        <v>1368.228737880346</v>
       </c>
       <c r="F74" t="n">
-        <v>34024</v>
+        <v>34030</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -9050,13 +9050,13 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1360.629829741298</v>
+        <v>1360.536327744384</v>
       </c>
       <c r="D75" t="n">
-        <v>1353.350012166587</v>
+        <v>1353.256322051655</v>
       </c>
       <c r="E75" t="n">
-        <v>1367.909647316008</v>
+        <v>1367.816333437114</v>
       </c>
       <c r="F75" t="n">
         <v>7458</v>
@@ -9201,13 +9201,13 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1358.35156941097</v>
+        <v>1358.362537034002</v>
       </c>
       <c r="D76" t="n">
-        <v>1353.595057523701</v>
+        <v>1353.605586861566</v>
       </c>
       <c r="E76" t="n">
-        <v>1363.10808129824</v>
+        <v>1363.119487206438</v>
       </c>
       <c r="F76" t="n">
         <v>21770</v>
@@ -9352,16 +9352,16 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1356.659189030883</v>
+        <v>1356.723067984446</v>
       </c>
       <c r="D77" t="n">
-        <v>1351.427525723481</v>
+        <v>1351.492064648607</v>
       </c>
       <c r="E77" t="n">
-        <v>1361.890852338284</v>
+        <v>1361.954071320285</v>
       </c>
       <c r="F77" t="n">
-        <v>17390</v>
+        <v>17391</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -9423,16 +9423,16 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1356.315996699775</v>
+        <v>1356.251164502632</v>
       </c>
       <c r="D78" t="n">
-        <v>1347.962635383271</v>
+        <v>1347.898733050661</v>
       </c>
       <c r="E78" t="n">
-        <v>1364.66935801628</v>
+        <v>1364.603595954603</v>
       </c>
       <c r="F78" t="n">
-        <v>5278</v>
+        <v>5279</v>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
@@ -9570,16 +9570,16 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1353.589096822576</v>
+        <v>1353.619358225659</v>
       </c>
       <c r="D79" t="n">
-        <v>1350.110024441854</v>
+        <v>1350.139748000316</v>
       </c>
       <c r="E79" t="n">
-        <v>1357.068169203298</v>
+        <v>1357.098968451002</v>
       </c>
       <c r="F79" t="n">
-        <v>55441</v>
+        <v>55449</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -9641,16 +9641,16 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1352.594843443062</v>
+        <v>1352.553938461892</v>
       </c>
       <c r="D80" t="n">
-        <v>1344.153229399912</v>
+        <v>1344.112601896761</v>
       </c>
       <c r="E80" t="n">
-        <v>1361.036457486212</v>
+        <v>1360.995275027023</v>
       </c>
       <c r="F80" t="n">
-        <v>4816</v>
+        <v>4817</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -9708,36 +9708,36 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>nvidia-nemotron-3.5-lightning-30b-a3b-nvfp4</t>
+          <t>gpt-oss-120b</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1352.51147013735</v>
+        <v>1352.281168955352</v>
       </c>
       <c r="D81" t="n">
-        <v>1345.00927172935</v>
+        <v>1347.888649621441</v>
       </c>
       <c r="E81" t="n">
-        <v>1360.01366854535</v>
+        <v>1356.673688289262</v>
       </c>
       <c r="F81" t="n">
-        <v>7900</v>
+        <v>29955</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>OpenMDW-1.1</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>30</v>
+        <v>117</v>
       </c>
       <c r="J81" t="n">
-        <v>3</v>
+        <v>5.1</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -9746,35 +9746,35 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>override</t>
         </is>
       </c>
       <c r="M81" t="n">
-        <v>60</v>
+        <v>234</v>
       </c>
       <c r="N81" t="n">
-        <v>75</v>
+        <v>292.5</v>
       </c>
       <c r="O81" t="n">
-        <v>30</v>
+        <v>117</v>
       </c>
       <c r="P81" t="n">
-        <v>37.5</v>
+        <v>146.2</v>
       </c>
       <c r="Q81" t="n">
-        <v>15</v>
+        <v>58.5</v>
       </c>
       <c r="R81" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="S81" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T81" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>73.09999999999999</v>
+      </c>
+      <c r="S81" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T81" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="U81" s="6" t="inlineStr">
@@ -9782,14 +9782,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V81" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W81" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="V81" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W81" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="X81" s="6" t="inlineStr">
@@ -9797,14 +9797,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y81" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z81" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="Y81" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z81" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AA81" s="6" t="inlineStr">
@@ -9812,9 +9812,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB81" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AB81" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AC81" s="6" t="inlineStr">
@@ -9827,9 +9827,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE81" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AE81" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AF81" s="6" t="inlineStr">
@@ -9844,12 +9844,12 @@
       </c>
       <c r="AH81" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>B200 SXM</t>
         </is>
       </c>
     </row>
@@ -9859,36 +9859,36 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>gpt-oss-120b</t>
+          <t>nvidia-nemotron-3.5-lightning-30b-a3b-nvfp4</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1352.332776319441</v>
+        <v>1351.475005023252</v>
       </c>
       <c r="D82" t="n">
-        <v>1347.940406225627</v>
+        <v>1344.151074913183</v>
       </c>
       <c r="E82" t="n">
-        <v>1356.725146413255</v>
+        <v>1358.798935133322</v>
       </c>
       <c r="F82" t="n">
-        <v>29948</v>
+        <v>8338</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>OpenMDW-1.1</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>117</v>
+        <v>30</v>
       </c>
       <c r="J82" t="n">
-        <v>5.1</v>
+        <v>3</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -9897,35 +9897,35 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>name_parsing</t>
         </is>
       </c>
       <c r="M82" t="n">
-        <v>234</v>
+        <v>60</v>
       </c>
       <c r="N82" t="n">
-        <v>292.5</v>
+        <v>75</v>
       </c>
       <c r="O82" t="n">
-        <v>117</v>
+        <v>30</v>
       </c>
       <c r="P82" t="n">
-        <v>146.2</v>
+        <v>37.5</v>
       </c>
       <c r="Q82" t="n">
-        <v>58.5</v>
+        <v>15</v>
       </c>
       <c r="R82" t="n">
-        <v>73.09999999999999</v>
-      </c>
-      <c r="S82" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T82" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>18.8</v>
+      </c>
+      <c r="S82" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T82" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="U82" s="6" t="inlineStr">
@@ -9933,14 +9933,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V82" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W82" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="V82" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W82" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="X82" s="6" t="inlineStr">
@@ -9948,14 +9948,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y82" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z82" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="Y82" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z82" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA82" s="6" t="inlineStr">
@@ -9963,9 +9963,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB82" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AB82" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AC82" s="6" t="inlineStr">
@@ -9978,9 +9978,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE82" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AE82" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AF82" s="6" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="AH82" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>B200 SXM</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -10014,16 +10014,16 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1349.448486430703</v>
+        <v>1349.385600535102</v>
       </c>
       <c r="D83" t="n">
-        <v>1341.929139028817</v>
+        <v>1341.863248877311</v>
       </c>
       <c r="E83" t="n">
-        <v>1356.96783383259</v>
+        <v>1356.907952192894</v>
       </c>
       <c r="F83" t="n">
-        <v>6277</v>
+        <v>6273</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -10085,13 +10085,13 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1347.51868915999</v>
+        <v>1347.518180127426</v>
       </c>
       <c r="D84" t="n">
-        <v>1335.836280330632</v>
+        <v>1335.835962251098</v>
       </c>
       <c r="E84" t="n">
-        <v>1359.201097989348</v>
+        <v>1359.200398003755</v>
       </c>
       <c r="F84" t="n">
         <v>2549</v>
@@ -10236,13 +10236,13 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1346.950085306217</v>
+        <v>1346.924014156633</v>
       </c>
       <c r="D85" t="n">
-        <v>1337.490495217058</v>
+        <v>1337.464424122878</v>
       </c>
       <c r="E85" t="n">
-        <v>1356.409675395377</v>
+        <v>1356.383604190388</v>
       </c>
       <c r="F85" t="n">
         <v>3926</v>
@@ -10387,16 +10387,16 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1345.763906813502</v>
+        <v>1345.871985905859</v>
       </c>
       <c r="D86" t="n">
-        <v>1337.999184806236</v>
+        <v>1338.110332807373</v>
       </c>
       <c r="E86" t="n">
-        <v>1353.528628820767</v>
+        <v>1353.633639004345</v>
       </c>
       <c r="F86" t="n">
-        <v>6752</v>
+        <v>6753</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -10538,16 +10538,16 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1344.163063069389</v>
+        <v>1343.989890451668</v>
       </c>
       <c r="D87" t="n">
-        <v>1336.829460267159</v>
+        <v>1336.655945842613</v>
       </c>
       <c r="E87" t="n">
-        <v>1351.496665871619</v>
+        <v>1351.323835060723</v>
       </c>
       <c r="F87" t="n">
-        <v>6851</v>
+        <v>6850</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -10609,13 +10609,13 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1343.164711343419</v>
+        <v>1343.13567017794</v>
       </c>
       <c r="D88" t="n">
-        <v>1333.144368501649</v>
+        <v>1333.115335490931</v>
       </c>
       <c r="E88" t="n">
-        <v>1353.185054185188</v>
+        <v>1353.156004864949</v>
       </c>
       <c r="F88" t="n">
         <v>3313</v>
@@ -10756,36 +10756,36 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>gemma-3-12b-it</t>
+          <t>granite-4.2-30b</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1341.687031079548</v>
+        <v>1341.881359143581</v>
       </c>
       <c r="D89" t="n">
-        <v>1332.174490850284</v>
+        <v>1331.197640047707</v>
       </c>
       <c r="E89" t="n">
-        <v>1351.199571308813</v>
+        <v>1352.565078239455</v>
       </c>
       <c r="F89" t="n">
-        <v>3829</v>
+        <v>3255</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Gemma</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="J89" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -10798,22 +10798,22 @@
         </is>
       </c>
       <c r="M89" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="N89" t="n">
+        <v>75</v>
+      </c>
+      <c r="O89" t="n">
         <v>30</v>
       </c>
-      <c r="O89" t="n">
-        <v>12</v>
-      </c>
       <c r="P89" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="Q89" t="n">
         <v>15</v>
       </c>
-      <c r="Q89" t="n">
-        <v>6</v>
-      </c>
       <c r="R89" t="n">
-        <v>7.5</v>
+        <v>18.8</v>
       </c>
       <c r="S89" s="6" t="inlineStr">
         <is>
@@ -10907,64 +10907,64 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>granite-4.2-30b</t>
+          <t>gemma-3-12b-it</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1341.638117382305</v>
+        <v>1341.677793953718</v>
       </c>
       <c r="D90" t="n">
-        <v>1330.963273393659</v>
+        <v>1332.165104423279</v>
       </c>
       <c r="E90" t="n">
-        <v>1352.312961370952</v>
+        <v>1351.190483484158</v>
       </c>
       <c r="F90" t="n">
-        <v>3261</v>
+        <v>3829</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>Gemma</t>
         </is>
       </c>
       <c r="I90" t="n">
+        <v>12</v>
+      </c>
+      <c r="J90" t="n">
+        <v>12</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>dense</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>name_parsing</t>
+        </is>
+      </c>
+      <c r="M90" t="n">
+        <v>24</v>
+      </c>
+      <c r="N90" t="n">
         <v>30</v>
       </c>
-      <c r="J90" t="n">
-        <v>30</v>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>dense</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>name_parsing</t>
-        </is>
-      </c>
-      <c r="M90" t="n">
-        <v>60</v>
-      </c>
-      <c r="N90" t="n">
-        <v>75</v>
-      </c>
       <c r="O90" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="P90" t="n">
-        <v>37.5</v>
+        <v>15</v>
       </c>
       <c r="Q90" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="R90" t="n">
-        <v>18.8</v>
+        <v>7.5</v>
       </c>
       <c r="S90" s="6" t="inlineStr">
         <is>
@@ -11062,16 +11062,16 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1335.791506700847</v>
+        <v>1335.796516611706</v>
       </c>
       <c r="D91" t="n">
-        <v>1331.32518453727</v>
+        <v>1331.329904957454</v>
       </c>
       <c r="E91" t="n">
-        <v>1340.257828864424</v>
+        <v>1340.263128265959</v>
       </c>
       <c r="F91" t="n">
-        <v>25087</v>
+        <v>25090</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -11213,13 +11213,13 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1335.09086026298</v>
+        <v>1335.161206879887</v>
       </c>
       <c r="D92" t="n">
-        <v>1331.361258892365</v>
+        <v>1331.43110857638</v>
       </c>
       <c r="E92" t="n">
-        <v>1338.820461633594</v>
+        <v>1338.891305183393</v>
       </c>
       <c r="F92" t="n">
         <v>41375</v>
@@ -11364,13 +11364,13 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1333.227625300524</v>
+        <v>1333.294696415142</v>
       </c>
       <c r="D93" t="n">
-        <v>1329.620940536771</v>
+        <v>1329.68779081218</v>
       </c>
       <c r="E93" t="n">
-        <v>1336.834310064276</v>
+        <v>1336.901602018104</v>
       </c>
       <c r="F93" t="n">
         <v>59656</v>
@@ -11515,16 +11515,16 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1329.979557226922</v>
+        <v>1329.956788071538</v>
       </c>
       <c r="D94" t="n">
-        <v>1323.764370744892</v>
+        <v>1323.740891736034</v>
       </c>
       <c r="E94" t="n">
-        <v>1336.194743708952</v>
+        <v>1336.172684407041</v>
       </c>
       <c r="F94" t="n">
-        <v>11454</v>
+        <v>11452</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -11662,36 +11662,36 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>llama-3.3-nemotron-49b-super-v1</t>
+          <t>molmo-2-8b</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1327.753815325055</v>
+        <v>1328.001554984101</v>
       </c>
       <c r="D95" t="n">
-        <v>1315.615179720901</v>
+        <v>1306.617680440953</v>
       </c>
       <c r="E95" t="n">
-        <v>1339.892450929209</v>
+        <v>1349.385429527249</v>
       </c>
       <c r="F95" t="n">
-        <v>2218</v>
+        <v>791</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Ai2</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="J95" t="n">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -11704,26 +11704,26 @@
         </is>
       </c>
       <c r="M95" t="n">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="N95" t="n">
-        <v>122.5</v>
+        <v>20</v>
       </c>
       <c r="O95" t="n">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="P95" t="n">
-        <v>61.2</v>
+        <v>10</v>
       </c>
       <c r="Q95" t="n">
-        <v>24.5</v>
+        <v>4</v>
       </c>
       <c r="R95" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="S95" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>5</v>
+      </c>
+      <c r="S95" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="T95" s="6" t="inlineStr">
@@ -11736,9 +11736,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V95" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="V95" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W95" s="6" t="inlineStr">
@@ -11798,7 +11798,7 @@
       </c>
       <c r="AH95" t="inlineStr">
         <is>
-          <t>H200 SXM</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI95" t="inlineStr">
@@ -11813,36 +11813,36 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>molmo-2-8b</t>
+          <t>llama-3.3-nemotron-49b-super-v1</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1327.589186669527</v>
+        <v>1327.742560939972</v>
       </c>
       <c r="D96" t="n">
-        <v>1306.206186618505</v>
+        <v>1315.604253773855</v>
       </c>
       <c r="E96" t="n">
-        <v>1348.97218672055</v>
+        <v>1339.880868106089</v>
       </c>
       <c r="F96" t="n">
-        <v>792</v>
+        <v>2218</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Ai2</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="J96" t="n">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
@@ -11855,26 +11855,26 @@
         </is>
       </c>
       <c r="M96" t="n">
-        <v>16</v>
+        <v>98</v>
       </c>
       <c r="N96" t="n">
-        <v>20</v>
+        <v>122.5</v>
       </c>
       <c r="O96" t="n">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="P96" t="n">
-        <v>10</v>
+        <v>61.2</v>
       </c>
       <c r="Q96" t="n">
-        <v>4</v>
+        <v>24.5</v>
       </c>
       <c r="R96" t="n">
-        <v>5</v>
-      </c>
-      <c r="S96" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>30.6</v>
+      </c>
+      <c r="S96" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="T96" s="6" t="inlineStr">
@@ -11887,9 +11887,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V96" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="V96" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="W96" s="6" t="inlineStr">
@@ -11949,7 +11949,7 @@
       </c>
       <c r="AH96" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>H200 SXM</t>
         </is>
       </c>
       <c r="AI96" t="inlineStr">
@@ -11964,36 +11964,36 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>qwen3-30b-a3b</t>
+          <t>llama-4-maverick-17b-128e-instruct</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1326.905675335539</v>
+        <v>1326.872255865815</v>
       </c>
       <c r="D97" t="n">
-        <v>1322.148876806961</v>
+        <v>1322.589961132986</v>
       </c>
       <c r="E97" t="n">
-        <v>1331.662473864117</v>
+        <v>1331.154550598645</v>
       </c>
       <c r="F97" t="n">
-        <v>26087</v>
+        <v>39359</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>Llama 4</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>30</v>
+        <v>400</v>
       </c>
       <c r="J97" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
@@ -12002,95 +12002,95 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>override</t>
         </is>
       </c>
       <c r="M97" t="n">
-        <v>60</v>
+        <v>800</v>
       </c>
       <c r="N97" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="O97" t="n">
-        <v>30</v>
+        <v>400</v>
       </c>
       <c r="P97" t="n">
-        <v>37.5</v>
+        <v>500</v>
       </c>
       <c r="Q97" t="n">
-        <v>15</v>
+        <v>200</v>
       </c>
       <c r="R97" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="S97" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T97" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U97" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V97" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W97" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X97" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y97" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z97" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA97" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB97" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC97" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD97" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE97" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF97" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>250</v>
+      </c>
+      <c r="S97" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T97" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U97" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V97" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W97" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X97" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y97" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z97" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA97" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB97" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC97" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD97" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE97" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF97" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AG97" s="6" t="inlineStr">
@@ -12100,12 +12100,12 @@
       </c>
       <c r="AH97" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -12115,36 +12115,36 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>llama-4-maverick-17b-128e-instruct</t>
+          <t>qwen3-30b-a3b</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1326.846199509592</v>
+        <v>1326.871251175439</v>
       </c>
       <c r="D98" t="n">
-        <v>1322.56405848437</v>
+        <v>1322.114277507411</v>
       </c>
       <c r="E98" t="n">
-        <v>1331.128340534815</v>
+        <v>1331.628224843467</v>
       </c>
       <c r="F98" t="n">
-        <v>39355</v>
+        <v>26089</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Llama 4</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>400</v>
+        <v>30</v>
       </c>
       <c r="J98" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -12153,95 +12153,95 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>name_parsing</t>
         </is>
       </c>
       <c r="M98" t="n">
-        <v>800</v>
+        <v>60</v>
       </c>
       <c r="N98" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="O98" t="n">
-        <v>400</v>
+        <v>30</v>
       </c>
       <c r="P98" t="n">
-        <v>500</v>
+        <v>37.5</v>
       </c>
       <c r="Q98" t="n">
-        <v>200</v>
+        <v>15</v>
       </c>
       <c r="R98" t="n">
-        <v>250</v>
-      </c>
-      <c r="S98" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T98" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U98" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V98" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W98" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X98" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y98" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z98" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA98" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB98" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC98" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD98" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AE98" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF98" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>18.8</v>
+      </c>
+      <c r="S98" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T98" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U98" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V98" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W98" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X98" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y98" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z98" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA98" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB98" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC98" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD98" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE98" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF98" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AG98" s="6" t="inlineStr">
@@ -12251,12 +12251,12 @@
       </c>
       <c r="AH98" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -12270,13 +12270,13 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1323.306270757623</v>
+        <v>1323.319330574949</v>
       </c>
       <c r="D99" t="n">
-        <v>1315.032280616054</v>
+        <v>1315.045253788692</v>
       </c>
       <c r="E99" t="n">
-        <v>1331.580260899192</v>
+        <v>1331.593407361206</v>
       </c>
       <c r="F99" t="n">
         <v>6795</v>
@@ -12341,16 +12341,16 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1321.403411928126</v>
+        <v>1321.461619981063</v>
       </c>
       <c r="D100" t="n">
-        <v>1316.664372435625</v>
+        <v>1316.722318858682</v>
       </c>
       <c r="E100" t="n">
-        <v>1326.142451420626</v>
+        <v>1326.200921103444</v>
       </c>
       <c r="F100" t="n">
-        <v>29735</v>
+        <v>29740</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -12492,16 +12492,16 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1320.935942067691</v>
+        <v>1320.925093494094</v>
       </c>
       <c r="D101" t="n">
-        <v>1313.618289635401</v>
+        <v>1313.608079170605</v>
       </c>
       <c r="E101" t="n">
-        <v>1328.253594499981</v>
+        <v>1328.242107817583</v>
       </c>
       <c r="F101" t="n">
-        <v>6898</v>
+        <v>6899</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -12563,13 +12563,13 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1317.970085124525</v>
+        <v>1318.001842050658</v>
       </c>
       <c r="D102" t="n">
-        <v>1312.265170208795</v>
+        <v>1312.296842722386</v>
       </c>
       <c r="E102" t="n">
-        <v>1323.675000040256</v>
+        <v>1323.706841378929</v>
       </c>
       <c r="F102" t="n">
         <v>16478</v>
@@ -12634,16 +12634,16 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1317.563947278451</v>
+        <v>1317.601673233484</v>
       </c>
       <c r="D103" t="n">
-        <v>1314.059336507282</v>
+        <v>1314.096407074558</v>
       </c>
       <c r="E103" t="n">
-        <v>1321.068558049619</v>
+        <v>1321.10693939241</v>
       </c>
       <c r="F103" t="n">
-        <v>54410</v>
+        <v>54412</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -12785,13 +12785,13 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1317.228824040889</v>
+        <v>1317.224214431203</v>
       </c>
       <c r="D104" t="n">
-        <v>1310.811213251904</v>
+        <v>1310.806284494433</v>
       </c>
       <c r="E104" t="n">
-        <v>1323.646434829874</v>
+        <v>1323.642144367973</v>
       </c>
       <c r="F104" t="n">
         <v>10393</v>
@@ -12936,16 +12936,16 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1317.153550106891</v>
+        <v>1317.174965633139</v>
       </c>
       <c r="D105" t="n">
-        <v>1311.963023768576</v>
+        <v>1311.984530985038</v>
       </c>
       <c r="E105" t="n">
-        <v>1322.344076445207</v>
+        <v>1322.36540028124</v>
       </c>
       <c r="F105" t="n">
-        <v>22079</v>
+        <v>22082</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -13087,16 +13087,16 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1314.286511070414</v>
+        <v>1314.243103320097</v>
       </c>
       <c r="D106" t="n">
-        <v>1308.745349138193</v>
+        <v>1308.702561221296</v>
       </c>
       <c r="E106" t="n">
-        <v>1319.827673002635</v>
+        <v>1319.783645418897</v>
       </c>
       <c r="F106" t="n">
-        <v>15326</v>
+        <v>15325</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -13238,13 +13238,13 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1314.180591859558</v>
+        <v>1314.227067576111</v>
       </c>
       <c r="D107" t="n">
-        <v>1310.245082118156</v>
+        <v>1310.291404541636</v>
       </c>
       <c r="E107" t="n">
-        <v>1318.11610160096</v>
+        <v>1318.162730610587</v>
       </c>
       <c r="F107" t="n">
         <v>45459</v>
@@ -13389,13 +13389,13 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1314.090679516839</v>
+        <v>1314.103236710038</v>
       </c>
       <c r="D108" t="n">
-        <v>1309.525050906721</v>
+        <v>1309.537237186629</v>
       </c>
       <c r="E108" t="n">
-        <v>1318.656308126956</v>
+        <v>1318.669236233447</v>
       </c>
       <c r="F108" t="n">
         <v>24739</v>
@@ -13536,13 +13536,13 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1307.072453126525</v>
+        <v>1307.09372056031</v>
       </c>
       <c r="D109" t="n">
-        <v>1302.358209213975</v>
+        <v>1302.379323460239</v>
       </c>
       <c r="E109" t="n">
-        <v>1311.786697039076</v>
+        <v>1311.808117660382</v>
       </c>
       <c r="F109" t="n">
         <v>24572</v>
@@ -13607,16 +13607,16 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1306.687786222039</v>
+        <v>1306.719990840608</v>
       </c>
       <c r="D110" t="n">
-        <v>1298.37803356478</v>
+        <v>1298.410194594378</v>
       </c>
       <c r="E110" t="n">
-        <v>1314.997538879297</v>
+        <v>1315.029787086838</v>
       </c>
       <c r="F110" t="n">
-        <v>5683</v>
+        <v>5682</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -13758,13 +13758,13 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1306.370943737809</v>
+        <v>1306.385492804531</v>
       </c>
       <c r="D111" t="n">
-        <v>1300.693354534092</v>
+        <v>1300.707894292024</v>
       </c>
       <c r="E111" t="n">
-        <v>1312.048532941525</v>
+        <v>1312.063091317038</v>
       </c>
       <c r="F111" t="n">
         <v>19621</v>
@@ -13905,16 +13905,16 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1305.876309708764</v>
+        <v>1305.950011318909</v>
       </c>
       <c r="D112" t="n">
-        <v>1295.683653371157</v>
+        <v>1295.766205519386</v>
       </c>
       <c r="E112" t="n">
-        <v>1316.068966046371</v>
+        <v>1316.133817118432</v>
       </c>
       <c r="F112" t="n">
-        <v>4018</v>
+        <v>4023</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -14056,13 +14056,13 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1305.378531828526</v>
+        <v>1305.415373845446</v>
       </c>
       <c r="D113" t="n">
-        <v>1300.925286574166</v>
+        <v>1300.961611856883</v>
       </c>
       <c r="E113" t="n">
-        <v>1309.831777082886</v>
+        <v>1309.869135834009</v>
       </c>
       <c r="F113" t="n">
         <v>28073</v>
@@ -14127,13 +14127,13 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1303.14464419154</v>
+        <v>1303.139188416097</v>
       </c>
       <c r="D114" t="n">
-        <v>1293.826123608794</v>
+        <v>1293.820515599685</v>
       </c>
       <c r="E114" t="n">
-        <v>1312.463164774285</v>
+        <v>1312.457861232509</v>
       </c>
       <c r="F114" t="n">
         <v>4171</v>
@@ -14278,16 +14278,16 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1303.120844075811</v>
+        <v>1303.067209740016</v>
       </c>
       <c r="D115" t="n">
-        <v>1298.571626298301</v>
+        <v>1298.517955111787</v>
       </c>
       <c r="E115" t="n">
-        <v>1307.670061853321</v>
+        <v>1307.616464368245</v>
       </c>
       <c r="F115" t="n">
-        <v>32614</v>
+        <v>32618</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -14429,13 +14429,13 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1302.75730853708</v>
+        <v>1302.780805614644</v>
       </c>
       <c r="D116" t="n">
-        <v>1298.669894849308</v>
+        <v>1298.693043160571</v>
       </c>
       <c r="E116" t="n">
-        <v>1306.844722224853</v>
+        <v>1306.868568068716</v>
       </c>
       <c r="F116" t="n">
         <v>39406</v>
@@ -14580,13 +14580,13 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1298.680405419868</v>
+        <v>1298.672434905425</v>
       </c>
       <c r="D117" t="n">
-        <v>1290.91596903893</v>
+        <v>1290.908022846226</v>
       </c>
       <c r="E117" t="n">
-        <v>1306.444841800806</v>
+        <v>1306.436846964624</v>
       </c>
       <c r="F117" t="n">
         <v>7140</v>
@@ -14731,16 +14731,16 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1294.132717262369</v>
+        <v>1293.739316636233</v>
       </c>
       <c r="D118" t="n">
-        <v>1282.281709156009</v>
+        <v>1281.868189643009</v>
       </c>
       <c r="E118" t="n">
-        <v>1305.98372536873</v>
+        <v>1305.610443629456</v>
       </c>
       <c r="F118" t="n">
-        <v>3081</v>
+        <v>3072</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -14882,13 +14882,13 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1293.120910961341</v>
+        <v>1293.14290962131</v>
       </c>
       <c r="D119" t="n">
-        <v>1289.372807939467</v>
+        <v>1289.394543017066</v>
       </c>
       <c r="E119" t="n">
-        <v>1296.869013983214</v>
+        <v>1296.891276225555</v>
       </c>
       <c r="F119" t="n">
         <v>55240</v>
@@ -15033,13 +15033,13 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1289.239171510391</v>
+        <v>1289.279033781331</v>
       </c>
       <c r="D120" t="n">
-        <v>1281.931503762501</v>
+        <v>1281.971433832333</v>
       </c>
       <c r="E120" t="n">
-        <v>1296.54683925828</v>
+        <v>1296.586633730328</v>
       </c>
       <c r="F120" t="n">
         <v>8662</v>
@@ -15100,13 +15100,13 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1289.176333478544</v>
+        <v>1289.200527255853</v>
       </c>
       <c r="D121" t="n">
-        <v>1285.77954778184</v>
+        <v>1285.803356571456</v>
       </c>
       <c r="E121" t="n">
-        <v>1292.573119175248</v>
+        <v>1292.59769794025</v>
       </c>
       <c r="F121" t="n">
         <v>75754</v>
@@ -15251,16 +15251,16 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1287.13662443652</v>
+        <v>1286.647994357583</v>
       </c>
       <c r="D122" t="n">
-        <v>1275.707061838717</v>
+        <v>1275.193865030548</v>
       </c>
       <c r="E122" t="n">
-        <v>1298.566187034324</v>
+        <v>1298.102123684618</v>
       </c>
       <c r="F122" t="n">
-        <v>3098</v>
+        <v>3087</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -15402,13 +15402,13 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1286.263594702147</v>
+        <v>1286.332589957392</v>
       </c>
       <c r="D123" t="n">
-        <v>1276.294199144719</v>
+        <v>1276.363430779844</v>
       </c>
       <c r="E123" t="n">
-        <v>1296.232990259574</v>
+        <v>1296.301749134941</v>
       </c>
       <c r="F123" t="n">
         <v>3749</v>
@@ -15553,13 +15553,13 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1285.880494203145</v>
+        <v>1285.917189975333</v>
       </c>
       <c r="D124" t="n">
-        <v>1275.418074339221</v>
+        <v>1275.455104993011</v>
       </c>
       <c r="E124" t="n">
-        <v>1296.342914067069</v>
+        <v>1296.379274957655</v>
       </c>
       <c r="F124" t="n">
         <v>2846</v>
@@ -15704,16 +15704,16 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1285.607759583624</v>
+        <v>1285.540579707651</v>
       </c>
       <c r="D125" t="n">
-        <v>1277.110466744106</v>
+        <v>1277.045109474411</v>
       </c>
       <c r="E125" t="n">
-        <v>1294.105052423142</v>
+        <v>1294.036049940892</v>
       </c>
       <c r="F125" t="n">
-        <v>5531</v>
+        <v>5532</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -15855,16 +15855,16 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1285.509174928074</v>
+        <v>1285.502977760191</v>
       </c>
       <c r="D126" t="n">
-        <v>1278.180112517494</v>
+        <v>1278.176597635265</v>
       </c>
       <c r="E126" t="n">
-        <v>1292.838237338654</v>
+        <v>1292.829357885116</v>
       </c>
       <c r="F126" t="n">
-        <v>8114</v>
+        <v>8117</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -16006,13 +16006,13 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1280.080215910944</v>
+        <v>1280.095145709489</v>
       </c>
       <c r="D127" t="n">
-        <v>1273.219833692552</v>
+        <v>1273.23488789022</v>
       </c>
       <c r="E127" t="n">
-        <v>1286.940598129335</v>
+        <v>1286.955403528757</v>
       </c>
       <c r="F127" t="n">
         <v>10072</v>
@@ -16153,13 +16153,13 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1276.805979397631</v>
+        <v>1276.886404176034</v>
       </c>
       <c r="D128" t="n">
-        <v>1271.482605231465</v>
+        <v>1271.56337423121</v>
       </c>
       <c r="E128" t="n">
-        <v>1282.129353563797</v>
+        <v>1282.209434120858</v>
       </c>
       <c r="F128" t="n">
         <v>19659</v>
@@ -16304,13 +16304,13 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1276.223522019515</v>
+        <v>1276.280650153717</v>
       </c>
       <c r="D129" t="n">
-        <v>1272.633273753839</v>
+        <v>1272.690574706066</v>
       </c>
       <c r="E129" t="n">
-        <v>1279.813770285191</v>
+        <v>1279.870725601368</v>
       </c>
       <c r="F129" t="n">
         <v>156876</v>
@@ -16455,13 +16455,13 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1276.006485554662</v>
+        <v>1276.07434601668</v>
       </c>
       <c r="D130" t="n">
-        <v>1269.425984647893</v>
+        <v>1269.493876429675</v>
       </c>
       <c r="E130" t="n">
-        <v>1282.58698646143</v>
+        <v>1282.654815603685</v>
       </c>
       <c r="F130" t="n">
         <v>9866</v>
@@ -16606,13 +16606,13 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1274.215886316556</v>
+        <v>1274.251563079231</v>
       </c>
       <c r="D131" t="n">
-        <v>1268.296327223336</v>
+        <v>1268.331606850459</v>
       </c>
       <c r="E131" t="n">
-        <v>1280.135445409776</v>
+        <v>1280.171519308002</v>
       </c>
       <c r="F131" t="n">
         <v>14681</v>
@@ -16757,13 +16757,13 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1270.430014394942</v>
+        <v>1270.468896624686</v>
       </c>
       <c r="D132" t="n">
-        <v>1262.299836517089</v>
+        <v>1262.338710112957</v>
       </c>
       <c r="E132" t="n">
-        <v>1278.560192272795</v>
+        <v>1278.599083136414</v>
       </c>
       <c r="F132" t="n">
         <v>5432</v>
@@ -16908,13 +16908,13 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1266.986226174229</v>
+        <v>1267.022305044308</v>
       </c>
       <c r="D133" t="n">
-        <v>1262.086719584401</v>
+        <v>1262.122463188917</v>
       </c>
       <c r="E133" t="n">
-        <v>1271.885732764058</v>
+        <v>1271.9221468997</v>
       </c>
       <c r="F133" t="n">
         <v>27124</v>
@@ -17059,13 +17059,13 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1266.705111851036</v>
+        <v>1266.72944408479</v>
       </c>
       <c r="D134" t="n">
-        <v>1262.873197809272</v>
+        <v>1262.897190588238</v>
       </c>
       <c r="E134" t="n">
-        <v>1270.537025892801</v>
+        <v>1270.561697581343</v>
       </c>
       <c r="F134" t="n">
         <v>54611</v>
@@ -17210,13 +17210,13 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1265.008718548055</v>
+        <v>1265.073093637715</v>
       </c>
       <c r="D135" t="n">
-        <v>1258.730967561228</v>
+        <v>1258.795595157252</v>
       </c>
       <c r="E135" t="n">
-        <v>1271.286469534882</v>
+        <v>1271.350592118177</v>
       </c>
       <c r="F135" t="n">
         <v>15147</v>
@@ -17361,13 +17361,13 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1261.457012555319</v>
+        <v>1261.531659101513</v>
       </c>
       <c r="D136" t="n">
-        <v>1256.506331226115</v>
+        <v>1256.581079186756</v>
       </c>
       <c r="E136" t="n">
-        <v>1266.407693884523</v>
+        <v>1266.482239016271</v>
       </c>
       <c r="F136" t="n">
         <v>37325</v>
@@ -17512,13 +17512,13 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1261.418384287014</v>
+        <v>1261.505125083183</v>
       </c>
       <c r="D137" t="n">
-        <v>1257.095372265835</v>
+        <v>1257.182434763115</v>
       </c>
       <c r="E137" t="n">
-        <v>1265.741396308194</v>
+        <v>1265.82781540325</v>
       </c>
       <c r="F137" t="n">
         <v>77554</v>
@@ -17583,13 +17583,13 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1256.095997461869</v>
+        <v>1256.131460119295</v>
       </c>
       <c r="D138" t="n">
-        <v>1251.487543508152</v>
+        <v>1251.522542606884</v>
       </c>
       <c r="E138" t="n">
-        <v>1260.704451415586</v>
+        <v>1260.740377631706</v>
       </c>
       <c r="F138" t="n">
         <v>24126</v>
@@ -17734,13 +17734,13 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1251.426863726466</v>
+        <v>1251.470534125006</v>
       </c>
       <c r="D139" t="n">
-        <v>1240.647385537153</v>
+        <v>1240.691270103636</v>
       </c>
       <c r="E139" t="n">
-        <v>1262.206341915779</v>
+        <v>1262.249798146377</v>
       </c>
       <c r="F139" t="n">
         <v>3334</v>
@@ -17885,13 +17885,13 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1250.063897855776</v>
+        <v>1250.146185924149</v>
       </c>
       <c r="D140" t="n">
-        <v>1243.458631969112</v>
+        <v>1243.540959907107</v>
       </c>
       <c r="E140" t="n">
-        <v>1256.66916374244</v>
+        <v>1256.751411941192</v>
       </c>
       <c r="F140" t="n">
         <v>10140</v>
@@ -18036,13 +18036,13 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>1239.541004720539</v>
+        <v>1239.577376072255</v>
       </c>
       <c r="D141" t="n">
-        <v>1232.312890024259</v>
+        <v>1232.349362506243</v>
       </c>
       <c r="E141" t="n">
-        <v>1246.76911941682</v>
+        <v>1246.805389638267</v>
       </c>
       <c r="F141" t="n">
         <v>8858</v>
@@ -18103,13 +18103,13 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1237.418932683709</v>
+        <v>1237.457707064677</v>
       </c>
       <c r="D142" t="n">
-        <v>1228.327608065531</v>
+        <v>1228.366587887559</v>
       </c>
       <c r="E142" t="n">
-        <v>1246.510257301887</v>
+        <v>1246.548826241795</v>
       </c>
       <c r="F142" t="n">
         <v>4781</v>
@@ -18254,13 +18254,13 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>1233.818943391546</v>
+        <v>1233.887971881121</v>
       </c>
       <c r="D143" t="n">
-        <v>1228.26855555853</v>
+        <v>1228.337977245051</v>
       </c>
       <c r="E143" t="n">
-        <v>1239.369331224561</v>
+        <v>1239.437966517192</v>
       </c>
       <c r="F143" t="n">
         <v>26195</v>
@@ -18405,13 +18405,13 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>1233.139155071626</v>
+        <v>1233.22398756846</v>
       </c>
       <c r="D144" t="n">
-        <v>1227.867725587867</v>
+        <v>1227.952970289545</v>
       </c>
       <c r="E144" t="n">
-        <v>1238.410584555385</v>
+        <v>1238.495004847374</v>
       </c>
       <c r="F144" t="n">
         <v>39302</v>
@@ -18556,13 +18556,13 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1229.185278074733</v>
+        <v>1229.278184954976</v>
       </c>
       <c r="D145" t="n">
-        <v>1224.626890929222</v>
+        <v>1224.720006277914</v>
       </c>
       <c r="E145" t="n">
-        <v>1233.743665220244</v>
+        <v>1233.836363632039</v>
       </c>
       <c r="F145" t="n">
         <v>51416</v>
@@ -18707,13 +18707,13 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>1226.484571676177</v>
+        <v>1226.576953903234</v>
       </c>
       <c r="D146" t="n">
-        <v>1221.703530743197</v>
+        <v>1221.796268064159</v>
       </c>
       <c r="E146" t="n">
-        <v>1231.265612609156</v>
+        <v>1231.357639742309</v>
       </c>
       <c r="F146" t="n">
         <v>54036</v>
@@ -18778,13 +18778,13 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>1223.293512856074</v>
+        <v>1223.358701780853</v>
       </c>
       <c r="D147" t="n">
-        <v>1219.553020095896</v>
+        <v>1219.618397782858</v>
       </c>
       <c r="E147" t="n">
-        <v>1227.034005616251</v>
+        <v>1227.099005778848</v>
       </c>
       <c r="F147" t="n">
         <v>104642</v>
@@ -18929,13 +18929,13 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1222.839164583437</v>
+        <v>1222.868906093744</v>
       </c>
       <c r="D148" t="n">
-        <v>1215.85885705728</v>
+        <v>1215.888382531651</v>
       </c>
       <c r="E148" t="n">
-        <v>1229.819472109594</v>
+        <v>1229.849429655838</v>
       </c>
       <c r="F148" t="n">
         <v>9818</v>
@@ -19080,13 +19080,13 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1220.306555015113</v>
+        <v>1220.334446983204</v>
       </c>
       <c r="D149" t="n">
-        <v>1209.631813101653</v>
+        <v>1209.659834979211</v>
       </c>
       <c r="E149" t="n">
-        <v>1230.981296928573</v>
+        <v>1231.009058987198</v>
       </c>
       <c r="F149" t="n">
         <v>2896</v>
@@ -19231,13 +19231,13 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1212.627420901443</v>
+        <v>1212.722342949757</v>
       </c>
       <c r="D150" t="n">
-        <v>1201.847338780368</v>
+        <v>1201.942959320907</v>
       </c>
       <c r="E150" t="n">
-        <v>1223.407503022517</v>
+        <v>1223.501726578608</v>
       </c>
       <c r="F150" t="n">
         <v>4652</v>
@@ -19378,13 +19378,13 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1212.587667880785</v>
+        <v>1212.648930296592</v>
       </c>
       <c r="D151" t="n">
-        <v>1207.54938797769</v>
+        <v>1207.610946813412</v>
       </c>
       <c r="E151" t="n">
-        <v>1217.625947783881</v>
+        <v>1217.686913779772</v>
       </c>
       <c r="F151" t="n">
         <v>24146</v>
@@ -19525,13 +19525,13 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1211.105468508872</v>
+        <v>1211.117086681836</v>
       </c>
       <c r="D152" t="n">
-        <v>1206.943614424467</v>
+        <v>1206.954977135417</v>
       </c>
       <c r="E152" t="n">
-        <v>1215.267322593277</v>
+        <v>1215.279196228254</v>
       </c>
       <c r="F152" t="n">
         <v>49605</v>
@@ -19676,13 +19676,13 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>1208.156273724011</v>
+        <v>1208.237867821241</v>
       </c>
       <c r="D153" t="n">
-        <v>1197.059730738627</v>
+        <v>1197.141768736793</v>
       </c>
       <c r="E153" t="n">
-        <v>1219.252816709395</v>
+        <v>1219.33396690569</v>
       </c>
       <c r="F153" t="n">
         <v>3090</v>
@@ -19827,13 +19827,13 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1203.598989581285</v>
+        <v>1203.690513504918</v>
       </c>
       <c r="D154" t="n">
-        <v>1197.484489083272</v>
+        <v>1197.576407433956</v>
       </c>
       <c r="E154" t="n">
-        <v>1209.713490079299</v>
+        <v>1209.804619575881</v>
       </c>
       <c r="F154" t="n">
         <v>21741</v>
@@ -19978,13 +19978,13 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>1199.870137113649</v>
+        <v>1199.875433521449</v>
       </c>
       <c r="D155" t="n">
-        <v>1195.764538332102</v>
+        <v>1195.769511112203</v>
       </c>
       <c r="E155" t="n">
-        <v>1203.975735895196</v>
+        <v>1203.981355930695</v>
       </c>
       <c r="F155" t="n">
         <v>46616</v>
@@ -20129,13 +20129,13 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1197.547988261902</v>
+        <v>1197.636129157049</v>
       </c>
       <c r="D156" t="n">
-        <v>1192.385871527069</v>
+        <v>1192.474177642018</v>
       </c>
       <c r="E156" t="n">
-        <v>1202.710104996736</v>
+        <v>1202.798080672081</v>
       </c>
       <c r="F156" t="n">
         <v>25055</v>
@@ -20280,13 +20280,13 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1196.77083123414</v>
+        <v>1196.864466823537</v>
       </c>
       <c r="D157" t="n">
-        <v>1192.505263741328</v>
+        <v>1192.599333914645</v>
       </c>
       <c r="E157" t="n">
-        <v>1201.036398726952</v>
+        <v>1201.129599732428</v>
       </c>
       <c r="F157" t="n">
         <v>73503</v>
@@ -20431,13 +20431,13 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1195.081674146236</v>
+        <v>1195.176657690495</v>
       </c>
       <c r="D158" t="n">
-        <v>1188.971511328272</v>
+        <v>1189.066873381196</v>
       </c>
       <c r="E158" t="n">
-        <v>1201.1918369642</v>
+        <v>1201.286441999794</v>
       </c>
       <c r="F158" t="n">
         <v>32191</v>
@@ -20498,13 +20498,13 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>1190.705425365712</v>
+        <v>1190.790070228298</v>
       </c>
       <c r="D159" t="n">
-        <v>1183.593365704416</v>
+        <v>1183.678501346077</v>
       </c>
       <c r="E159" t="n">
-        <v>1197.817485027008</v>
+        <v>1197.90163911052</v>
       </c>
       <c r="F159" t="n">
         <v>17839</v>
@@ -20649,13 +20649,13 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1190.519174273191</v>
+        <v>1190.565158201856</v>
       </c>
       <c r="D160" t="n">
-        <v>1183.333430045363</v>
+        <v>1183.379449520311</v>
       </c>
       <c r="E160" t="n">
-        <v>1197.70491850102</v>
+        <v>1197.750866883401</v>
       </c>
       <c r="F160" t="n">
         <v>9901</v>
@@ -20796,13 +20796,13 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1184.487773571406</v>
+        <v>1184.586118722963</v>
       </c>
       <c r="D161" t="n">
-        <v>1173.017555701786</v>
+        <v>1173.116802643377</v>
       </c>
       <c r="E161" t="n">
-        <v>1195.957991441026</v>
+        <v>1196.055434802548</v>
       </c>
       <c r="F161" t="n">
         <v>4932</v>
@@ -20947,13 +20947,13 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1184.363582390728</v>
+        <v>1184.457852460181</v>
       </c>
       <c r="D162" t="n">
-        <v>1174.937524356384</v>
+        <v>1175.03252626836</v>
       </c>
       <c r="E162" t="n">
-        <v>1193.789640425073</v>
+        <v>1193.883178652003</v>
       </c>
       <c r="F162" t="n">
         <v>8214</v>
@@ -21098,13 +21098,13 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1183.39558780092</v>
+        <v>1183.467287378368</v>
       </c>
       <c r="D163" t="n">
-        <v>1176.573362165759</v>
+        <v>1176.645481957441</v>
       </c>
       <c r="E163" t="n">
-        <v>1190.217813436081</v>
+        <v>1190.289092799296</v>
       </c>
       <c r="F163" t="n">
         <v>15483</v>
@@ -21245,13 +21245,13 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>1182.688917105236</v>
+        <v>1182.783266653251</v>
       </c>
       <c r="D164" t="n">
-        <v>1174.011891908482</v>
+        <v>1174.106585705613</v>
       </c>
       <c r="E164" t="n">
-        <v>1191.36594230199</v>
+        <v>1191.459947600889</v>
       </c>
       <c r="F164" t="n">
         <v>6638</v>
@@ -21396,13 +21396,13 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>1182.58102996496</v>
+        <v>1182.680879846741</v>
       </c>
       <c r="D165" t="n">
-        <v>1172.932809251486</v>
+        <v>1173.0333972797</v>
       </c>
       <c r="E165" t="n">
-        <v>1192.229250678434</v>
+        <v>1192.328362413783</v>
       </c>
       <c r="F165" t="n">
         <v>7968</v>
@@ -21463,13 +21463,13 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1182.317895413172</v>
+        <v>1182.416020808129</v>
       </c>
       <c r="D166" t="n">
-        <v>1174.331688805156</v>
+        <v>1174.430358038491</v>
       </c>
       <c r="E166" t="n">
-        <v>1190.304102021189</v>
+        <v>1190.401683577768</v>
       </c>
       <c r="F166" t="n">
         <v>12637</v>
@@ -21530,13 +21530,13 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>1182.163302270157</v>
+        <v>1182.208483325405</v>
       </c>
       <c r="D167" t="n">
-        <v>1176.094942369939</v>
+        <v>1176.14041343315</v>
       </c>
       <c r="E167" t="n">
-        <v>1188.231662170374</v>
+        <v>1188.27655321766</v>
       </c>
       <c r="F167" t="n">
         <v>23893</v>
@@ -21681,13 +21681,13 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>1179.609286795776</v>
+        <v>1179.708500162761</v>
       </c>
       <c r="D168" t="n">
-        <v>1173.701080233889</v>
+        <v>1173.800694559663</v>
       </c>
       <c r="E168" t="n">
-        <v>1185.517493357663</v>
+        <v>1185.616305765858</v>
       </c>
       <c r="F168" t="n">
         <v>32832</v>
@@ -21748,13 +21748,13 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1178.551418803225</v>
+        <v>1178.625111297429</v>
       </c>
       <c r="D169" t="n">
-        <v>1167.366760005377</v>
+        <v>1167.440873549073</v>
       </c>
       <c r="E169" t="n">
-        <v>1189.736077601074</v>
+        <v>1189.809349045785</v>
       </c>
       <c r="F169" t="n">
         <v>3188</v>
@@ -21899,13 +21899,13 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>1177.307145004128</v>
+        <v>1177.398692913518</v>
       </c>
       <c r="D170" t="n">
-        <v>1167.511433087625</v>
+        <v>1167.603665228694</v>
       </c>
       <c r="E170" t="n">
-        <v>1187.102856920632</v>
+        <v>1187.193720598343</v>
       </c>
       <c r="F170" t="n">
         <v>6535</v>
@@ -22046,13 +22046,13 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1175.503556160478</v>
+        <v>1175.603789166204</v>
       </c>
       <c r="D171" t="n">
-        <v>1165.110325207351</v>
+        <v>1165.211336690892</v>
       </c>
       <c r="E171" t="n">
-        <v>1185.896787113606</v>
+        <v>1185.996241641517</v>
       </c>
       <c r="F171" t="n">
         <v>5006</v>
@@ -22193,13 +22193,13 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1172.539715141989</v>
+        <v>1172.635535912681</v>
       </c>
       <c r="D172" t="n">
-        <v>1166.347631451381</v>
+        <v>1166.44407728531</v>
       </c>
       <c r="E172" t="n">
-        <v>1178.731798832598</v>
+        <v>1178.826994540053</v>
       </c>
       <c r="F172" t="n">
         <v>22479</v>
@@ -22340,13 +22340,13 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>1170.712637332995</v>
+        <v>1170.803092780079</v>
       </c>
       <c r="D173" t="n">
-        <v>1163.314334075197</v>
+        <v>1163.405265269036</v>
       </c>
       <c r="E173" t="n">
-        <v>1178.110940590793</v>
+        <v>1178.200920291123</v>
       </c>
       <c r="F173" t="n">
         <v>16056</v>
@@ -22487,13 +22487,13 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>1170.7123529225</v>
+        <v>1170.796187937212</v>
       </c>
       <c r="D174" t="n">
-        <v>1164.798281220998</v>
+        <v>1164.882436972965</v>
       </c>
       <c r="E174" t="n">
-        <v>1176.626424624003</v>
+        <v>1176.70993890146</v>
       </c>
       <c r="F174" t="n">
         <v>17766</v>
@@ -22638,13 +22638,13 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>1170.307200281326</v>
+        <v>1170.397321762237</v>
       </c>
       <c r="D175" t="n">
-        <v>1164.816730428847</v>
+        <v>1164.90749278488</v>
       </c>
       <c r="E175" t="n">
-        <v>1175.797670133804</v>
+        <v>1175.887150739595</v>
       </c>
       <c r="F175" t="n">
         <v>38492</v>
@@ -22789,13 +22789,13 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>1167.053726638339</v>
+        <v>1167.146718355752</v>
       </c>
       <c r="D176" t="n">
-        <v>1158.998275342913</v>
+        <v>1159.091815037303</v>
       </c>
       <c r="E176" t="n">
-        <v>1175.109177933766</v>
+        <v>1175.201621674202</v>
       </c>
       <c r="F176" t="n">
         <v>10224</v>
@@ -22936,13 +22936,13 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>1166.449590375488</v>
+        <v>1166.512465531462</v>
       </c>
       <c r="D177" t="n">
-        <v>1158.744301150416</v>
+        <v>1158.807356999116</v>
       </c>
       <c r="E177" t="n">
-        <v>1174.15487960056</v>
+        <v>1174.217574063807</v>
       </c>
       <c r="F177" t="n">
         <v>7936</v>
@@ -23087,13 +23087,13 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>1164.071931755805</v>
+        <v>1164.157668220946</v>
       </c>
       <c r="D178" t="n">
-        <v>1152.173630759737</v>
+        <v>1152.260240896274</v>
       </c>
       <c r="E178" t="n">
-        <v>1175.970232751874</v>
+        <v>1176.055095545616</v>
       </c>
       <c r="F178" t="n">
         <v>3777</v>
@@ -23234,13 +23234,13 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>1156.244874083286</v>
+        <v>1156.337739676224</v>
       </c>
       <c r="D179" t="n">
-        <v>1147.860262766879</v>
+        <v>1147.953441134538</v>
       </c>
       <c r="E179" t="n">
-        <v>1164.629485399693</v>
+        <v>1164.722038217911</v>
       </c>
       <c r="F179" t="n">
         <v>6837</v>
@@ -23385,13 +23385,13 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>1154.322415249381</v>
+        <v>1154.412206453709</v>
       </c>
       <c r="D180" t="n">
-        <v>1141.741712805542</v>
+        <v>1141.832369839805</v>
       </c>
       <c r="E180" t="n">
-        <v>1166.90311769322</v>
+        <v>1166.992043067612</v>
       </c>
       <c r="F180" t="n">
         <v>3585</v>
@@ -23536,13 +23536,13 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>1154.137736555992</v>
+        <v>1154.176409601761</v>
       </c>
       <c r="D181" t="n">
-        <v>1142.655466901417</v>
+        <v>1142.694648515468</v>
       </c>
       <c r="E181" t="n">
-        <v>1165.620006210568</v>
+        <v>1165.658170688055</v>
       </c>
       <c r="F181" t="n">
         <v>3231</v>
@@ -23687,13 +23687,13 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>1152.016724746712</v>
+        <v>1152.112063779021</v>
       </c>
       <c r="D182" t="n">
-        <v>1138.870589404032</v>
+        <v>1138.967215228788</v>
       </c>
       <c r="E182" t="n">
-        <v>1165.162860089391</v>
+        <v>1165.256912329254</v>
       </c>
       <c r="F182" t="n">
         <v>4155</v>
@@ -23834,13 +23834,13 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>1151.867780036624</v>
+        <v>1151.963127494305</v>
       </c>
       <c r="D183" t="n">
-        <v>1136.572282979625</v>
+        <v>1136.669448000337</v>
       </c>
       <c r="E183" t="n">
-        <v>1167.163277093623</v>
+        <v>1167.256806988273</v>
       </c>
       <c r="F183" t="n">
         <v>1679</v>
@@ -23981,13 +23981,13 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>1150.305623848684</v>
+        <v>1150.404038430115</v>
       </c>
       <c r="D184" t="n">
-        <v>1138.084720991449</v>
+        <v>1138.184651467058</v>
       </c>
       <c r="E184" t="n">
-        <v>1162.52652670592</v>
+        <v>1162.623425393171</v>
       </c>
       <c r="F184" t="n">
         <v>2572</v>
@@ -24128,13 +24128,13 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>1149.113981209444</v>
+        <v>1149.210213270563</v>
       </c>
       <c r="D185" t="n">
-        <v>1139.907890378568</v>
+        <v>1140.005250664367</v>
       </c>
       <c r="E185" t="n">
-        <v>1158.32007204032</v>
+        <v>1158.415175876759</v>
       </c>
       <c r="F185" t="n">
         <v>7044</v>
@@ -24279,13 +24279,13 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>1149.024378789645</v>
+        <v>1149.116211358035</v>
       </c>
       <c r="D186" t="n">
-        <v>1142.378996729087</v>
+        <v>1142.471264182049</v>
       </c>
       <c r="E186" t="n">
-        <v>1155.669760850202</v>
+        <v>1155.76115853402</v>
       </c>
       <c r="F186" t="n">
         <v>19402</v>
@@ -24430,13 +24430,13 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>1147.62602558642</v>
+        <v>1147.727492216463</v>
       </c>
       <c r="D187" t="n">
-        <v>1130.601659502471</v>
+        <v>1130.705003611322</v>
       </c>
       <c r="E187" t="n">
-        <v>1164.65039167037</v>
+        <v>1164.749980821604</v>
       </c>
       <c r="F187" t="n">
         <v>1295</v>
@@ -24577,13 +24577,13 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>1143.492563501356</v>
+        <v>1143.577361089211</v>
       </c>
       <c r="D188" t="n">
-        <v>1133.613560128593</v>
+        <v>1133.698882231564</v>
       </c>
       <c r="E188" t="n">
-        <v>1153.371566874119</v>
+        <v>1153.455839946857</v>
       </c>
       <c r="F188" t="n">
         <v>4737</v>
@@ -24728,13 +24728,13 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>1142.754073066245</v>
+        <v>1142.837703040665</v>
       </c>
       <c r="D189" t="n">
-        <v>1136.314451870971</v>
+        <v>1136.398273290433</v>
       </c>
       <c r="E189" t="n">
-        <v>1149.193694261519</v>
+        <v>1149.277132790898</v>
       </c>
       <c r="F189" t="n">
         <v>12297</v>
@@ -24879,13 +24879,13 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>1141.104989551175</v>
+        <v>1141.204274337716</v>
       </c>
       <c r="D190" t="n">
-        <v>1134.417163776232</v>
+        <v>1134.517192209874</v>
       </c>
       <c r="E190" t="n">
-        <v>1147.792815326117</v>
+        <v>1147.891356465557</v>
       </c>
       <c r="F190" t="n">
         <v>19367</v>
@@ -25026,13 +25026,13 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>1141.087233115083</v>
+        <v>1141.176978841656</v>
       </c>
       <c r="D191" t="n">
-        <v>1134.370711211066</v>
+        <v>1134.461000737156</v>
       </c>
       <c r="E191" t="n">
-        <v>1147.8037550191</v>
+        <v>1147.892956946156</v>
       </c>
       <c r="F191" t="n">
         <v>19174</v>
@@ -25177,13 +25177,13 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>1138.872819478582</v>
+        <v>1138.972119422011</v>
       </c>
       <c r="D192" t="n">
-        <v>1127.945030532947</v>
+        <v>1128.0452367264</v>
       </c>
       <c r="E192" t="n">
-        <v>1149.800608424217</v>
+        <v>1149.899002117621</v>
       </c>
       <c r="F192" t="n">
         <v>4964</v>
@@ -25328,13 +25328,13 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>1137.323873394339</v>
+        <v>1137.371797847913</v>
       </c>
       <c r="D193" t="n">
-        <v>1127.848137012032</v>
+        <v>1127.896707387859</v>
       </c>
       <c r="E193" t="n">
-        <v>1146.799609776646</v>
+        <v>1146.846888307966</v>
       </c>
       <c r="F193" t="n">
         <v>8925</v>
@@ -25479,13 +25479,13 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>1136.462196752434</v>
+        <v>1136.559192373644</v>
       </c>
       <c r="D194" t="n">
-        <v>1127.58389810284</v>
+        <v>1127.68160661289</v>
       </c>
       <c r="E194" t="n">
-        <v>1145.340495402028</v>
+        <v>1145.436778134398</v>
       </c>
       <c r="F194" t="n">
         <v>7366</v>
@@ -25630,13 +25630,13 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>1130.433110303826</v>
+        <v>1130.526520499723</v>
       </c>
       <c r="D195" t="n">
-        <v>1121.615896454672</v>
+        <v>1121.710072197614</v>
       </c>
       <c r="E195" t="n">
-        <v>1139.250324152979</v>
+        <v>1139.342968801832</v>
       </c>
       <c r="F195" t="n">
         <v>11118</v>
@@ -25777,13 +25777,13 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>1129.401187282188</v>
+        <v>1129.496831205522</v>
       </c>
       <c r="D196" t="n">
-        <v>1121.982573606233</v>
+        <v>1122.078635593147</v>
       </c>
       <c r="E196" t="n">
-        <v>1136.819800958142</v>
+        <v>1136.915026817896</v>
       </c>
       <c r="F196" t="n">
         <v>20685</v>
@@ -25928,13 +25928,13 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>1127.772525267331</v>
+        <v>1127.858665927822</v>
       </c>
       <c r="D197" t="n">
-        <v>1121.377766303772</v>
+        <v>1121.464259621924</v>
       </c>
       <c r="E197" t="n">
-        <v>1134.16728423089</v>
+        <v>1134.25307223372</v>
       </c>
       <c r="F197" t="n">
         <v>20118</v>
@@ -26079,13 +26079,13 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>1127.065840796192</v>
+        <v>1127.159385869897</v>
       </c>
       <c r="D198" t="n">
-        <v>1114.997965430797</v>
+        <v>1115.093141654017</v>
       </c>
       <c r="E198" t="n">
-        <v>1139.133716161586</v>
+        <v>1139.225630085777</v>
       </c>
       <c r="F198" t="n">
         <v>2921</v>
@@ -26226,13 +26226,13 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>1126.535742370462</v>
+        <v>1126.630803882266</v>
       </c>
       <c r="D199" t="n">
-        <v>1110.968957751289</v>
+        <v>1111.065871666322</v>
       </c>
       <c r="E199" t="n">
-        <v>1142.102526989636</v>
+        <v>1142.19573609821</v>
       </c>
       <c r="F199" t="n">
         <v>1785</v>
@@ -26373,13 +26373,13 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>1121.155741326663</v>
+        <v>1121.254380076746</v>
       </c>
       <c r="D200" t="n">
-        <v>1110.192839526694</v>
+        <v>1110.292331773717</v>
       </c>
       <c r="E200" t="n">
-        <v>1132.118643126633</v>
+        <v>1132.216428379775</v>
       </c>
       <c r="F200" t="n">
         <v>5182</v>
@@ -26520,13 +26520,13 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>1118.809885876419</v>
+        <v>1118.884814939762</v>
       </c>
       <c r="D201" t="n">
-        <v>1100.70677018545</v>
+        <v>1100.783687933203</v>
       </c>
       <c r="E201" t="n">
-        <v>1136.913001567389</v>
+        <v>1136.985941946321</v>
       </c>
       <c r="F201" t="n">
         <v>1143</v>
@@ -26671,13 +26671,13 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>1116.226023447982</v>
+        <v>1116.278958199592</v>
       </c>
       <c r="D202" t="n">
-        <v>1108.503133685214</v>
+        <v>1108.556472498248</v>
       </c>
       <c r="E202" t="n">
-        <v>1123.948913210749</v>
+        <v>1124.001443900936</v>
       </c>
       <c r="F202" t="n">
         <v>10854</v>
@@ -26822,13 +26822,13 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>1114.852138847118</v>
+        <v>1114.950966261846</v>
       </c>
       <c r="D203" t="n">
-        <v>1105.736013874435</v>
+        <v>1105.836081408366</v>
       </c>
       <c r="E203" t="n">
-        <v>1123.968263819801</v>
+        <v>1124.065851115326</v>
       </c>
       <c r="F203" t="n">
         <v>6923</v>
@@ -26969,13 +26969,13 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>1114.297262814518</v>
+        <v>1114.384392235172</v>
       </c>
       <c r="D204" t="n">
-        <v>1099.945035585688</v>
+        <v>1100.033384365084</v>
       </c>
       <c r="E204" t="n">
-        <v>1128.649490043347</v>
+        <v>1128.735400105261</v>
       </c>
       <c r="F204" t="n">
         <v>2199</v>
@@ -27116,13 +27116,13 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>1110.782030088067</v>
+        <v>1110.846366070986</v>
       </c>
       <c r="D205" t="n">
-        <v>1102.89918151157</v>
+        <v>1102.963737269152</v>
       </c>
       <c r="E205" t="n">
-        <v>1118.664878664565</v>
+        <v>1118.728994872821</v>
       </c>
       <c r="F205" t="n">
         <v>8045</v>
@@ -27267,13 +27267,13 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>1109.889249398658</v>
+        <v>1109.988611655951</v>
       </c>
       <c r="D206" t="n">
-        <v>1100.619618889044</v>
+        <v>1100.719705821361</v>
       </c>
       <c r="E206" t="n">
-        <v>1119.158879908272</v>
+        <v>1119.257517490541</v>
       </c>
       <c r="F206" t="n">
         <v>8977</v>
@@ -27418,13 +27418,13 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>1107.603420433528</v>
+        <v>1107.697437069311</v>
       </c>
       <c r="D207" t="n">
-        <v>1100.55916537564</v>
+        <v>1100.65368818828</v>
       </c>
       <c r="E207" t="n">
-        <v>1114.647675491416</v>
+        <v>1114.741185950342</v>
       </c>
       <c r="F207" t="n">
         <v>14148</v>
@@ -27569,13 +27569,13 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>1093.210195998088</v>
+        <v>1093.266532175074</v>
       </c>
       <c r="D208" t="n">
-        <v>1081.743295529676</v>
+        <v>1081.800557579536</v>
       </c>
       <c r="E208" t="n">
-        <v>1104.6770964665</v>
+        <v>1104.732506770612</v>
       </c>
       <c r="F208" t="n">
         <v>4780</v>
@@ -27720,13 +27720,13 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>1090.630051015068</v>
+        <v>1090.732009402171</v>
       </c>
       <c r="D209" t="n">
-        <v>1081.306485929979</v>
+        <v>1081.409149222045</v>
       </c>
       <c r="E209" t="n">
-        <v>1099.953616100157</v>
+        <v>1100.054869582297</v>
       </c>
       <c r="F209" t="n">
         <v>7597</v>
@@ -27871,13 +27871,13 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>1073.326250613429</v>
+        <v>1073.412888447052</v>
       </c>
       <c r="D210" t="n">
-        <v>1062.184614507814</v>
+        <v>1062.272204006958</v>
       </c>
       <c r="E210" t="n">
-        <v>1084.467886719045</v>
+        <v>1084.553572887147</v>
       </c>
       <c r="F210" t="n">
         <v>6328</v>
@@ -28022,13 +28022,13 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>1070.488243672501</v>
+        <v>1070.58657323053</v>
       </c>
       <c r="D211" t="n">
-        <v>1060.648933804663</v>
+        <v>1060.749256363124</v>
       </c>
       <c r="E211" t="n">
-        <v>1080.327553540338</v>
+        <v>1080.423890097937</v>
       </c>
       <c r="F211" t="n">
         <v>6965</v>
@@ -28169,13 +28169,13 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>1069.566622019539</v>
+        <v>1069.678113048585</v>
       </c>
       <c r="D212" t="n">
-        <v>1058.155395264594</v>
+        <v>1058.26887001264</v>
       </c>
       <c r="E212" t="n">
-        <v>1080.977848774484</v>
+        <v>1081.08735608453</v>
       </c>
       <c r="F212" t="n">
         <v>5745</v>
@@ -28316,13 +28316,13 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>1067.146571193159</v>
+        <v>1067.251869608598</v>
       </c>
       <c r="D213" t="n">
-        <v>1051.984733028546</v>
+        <v>1052.092274142969</v>
       </c>
       <c r="E213" t="n">
-        <v>1082.308409357772</v>
+        <v>1082.411465074227</v>
       </c>
       <c r="F213" t="n">
         <v>1743</v>
@@ -28463,13 +28463,13 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>1062.899665756374</v>
+        <v>1063.004524459527</v>
       </c>
       <c r="D214" t="n">
-        <v>1050.970725880895</v>
+        <v>1051.077468302807</v>
       </c>
       <c r="E214" t="n">
-        <v>1074.828605631853</v>
+        <v>1074.931580616247</v>
       </c>
       <c r="F214" t="n">
         <v>3924</v>
@@ -28610,13 +28610,13 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>1056.103217399482</v>
+        <v>1056.201116779131</v>
       </c>
       <c r="D215" t="n">
-        <v>1044.461786555185</v>
+        <v>1044.560629279451</v>
       </c>
       <c r="E215" t="n">
-        <v>1067.744648243779</v>
+        <v>1067.841604278811</v>
       </c>
       <c r="F215" t="n">
         <v>4658</v>
@@ -28757,13 +28757,13 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>1041.851444055326</v>
+        <v>1041.952704313323</v>
       </c>
       <c r="D216" t="n">
-        <v>1030.509420815258</v>
+        <v>1030.612654921714</v>
       </c>
       <c r="E216" t="n">
-        <v>1053.193467295393</v>
+        <v>1053.292753704932</v>
       </c>
       <c r="F216" t="n">
         <v>4845</v>
@@ -28904,13 +28904,13 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>1024.302983578282</v>
+        <v>1024.401568277975</v>
       </c>
       <c r="D217" t="n">
-        <v>1010.749603619215</v>
+        <v>1010.849731748132</v>
       </c>
       <c r="E217" t="n">
-        <v>1037.856363537348</v>
+        <v>1037.953404807818</v>
       </c>
       <c r="F217" t="n">
         <v>2658</v>
@@ -29051,13 +29051,13 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>1022.984203533018</v>
+        <v>1023.087799394241</v>
       </c>
       <c r="D218" t="n">
-        <v>1012.163772927928</v>
+        <v>1012.269377897513</v>
       </c>
       <c r="E218" t="n">
-        <v>1033.804634138107</v>
+        <v>1033.906220890968</v>
       </c>
       <c r="F218" t="n">
         <v>6310</v>
@@ -29198,13 +29198,13 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>995.3978998300622</v>
+        <v>995.4947028929535</v>
       </c>
       <c r="D219" t="n">
-        <v>982.8820028525754</v>
+        <v>982.980842572106</v>
       </c>
       <c r="E219" t="n">
-        <v>1007.913796807549</v>
+        <v>1008.008563213801</v>
       </c>
       <c r="F219" t="n">
         <v>4914</v>
@@ -29345,13 +29345,13 @@
         </is>
       </c>
       <c r="C220" t="n">
-        <v>992.0770785515656</v>
+        <v>992.1801127026608</v>
       </c>
       <c r="D220" t="n">
-        <v>979.7581859388351</v>
+        <v>979.8633273881013</v>
       </c>
       <c r="E220" t="n">
-        <v>1004.395971164296</v>
+        <v>1004.49689801722</v>
       </c>
       <c r="F220" t="n">
         <v>4203</v>
@@ -29492,13 +29492,13 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>981.8566477774898</v>
+        <v>981.9663912088785</v>
       </c>
       <c r="D221" t="n">
-        <v>968.3949455126715</v>
+        <v>968.5073470747749</v>
       </c>
       <c r="E221" t="n">
-        <v>995.3183500423079</v>
+        <v>995.425435342982</v>
       </c>
       <c r="F221" t="n">
         <v>3412</v>
@@ -29639,13 +29639,13 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>974.5226030688839</v>
+        <v>974.6359104810257</v>
       </c>
       <c r="D222" t="n">
-        <v>958.8150586952311</v>
+        <v>958.9318323938591</v>
       </c>
       <c r="E222" t="n">
-        <v>990.2301474425369</v>
+        <v>990.3399885681924</v>
       </c>
       <c r="F222" t="n">
         <v>2391</v>
@@ -29790,13 +29790,13 @@
         </is>
       </c>
       <c r="C223" t="n">
-        <v>952.7543209905339</v>
+        <v>952.8533162811774</v>
       </c>
       <c r="D223" t="n">
-        <v>940.0971541531612</v>
+        <v>940.1989106518037</v>
       </c>
       <c r="E223" t="n">
-        <v>965.4114878279065</v>
+        <v>965.5077219105511</v>
       </c>
       <c r="F223" t="n">
         <v>3287</v>
@@ -30579,7 +30579,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>glm-5.3-max</t>
+          <t>kimi-k3-max</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -30594,7 +30594,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>kimi-k3-max</t>
+          <t>glm-5.3-max</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -30860,38 +30860,38 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>minimax-m3</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>428</v>
-      </c>
-      <c r="C17" t="n">
-        <v>23</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>glm-4.7</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>aa_single_scrape</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>glm-4.7</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+          <t>minimax-m3</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>428</v>
+      </c>
+      <c r="C18" t="n">
+        <v>23</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>aa_single_scrape</t>
         </is>
       </c>
     </row>
@@ -31354,7 +31354,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-terminus</t>
+          <t>minimax-m2.7</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -31369,7 +31369,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>minimax-m2.7</t>
+          <t>deepseek-v3.1-terminus</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -31819,38 +31819,38 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>trinity-large-preview</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>70</v>
-      </c>
-      <c r="C66" t="n">
-        <v>70</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>dense</t>
-        </is>
-      </c>
+          <t>glm-4.6v</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>glm-4.6v</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr"/>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
+          <t>trinity-large-preview</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>70</v>
+      </c>
+      <c r="C67" t="n">
+        <v>70</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>dense</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>override</t>
         </is>
       </c>
     </row>
@@ -31895,46 +31895,46 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>trinity-large-thinking</t>
+          <t>qwen3-next-80b-a3b-thinking</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C70" t="n">
-        <v>70</v>
+        <v>3</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>qwen3-next-80b-a3b-thinking</t>
+          <t>trinity-large-thinking</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C71" t="n">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>override</t>
         </is>
       </c>
     </row>
@@ -32108,14 +32108,14 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>nvidia-nemotron-3.5-lightning-30b-a3b-nvfp4</t>
+          <t>gpt-oss-120b</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>30</v>
+        <v>117</v>
       </c>
       <c r="C81" t="n">
-        <v>3</v>
+        <v>5.1</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -32124,21 +32124,21 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>override</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>gpt-oss-120b</t>
+          <t>nvidia-nemotron-3.5-lightning-30b-a3b-nvfp4</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>117</v>
+        <v>30</v>
       </c>
       <c r="C82" t="n">
-        <v>5.1</v>
+        <v>3</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -32147,7 +32147,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
@@ -32276,14 +32276,14 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>gemma-3-12b-it</t>
+          <t>granite-4.2-30b</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C89" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -32299,14 +32299,14 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>granite-4.2-30b</t>
+          <t>gemma-3-12b-it</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="C90" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -32414,14 +32414,14 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>llama-3.3-nemotron-49b-super-v1</t>
+          <t>molmo-2-8b</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="C95" t="n">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -32437,14 +32437,14 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>molmo-2-8b</t>
+          <t>llama-3.3-nemotron-49b-super-v1</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="C96" t="n">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -32460,14 +32460,14 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>qwen3-30b-a3b</t>
+          <t>llama-4-maverick-17b-128e-instruct</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>30</v>
+        <v>400</v>
       </c>
       <c r="C97" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -32476,21 +32476,21 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>override</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>llama-4-maverick-17b-128e-instruct</t>
+          <t>qwen3-30b-a3b</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>400</v>
+        <v>30</v>
       </c>
       <c r="C98" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -32499,7 +32499,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>

--- a/arena_enrichment/output/arena_leaderboard_enriched.xlsx
+++ b/arena_enrichment/output/arena_leaderboard_enriched.xlsx
@@ -674,16 +674,16 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1487.96379974045</v>
+        <v>1488.027768355495</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1483.097721221994</v>
+        <v>1483.235761343442</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1492.829878258905</v>
+        <v>1492.819775367549</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>26400</v>
+        <v>27719</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -745,16 +745,16 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1479.739623919958</v>
+        <v>1479.615142075082</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1470.292022219788</v>
+        <v>1470.221599952889</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1489.187225620129</v>
+        <v>1489.008684197275</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>4026</v>
+        <v>4074</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -816,16 +816,16 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1479.600069361725</v>
+        <v>1479.393894575315</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1473.855949197933</v>
+        <v>1473.786641884639</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1485.344189525517</v>
+        <v>1485.001147265991</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>15904</v>
+        <v>17268</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -883,24 +883,24 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>deepseek-v4.1-flash-max</t>
+          <t>glm-5.2-max</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1476.507260804565</v>
+        <v>1475.426372376843</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1468.86531866466</v>
+        <v>1471.117362949654</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1484.149202944471</v>
+        <v>1479.735381804031</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>6630</v>
+        <v>44949</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Z.ai</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -954,20 +954,20 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>glm-5.2-max</t>
+          <t>glm-5.3-flash</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1475.556978453393</v>
+        <v>1473.671056356273</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1471.19936538269</v>
+        <v>1468.245369498502</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1479.914591524097</v>
+        <v>1479.096743214043</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>43570</v>
+        <v>21644</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -1025,24 +1025,24 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>glm-5.3-flash</t>
+          <t>deepseek-v4.1-flash-max</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1474.169437506117</v>
+        <v>1472.76550807406</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1468.60933969106</v>
+        <v>1465.690201492429</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1479.729535321175</v>
+        <v>1479.840814655691</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>19103</v>
+        <v>8125</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Z.ai</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1100,16 +1100,16 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1467.421865877426</v>
+        <v>1467.37081204811</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1463.767378060909</v>
+        <v>1463.741218959708</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1471.076353693943</v>
+        <v>1471.000405136512</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>69225</v>
+        <v>70317</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -1171,16 +1171,16 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1465.067829455567</v>
+        <v>1464.518979823142</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1461.35251669817</v>
+        <v>1460.829553170478</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1468.783142212964</v>
+        <v>1468.208406475807</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>56463</v>
+        <v>57877</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -1242,16 +1242,16 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1464.358629793212</v>
+        <v>1464.15093544915</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1457.744251415794</v>
+        <v>1457.532860157122</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1470.97300817063</v>
+        <v>1470.769010741177</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>9857</v>
+        <v>9825</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
@@ -1313,16 +1313,16 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1460.921200391414</v>
+        <v>1461.011639646345</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1456.486500337385</v>
+        <v>1456.579460797846</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1465.355900445444</v>
+        <v>1465.443818494846</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>39971</v>
+        <v>39950</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
@@ -1464,16 +1464,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1457.519194981193</v>
+        <v>1457.720783320416</v>
       </c>
       <c r="D12" t="n">
-        <v>1453.614157489936</v>
+        <v>1453.819210794446</v>
       </c>
       <c r="E12" t="n">
-        <v>1461.424232472449</v>
+        <v>1461.622355846386</v>
       </c>
       <c r="F12" t="n">
-        <v>57564</v>
+        <v>57549</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1615,16 +1615,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1457.204104340015</v>
+        <v>1457.653649118527</v>
       </c>
       <c r="D13" t="n">
-        <v>1452.951346776452</v>
+        <v>1453.401589600839</v>
       </c>
       <c r="E13" t="n">
-        <v>1461.456861903579</v>
+        <v>1461.905708636216</v>
       </c>
       <c r="F13" t="n">
-        <v>29152</v>
+        <v>29203</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1766,16 +1766,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1456.815774346154</v>
+        <v>1457.440394984297</v>
       </c>
       <c r="D14" t="n">
-        <v>1450.114501747806</v>
+        <v>1450.858745882494</v>
       </c>
       <c r="E14" t="n">
-        <v>1463.517046944502</v>
+        <v>1464.0220440861</v>
       </c>
       <c r="F14" t="n">
-        <v>9839</v>
+        <v>10239</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1917,16 +1917,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1454.674683965486</v>
+        <v>1454.997373386936</v>
       </c>
       <c r="D15" t="n">
-        <v>1450.702010418247</v>
+        <v>1451.02490955859</v>
       </c>
       <c r="E15" t="n">
-        <v>1458.647357512725</v>
+        <v>1458.96983721528</v>
       </c>
       <c r="F15" t="n">
-        <v>54884</v>
+        <v>54823</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1988,16 +1988,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1453.666919828227</v>
+        <v>1453.727153840523</v>
       </c>
       <c r="D16" t="n">
-        <v>1444.283478917564</v>
+        <v>1445.543146608404</v>
       </c>
       <c r="E16" t="n">
-        <v>1463.050360738891</v>
+        <v>1461.91116107264</v>
       </c>
       <c r="F16" t="n">
-        <v>4067</v>
+        <v>5465</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -2059,16 +2059,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1452.700393447212</v>
+        <v>1452.725186989559</v>
       </c>
       <c r="D17" t="n">
-        <v>1445.255816295289</v>
+        <v>1445.280785843011</v>
       </c>
       <c r="E17" t="n">
-        <v>1460.144970599134</v>
+        <v>1460.169588136107</v>
       </c>
       <c r="F17" t="n">
-        <v>6135</v>
+        <v>6137</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -2210,16 +2210,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1450.322097222436</v>
+        <v>1450.216689507568</v>
       </c>
       <c r="D18" t="n">
-        <v>1447.031991738154</v>
+        <v>1446.929149916141</v>
       </c>
       <c r="E18" t="n">
-        <v>1453.612202706719</v>
+        <v>1453.504229098995</v>
       </c>
       <c r="F18" t="n">
-        <v>74638</v>
+        <v>74623</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -2361,16 +2361,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1442.272203650681</v>
+        <v>1441.748598192381</v>
       </c>
       <c r="D19" t="n">
-        <v>1437.668069064474</v>
+        <v>1437.225364948475</v>
       </c>
       <c r="E19" t="n">
-        <v>1446.876338236888</v>
+        <v>1446.271831436289</v>
       </c>
       <c r="F19" t="n">
-        <v>32778</v>
+        <v>34594</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -2512,16 +2512,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1441.76065727842</v>
+        <v>1441.569858163239</v>
       </c>
       <c r="D20" t="n">
-        <v>1438.58007878054</v>
+        <v>1438.415460334742</v>
       </c>
       <c r="E20" t="n">
-        <v>1444.941235776301</v>
+        <v>1444.724255991736</v>
       </c>
       <c r="F20" t="n">
-        <v>86319</v>
+        <v>88092</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -2663,16 +2663,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1441.439229389047</v>
+        <v>1441.527333291579</v>
       </c>
       <c r="D21" t="n">
-        <v>1435.373551651657</v>
+        <v>1435.463199494398</v>
       </c>
       <c r="E21" t="n">
-        <v>1447.504907126436</v>
+        <v>1447.591467088759</v>
       </c>
       <c r="F21" t="n">
-        <v>12217</v>
+        <v>12219</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -2734,16 +2734,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1440.455319157471</v>
+        <v>1439.738386572274</v>
       </c>
       <c r="D22" t="n">
-        <v>1436.457079997135</v>
+        <v>1435.784625596188</v>
       </c>
       <c r="E22" t="n">
-        <v>1444.453558317808</v>
+        <v>1443.69214754836</v>
       </c>
       <c r="F22" t="n">
-        <v>56646</v>
+        <v>58171</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2881,68 +2881,148 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>deepseek-v4-flash-high-preview</t>
+          <t>qwen3.8-27b</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1438.511249621712</v>
+        <v>1438.527970325345</v>
       </c>
       <c r="D23" t="n">
-        <v>1434.396137039189</v>
+        <v>1433.077908944736</v>
       </c>
       <c r="E23" t="n">
-        <v>1442.626362204234</v>
+        <v>1443.978031705955</v>
       </c>
       <c r="F23" t="n">
-        <v>51747</v>
+        <v>17777</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>27</v>
+      </c>
+      <c r="J23" t="n">
+        <v>27</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>dense</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="inlineStr"/>
-      <c r="AB23" t="inlineStr"/>
-      <c r="AC23" t="inlineStr"/>
-      <c r="AD23" t="inlineStr"/>
-      <c r="AE23" t="inlineStr"/>
-      <c r="AF23" t="inlineStr"/>
-      <c r="AG23" t="inlineStr"/>
+          <t>name_parsing</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>54</v>
+      </c>
+      <c r="N23" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="O23" t="n">
+        <v>27</v>
+      </c>
+      <c r="P23" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="R23" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="S23" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T23" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U23" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V23" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W23" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X23" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y23" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z23" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA23" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB23" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC23" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD23" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE23" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF23" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG23" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -2952,148 +3032,68 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>qwen3.8-27b</t>
+          <t>deepseek-v4-flash-high-preview</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1437.646141726179</v>
+        <v>1438.477331717716</v>
       </c>
       <c r="D24" t="n">
-        <v>1432.044727574102</v>
+        <v>1434.364175827434</v>
       </c>
       <c r="E24" t="n">
-        <v>1443.247555878256</v>
+        <v>1442.590487607998</v>
       </c>
       <c r="F24" t="n">
-        <v>16383</v>
+        <v>51691</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>27</v>
-      </c>
-      <c r="J24" t="n">
-        <v>27</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>dense</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>name_parsing</t>
-        </is>
-      </c>
-      <c r="M24" t="n">
-        <v>54</v>
-      </c>
-      <c r="N24" t="n">
-        <v>67.5</v>
-      </c>
-      <c r="O24" t="n">
-        <v>27</v>
-      </c>
-      <c r="P24" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="R24" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="S24" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T24" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U24" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V24" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W24" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X24" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y24" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z24" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA24" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB24" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC24" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD24" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE24" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF24" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG24" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -3107,16 +3107,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1437.596854856683</v>
+        <v>1437.492243548209</v>
       </c>
       <c r="D25" t="n">
-        <v>1430.148118576312</v>
+        <v>1430.050380624826</v>
       </c>
       <c r="E25" t="n">
-        <v>1445.045591137053</v>
+        <v>1444.934106471592</v>
       </c>
       <c r="F25" t="n">
-        <v>6078</v>
+        <v>6083</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -3258,16 +3258,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1436.082397683043</v>
+        <v>1435.884601459908</v>
       </c>
       <c r="D26" t="n">
-        <v>1432.034761007065</v>
+        <v>1431.839115630689</v>
       </c>
       <c r="E26" t="n">
-        <v>1440.13003435902</v>
+        <v>1439.930087289127</v>
       </c>
       <c r="F26" t="n">
-        <v>51871</v>
+        <v>51869</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -3409,16 +3409,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1433.524268439191</v>
+        <v>1433.739132510029</v>
       </c>
       <c r="D27" t="n">
-        <v>1429.290248475836</v>
+        <v>1429.507860766121</v>
       </c>
       <c r="E27" t="n">
-        <v>1437.758288402545</v>
+        <v>1437.970404253938</v>
       </c>
       <c r="F27" t="n">
-        <v>47276</v>
+        <v>47292</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -3480,16 +3480,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1430.338606634385</v>
+        <v>1430.504886477788</v>
       </c>
       <c r="D28" t="n">
-        <v>1423.826285662016</v>
+        <v>1423.992345581362</v>
       </c>
       <c r="E28" t="n">
-        <v>1436.850927606753</v>
+        <v>1437.017427374215</v>
       </c>
       <c r="F28" t="n">
-        <v>8358</v>
+        <v>8355</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -3631,16 +3631,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1430.179839306566</v>
+        <v>1430.043446718033</v>
       </c>
       <c r="D29" t="n">
-        <v>1427.08413799048</v>
+        <v>1426.948812484133</v>
       </c>
       <c r="E29" t="n">
-        <v>1433.275540622652</v>
+        <v>1433.138080951932</v>
       </c>
       <c r="F29" t="n">
-        <v>63241</v>
+        <v>63225</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -3782,16 +3782,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1426.128306883759</v>
+        <v>1426.93139319545</v>
       </c>
       <c r="D30" t="n">
-        <v>1419.708380881053</v>
+        <v>1420.518446848027</v>
       </c>
       <c r="E30" t="n">
-        <v>1432.548232886464</v>
+        <v>1433.344339542874</v>
       </c>
       <c r="F30" t="n">
-        <v>11693</v>
+        <v>11757</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -3853,16 +3853,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1425.48234333038</v>
+        <v>1426.424051750329</v>
       </c>
       <c r="D31" t="n">
-        <v>1418.585864531288</v>
+        <v>1419.535993546036</v>
       </c>
       <c r="E31" t="n">
-        <v>1432.378822129473</v>
+        <v>1433.31210995462</v>
       </c>
       <c r="F31" t="n">
-        <v>11450</v>
+        <v>11532</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -4000,68 +4000,148 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>deepseek-v3.2-exp-thinking</t>
+          <t>muse-glimmer</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1424.943001618631</v>
+        <v>1424.924915090035</v>
       </c>
       <c r="D32" t="n">
-        <v>1418.363420810067</v>
+        <v>1415.229433023199</v>
       </c>
       <c r="E32" t="n">
-        <v>1431.522582427195</v>
+        <v>1434.62039715687</v>
       </c>
       <c r="F32" t="n">
-        <v>8942</v>
+        <v>3897</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>30</v>
+      </c>
+      <c r="J32" t="n">
+        <v>30</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>dense</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
-      <c r="AA32" t="inlineStr"/>
-      <c r="AB32" t="inlineStr"/>
-      <c r="AC32" t="inlineStr"/>
-      <c r="AD32" t="inlineStr"/>
-      <c r="AE32" t="inlineStr"/>
-      <c r="AF32" t="inlineStr"/>
-      <c r="AG32" t="inlineStr"/>
+          <t>aa_single_scrape</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
+        <v>60</v>
+      </c>
+      <c r="N32" t="n">
+        <v>75</v>
+      </c>
+      <c r="O32" t="n">
+        <v>30</v>
+      </c>
+      <c r="P32" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>15</v>
+      </c>
+      <c r="R32" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="S32" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T32" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U32" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V32" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W32" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X32" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y32" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z32" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA32" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB32" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC32" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD32" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE32" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF32" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG32" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -4071,20 +4151,20 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>deepseek-v3.2</t>
+          <t>deepseek-v3.2-exp-thinking</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1424.727195013049</v>
+        <v>1424.899244260691</v>
       </c>
       <c r="D33" t="n">
-        <v>1421.23070491309</v>
+        <v>1418.321775239341</v>
       </c>
       <c r="E33" t="n">
-        <v>1428.223685113009</v>
+        <v>1431.476713282041</v>
       </c>
       <c r="F33" t="n">
-        <v>48010</v>
+        <v>8948</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -4142,148 +4222,68 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>muse-glimmer</t>
+          <t>deepseek-v3.2</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1424.351645409489</v>
+        <v>1424.88463958302</v>
       </c>
       <c r="D34" t="n">
-        <v>1414.661688576071</v>
+        <v>1421.389557348873</v>
       </c>
       <c r="E34" t="n">
-        <v>1434.041602242908</v>
+        <v>1428.379721817166</v>
       </c>
       <c r="F34" t="n">
-        <v>3893</v>
+        <v>48004</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>30</v>
-      </c>
-      <c r="J34" t="n">
-        <v>30</v>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>dense</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>aa_single_scrape</t>
-        </is>
-      </c>
-      <c r="M34" t="n">
-        <v>60</v>
-      </c>
-      <c r="N34" t="n">
-        <v>75</v>
-      </c>
-      <c r="O34" t="n">
-        <v>30</v>
-      </c>
-      <c r="P34" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>15</v>
-      </c>
-      <c r="R34" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="S34" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T34" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U34" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V34" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W34" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X34" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y34" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z34" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA34" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB34" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC34" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD34" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE34" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF34" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG34" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr"/>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -4297,16 +4297,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1424.192443477933</v>
+        <v>1424.207107976129</v>
       </c>
       <c r="D35" t="n">
-        <v>1420.284186184221</v>
+        <v>1420.299184114695</v>
       </c>
       <c r="E35" t="n">
-        <v>1428.100700771646</v>
+        <v>1428.115031837564</v>
       </c>
       <c r="F35" t="n">
-        <v>35678</v>
+        <v>35668</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1422.621251561802</v>
+        <v>1422.63810922664</v>
       </c>
       <c r="D36" t="n">
-        <v>1419.038843535589</v>
+        <v>1419.05689958125</v>
       </c>
       <c r="E36" t="n">
-        <v>1426.203659588015</v>
+        <v>1426.219318872029</v>
       </c>
       <c r="F36" t="n">
-        <v>41980</v>
+        <v>41966</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -4439,16 +4439,16 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1422.395723229489</v>
+        <v>1422.364551154884</v>
       </c>
       <c r="D37" t="n">
-        <v>1419.837719541384</v>
+        <v>1419.807601048771</v>
       </c>
       <c r="E37" t="n">
-        <v>1424.953726917595</v>
+        <v>1424.921501260998</v>
       </c>
       <c r="F37" t="n">
-        <v>97815</v>
+        <v>97808</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -4590,16 +4590,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1421.927380581456</v>
+        <v>1422.027413572087</v>
       </c>
       <c r="D38" t="n">
-        <v>1415.538737617708</v>
+        <v>1415.63818303227</v>
       </c>
       <c r="E38" t="n">
-        <v>1428.316023545204</v>
+        <v>1428.416644111903</v>
       </c>
       <c r="F38" t="n">
-        <v>11947</v>
+        <v>11943</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -4661,16 +4661,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1421.556582498042</v>
+        <v>1421.588783462151</v>
       </c>
       <c r="D39" t="n">
-        <v>1415.863771764289</v>
+        <v>1415.895420047521</v>
       </c>
       <c r="E39" t="n">
-        <v>1427.249393231795</v>
+        <v>1427.28214687678</v>
       </c>
       <c r="F39" t="n">
-        <v>18065</v>
+        <v>18060</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -4732,16 +4732,16 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1418.588101347315</v>
+        <v>1418.632796184962</v>
       </c>
       <c r="D40" t="n">
-        <v>1412.049884099408</v>
+        <v>1412.096527854002</v>
       </c>
       <c r="E40" t="n">
-        <v>1425.126318595222</v>
+        <v>1425.169064515922</v>
       </c>
       <c r="F40" t="n">
-        <v>11537</v>
+        <v>11539</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -4883,16 +4883,16 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1418.278285215693</v>
+        <v>1418.176994107235</v>
       </c>
       <c r="D41" t="n">
-        <v>1413.369300357512</v>
+        <v>1413.268225982842</v>
       </c>
       <c r="E41" t="n">
-        <v>1423.187270073875</v>
+        <v>1423.085762231629</v>
       </c>
       <c r="F41" t="n">
-        <v>26960</v>
+        <v>26967</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -5030,20 +5030,20 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-terminus-thinking</t>
+          <t>deepseek-v3.1</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1417.289543694113</v>
+        <v>1417.161803158608</v>
       </c>
       <c r="D42" t="n">
-        <v>1407.153495527391</v>
+        <v>1411.092422280057</v>
       </c>
       <c r="E42" t="n">
-        <v>1427.425591860834</v>
+        <v>1423.231184037159</v>
       </c>
       <c r="F42" t="n">
-        <v>3351</v>
+        <v>14540</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -5101,20 +5101,20 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>deepseek-v3.1</t>
+          <t>deepseek-v3.1-terminus-thinking</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1417.109286221506</v>
+        <v>1416.927654322016</v>
       </c>
       <c r="D43" t="n">
-        <v>1411.040506623166</v>
+        <v>1406.799166716881</v>
       </c>
       <c r="E43" t="n">
-        <v>1423.178065819845</v>
+        <v>1427.056141927152</v>
       </c>
       <c r="F43" t="n">
-        <v>14543</v>
+        <v>3357</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -5176,16 +5176,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1416.165025336352</v>
+        <v>1416.082717859271</v>
       </c>
       <c r="D44" t="n">
-        <v>1411.866998667901</v>
+        <v>1411.78671457623</v>
       </c>
       <c r="E44" t="n">
-        <v>1420.463052004802</v>
+        <v>1420.378721142313</v>
       </c>
       <c r="F44" t="n">
-        <v>29671</v>
+        <v>29666</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -5327,16 +5327,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1415.937825352686</v>
+        <v>1416.001886592228</v>
       </c>
       <c r="D45" t="n">
-        <v>1409.260655682358</v>
+        <v>1409.324590646791</v>
       </c>
       <c r="E45" t="n">
-        <v>1422.614995023013</v>
+        <v>1422.679182537664</v>
       </c>
       <c r="F45" t="n">
-        <v>11408</v>
+        <v>11413</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -5398,16 +5398,16 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1414.798693847168</v>
+        <v>1414.920634971134</v>
       </c>
       <c r="D46" t="n">
-        <v>1411.349677702175</v>
+        <v>1411.495068497981</v>
       </c>
       <c r="E46" t="n">
-        <v>1418.24770999216</v>
+        <v>1418.346201444288</v>
       </c>
       <c r="F46" t="n">
-        <v>77968</v>
+        <v>79403</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -5469,16 +5469,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1414.735786359272</v>
+        <v>1414.719329220982</v>
       </c>
       <c r="D47" t="n">
-        <v>1405.006127557881</v>
+        <v>1404.992540263092</v>
       </c>
       <c r="E47" t="n">
-        <v>1424.465445160664</v>
+        <v>1424.446118178873</v>
       </c>
       <c r="F47" t="n">
-        <v>3600</v>
+        <v>3602</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -5536,24 +5536,24 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>qwen3-vl-235b-a22b-instruct</t>
+          <t>mistral-large-3</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1413.373119312256</v>
+        <v>1413.71702688143</v>
       </c>
       <c r="D48" t="n">
-        <v>1406.823541256837</v>
+        <v>1410.814913463878</v>
       </c>
       <c r="E48" t="n">
-        <v>1419.922697367675</v>
+        <v>1416.619140298982</v>
       </c>
       <c r="F48" t="n">
-        <v>11241</v>
+        <v>78986</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Mistral</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5562,10 +5562,10 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>235</v>
+        <v>675</v>
       </c>
       <c r="J48" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -5574,26 +5574,26 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>aa_single_scrape</t>
         </is>
       </c>
       <c r="M48" t="n">
-        <v>470</v>
+        <v>1350</v>
       </c>
       <c r="N48" t="n">
-        <v>587.5</v>
+        <v>1687.5</v>
       </c>
       <c r="O48" t="n">
-        <v>235</v>
+        <v>675</v>
       </c>
       <c r="P48" t="n">
-        <v>293.8</v>
+        <v>843.8</v>
       </c>
       <c r="Q48" t="n">
-        <v>117.5</v>
+        <v>337.5</v>
       </c>
       <c r="R48" t="n">
-        <v>146.9</v>
+        <v>421.9</v>
       </c>
       <c r="S48" s="5" t="inlineStr">
         <is>
@@ -5650,9 +5650,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AD48" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AD48" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AE48" s="5" t="inlineStr">
@@ -5665,9 +5665,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AG48" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AG48" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AH48" t="inlineStr">
@@ -5687,24 +5687,24 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>mistral-large-3</t>
+          <t>qwen3-vl-235b-a22b-instruct</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1413.254189810875</v>
+        <v>1413.393658132285</v>
       </c>
       <c r="D49" t="n">
-        <v>1410.341946753164</v>
+        <v>1406.84752602769</v>
       </c>
       <c r="E49" t="n">
-        <v>1416.166432868587</v>
+        <v>1419.93979023688</v>
       </c>
       <c r="F49" t="n">
-        <v>77456</v>
+        <v>11250</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Mistral</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5713,10 +5713,10 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>675</v>
+        <v>235</v>
       </c>
       <c r="J49" t="n">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -5725,26 +5725,26 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>aa_single_scrape</t>
+          <t>name_parsing</t>
         </is>
       </c>
       <c r="M49" t="n">
-        <v>1350</v>
+        <v>470</v>
       </c>
       <c r="N49" t="n">
-        <v>1687.5</v>
+        <v>587.5</v>
       </c>
       <c r="O49" t="n">
-        <v>675</v>
+        <v>235</v>
       </c>
       <c r="P49" t="n">
-        <v>843.8</v>
+        <v>293.8</v>
       </c>
       <c r="Q49" t="n">
-        <v>337.5</v>
+        <v>117.5</v>
       </c>
       <c r="R49" t="n">
-        <v>421.9</v>
+        <v>146.9</v>
       </c>
       <c r="S49" s="5" t="inlineStr">
         <is>
@@ -5801,9 +5801,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AD49" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AD49" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AE49" s="5" t="inlineStr">
@@ -5816,9 +5816,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AG49" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AG49" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AH49" t="inlineStr">
@@ -5842,16 +5842,16 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1411.330128492524</v>
+        <v>1411.283541364948</v>
       </c>
       <c r="D50" t="n">
-        <v>1406.387641870443</v>
+        <v>1406.342050636693</v>
       </c>
       <c r="E50" t="n">
-        <v>1416.272615114605</v>
+        <v>1416.225032093203</v>
       </c>
       <c r="F50" t="n">
-        <v>23659</v>
+        <v>23668</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -5993,16 +5993,16 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1409.346453228037</v>
+        <v>1408.934250793886</v>
       </c>
       <c r="D51" t="n">
-        <v>1401.923414769256</v>
+        <v>1401.513395538369</v>
       </c>
       <c r="E51" t="n">
-        <v>1416.769491686817</v>
+        <v>1416.355106049402</v>
       </c>
       <c r="F51" t="n">
-        <v>6878</v>
+        <v>6871</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1408.679541585013</v>
+        <v>1408.847189945266</v>
       </c>
       <c r="D52" t="n">
-        <v>1404.378363793411</v>
+        <v>1404.547032597415</v>
       </c>
       <c r="E52" t="n">
-        <v>1412.980719376616</v>
+        <v>1413.147347293117</v>
       </c>
       <c r="F52" t="n">
-        <v>28640</v>
+        <v>28618</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -6215,16 +6215,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1405.382356454817</v>
+        <v>1405.104088409852</v>
       </c>
       <c r="D53" t="n">
-        <v>1400.341485874024</v>
+        <v>1400.173688477651</v>
       </c>
       <c r="E53" t="n">
-        <v>1410.42322703561</v>
+        <v>1410.034488342053</v>
       </c>
       <c r="F53" t="n">
-        <v>24758</v>
+        <v>26446</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -6366,13 +6366,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1402.509401125762</v>
+        <v>1402.514885725651</v>
       </c>
       <c r="D54" t="n">
-        <v>1397.97121263939</v>
+        <v>1397.976702427165</v>
       </c>
       <c r="E54" t="n">
-        <v>1407.047589612134</v>
+        <v>1407.053069024138</v>
       </c>
       <c r="F54" t="n">
         <v>37284</v>
@@ -6517,16 +6517,16 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1401.268988164244</v>
+        <v>1401.147784004097</v>
       </c>
       <c r="D55" t="n">
-        <v>1394.843971028825</v>
+        <v>1394.723036303906</v>
       </c>
       <c r="E55" t="n">
-        <v>1407.694005299664</v>
+        <v>1407.572531704287</v>
       </c>
       <c r="F55" t="n">
-        <v>11119</v>
+        <v>11123</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -6668,13 +6668,13 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1400.012595735459</v>
+        <v>1400.029394812505</v>
       </c>
       <c r="D56" t="n">
-        <v>1393.424576177048</v>
+        <v>1393.442825219014</v>
       </c>
       <c r="E56" t="n">
-        <v>1406.60061529387</v>
+        <v>1406.615964405995</v>
       </c>
       <c r="F56" t="n">
         <v>8776</v>
@@ -6819,16 +6819,16 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1399.033589914891</v>
+        <v>1398.917802883869</v>
       </c>
       <c r="D57" t="n">
-        <v>1394.243760908307</v>
+        <v>1394.129073157556</v>
       </c>
       <c r="E57" t="n">
-        <v>1403.823418921475</v>
+        <v>1403.706532610182</v>
       </c>
       <c r="F57" t="n">
-        <v>22602</v>
+        <v>22607</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -6970,13 +6970,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1398.154358095204</v>
+        <v>1398.131709342381</v>
       </c>
       <c r="D58" t="n">
-        <v>1393.259705767154</v>
+        <v>1393.236456623881</v>
       </c>
       <c r="E58" t="n">
-        <v>1403.049010423254</v>
+        <v>1403.026962060881</v>
       </c>
       <c r="F58" t="n">
         <v>18524</v>
@@ -7121,16 +7121,16 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1395.690564742793</v>
+        <v>1395.644493084921</v>
       </c>
       <c r="D59" t="n">
-        <v>1391.79009886159</v>
+        <v>1391.743584630641</v>
       </c>
       <c r="E59" t="n">
-        <v>1399.591030623996</v>
+        <v>1399.545401539201</v>
       </c>
       <c r="F59" t="n">
-        <v>44754</v>
+        <v>44762</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -7272,16 +7272,16 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1394.902971935868</v>
+        <v>1394.721573546292</v>
       </c>
       <c r="D60" t="n">
-        <v>1388.046779429934</v>
+        <v>1387.869769710979</v>
       </c>
       <c r="E60" t="n">
-        <v>1401.759164441802</v>
+        <v>1401.573377381606</v>
       </c>
       <c r="F60" t="n">
-        <v>7797</v>
+        <v>7809</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -7423,16 +7423,16 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1394.124342656936</v>
+        <v>1393.876292885215</v>
       </c>
       <c r="D61" t="n">
-        <v>1389.881105558061</v>
+        <v>1389.635684824487</v>
       </c>
       <c r="E61" t="n">
-        <v>1398.367579755811</v>
+        <v>1398.116900945943</v>
       </c>
       <c r="F61" t="n">
-        <v>30420</v>
+        <v>30410</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -7574,16 +7574,16 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1393.195761368101</v>
+        <v>1393.218901680072</v>
       </c>
       <c r="D62" t="n">
-        <v>1389.636078731906</v>
+        <v>1389.661129148547</v>
       </c>
       <c r="E62" t="n">
-        <v>1396.755444004296</v>
+        <v>1396.776674211597</v>
       </c>
       <c r="F62" t="n">
-        <v>60243</v>
+        <v>60236</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -7645,16 +7645,16 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1391.637850357952</v>
+        <v>1391.686220300875</v>
       </c>
       <c r="D63" t="n">
-        <v>1388.147052298645</v>
+        <v>1388.19753769919</v>
       </c>
       <c r="E63" t="n">
-        <v>1395.12864841726</v>
+        <v>1395.174902902559</v>
       </c>
       <c r="F63" t="n">
-        <v>48020</v>
+        <v>48012</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -7716,16 +7716,16 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1390.810555901599</v>
+        <v>1390.839111536408</v>
       </c>
       <c r="D64" t="n">
-        <v>1386.912808096014</v>
+        <v>1386.941984139183</v>
       </c>
       <c r="E64" t="n">
-        <v>1394.708303707184</v>
+        <v>1394.736238933634</v>
       </c>
       <c r="F64" t="n">
-        <v>42743</v>
+        <v>42734</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -7787,16 +7787,16 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1387.384553753814</v>
+        <v>1387.365681487454</v>
       </c>
       <c r="D65" t="n">
-        <v>1382.389645990387</v>
+        <v>1382.371457549832</v>
       </c>
       <c r="E65" t="n">
-        <v>1392.379461517241</v>
+        <v>1392.359905425076</v>
       </c>
       <c r="F65" t="n">
-        <v>25012</v>
+        <v>25011</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -7938,13 +7938,13 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1386.888327753732</v>
+        <v>1387.082562410915</v>
       </c>
       <c r="D66" t="n">
-        <v>1380.702688230775</v>
+        <v>1380.898526865866</v>
       </c>
       <c r="E66" t="n">
-        <v>1393.07396727669</v>
+        <v>1393.266597955964</v>
       </c>
       <c r="F66" t="n">
         <v>11118</v>
@@ -8009,16 +8009,16 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1384.587964771323</v>
+        <v>1384.552537274528</v>
       </c>
       <c r="D67" t="n">
-        <v>1379.401108208978</v>
+        <v>1379.367489464706</v>
       </c>
       <c r="E67" t="n">
-        <v>1389.774821333668</v>
+        <v>1389.73758508435</v>
       </c>
       <c r="F67" t="n">
-        <v>17192</v>
+        <v>17187</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -8080,16 +8080,16 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1382.627077063453</v>
+        <v>1382.776203902379</v>
       </c>
       <c r="D68" t="n">
-        <v>1377.708572055231</v>
+        <v>1377.857461885636</v>
       </c>
       <c r="E68" t="n">
-        <v>1387.545582071676</v>
+        <v>1387.694945919122</v>
       </c>
       <c r="F68" t="n">
-        <v>23179</v>
+        <v>23182</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -8227,144 +8227,68 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>trinity-large-preview</t>
+          <t>glm-4.6v</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1378.69339628282</v>
+        <v>1378.904334248768</v>
       </c>
       <c r="D69" t="n">
-        <v>1374.428547214192</v>
+        <v>1367.724340989975</v>
       </c>
       <c r="E69" t="n">
-        <v>1382.958245351449</v>
+        <v>1390.08432750756</v>
       </c>
       <c r="F69" t="n">
-        <v>31227</v>
-      </c>
-      <c r="G69" t="inlineStr"/>
+        <v>2830</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Z.ai</t>
+        </is>
+      </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
-        </is>
-      </c>
-      <c r="I69" t="n">
-        <v>70</v>
-      </c>
-      <c r="J69" t="n">
-        <v>70</v>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>dense</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
-          <t>override</t>
-        </is>
-      </c>
-      <c r="M69" t="n">
-        <v>140</v>
-      </c>
-      <c r="N69" t="n">
-        <v>175</v>
-      </c>
-      <c r="O69" t="n">
-        <v>70</v>
-      </c>
-      <c r="P69" t="n">
-        <v>87.5</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>35</v>
-      </c>
-      <c r="R69" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="S69" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T69" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U69" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V69" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W69" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X69" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y69" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z69" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA69" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB69" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC69" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD69" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE69" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF69" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG69" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
+      <c r="V69" t="inlineStr"/>
+      <c r="W69" t="inlineStr"/>
+      <c r="X69" t="inlineStr"/>
+      <c r="Y69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr"/>
+      <c r="AA69" t="inlineStr"/>
+      <c r="AB69" t="inlineStr"/>
+      <c r="AC69" t="inlineStr"/>
+      <c r="AD69" t="inlineStr"/>
+      <c r="AE69" t="inlineStr"/>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="inlineStr"/>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>B200 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>RTX PRO 6000</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -8374,68 +8298,144 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>glm-4.6v</t>
+          <t>trinity-large-preview</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1378.634932239104</v>
+        <v>1378.602728468169</v>
       </c>
       <c r="D70" t="n">
-        <v>1367.451716566189</v>
+        <v>1374.33733439781</v>
       </c>
       <c r="E70" t="n">
-        <v>1389.818147912019</v>
+        <v>1382.868122538527</v>
       </c>
       <c r="F70" t="n">
-        <v>2830</v>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Z.ai</t>
-        </is>
-      </c>
+        <v>31220</v>
+      </c>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>70</v>
+      </c>
+      <c r="J70" t="n">
+        <v>70</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>dense</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="inlineStr"/>
-      <c r="S70" t="inlineStr"/>
-      <c r="T70" t="inlineStr"/>
-      <c r="U70" t="inlineStr"/>
-      <c r="V70" t="inlineStr"/>
-      <c r="W70" t="inlineStr"/>
-      <c r="X70" t="inlineStr"/>
-      <c r="Y70" t="inlineStr"/>
-      <c r="Z70" t="inlineStr"/>
-      <c r="AA70" t="inlineStr"/>
-      <c r="AB70" t="inlineStr"/>
-      <c r="AC70" t="inlineStr"/>
-      <c r="AD70" t="inlineStr"/>
-      <c r="AE70" t="inlineStr"/>
-      <c r="AF70" t="inlineStr"/>
-      <c r="AG70" t="inlineStr"/>
+          <t>override</t>
+        </is>
+      </c>
+      <c r="M70" t="n">
+        <v>140</v>
+      </c>
+      <c r="N70" t="n">
+        <v>175</v>
+      </c>
+      <c r="O70" t="n">
+        <v>70</v>
+      </c>
+      <c r="P70" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>35</v>
+      </c>
+      <c r="R70" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="S70" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T70" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U70" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V70" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W70" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X70" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y70" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z70" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA70" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB70" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC70" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD70" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE70" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF70" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG70" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>B200 SXM</t>
         </is>
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>RTX PRO 6000</t>
         </is>
       </c>
     </row>
@@ -8449,16 +8449,16 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1375.333080409216</v>
+        <v>1375.249838058633</v>
       </c>
       <c r="D71" t="n">
-        <v>1370.61721938999</v>
+        <v>1370.534232009159</v>
       </c>
       <c r="E71" t="n">
-        <v>1380.048941428441</v>
+        <v>1379.965444108106</v>
       </c>
       <c r="F71" t="n">
-        <v>25827</v>
+        <v>25826</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -8600,16 +8600,16 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1373.341609138925</v>
+        <v>1373.28095913468</v>
       </c>
       <c r="D72" t="n">
-        <v>1369.077553825379</v>
+        <v>1369.016695636827</v>
       </c>
       <c r="E72" t="n">
-        <v>1377.605664452471</v>
+        <v>1377.545222632533</v>
       </c>
       <c r="F72" t="n">
-        <v>30453</v>
+        <v>30454</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -8671,16 +8671,16 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1369.337244141478</v>
+        <v>1369.379870939476</v>
       </c>
       <c r="D73" t="n">
-        <v>1363.453871304014</v>
+        <v>1363.496361363839</v>
       </c>
       <c r="E73" t="n">
-        <v>1375.220616978941</v>
+        <v>1375.263380515114</v>
       </c>
       <c r="F73" t="n">
-        <v>13373</v>
+        <v>13382</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -8822,16 +8822,16 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1367.621378017926</v>
+        <v>1367.397818654712</v>
       </c>
       <c r="D74" t="n">
-        <v>1363.015969885764</v>
+        <v>1362.795106651039</v>
       </c>
       <c r="E74" t="n">
-        <v>1372.226786150087</v>
+        <v>1372.000530658386</v>
       </c>
       <c r="F74" t="n">
-        <v>30277</v>
+        <v>30281</v>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
@@ -8969,16 +8969,16 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1365.368821840935</v>
+        <v>1365.398502518858</v>
       </c>
       <c r="D75" t="n">
-        <v>1361.658890737217</v>
+        <v>1361.687713255282</v>
       </c>
       <c r="E75" t="n">
-        <v>1369.078752944654</v>
+        <v>1369.109291782434</v>
       </c>
       <c r="F75" t="n">
-        <v>46433</v>
+        <v>46437</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -9120,16 +9120,16 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1365.004324289416</v>
+        <v>1364.814945454096</v>
       </c>
       <c r="D76" t="n">
-        <v>1359.279521919622</v>
+        <v>1359.089024918612</v>
       </c>
       <c r="E76" t="n">
-        <v>1370.729126659209</v>
+        <v>1370.54086598958</v>
       </c>
       <c r="F76" t="n">
-        <v>11983</v>
+        <v>11979</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -9191,16 +9191,16 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1363.940722226001</v>
+        <v>1364.007351445573</v>
       </c>
       <c r="D77" t="n">
-        <v>1359.636690398483</v>
+        <v>1359.702894260482</v>
       </c>
       <c r="E77" t="n">
-        <v>1368.244754053519</v>
+        <v>1368.311808630664</v>
       </c>
       <c r="F77" t="n">
-        <v>34045</v>
+        <v>34048</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -9262,16 +9262,16 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1360.441449316562</v>
+        <v>1360.527707348794</v>
       </c>
       <c r="D78" t="n">
-        <v>1353.3085636749</v>
+        <v>1353.396045122099</v>
       </c>
       <c r="E78" t="n">
-        <v>1367.574334958224</v>
+        <v>1367.659369575488</v>
       </c>
       <c r="F78" t="n">
-        <v>7864</v>
+        <v>7861</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -9413,13 +9413,13 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1358.472950490656</v>
+        <v>1358.449197654003</v>
       </c>
       <c r="D79" t="n">
-        <v>1353.715077602223</v>
+        <v>1353.690870778885</v>
       </c>
       <c r="E79" t="n">
-        <v>1363.230823379089</v>
+        <v>1363.207524529121</v>
       </c>
       <c r="F79" t="n">
         <v>21770</v>
@@ -9564,16 +9564,16 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1356.56403534334</v>
+        <v>1356.45653708856</v>
       </c>
       <c r="D80" t="n">
-        <v>1351.328614147505</v>
+        <v>1351.221118051274</v>
       </c>
       <c r="E80" t="n">
-        <v>1361.799456539176</v>
+        <v>1361.691956125846</v>
       </c>
       <c r="F80" t="n">
-        <v>17352</v>
+        <v>17353</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -9635,16 +9635,16 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1355.851351296897</v>
+        <v>1355.957579807005</v>
       </c>
       <c r="D81" t="n">
-        <v>1347.582655478127</v>
+        <v>1347.690443363504</v>
       </c>
       <c r="E81" t="n">
-        <v>1364.120047115666</v>
+        <v>1364.224716250506</v>
       </c>
       <c r="F81" t="n">
-        <v>5419</v>
+        <v>5421</v>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
@@ -9782,13 +9782,13 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1353.639227283278</v>
+        <v>1353.698415166401</v>
       </c>
       <c r="D82" t="n">
-        <v>1350.160793713557</v>
+        <v>1350.219380659513</v>
       </c>
       <c r="E82" t="n">
-        <v>1357.117660853</v>
+        <v>1357.17744967329</v>
       </c>
       <c r="F82" t="n">
         <v>55477</v>
@@ -9853,16 +9853,16 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1352.381707981045</v>
+        <v>1352.264341847894</v>
       </c>
       <c r="D83" t="n">
-        <v>1343.934782640447</v>
+        <v>1343.818644627783</v>
       </c>
       <c r="E83" t="n">
-        <v>1360.828633321642</v>
+        <v>1360.710039068005</v>
       </c>
       <c r="F83" t="n">
-        <v>4809</v>
+        <v>4811</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -9924,16 +9924,16 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1351.630973965965</v>
+        <v>1351.701828685937</v>
       </c>
       <c r="D84" t="n">
-        <v>1347.251480988719</v>
+        <v>1347.324857486818</v>
       </c>
       <c r="E84" t="n">
-        <v>1356.010466943212</v>
+        <v>1356.078799885056</v>
       </c>
       <c r="F84" t="n">
-        <v>30021</v>
+        <v>30039</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -10075,16 +10075,16 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1349.289787981367</v>
+        <v>1349.393778453777</v>
       </c>
       <c r="D85" t="n">
-        <v>1341.759363005375</v>
+        <v>1341.865598512213</v>
       </c>
       <c r="E85" t="n">
-        <v>1356.820212957358</v>
+        <v>1356.92195839534</v>
       </c>
       <c r="F85" t="n">
-        <v>6267</v>
+        <v>6272</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -10142,20 +10142,20 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>llama-3.1-nemotron-ultra-253b-v1</t>
+          <t>nvidia-nemotron-3.5-lightning-30b-a3b-nvfp4</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1347.66039007213</v>
+        <v>1348.638015425588</v>
       </c>
       <c r="D86" t="n">
-        <v>1335.979088037577</v>
+        <v>1342.531248179645</v>
       </c>
       <c r="E86" t="n">
-        <v>1359.341692106682</v>
+        <v>1354.744782671531</v>
       </c>
       <c r="F86" t="n">
-        <v>2549</v>
+        <v>14326</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -10164,18 +10164,18 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Nvidia Open Model</t>
+          <t>OpenMDW-1.1</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>253</v>
+        <v>30</v>
       </c>
       <c r="J86" t="n">
-        <v>253</v>
+        <v>3</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -10184,76 +10184,76 @@
         </is>
       </c>
       <c r="M86" t="n">
-        <v>506</v>
+        <v>60</v>
       </c>
       <c r="N86" t="n">
-        <v>632.5</v>
+        <v>75</v>
       </c>
       <c r="O86" t="n">
-        <v>253</v>
+        <v>30</v>
       </c>
       <c r="P86" t="n">
-        <v>316.2</v>
+        <v>37.5</v>
       </c>
       <c r="Q86" t="n">
-        <v>126.5</v>
+        <v>15</v>
       </c>
       <c r="R86" t="n">
-        <v>158.1</v>
-      </c>
-      <c r="S86" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T86" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U86" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V86" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W86" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X86" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y86" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z86" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA86" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB86" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC86" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>18.8</v>
+      </c>
+      <c r="S86" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T86" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U86" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V86" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W86" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X86" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y86" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z86" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA86" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB86" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC86" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AD86" s="4" t="inlineStr">
@@ -10261,14 +10261,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE86" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF86" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AE86" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF86" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AG86" s="4" t="inlineStr">
@@ -10278,12 +10278,12 @@
       </c>
       <c r="AH86" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -10293,36 +10293,36 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>qwen3-32b</t>
+          <t>llama-3.1-nemotron-ultra-253b-v1</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1346.954121413984</v>
+        <v>1347.63978619981</v>
       </c>
       <c r="D87" t="n">
-        <v>1337.495056636261</v>
+        <v>1335.959897927538</v>
       </c>
       <c r="E87" t="n">
-        <v>1356.413186191707</v>
+        <v>1359.319674472084</v>
       </c>
       <c r="F87" t="n">
-        <v>3926</v>
+        <v>2549</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>Nvidia Open Model</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>32</v>
+        <v>253</v>
       </c>
       <c r="J87" t="n">
-        <v>32</v>
+        <v>253</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -10335,76 +10335,76 @@
         </is>
       </c>
       <c r="M87" t="n">
-        <v>64</v>
+        <v>506</v>
       </c>
       <c r="N87" t="n">
-        <v>80</v>
+        <v>632.5</v>
       </c>
       <c r="O87" t="n">
-        <v>32</v>
+        <v>253</v>
       </c>
       <c r="P87" t="n">
-        <v>40</v>
+        <v>316.2</v>
       </c>
       <c r="Q87" t="n">
-        <v>16</v>
+        <v>126.5</v>
       </c>
       <c r="R87" t="n">
-        <v>20</v>
-      </c>
-      <c r="S87" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T87" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U87" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V87" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W87" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X87" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y87" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z87" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA87" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB87" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC87" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>158.1</v>
+      </c>
+      <c r="S87" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T87" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U87" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V87" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W87" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X87" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y87" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z87" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA87" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB87" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC87" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AD87" s="4" t="inlineStr">
@@ -10412,14 +10412,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE87" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF87" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AE87" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF87" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AG87" s="4" t="inlineStr">
@@ -10429,12 +10429,12 @@
       </c>
       <c r="AH87" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -10444,40 +10444,40 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>nvidia-nemotron-3.5-lightning-30b-a3b-nvfp4</t>
+          <t>qwen3-32b</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1346.796171415899</v>
+        <v>1346.941718728933</v>
       </c>
       <c r="D88" t="n">
-        <v>1340.487082223989</v>
+        <v>1337.483550820804</v>
       </c>
       <c r="E88" t="n">
-        <v>1353.105260607809</v>
+        <v>1356.399886637062</v>
       </c>
       <c r="F88" t="n">
-        <v>12912</v>
+        <v>3926</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>OpenMDW-1.1</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J88" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -10486,22 +10486,22 @@
         </is>
       </c>
       <c r="M88" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="N88" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="O88" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P88" t="n">
-        <v>37.5</v>
+        <v>40</v>
       </c>
       <c r="Q88" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R88" t="n">
-        <v>18.8</v>
+        <v>20</v>
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
@@ -10599,13 +10599,13 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1343.655870057903</v>
+        <v>1343.790491861378</v>
       </c>
       <c r="D89" t="n">
-        <v>1336.343089462374</v>
+        <v>1336.479311392364</v>
       </c>
       <c r="E89" t="n">
-        <v>1350.968650653432</v>
+        <v>1351.101672330391</v>
       </c>
       <c r="F89" t="n">
         <v>6889</v>
@@ -10670,16 +10670,16 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1343.419198291101</v>
+        <v>1343.23601620115</v>
       </c>
       <c r="D90" t="n">
-        <v>1335.658511683877</v>
+        <v>1335.477497952291</v>
       </c>
       <c r="E90" t="n">
-        <v>1351.179884898326</v>
+        <v>1350.994534450009</v>
       </c>
       <c r="F90" t="n">
-        <v>6817</v>
+        <v>6819</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -10821,13 +10821,13 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1342.920054673199</v>
+        <v>1342.90837339088</v>
       </c>
       <c r="D91" t="n">
-        <v>1332.898703524842</v>
+        <v>1332.887583633109</v>
       </c>
       <c r="E91" t="n">
-        <v>1352.941405821556</v>
+        <v>1352.929163148651</v>
       </c>
       <c r="F91" t="n">
         <v>3308</v>
@@ -10972,13 +10972,13 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1341.774036215396</v>
+        <v>1341.753768013428</v>
       </c>
       <c r="D92" t="n">
-        <v>1332.261338097639</v>
+        <v>1332.241683836977</v>
       </c>
       <c r="E92" t="n">
-        <v>1351.286734333153</v>
+        <v>1351.26585218988</v>
       </c>
       <c r="F92" t="n">
         <v>3829</v>
@@ -11123,16 +11123,16 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1341.451914845616</v>
+        <v>1339.754013372682</v>
       </c>
       <c r="D93" t="n">
-        <v>1330.966521072205</v>
+        <v>1329.294586317335</v>
       </c>
       <c r="E93" t="n">
-        <v>1351.937308619028</v>
+        <v>1350.213440428028</v>
       </c>
       <c r="F93" t="n">
-        <v>3385</v>
+        <v>3416</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -11274,16 +11274,16 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1335.844803651216</v>
+        <v>1335.887162152065</v>
       </c>
       <c r="D94" t="n">
-        <v>1331.37674345525</v>
+        <v>1331.418704307066</v>
       </c>
       <c r="E94" t="n">
-        <v>1340.312863847182</v>
+        <v>1340.355619997063</v>
       </c>
       <c r="F94" t="n">
-        <v>25080</v>
+        <v>25084</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -11425,13 +11425,13 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1335.396767906277</v>
+        <v>1335.350784796819</v>
       </c>
       <c r="D95" t="n">
-        <v>1331.666099139839</v>
+        <v>1331.619375269566</v>
       </c>
       <c r="E95" t="n">
-        <v>1339.127436672714</v>
+        <v>1339.082194324071</v>
       </c>
       <c r="F95" t="n">
         <v>41375</v>
@@ -11576,13 +11576,13 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1333.535599215408</v>
+        <v>1333.488510616226</v>
       </c>
       <c r="D96" t="n">
-        <v>1329.929293474895</v>
+        <v>1329.882089784069</v>
       </c>
       <c r="E96" t="n">
-        <v>1337.14190495592</v>
+        <v>1337.094931448383</v>
       </c>
       <c r="F96" t="n">
         <v>59656</v>
@@ -11727,16 +11727,16 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1329.135152009183</v>
+        <v>1329.149177354398</v>
       </c>
       <c r="D97" t="n">
-        <v>1322.988160453112</v>
+        <v>1323.00210756666</v>
       </c>
       <c r="E97" t="n">
-        <v>1335.282143565255</v>
+        <v>1335.296247142136</v>
       </c>
       <c r="F97" t="n">
-        <v>11798</v>
+        <v>11794</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -11878,13 +11878,13 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1327.833283363378</v>
+        <v>1327.817417702807</v>
       </c>
       <c r="D98" t="n">
-        <v>1315.696832203158</v>
+        <v>1315.682672489192</v>
       </c>
       <c r="E98" t="n">
-        <v>1339.969734523598</v>
+        <v>1339.952162916422</v>
       </c>
       <c r="F98" t="n">
         <v>2218</v>
@@ -12029,13 +12029,13 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1326.968998306045</v>
+        <v>1326.970503033269</v>
       </c>
       <c r="D99" t="n">
-        <v>1322.684655654117</v>
+        <v>1322.685239792983</v>
       </c>
       <c r="E99" t="n">
-        <v>1331.253340957974</v>
+        <v>1331.255766273555</v>
       </c>
       <c r="F99" t="n">
         <v>39266</v>
@@ -12180,16 +12180,16 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1326.561610886256</v>
+        <v>1326.568297418625</v>
       </c>
       <c r="D100" t="n">
-        <v>1321.802081810471</v>
+        <v>1321.808821524116</v>
       </c>
       <c r="E100" t="n">
-        <v>1331.32113996204</v>
+        <v>1331.327773313134</v>
       </c>
       <c r="F100" t="n">
-        <v>26041</v>
+        <v>26036</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -12331,13 +12331,13 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1323.428629689143</v>
+        <v>1323.398766612131</v>
       </c>
       <c r="D101" t="n">
-        <v>1315.154546040138</v>
+        <v>1315.125148461245</v>
       </c>
       <c r="E101" t="n">
-        <v>1331.702713338147</v>
+        <v>1331.672384763016</v>
       </c>
       <c r="F101" t="n">
         <v>6795</v>
@@ -12402,16 +12402,16 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1322.417911252836</v>
+        <v>1322.614596574088</v>
       </c>
       <c r="D102" t="n">
-        <v>1315.114004528849</v>
+        <v>1315.313609654477</v>
       </c>
       <c r="E102" t="n">
-        <v>1329.721817976822</v>
+        <v>1329.915583493699</v>
       </c>
       <c r="F102" t="n">
-        <v>6933</v>
+        <v>6934</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -12473,13 +12473,13 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1321.817291873444</v>
+        <v>1321.855445026273</v>
       </c>
       <c r="D103" t="n">
-        <v>1300.615062884243</v>
+        <v>1300.659302405044</v>
       </c>
       <c r="E103" t="n">
-        <v>1343.019520862645</v>
+        <v>1343.051587647502</v>
       </c>
       <c r="F103" t="n">
         <v>818</v>
@@ -12624,16 +12624,16 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1321.564688291112</v>
+        <v>1321.58165610929</v>
       </c>
       <c r="D104" t="n">
-        <v>1316.821569779454</v>
+        <v>1316.8365391562</v>
       </c>
       <c r="E104" t="n">
-        <v>1326.307806802771</v>
+        <v>1326.326773062379</v>
       </c>
       <c r="F104" t="n">
-        <v>29673</v>
+        <v>29668</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -12775,13 +12775,13 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1318.126697478903</v>
+        <v>1318.089425765077</v>
       </c>
       <c r="D105" t="n">
-        <v>1312.422283057305</v>
+        <v>1312.385328424837</v>
       </c>
       <c r="E105" t="n">
-        <v>1323.831111900501</v>
+        <v>1323.793523105317</v>
       </c>
       <c r="F105" t="n">
         <v>16478</v>
@@ -12846,16 +12846,16 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1317.837885226339</v>
+        <v>1317.788321856259</v>
       </c>
       <c r="D106" t="n">
-        <v>1314.329395969462</v>
+        <v>1314.27865960886</v>
       </c>
       <c r="E106" t="n">
-        <v>1321.346374483216</v>
+        <v>1321.297984103657</v>
       </c>
       <c r="F106" t="n">
-        <v>54368</v>
+        <v>54371</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -12997,16 +12997,16 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1317.605292382493</v>
+        <v>1317.586336181587</v>
       </c>
       <c r="D107" t="n">
-        <v>1311.184651432275</v>
+        <v>1311.164885997544</v>
       </c>
       <c r="E107" t="n">
-        <v>1324.02593333271</v>
+        <v>1324.007786365631</v>
       </c>
       <c r="F107" t="n">
-        <v>10372</v>
+        <v>10371</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -13148,16 +13148,16 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1317.373804129622</v>
+        <v>1317.34354855468</v>
       </c>
       <c r="D108" t="n">
-        <v>1312.182341687731</v>
+        <v>1312.151781278129</v>
       </c>
       <c r="E108" t="n">
-        <v>1322.565266571514</v>
+        <v>1322.535315831231</v>
       </c>
       <c r="F108" t="n">
-        <v>22041</v>
+        <v>22038</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -13299,13 +13299,13 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1314.416410467281</v>
+        <v>1314.374079986559</v>
       </c>
       <c r="D109" t="n">
-        <v>1310.481278006264</v>
+        <v>1310.438986850528</v>
       </c>
       <c r="E109" t="n">
-        <v>1318.351542928297</v>
+        <v>1318.30917312259</v>
       </c>
       <c r="F109" t="n">
         <v>45459</v>
@@ -13450,13 +13450,13 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1314.181791858227</v>
+        <v>1314.153397072419</v>
       </c>
       <c r="D110" t="n">
-        <v>1309.615149812134</v>
+        <v>1309.586389242329</v>
       </c>
       <c r="E110" t="n">
-        <v>1318.748433904321</v>
+        <v>1318.720404902508</v>
       </c>
       <c r="F110" t="n">
         <v>24739</v>
@@ -13597,16 +13597,16 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1313.429857546169</v>
+        <v>1313.525399923312</v>
       </c>
       <c r="D111" t="n">
-        <v>1307.941605317209</v>
+        <v>1308.037076863434</v>
       </c>
       <c r="E111" t="n">
-        <v>1318.918109775128</v>
+        <v>1319.01372298319</v>
       </c>
       <c r="F111" t="n">
-        <v>15731</v>
+        <v>15724</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -13748,13 +13748,13 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1307.223937498989</v>
+        <v>1307.193014915279</v>
       </c>
       <c r="D112" t="n">
-        <v>1302.50981426102</v>
+        <v>1302.478973336676</v>
       </c>
       <c r="E112" t="n">
-        <v>1311.938060736957</v>
+        <v>1311.907056493883</v>
       </c>
       <c r="F112" t="n">
         <v>24572</v>
@@ -13819,13 +13819,13 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1306.630079808497</v>
+        <v>1306.605417251318</v>
       </c>
       <c r="D113" t="n">
-        <v>1300.953513055197</v>
+        <v>1300.929339296507</v>
       </c>
       <c r="E113" t="n">
-        <v>1312.306646561796</v>
+        <v>1312.281495206129</v>
       </c>
       <c r="F113" t="n">
         <v>19621</v>
@@ -13966,16 +13966,16 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1306.288859530953</v>
+        <v>1306.478628109015</v>
       </c>
       <c r="D114" t="n">
-        <v>1298.038117360211</v>
+        <v>1298.22632596132</v>
       </c>
       <c r="E114" t="n">
-        <v>1314.539601701695</v>
+        <v>1314.73093025671</v>
       </c>
       <c r="F114" t="n">
-        <v>5817</v>
+        <v>5811</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -14117,13 +14117,13 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1305.57381347688</v>
+        <v>1305.537362219416</v>
       </c>
       <c r="D115" t="n">
-        <v>1301.11881487105</v>
+        <v>1301.081613969688</v>
       </c>
       <c r="E115" t="n">
-        <v>1310.02881208271</v>
+        <v>1309.993110469145</v>
       </c>
       <c r="F115" t="n">
         <v>28073</v>
@@ -14188,16 +14188,16 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1304.060509069387</v>
+        <v>1304.697817282826</v>
       </c>
       <c r="D116" t="n">
-        <v>1294.037370112897</v>
+        <v>1294.681778635902</v>
       </c>
       <c r="E116" t="n">
-        <v>1314.083648025878</v>
+        <v>1314.71385592975</v>
       </c>
       <c r="F116" t="n">
-        <v>4168</v>
+        <v>4166</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -14339,13 +14339,13 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1303.258565855304</v>
+        <v>1303.238264983027</v>
       </c>
       <c r="D117" t="n">
-        <v>1293.94025355712</v>
+        <v>1293.920506790486</v>
       </c>
       <c r="E117" t="n">
-        <v>1312.576878153489</v>
+        <v>1312.556023175568</v>
       </c>
       <c r="F117" t="n">
         <v>4171</v>
@@ -14490,16 +14490,16 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1303.126242131119</v>
+        <v>1303.080256468803</v>
       </c>
       <c r="D118" t="n">
-        <v>1298.577779650801</v>
+        <v>1298.530132923503</v>
       </c>
       <c r="E118" t="n">
-        <v>1307.674704611438</v>
+        <v>1307.630380014103</v>
       </c>
       <c r="F118" t="n">
-        <v>32548</v>
+        <v>32556</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -14641,13 +14641,13 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1302.893192871758</v>
+        <v>1302.858096991783</v>
       </c>
       <c r="D119" t="n">
-        <v>1298.805000672484</v>
+        <v>1298.769563628147</v>
       </c>
       <c r="E119" t="n">
-        <v>1306.981385071032</v>
+        <v>1306.946630355419</v>
       </c>
       <c r="F119" t="n">
         <v>39406</v>
@@ -14792,13 +14792,13 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1298.76453141336</v>
+        <v>1298.743514000223</v>
       </c>
       <c r="D120" t="n">
-        <v>1291.000714143914</v>
+        <v>1290.98028822052</v>
       </c>
       <c r="E120" t="n">
-        <v>1306.528348682805</v>
+        <v>1306.506739779927</v>
       </c>
       <c r="F120" t="n">
         <v>7140</v>
@@ -14943,13 +14943,13 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1293.345879021566</v>
+        <v>1293.321654520926</v>
       </c>
       <c r="D121" t="n">
-        <v>1289.597612195103</v>
+        <v>1289.57322392304</v>
       </c>
       <c r="E121" t="n">
-        <v>1297.094145848029</v>
+        <v>1297.070085118811</v>
       </c>
       <c r="F121" t="n">
         <v>55240</v>
@@ -15090,36 +15090,36 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>granite-4.2-3b</t>
+          <t>gemma-2-27b-it</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1291.880100198349</v>
+        <v>1289.44579585212</v>
       </c>
       <c r="D122" t="n">
-        <v>1280.3029058835</v>
+        <v>1286.048454251964</v>
       </c>
       <c r="E122" t="n">
-        <v>1303.457294513197</v>
+        <v>1292.843137452277</v>
       </c>
       <c r="F122" t="n">
-        <v>3237</v>
+        <v>75754</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>Gemma license</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="J122" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
@@ -15132,22 +15132,22 @@
         </is>
       </c>
       <c r="M122" t="n">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="N122" t="n">
-        <v>7.5</v>
+        <v>67.5</v>
       </c>
       <c r="O122" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="P122" t="n">
-        <v>3.8</v>
+        <v>33.8</v>
       </c>
       <c r="Q122" t="n">
-        <v>1.5</v>
+        <v>13.5</v>
       </c>
       <c r="R122" t="n">
-        <v>1.9</v>
+        <v>16.9</v>
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
@@ -15241,148 +15241,64 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>gemma-2-27b-it</t>
+          <t>jamba-1.5-large</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1289.481012492317</v>
+        <v>1289.433482059348</v>
       </c>
       <c r="D123" t="n">
-        <v>1286.084076837895</v>
+        <v>1282.127621895249</v>
       </c>
       <c r="E123" t="n">
-        <v>1292.877948146738</v>
+        <v>1296.739342223447</v>
       </c>
       <c r="F123" t="n">
-        <v>75754</v>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
+        <v>8662</v>
+      </c>
+      <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Gemma license</t>
-        </is>
-      </c>
-      <c r="I123" t="n">
-        <v>27</v>
-      </c>
-      <c r="J123" t="n">
-        <v>27</v>
-      </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>dense</t>
-        </is>
-      </c>
+          <t>Jamba Open</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr">
         <is>
-          <t>name_parsing</t>
-        </is>
-      </c>
-      <c r="M123" t="n">
-        <v>54</v>
-      </c>
-      <c r="N123" t="n">
-        <v>67.5</v>
-      </c>
-      <c r="O123" t="n">
-        <v>27</v>
-      </c>
-      <c r="P123" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="Q123" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="R123" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="S123" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T123" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U123" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V123" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W123" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X123" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y123" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z123" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA123" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB123" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC123" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD123" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE123" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF123" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG123" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr"/>
+      <c r="P123" t="inlineStr"/>
+      <c r="Q123" t="inlineStr"/>
+      <c r="R123" t="inlineStr"/>
+      <c r="S123" t="inlineStr"/>
+      <c r="T123" t="inlineStr"/>
+      <c r="U123" t="inlineStr"/>
+      <c r="V123" t="inlineStr"/>
+      <c r="W123" t="inlineStr"/>
+      <c r="X123" t="inlineStr"/>
+      <c r="Y123" t="inlineStr"/>
+      <c r="Z123" t="inlineStr"/>
+      <c r="AA123" t="inlineStr"/>
+      <c r="AB123" t="inlineStr"/>
+      <c r="AC123" t="inlineStr"/>
+      <c r="AD123" t="inlineStr"/>
+      <c r="AE123" t="inlineStr"/>
+      <c r="AF123" t="inlineStr"/>
+      <c r="AG123" t="inlineStr"/>
       <c r="AH123" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -15392,64 +15308,148 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>jamba-1.5-large</t>
+          <t>granite-4.2-3b</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1289.475213796571</v>
+        <v>1289.195559251609</v>
       </c>
       <c r="D124" t="n">
-        <v>1282.168622671922</v>
+        <v>1277.614050752003</v>
       </c>
       <c r="E124" t="n">
-        <v>1296.781804921221</v>
+        <v>1300.777067751214</v>
       </c>
       <c r="F124" t="n">
-        <v>8662</v>
-      </c>
-      <c r="G124" t="inlineStr"/>
+        <v>3266</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Jamba Open</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="I124" t="n">
+        <v>3</v>
+      </c>
+      <c r="J124" t="n">
+        <v>3</v>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>dense</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
-      <c r="O124" t="inlineStr"/>
-      <c r="P124" t="inlineStr"/>
-      <c r="Q124" t="inlineStr"/>
-      <c r="R124" t="inlineStr"/>
-      <c r="S124" t="inlineStr"/>
-      <c r="T124" t="inlineStr"/>
-      <c r="U124" t="inlineStr"/>
-      <c r="V124" t="inlineStr"/>
-      <c r="W124" t="inlineStr"/>
-      <c r="X124" t="inlineStr"/>
-      <c r="Y124" t="inlineStr"/>
-      <c r="Z124" t="inlineStr"/>
-      <c r="AA124" t="inlineStr"/>
-      <c r="AB124" t="inlineStr"/>
-      <c r="AC124" t="inlineStr"/>
-      <c r="AD124" t="inlineStr"/>
-      <c r="AE124" t="inlineStr"/>
-      <c r="AF124" t="inlineStr"/>
-      <c r="AG124" t="inlineStr"/>
+          <t>name_parsing</t>
+        </is>
+      </c>
+      <c r="M124" t="n">
+        <v>6</v>
+      </c>
+      <c r="N124" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="O124" t="n">
+        <v>3</v>
+      </c>
+      <c r="P124" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R124" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S124" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T124" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U124" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V124" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W124" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X124" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y124" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z124" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA124" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB124" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC124" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD124" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE124" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF124" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG124" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH124" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -15463,16 +15463,16 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1289.088790909675</v>
+        <v>1287.618860268671</v>
       </c>
       <c r="D125" t="n">
-        <v>1277.885978320857</v>
+        <v>1276.45584953181</v>
       </c>
       <c r="E125" t="n">
-        <v>1300.291603498494</v>
+        <v>1298.781871005531</v>
       </c>
       <c r="F125" t="n">
-        <v>3218</v>
+        <v>3255</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -15614,16 +15614,16 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1286.900701578481</v>
+        <v>1286.768820098388</v>
       </c>
       <c r="D126" t="n">
-        <v>1278.448110461977</v>
+        <v>1278.320532266788</v>
       </c>
       <c r="E126" t="n">
-        <v>1295.353292694985</v>
+        <v>1295.217107929989</v>
       </c>
       <c r="F126" t="n">
-        <v>5576</v>
+        <v>5581</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -15765,13 +15765,13 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1286.597987879601</v>
+        <v>1286.552312852134</v>
       </c>
       <c r="D127" t="n">
-        <v>1276.630337546758</v>
+        <v>1276.58571255348</v>
       </c>
       <c r="E127" t="n">
-        <v>1296.565638212444</v>
+        <v>1296.518913150787</v>
       </c>
       <c r="F127" t="n">
         <v>3749</v>
@@ -15916,16 +15916,16 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1286.500737232978</v>
+        <v>1286.465300433618</v>
       </c>
       <c r="D128" t="n">
-        <v>1279.229214878799</v>
+        <v>1279.190416432475</v>
       </c>
       <c r="E128" t="n">
-        <v>1293.772259587157</v>
+        <v>1293.740184434761</v>
       </c>
       <c r="F128" t="n">
-        <v>8285</v>
+        <v>8278</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -16067,13 +16067,13 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1286.085289365471</v>
+        <v>1286.055811882577</v>
       </c>
       <c r="D129" t="n">
-        <v>1275.624748234753</v>
+        <v>1275.596397752076</v>
       </c>
       <c r="E129" t="n">
-        <v>1296.545830496188</v>
+        <v>1296.515226013077</v>
       </c>
       <c r="F129" t="n">
         <v>2846</v>
@@ -16218,13 +16218,13 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1280.391750705654</v>
+        <v>1280.367998734232</v>
       </c>
       <c r="D130" t="n">
-        <v>1273.532998971313</v>
+        <v>1273.509941818239</v>
       </c>
       <c r="E130" t="n">
-        <v>1287.250502439996</v>
+        <v>1287.226055650224</v>
       </c>
       <c r="F130" t="n">
         <v>10072</v>
@@ -16365,13 +16365,13 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1277.124396623984</v>
+        <v>1277.075573481362</v>
       </c>
       <c r="D131" t="n">
-        <v>1271.803831570479</v>
+        <v>1271.756008526501</v>
       </c>
       <c r="E131" t="n">
-        <v>1282.44496167749</v>
+        <v>1282.395138436223</v>
       </c>
       <c r="F131" t="n">
         <v>19659</v>
@@ -16516,13 +16516,13 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1276.542808061702</v>
+        <v>1276.498614867255</v>
       </c>
       <c r="D132" t="n">
-        <v>1272.955074615081</v>
+        <v>1272.911616348642</v>
       </c>
       <c r="E132" t="n">
-        <v>1280.130541508322</v>
+        <v>1280.085613385869</v>
       </c>
       <c r="F132" t="n">
         <v>156876</v>
@@ -16667,13 +16667,13 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1276.286565745268</v>
+        <v>1276.241659655763</v>
       </c>
       <c r="D133" t="n">
-        <v>1269.706936974068</v>
+        <v>1269.662513617844</v>
       </c>
       <c r="E133" t="n">
-        <v>1282.866194516468</v>
+        <v>1282.820805693682</v>
       </c>
       <c r="F133" t="n">
         <v>9866</v>
@@ -16818,13 +16818,13 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1274.410868214498</v>
+        <v>1274.376357995334</v>
       </c>
       <c r="D134" t="n">
-        <v>1268.489946164187</v>
+        <v>1268.455054055693</v>
       </c>
       <c r="E134" t="n">
-        <v>1280.33179026481</v>
+        <v>1280.297661934974</v>
       </c>
       <c r="F134" t="n">
         <v>14681</v>
@@ -16969,13 +16969,13 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1270.620772533712</v>
+        <v>1270.582770050619</v>
       </c>
       <c r="D135" t="n">
-        <v>1262.49103860859</v>
+        <v>1262.453592537177</v>
       </c>
       <c r="E135" t="n">
-        <v>1278.750506458835</v>
+        <v>1278.711947564061</v>
       </c>
       <c r="F135" t="n">
         <v>5432</v>
@@ -17120,13 +17120,13 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1267.243525179488</v>
+        <v>1267.208966085903</v>
       </c>
       <c r="D136" t="n">
-        <v>1262.343249026724</v>
+        <v>1262.308473492927</v>
       </c>
       <c r="E136" t="n">
-        <v>1272.143801332252</v>
+        <v>1272.109458678879</v>
       </c>
       <c r="F136" t="n">
         <v>27124</v>
@@ -17271,13 +17271,13 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1267.010270285895</v>
+        <v>1266.974374429908</v>
       </c>
       <c r="D137" t="n">
-        <v>1263.178175767925</v>
+        <v>1263.141950885822</v>
       </c>
       <c r="E137" t="n">
-        <v>1270.842364803866</v>
+        <v>1270.806797973994</v>
       </c>
       <c r="F137" t="n">
         <v>54611</v>
@@ -17422,13 +17422,13 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1265.377578658984</v>
+        <v>1265.328158708027</v>
       </c>
       <c r="D138" t="n">
-        <v>1259.10223890535</v>
+        <v>1259.053843776338</v>
       </c>
       <c r="E138" t="n">
-        <v>1271.652918412619</v>
+        <v>1271.602473639715</v>
       </c>
       <c r="F138" t="n">
         <v>15147</v>
@@ -17573,13 +17573,13 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1261.808317128897</v>
+        <v>1261.76488088378</v>
       </c>
       <c r="D139" t="n">
-        <v>1256.859249582767</v>
+        <v>1256.816386948708</v>
       </c>
       <c r="E139" t="n">
-        <v>1266.757384675027</v>
+        <v>1266.713374818851</v>
       </c>
       <c r="F139" t="n">
         <v>37325</v>
@@ -17724,13 +17724,13 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1261.754021302668</v>
+        <v>1261.702582446025</v>
       </c>
       <c r="D140" t="n">
-        <v>1257.434227866158</v>
+        <v>1257.383814774923</v>
       </c>
       <c r="E140" t="n">
-        <v>1266.073814739178</v>
+        <v>1266.021350117127</v>
       </c>
       <c r="F140" t="n">
         <v>77554</v>
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>1256.302775074545</v>
+        <v>1256.27072894919</v>
       </c>
       <c r="D141" t="n">
-        <v>1251.692832254765</v>
+        <v>1251.660164590519</v>
       </c>
       <c r="E141" t="n">
-        <v>1260.912717894326</v>
+        <v>1260.881293307861</v>
       </c>
       <c r="F141" t="n">
         <v>24126</v>
@@ -17946,13 +17946,13 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1251.658905884851</v>
+        <v>1251.63397879215</v>
       </c>
       <c r="D142" t="n">
-        <v>1240.880993553414</v>
+        <v>1240.85711829353</v>
       </c>
       <c r="E142" t="n">
-        <v>1262.436818216289</v>
+        <v>1262.410839290771</v>
       </c>
       <c r="F142" t="n">
         <v>3334</v>
@@ -18097,13 +18097,13 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>1250.40800698115</v>
+        <v>1250.355273553091</v>
       </c>
       <c r="D143" t="n">
-        <v>1243.803588926578</v>
+        <v>1243.751406986555</v>
       </c>
       <c r="E143" t="n">
-        <v>1257.012425035722</v>
+        <v>1256.959140119627</v>
       </c>
       <c r="F143" t="n">
         <v>10140</v>
@@ -18248,13 +18248,13 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>1239.791626964324</v>
+        <v>1239.750878820273</v>
       </c>
       <c r="D144" t="n">
-        <v>1232.56462441913</v>
+        <v>1232.524626953554</v>
       </c>
       <c r="E144" t="n">
-        <v>1247.018629509519</v>
+        <v>1246.977130686992</v>
       </c>
       <c r="F144" t="n">
         <v>8858</v>
@@ -18315,13 +18315,13 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1237.623139776393</v>
+        <v>1237.582301029211</v>
       </c>
       <c r="D145" t="n">
-        <v>1228.533252556789</v>
+        <v>1228.493514450835</v>
       </c>
       <c r="E145" t="n">
-        <v>1246.713026995996</v>
+        <v>1246.671087607587</v>
       </c>
       <c r="F145" t="n">
         <v>4781</v>
@@ -18466,13 +18466,13 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>1234.17057871337</v>
+        <v>1234.128338182251</v>
       </c>
       <c r="D146" t="n">
-        <v>1228.622985439499</v>
+        <v>1228.581819001509</v>
       </c>
       <c r="E146" t="n">
-        <v>1239.718171987241</v>
+        <v>1239.674857362992</v>
       </c>
       <c r="F146" t="n">
         <v>26195</v>
@@ -18617,13 +18617,13 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>1233.514017666563</v>
+        <v>1233.461069345032</v>
       </c>
       <c r="D147" t="n">
-        <v>1228.245700377881</v>
+        <v>1228.19397954118</v>
       </c>
       <c r="E147" t="n">
-        <v>1238.782334955245</v>
+        <v>1238.728159148884</v>
       </c>
       <c r="F147" t="n">
         <v>39302</v>
@@ -18768,13 +18768,13 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1229.571284318159</v>
+        <v>1229.517994684658</v>
       </c>
       <c r="D148" t="n">
-        <v>1225.015482286002</v>
+        <v>1224.96296587704</v>
       </c>
       <c r="E148" t="n">
-        <v>1234.127086350315</v>
+        <v>1234.073023492276</v>
       </c>
       <c r="F148" t="n">
         <v>51416</v>
@@ -18919,13 +18919,13 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1226.854964874567</v>
+        <v>1226.802948578299</v>
       </c>
       <c r="D149" t="n">
-        <v>1222.077019860073</v>
+        <v>1222.026040323814</v>
       </c>
       <c r="E149" t="n">
-        <v>1231.632909889062</v>
+        <v>1231.579856832783</v>
       </c>
       <c r="F149" t="n">
         <v>54036</v>
@@ -18990,13 +18990,13 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1223.613270689552</v>
+        <v>1223.564718458742</v>
       </c>
       <c r="D150" t="n">
-        <v>1219.875280697771</v>
+        <v>1219.827495339113</v>
       </c>
       <c r="E150" t="n">
-        <v>1227.351260681332</v>
+        <v>1227.301941578372</v>
       </c>
       <c r="F150" t="n">
         <v>104642</v>
@@ -19141,13 +19141,13 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1223.058179234768</v>
+        <v>1223.025510252321</v>
       </c>
       <c r="D151" t="n">
-        <v>1216.077310707715</v>
+        <v>1216.044746985433</v>
       </c>
       <c r="E151" t="n">
-        <v>1230.039047761821</v>
+        <v>1230.006273519208</v>
       </c>
       <c r="F151" t="n">
         <v>9818</v>
@@ -19292,13 +19292,13 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1220.489984508439</v>
+        <v>1220.464907149936</v>
       </c>
       <c r="D152" t="n">
-        <v>1209.816565277781</v>
+        <v>1209.792843206129</v>
       </c>
       <c r="E152" t="n">
-        <v>1231.163403739097</v>
+        <v>1231.136971093744</v>
       </c>
       <c r="F152" t="n">
         <v>2896</v>
@@ -19443,13 +19443,13 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>1212.999951928986</v>
+        <v>1212.941462953383</v>
       </c>
       <c r="D153" t="n">
-        <v>1202.223527030576</v>
+        <v>1202.166935704659</v>
       </c>
       <c r="E153" t="n">
-        <v>1223.776376827396</v>
+        <v>1223.715990202107</v>
       </c>
       <c r="F153" t="n">
         <v>4652</v>
@@ -19590,13 +19590,13 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1212.834677941751</v>
+        <v>1212.794617405299</v>
       </c>
       <c r="D154" t="n">
-        <v>1207.798821580765</v>
+        <v>1207.759691764107</v>
       </c>
       <c r="E154" t="n">
-        <v>1217.870534302736</v>
+        <v>1217.82954304649</v>
       </c>
       <c r="F154" t="n">
         <v>24146</v>
@@ -19737,13 +19737,13 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>1211.248999921621</v>
+        <v>1211.22625176179</v>
       </c>
       <c r="D155" t="n">
-        <v>1207.086662985704</v>
+        <v>1207.063811581746</v>
       </c>
       <c r="E155" t="n">
-        <v>1215.411336857538</v>
+        <v>1215.388691941834</v>
       </c>
       <c r="F155" t="n">
         <v>49605</v>
@@ -19888,13 +19888,13 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1208.487460761463</v>
+        <v>1208.436152876716</v>
       </c>
       <c r="D156" t="n">
-        <v>1197.392917968392</v>
+        <v>1197.343158490181</v>
       </c>
       <c r="E156" t="n">
-        <v>1219.582003554534</v>
+        <v>1219.529147263251</v>
       </c>
       <c r="F156" t="n">
         <v>3090</v>
@@ -20039,13 +20039,13 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1203.972996950748</v>
+        <v>1203.918817582605</v>
       </c>
       <c r="D157" t="n">
-        <v>1197.861547136516</v>
+        <v>1197.808545003663</v>
       </c>
       <c r="E157" t="n">
-        <v>1210.084446764979</v>
+        <v>1210.029090161547</v>
       </c>
       <c r="F157" t="n">
         <v>21741</v>
@@ -20190,13 +20190,13 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1200.096034946859</v>
+        <v>1200.065722025012</v>
       </c>
       <c r="D158" t="n">
-        <v>1195.990187915383</v>
+        <v>1195.959613882201</v>
       </c>
       <c r="E158" t="n">
-        <v>1204.201881978334</v>
+        <v>1204.171830167824</v>
       </c>
       <c r="F158" t="n">
         <v>46616</v>
@@ -20341,13 +20341,13 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>1197.887478180555</v>
+        <v>1197.834356247969</v>
       </c>
       <c r="D159" t="n">
-        <v>1192.727365984326</v>
+        <v>1192.674910214171</v>
       </c>
       <c r="E159" t="n">
-        <v>1203.047590376783</v>
+        <v>1202.993802281768</v>
       </c>
       <c r="F159" t="n">
         <v>25055</v>
@@ -20492,13 +20492,13 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1197.143802380179</v>
+        <v>1197.089928453988</v>
       </c>
       <c r="D160" t="n">
-        <v>1192.882077290403</v>
+        <v>1192.829432957213</v>
       </c>
       <c r="E160" t="n">
-        <v>1201.405527469954</v>
+        <v>1201.350423950764</v>
       </c>
       <c r="F160" t="n">
         <v>73503</v>
@@ -20643,13 +20643,13 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1195.504447792736</v>
+        <v>1195.44974080998</v>
       </c>
       <c r="D161" t="n">
-        <v>1189.397116367535</v>
+        <v>1189.34354503825</v>
       </c>
       <c r="E161" t="n">
-        <v>1201.611779217937</v>
+        <v>1201.555936581709</v>
       </c>
       <c r="F161" t="n">
         <v>32191</v>
@@ -20710,13 +20710,13 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1191.06088264836</v>
+        <v>1191.008284159787</v>
       </c>
       <c r="D162" t="n">
-        <v>1183.951963914791</v>
+        <v>1183.900731492628</v>
       </c>
       <c r="E162" t="n">
-        <v>1198.169801381929</v>
+        <v>1198.115836826946</v>
       </c>
       <c r="F162" t="n">
         <v>17839</v>
@@ -20861,13 +20861,13 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1190.739743717147</v>
+        <v>1190.706260891543</v>
       </c>
       <c r="D163" t="n">
-        <v>1183.554867170991</v>
+        <v>1183.522143371488</v>
       </c>
       <c r="E163" t="n">
-        <v>1197.924620263302</v>
+        <v>1197.890378411597</v>
       </c>
       <c r="F163" t="n">
         <v>9901</v>
@@ -21008,13 +21008,13 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>1184.921661559237</v>
+        <v>1184.864849036392</v>
       </c>
       <c r="D164" t="n">
-        <v>1173.456690156448</v>
+        <v>1173.402176695087</v>
       </c>
       <c r="E164" t="n">
-        <v>1196.386632962025</v>
+        <v>1196.327521377697</v>
       </c>
       <c r="F164" t="n">
         <v>4932</v>
@@ -21159,13 +21159,13 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>1184.720057821337</v>
+        <v>1184.662346344112</v>
       </c>
       <c r="D165" t="n">
-        <v>1175.298247187072</v>
+        <v>1175.242574862465</v>
       </c>
       <c r="E165" t="n">
-        <v>1194.141868455603</v>
+        <v>1194.082117825759</v>
       </c>
       <c r="F165" t="n">
         <v>8214</v>
@@ -21310,13 +21310,13 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1183.7200276912</v>
+        <v>1183.674983481226</v>
       </c>
       <c r="D166" t="n">
-        <v>1176.900461073091</v>
+        <v>1176.856685198581</v>
       </c>
       <c r="E166" t="n">
-        <v>1190.539594309309</v>
+        <v>1190.49328176387</v>
       </c>
       <c r="F166" t="n">
         <v>15483</v>
@@ -21457,13 +21457,13 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>1183.122615582182</v>
+        <v>1183.062099151682</v>
       </c>
       <c r="D167" t="n">
-        <v>1174.44793519468</v>
+        <v>1174.388763734478</v>
       </c>
       <c r="E167" t="n">
-        <v>1191.797295969683</v>
+        <v>1191.735434568885</v>
       </c>
       <c r="F167" t="n">
         <v>6638</v>
@@ -21608,13 +21608,13 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>1183.028585717027</v>
+        <v>1182.968104847911</v>
       </c>
       <c r="D168" t="n">
-        <v>1173.384854799664</v>
+        <v>1173.326470826978</v>
       </c>
       <c r="E168" t="n">
-        <v>1192.67231663439</v>
+        <v>1192.609738868845</v>
       </c>
       <c r="F168" t="n">
         <v>7968</v>
@@ -21675,13 +21675,13 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1182.722254265433</v>
+        <v>1182.662665851587</v>
       </c>
       <c r="D169" t="n">
-        <v>1174.739302408802</v>
+        <v>1174.681250621774</v>
       </c>
       <c r="E169" t="n">
-        <v>1190.705206122064</v>
+        <v>1190.644081081399</v>
       </c>
       <c r="F169" t="n">
         <v>12637</v>
@@ -21742,13 +21742,13 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>1182.580207425577</v>
+        <v>1182.531473340811</v>
       </c>
       <c r="D170" t="n">
-        <v>1176.514444240397</v>
+        <v>1176.466802355689</v>
       </c>
       <c r="E170" t="n">
-        <v>1188.645970610757</v>
+        <v>1188.596144325934</v>
       </c>
       <c r="F170" t="n">
         <v>23893</v>
@@ -21893,13 +21893,13 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1180.029088085646</v>
+        <v>1179.969810577241</v>
       </c>
       <c r="D171" t="n">
-        <v>1174.123946062562</v>
+        <v>1174.065831559653</v>
       </c>
       <c r="E171" t="n">
-        <v>1185.934230108729</v>
+        <v>1185.873789594829</v>
       </c>
       <c r="F171" t="n">
         <v>32832</v>
@@ -21960,13 +21960,13 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1178.841396979863</v>
+        <v>1178.792091409978</v>
       </c>
       <c r="D172" t="n">
-        <v>1167.659236400208</v>
+        <v>1167.611564467324</v>
       </c>
       <c r="E172" t="n">
-        <v>1190.023557559519</v>
+        <v>1189.972618352631</v>
       </c>
       <c r="F172" t="n">
         <v>3188</v>
@@ -22111,13 +22111,13 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>1177.640280985732</v>
+        <v>1177.587637589965</v>
       </c>
       <c r="D173" t="n">
-        <v>1167.848621671482</v>
+        <v>1167.797933627503</v>
       </c>
       <c r="E173" t="n">
-        <v>1187.431940299982</v>
+        <v>1187.377341552427</v>
       </c>
       <c r="F173" t="n">
         <v>6535</v>
@@ -22258,13 +22258,13 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>1175.936595143977</v>
+        <v>1175.87496596959</v>
       </c>
       <c r="D174" t="n">
-        <v>1165.547772530588</v>
+        <v>1165.48827601419</v>
       </c>
       <c r="E174" t="n">
-        <v>1186.325417757367</v>
+        <v>1186.261655924992</v>
       </c>
       <c r="F174" t="n">
         <v>5006</v>
@@ -22405,13 +22405,13 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>1172.903527564176</v>
+        <v>1172.844659584705</v>
       </c>
       <c r="D175" t="n">
-        <v>1166.715696576387</v>
+        <v>1166.658565087027</v>
       </c>
       <c r="E175" t="n">
-        <v>1179.091358551965</v>
+        <v>1179.030754082383</v>
       </c>
       <c r="F175" t="n">
         <v>22479</v>
@@ -22552,13 +22552,13 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>1171.058262099578</v>
+        <v>1171.007811226852</v>
       </c>
       <c r="D176" t="n">
-        <v>1165.146801590663</v>
+        <v>1165.097445181217</v>
       </c>
       <c r="E176" t="n">
-        <v>1176.969722608493</v>
+        <v>1176.918177272487</v>
       </c>
       <c r="F176" t="n">
         <v>17766</v>
@@ -22703,13 +22703,13 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>1170.923566263318</v>
+        <v>1170.860716945817</v>
       </c>
       <c r="D177" t="n">
-        <v>1163.528536132091</v>
+        <v>1163.467115001569</v>
       </c>
       <c r="E177" t="n">
-        <v>1178.318596394545</v>
+        <v>1178.254318890064</v>
       </c>
       <c r="F177" t="n">
         <v>16056</v>
@@ -22850,13 +22850,13 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>1170.605641643544</v>
+        <v>1170.546413377787</v>
       </c>
       <c r="D178" t="n">
-        <v>1165.119180489963</v>
+        <v>1165.061406344309</v>
       </c>
       <c r="E178" t="n">
-        <v>1176.092102797124</v>
+        <v>1176.031420411265</v>
       </c>
       <c r="F178" t="n">
         <v>38492</v>
@@ -23001,13 +23001,13 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>1167.382209935082</v>
+        <v>1167.324666474387</v>
       </c>
       <c r="D179" t="n">
-        <v>1159.32981571365</v>
+        <v>1159.273885590321</v>
       </c>
       <c r="E179" t="n">
-        <v>1175.434604156513</v>
+        <v>1175.375447358454</v>
       </c>
       <c r="F179" t="n">
         <v>10224</v>
@@ -23148,13 +23148,13 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>1166.771004165502</v>
+        <v>1166.729530784196</v>
       </c>
       <c r="D180" t="n">
-        <v>1159.066716199311</v>
+        <v>1159.026218385671</v>
       </c>
       <c r="E180" t="n">
-        <v>1174.475292131693</v>
+        <v>1174.43284318272</v>
       </c>
       <c r="F180" t="n">
         <v>7936</v>
@@ -23299,13 +23299,13 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>1164.369696797338</v>
+        <v>1164.315549620803</v>
       </c>
       <c r="D181" t="n">
-        <v>1152.47615782555</v>
+        <v>1152.424367152545</v>
       </c>
       <c r="E181" t="n">
-        <v>1176.263235769127</v>
+        <v>1176.206732089061</v>
       </c>
       <c r="F181" t="n">
         <v>3777</v>
@@ -23446,13 +23446,13 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>1156.635747572472</v>
+        <v>1156.577535814665</v>
       </c>
       <c r="D182" t="n">
-        <v>1148.253021049645</v>
+        <v>1148.196145746999</v>
       </c>
       <c r="E182" t="n">
-        <v>1165.018474095298</v>
+        <v>1164.958925882331</v>
       </c>
       <c r="F182" t="n">
         <v>6837</v>
@@ -23597,13 +23597,13 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>1154.686126005697</v>
+        <v>1154.6424766466</v>
       </c>
       <c r="D183" t="n">
-        <v>1142.110287600747</v>
+        <v>1142.069188459458</v>
       </c>
       <c r="E183" t="n">
-        <v>1167.261964410646</v>
+        <v>1167.215764833741</v>
       </c>
       <c r="F183" t="n">
         <v>3585</v>
@@ -23748,13 +23748,13 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>1154.203357169331</v>
+        <v>1154.184400362589</v>
       </c>
       <c r="D184" t="n">
-        <v>1142.723847243598</v>
+        <v>1142.706854093555</v>
       </c>
       <c r="E184" t="n">
-        <v>1165.682867095064</v>
+        <v>1165.661946631623</v>
       </c>
       <c r="F184" t="n">
         <v>3231</v>
@@ -23899,13 +23899,13 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>1152.406619733301</v>
+        <v>1152.352654720046</v>
       </c>
       <c r="D185" t="n">
-        <v>1139.266983914888</v>
+        <v>1139.216068681143</v>
       </c>
       <c r="E185" t="n">
-        <v>1165.546255551714</v>
+        <v>1165.489240758948</v>
       </c>
       <c r="F185" t="n">
         <v>4155</v>
@@ -24046,13 +24046,13 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>1152.252258745428</v>
+        <v>1152.194534223784</v>
       </c>
       <c r="D186" t="n">
-        <v>1136.965883231404</v>
+        <v>1136.912280528981</v>
       </c>
       <c r="E186" t="n">
-        <v>1167.538634259451</v>
+        <v>1167.476787918587</v>
       </c>
       <c r="F186" t="n">
         <v>1679</v>
@@ -24193,13 +24193,13 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>1150.735432900148</v>
+        <v>1150.675571858312</v>
       </c>
       <c r="D187" t="n">
-        <v>1138.522676838016</v>
+        <v>1138.466624156734</v>
       </c>
       <c r="E187" t="n">
-        <v>1162.94818896228</v>
+        <v>1162.884519559889</v>
       </c>
       <c r="F187" t="n">
         <v>2572</v>
@@ -24340,13 +24340,13 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>1149.501447940807</v>
+        <v>1149.442515749466</v>
       </c>
       <c r="D188" t="n">
-        <v>1140.301983346428</v>
+        <v>1140.245823359795</v>
       </c>
       <c r="E188" t="n">
-        <v>1158.700912535185</v>
+        <v>1158.639208139137</v>
       </c>
       <c r="F188" t="n">
         <v>7044</v>
@@ -24491,13 +24491,13 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>1149.365296906258</v>
+        <v>1149.311373265291</v>
       </c>
       <c r="D189" t="n">
-        <v>1142.723016719938</v>
+        <v>1142.670453943912</v>
       </c>
       <c r="E189" t="n">
-        <v>1156.007577092578</v>
+        <v>1155.952292586671</v>
       </c>
       <c r="F189" t="n">
         <v>19402</v>
@@ -24642,13 +24642,13 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>1148.109341746606</v>
+        <v>1148.04887111106</v>
       </c>
       <c r="D190" t="n">
-        <v>1131.09449794266</v>
+        <v>1131.038565206457</v>
       </c>
       <c r="E190" t="n">
-        <v>1165.124185550552</v>
+        <v>1165.059177015663</v>
       </c>
       <c r="F190" t="n">
         <v>1295</v>
@@ -24789,13 +24789,13 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>1143.821243336896</v>
+        <v>1143.766258408719</v>
       </c>
       <c r="D191" t="n">
-        <v>1133.94487696283</v>
+        <v>1133.891478578556</v>
       </c>
       <c r="E191" t="n">
-        <v>1153.697609710961</v>
+        <v>1153.641038238881</v>
       </c>
       <c r="F191" t="n">
         <v>4737</v>
@@ -24940,13 +24940,13 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>1143.103306870834</v>
+        <v>1143.052638541754</v>
       </c>
       <c r="D192" t="n">
-        <v>1136.665291919232</v>
+        <v>1136.615455246039</v>
       </c>
       <c r="E192" t="n">
-        <v>1149.541321822436</v>
+        <v>1149.489821837469</v>
       </c>
       <c r="F192" t="n">
         <v>12297</v>
@@ -25091,13 +25091,13 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>1141.549820615385</v>
+        <v>1141.491946414473</v>
       </c>
       <c r="D193" t="n">
-        <v>1134.866587556676</v>
+        <v>1134.810642372896</v>
       </c>
       <c r="E193" t="n">
-        <v>1148.233053674095</v>
+        <v>1148.173250456051</v>
       </c>
       <c r="F193" t="n">
         <v>19367</v>
@@ -25238,13 +25238,13 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>1141.386184583804</v>
+        <v>1141.326060298105</v>
       </c>
       <c r="D194" t="n">
-        <v>1134.67304810667</v>
+        <v>1134.614320625994</v>
       </c>
       <c r="E194" t="n">
-        <v>1148.099321060937</v>
+        <v>1148.037799970215</v>
       </c>
       <c r="F194" t="n">
         <v>19174</v>
@@ -25389,13 +25389,13 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>1139.343274033538</v>
+        <v>1139.286841383948</v>
       </c>
       <c r="D195" t="n">
-        <v>1128.42041399417</v>
+        <v>1128.366302421678</v>
       </c>
       <c r="E195" t="n">
-        <v>1150.266134072907</v>
+        <v>1150.207380346217</v>
       </c>
       <c r="F195" t="n">
         <v>4964</v>
@@ -25540,13 +25540,13 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>1137.729281343497</v>
+        <v>1137.685762950222</v>
       </c>
       <c r="D196" t="n">
-        <v>1128.257807354003</v>
+        <v>1128.216257664946</v>
       </c>
       <c r="E196" t="n">
-        <v>1147.20075533299</v>
+        <v>1147.155268235498</v>
       </c>
       <c r="F196" t="n">
         <v>8925</v>
@@ -25691,13 +25691,13 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>1136.835887671599</v>
+        <v>1136.775357677685</v>
       </c>
       <c r="D197" t="n">
-        <v>1127.961644824905</v>
+        <v>1127.903066255798</v>
       </c>
       <c r="E197" t="n">
-        <v>1145.710130518293</v>
+        <v>1145.647649099572</v>
       </c>
       <c r="F197" t="n">
         <v>7366</v>
@@ -25842,13 +25842,13 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>1130.782669430284</v>
+        <v>1130.728898204252</v>
       </c>
       <c r="D198" t="n">
-        <v>1121.969881109721</v>
+        <v>1121.918221258459</v>
       </c>
       <c r="E198" t="n">
-        <v>1139.595457750846</v>
+        <v>1139.539575150045</v>
       </c>
       <c r="F198" t="n">
         <v>11118</v>
@@ -25989,13 +25989,13 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>1129.814613767177</v>
+        <v>1129.755777217232</v>
       </c>
       <c r="D199" t="n">
-        <v>1122.398633674938</v>
+        <v>1122.341286039562</v>
       </c>
       <c r="E199" t="n">
-        <v>1137.230593859417</v>
+        <v>1137.170268394901</v>
       </c>
       <c r="F199" t="n">
         <v>20685</v>
@@ -26140,13 +26140,13 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>1128.078214996834</v>
+        <v>1128.025077648558</v>
       </c>
       <c r="D200" t="n">
-        <v>1121.685988531752</v>
+        <v>1121.633996814569</v>
       </c>
       <c r="E200" t="n">
-        <v>1134.470441461916</v>
+        <v>1134.416158482547</v>
       </c>
       <c r="F200" t="n">
         <v>20118</v>
@@ -26291,13 +26291,13 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>1127.477895718214</v>
+        <v>1127.425545361239</v>
       </c>
       <c r="D201" t="n">
-        <v>1115.418749040319</v>
+        <v>1115.370425891694</v>
       </c>
       <c r="E201" t="n">
-        <v>1139.537042396109</v>
+        <v>1139.480664830784</v>
       </c>
       <c r="F201" t="n">
         <v>2921</v>
@@ -26438,13 +26438,13 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>1126.915039551167</v>
+        <v>1126.860182148613</v>
       </c>
       <c r="D202" t="n">
-        <v>1111.358369705838</v>
+        <v>1111.307912970874</v>
       </c>
       <c r="E202" t="n">
-        <v>1142.471709396497</v>
+        <v>1142.412451326351</v>
       </c>
       <c r="F202" t="n">
         <v>1785</v>
@@ -26585,13 +26585,13 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>1121.593799828769</v>
+        <v>1121.535780602153</v>
       </c>
       <c r="D203" t="n">
-        <v>1110.635539874031</v>
+        <v>1110.5797475164</v>
       </c>
       <c r="E203" t="n">
-        <v>1132.552059783507</v>
+        <v>1132.491813687906</v>
       </c>
       <c r="F203" t="n">
         <v>5182</v>
@@ -26732,13 +26732,13 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>1119.151680249208</v>
+        <v>1119.10356035111</v>
       </c>
       <c r="D204" t="n">
-        <v>1101.058503034318</v>
+        <v>1101.01525599601</v>
       </c>
       <c r="E204" t="n">
-        <v>1137.244857464098</v>
+        <v>1137.191864706212</v>
       </c>
       <c r="F204" t="n">
         <v>1143</v>
@@ -26883,13 +26883,13 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>1116.664107816309</v>
+        <v>1116.610000983294</v>
       </c>
       <c r="D205" t="n">
-        <v>1108.943984143436</v>
+        <v>1108.891206176441</v>
       </c>
       <c r="E205" t="n">
-        <v>1124.384231489182</v>
+        <v>1124.328795790148</v>
       </c>
       <c r="F205" t="n">
         <v>10854</v>
@@ -27034,13 +27034,13 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>1115.291708087597</v>
+        <v>1115.232690681141</v>
       </c>
       <c r="D206" t="n">
-        <v>1106.182896244702</v>
+        <v>1106.126949981866</v>
       </c>
       <c r="E206" t="n">
-        <v>1124.400519930494</v>
+        <v>1124.338431380416</v>
       </c>
       <c r="F206" t="n">
         <v>6923</v>
@@ -27181,13 +27181,13 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>1114.678356400187</v>
+        <v>1114.625465481543</v>
       </c>
       <c r="D207" t="n">
-        <v>1100.33240136893</v>
+        <v>1100.283054245387</v>
       </c>
       <c r="E207" t="n">
-        <v>1129.024311431443</v>
+        <v>1128.967876717697</v>
       </c>
       <c r="F207" t="n">
         <v>2199</v>
@@ -27328,13 +27328,13 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>1111.099515747623</v>
+        <v>1111.060148797839</v>
       </c>
       <c r="D208" t="n">
-        <v>1103.217879016683</v>
+        <v>1103.179691053792</v>
       </c>
       <c r="E208" t="n">
-        <v>1118.981152478563</v>
+        <v>1118.940606541886</v>
       </c>
       <c r="F208" t="n">
         <v>8045</v>
@@ -27479,13 +27479,13 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>1110.344376872507</v>
+        <v>1110.286383880642</v>
       </c>
       <c r="D209" t="n">
-        <v>1101.078942808533</v>
+        <v>1101.023015851098</v>
       </c>
       <c r="E209" t="n">
-        <v>1119.609810936482</v>
+        <v>1119.549751910186</v>
       </c>
       <c r="F209" t="n">
         <v>8977</v>
@@ -27630,13 +27630,13 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>1107.883809293634</v>
+        <v>1107.820685873594</v>
       </c>
       <c r="D210" t="n">
-        <v>1100.843103895604</v>
+        <v>1100.781488140327</v>
       </c>
       <c r="E210" t="n">
-        <v>1114.924514691663</v>
+        <v>1114.85988360686</v>
       </c>
       <c r="F210" t="n">
         <v>14148</v>
@@ -27781,13 +27781,13 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>1093.650771263668</v>
+        <v>1093.602000063279</v>
       </c>
       <c r="D211" t="n">
-        <v>1082.189583716249</v>
+        <v>1082.143535487479</v>
       </c>
       <c r="E211" t="n">
-        <v>1105.111958811087</v>
+        <v>1105.060464639079</v>
       </c>
       <c r="F211" t="n">
         <v>4780</v>
@@ -27932,13 +27932,13 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>1091.120671402036</v>
+        <v>1091.062874621235</v>
       </c>
       <c r="D212" t="n">
-        <v>1081.801071625925</v>
+        <v>1081.745171111184</v>
       </c>
       <c r="E212" t="n">
-        <v>1100.440271178146</v>
+        <v>1100.380578131286</v>
       </c>
       <c r="F212" t="n">
         <v>7597</v>
@@ -28083,13 +28083,13 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>1073.582687947118</v>
+        <v>1073.531669739624</v>
       </c>
       <c r="D213" t="n">
-        <v>1062.446215498886</v>
+        <v>1062.397697904385</v>
       </c>
       <c r="E213" t="n">
-        <v>1084.719160395351</v>
+        <v>1084.665641574863</v>
       </c>
       <c r="F213" t="n">
         <v>6328</v>
@@ -28234,13 +28234,13 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>1070.90569926612</v>
+        <v>1070.846014158475</v>
       </c>
       <c r="D214" t="n">
-        <v>1061.077482515277</v>
+        <v>1061.022724284413</v>
       </c>
       <c r="E214" t="n">
-        <v>1080.733916016963</v>
+        <v>1080.669304032536</v>
       </c>
       <c r="F214" t="n">
         <v>6965</v>
@@ -28381,13 +28381,13 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>1070.218718202035</v>
+        <v>1070.14877529671</v>
       </c>
       <c r="D215" t="n">
-        <v>1058.819080041133</v>
+        <v>1058.754135565208</v>
       </c>
       <c r="E215" t="n">
-        <v>1081.618356362936</v>
+        <v>1081.543415028212</v>
       </c>
       <c r="F215" t="n">
         <v>5745</v>
@@ -28528,13 +28528,13 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>1067.689501749973</v>
+        <v>1067.624204258822</v>
       </c>
       <c r="D216" t="n">
-        <v>1052.539279378577</v>
+        <v>1052.479513644123</v>
       </c>
       <c r="E216" t="n">
-        <v>1082.839724121369</v>
+        <v>1082.768894873521</v>
       </c>
       <c r="F216" t="n">
         <v>1743</v>
@@ -28675,13 +28675,13 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>1063.427626183649</v>
+        <v>1063.362204026688</v>
       </c>
       <c r="D217" t="n">
-        <v>1051.509118096184</v>
+        <v>1051.448498347585</v>
       </c>
       <c r="E217" t="n">
-        <v>1075.346134271114</v>
+        <v>1075.275909705792</v>
       </c>
       <c r="F217" t="n">
         <v>3924</v>
@@ -28822,13 +28822,13 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>1056.552374497664</v>
+        <v>1056.49762436076</v>
       </c>
       <c r="D218" t="n">
-        <v>1044.916266792639</v>
+        <v>1044.864108157092</v>
       </c>
       <c r="E218" t="n">
-        <v>1068.18848220269</v>
+        <v>1068.131140564428</v>
       </c>
       <c r="F218" t="n">
         <v>4658</v>
@@ -28969,13 +28969,13 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>1042.314446311175</v>
+        <v>1042.25138564033</v>
       </c>
       <c r="D219" t="n">
-        <v>1030.983163529046</v>
+        <v>1030.924891505641</v>
       </c>
       <c r="E219" t="n">
-        <v>1053.645729093304</v>
+        <v>1053.57787977502</v>
       </c>
       <c r="F219" t="n">
         <v>4845</v>
@@ -29116,13 +29116,13 @@
         </is>
       </c>
       <c r="C220" t="n">
-        <v>1024.751167518571</v>
+        <v>1024.69443832352</v>
       </c>
       <c r="D220" t="n">
-        <v>1011.206168989518</v>
+        <v>1011.153272410936</v>
       </c>
       <c r="E220" t="n">
-        <v>1038.296166047624</v>
+        <v>1038.235604236104</v>
       </c>
       <c r="F220" t="n">
         <v>2658</v>
@@ -29263,13 +29263,13 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>1023.509523221827</v>
+        <v>1023.446857036427</v>
       </c>
       <c r="D221" t="n">
-        <v>1012.700122651181</v>
+        <v>1012.642381582216</v>
       </c>
       <c r="E221" t="n">
-        <v>1034.318923792472</v>
+        <v>1034.251332490637</v>
       </c>
       <c r="F221" t="n">
         <v>6310</v>
@@ -29410,13 +29410,13 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>995.7983320291153</v>
+        <v>995.741030667294</v>
       </c>
       <c r="D222" t="n">
-        <v>983.2931046772851</v>
+        <v>983.2408536434494</v>
       </c>
       <c r="E222" t="n">
-        <v>1008.303559380945</v>
+        <v>1008.241207691139</v>
       </c>
       <c r="F222" t="n">
         <v>4914</v>
@@ -29557,13 +29557,13 @@
         </is>
       </c>
       <c r="C223" t="n">
-        <v>992.5359068718092</v>
+        <v>992.4680063598643</v>
       </c>
       <c r="D223" t="n">
-        <v>980.2283433109164</v>
+        <v>980.1655265581131</v>
       </c>
       <c r="E223" t="n">
-        <v>1004.843470432702</v>
+        <v>1004.770486161615</v>
       </c>
       <c r="F223" t="n">
         <v>4203</v>
@@ -29704,13 +29704,13 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>982.4744390023714</v>
+        <v>982.4067084039048</v>
       </c>
       <c r="D224" t="n">
-        <v>969.0269050380466</v>
+        <v>968.9657025469702</v>
       </c>
       <c r="E224" t="n">
-        <v>995.9219729666961</v>
+        <v>995.8477142608393</v>
       </c>
       <c r="F224" t="n">
         <v>3412</v>
@@ -29851,13 +29851,13 @@
         </is>
       </c>
       <c r="C225" t="n">
-        <v>975.1522066374537</v>
+        <v>975.0758191760643</v>
       </c>
       <c r="D225" t="n">
-        <v>959.4629551984033</v>
+        <v>959.3949693844793</v>
       </c>
       <c r="E225" t="n">
-        <v>990.8414580765041</v>
+        <v>990.7566689676493</v>
       </c>
       <c r="F225" t="n">
         <v>2391</v>
@@ -30002,13 +30002,13 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>953.179645425136</v>
+        <v>953.1188426237578</v>
       </c>
       <c r="D226" t="n">
-        <v>940.5375208579976</v>
+        <v>940.4833004033477</v>
       </c>
       <c r="E226" t="n">
-        <v>965.8217699922743</v>
+        <v>965.754384844168</v>
       </c>
       <c r="F226" t="n">
         <v>3287</v>
@@ -30836,7 +30836,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>deepseek-v4.1-flash-max</t>
+          <t>glm-5.2-max</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -30851,7 +30851,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>glm-5.2-max</t>
+          <t>glm-5.3-flash</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -30866,7 +30866,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>glm-5.3-flash</t>
+          <t>deepseek-v4.1-flash-max</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -31178,38 +31178,38 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>deepseek-v4-flash-high-preview</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
+          <t>qwen3.8-27b</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>27</v>
+      </c>
+      <c r="C23" t="n">
+        <v>27</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>dense</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>qwen3.8-27b</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>27</v>
-      </c>
-      <c r="C24" t="n">
-        <v>27</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>dense</t>
-        </is>
-      </c>
+          <t>deepseek-v4-flash-high-preview</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -31361,22 +31361,30 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>deepseek-v3.2-exp-thinking</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
+          <t>muse-glimmer</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>30</v>
+      </c>
+      <c r="C32" t="n">
+        <v>30</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>dense</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>aa_single_scrape</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>deepseek-v3.2</t>
+          <t>deepseek-v3.2-exp-thinking</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -31391,23 +31399,15 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>muse-glimmer</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>30</v>
-      </c>
-      <c r="C34" t="n">
-        <v>30</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>dense</t>
-        </is>
-      </c>
+          <t>deepseek-v3.2</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>aa_single_scrape</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -31543,7 +31543,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-terminus-thinking</t>
+          <t>deepseek-v3.1</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -31558,7 +31558,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>deepseek-v3.1</t>
+          <t>deepseek-v3.1-terminus-thinking</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -31641,14 +31641,14 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>qwen3-vl-235b-a22b-instruct</t>
+          <t>mistral-large-3</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>235</v>
+        <v>675</v>
       </c>
       <c r="C48" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -31657,21 +31657,21 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>aa_single_scrape</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>mistral-large-3</t>
+          <t>qwen3-vl-235b-a22b-instruct</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>675</v>
+        <v>235</v>
       </c>
       <c r="C49" t="n">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -31680,7 +31680,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>aa_single_scrape</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
@@ -32076,38 +32076,38 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>trinity-large-preview</t>
-        </is>
-      </c>
-      <c r="B69" t="n">
-        <v>70</v>
-      </c>
-      <c r="C69" t="n">
-        <v>70</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>dense</t>
-        </is>
-      </c>
+          <t>glm-4.6v</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>glm-4.6v</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr"/>
-      <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr"/>
+          <t>trinity-large-preview</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>70</v>
+      </c>
+      <c r="C70" t="n">
+        <v>70</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>dense</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>override</t>
         </is>
       </c>
     </row>
@@ -32403,18 +32403,18 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>llama-3.1-nemotron-ultra-253b-v1</t>
+          <t>nvidia-nemotron-3.5-lightning-30b-a3b-nvfp4</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>253</v>
+        <v>30</v>
       </c>
       <c r="C86" t="n">
-        <v>253</v>
+        <v>3</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -32426,14 +32426,14 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>qwen3-32b</t>
+          <t>llama-3.1-nemotron-ultra-253b-v1</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>32</v>
+        <v>253</v>
       </c>
       <c r="C87" t="n">
-        <v>32</v>
+        <v>253</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -32449,18 +32449,18 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>nvidia-nemotron-3.5-lightning-30b-a3b-nvfp4</t>
+          <t>qwen3-32b</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C88" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -33183,14 +33183,14 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>granite-4.2-3b</t>
+          <t>gemma-2-27b-it</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="C122" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -33206,38 +33206,38 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>gemma-2-27b-it</t>
-        </is>
-      </c>
-      <c r="B123" t="n">
-        <v>27</v>
-      </c>
-      <c r="C123" t="n">
-        <v>27</v>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>dense</t>
-        </is>
-      </c>
+          <t>jamba-1.5-large</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr"/>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>jamba-1.5-large</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr"/>
-      <c r="C124" t="inlineStr"/>
-      <c r="D124" t="inlineStr"/>
+          <t>granite-4.2-3b</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>3</v>
+      </c>
+      <c r="C124" t="n">
+        <v>3</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>dense</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>

--- a/arena_enrichment/output/arena_leaderboard_enriched.xlsx
+++ b/arena_enrichment/output/arena_leaderboard_enriched.xlsx
@@ -674,16 +674,16 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1488.027768355495</v>
+        <v>1488.357698689695</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1483.235761343442</v>
+        <v>1483.586114955416</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1492.819775367549</v>
+        <v>1493.129282423974</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>27719</v>
+        <v>28280</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -745,16 +745,16 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1479.615142075082</v>
+        <v>1480.075697959219</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1470.221599952889</v>
+        <v>1470.671204204633</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1489.008684197275</v>
+        <v>1489.480191713805</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>4074</v>
+        <v>4056</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -816,16 +816,16 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1479.393894575315</v>
+        <v>1478.49856297707</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1473.786641884639</v>
+        <v>1472.940423691248</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1485.001147265991</v>
+        <v>1484.056702262892</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>17268</v>
+        <v>17857</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -887,16 +887,16 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1475.426372376843</v>
+        <v>1475.769482146397</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1471.117362949654</v>
+        <v>1471.469242460478</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1479.735381804031</v>
+        <v>1480.069721832316</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>44949</v>
+        <v>45399</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -954,24 +954,24 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>glm-5.3-flash</t>
+          <t>deepseek-v4.1-flash-max</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1473.671056356273</v>
+        <v>1474.440278165399</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1468.245369498502</v>
+        <v>1467.511746655351</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1479.096743214043</v>
+        <v>1481.368809675447</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>21644</v>
+        <v>8728</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Z.ai</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1025,24 +1025,24 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>deepseek-v4.1-flash-max</t>
+          <t>glm-5.3-flash</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1472.76550807406</v>
+        <v>1473.000490016389</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1465.690201492429</v>
+        <v>1467.657830534031</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1479.840814655691</v>
+        <v>1478.343149498747</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>8125</v>
+        <v>22971</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Z.ai</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1100,16 +1100,16 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1467.37081204811</v>
+        <v>1467.514738875952</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1463.741218959708</v>
+        <v>1463.894610214051</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1471.000405136512</v>
+        <v>1471.134867537853</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>70317</v>
+        <v>70871</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -1171,16 +1171,16 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1464.518979823142</v>
+        <v>1464.565468868514</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1460.829553170478</v>
+        <v>1460.882819739498</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1468.208406475807</v>
+        <v>1468.24811799753</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>57877</v>
+        <v>58358</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -1242,16 +1242,16 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1464.15093544915</v>
+        <v>1464.278528826575</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1457.532860157122</v>
+        <v>1457.651781275999</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1470.769010741177</v>
+        <v>1470.905276377151</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>9825</v>
+        <v>9780</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
@@ -1313,16 +1313,16 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1461.011639646345</v>
+        <v>1460.959439730511</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1456.579460797846</v>
+        <v>1456.528424830495</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1465.443818494846</v>
+        <v>1465.390454630528</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>39950</v>
+        <v>39936</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
@@ -1464,16 +1464,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1457.720783320416</v>
+        <v>1457.760968878053</v>
       </c>
       <c r="D12" t="n">
-        <v>1453.819210794446</v>
+        <v>1453.856104015234</v>
       </c>
       <c r="E12" t="n">
-        <v>1461.622355846386</v>
+        <v>1461.665833740871</v>
       </c>
       <c r="F12" t="n">
-        <v>57549</v>
+        <v>57478</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1615,16 +1615,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1457.653649118527</v>
+        <v>1457.611917586408</v>
       </c>
       <c r="D13" t="n">
-        <v>1453.401589600839</v>
+        <v>1453.359457622837</v>
       </c>
       <c r="E13" t="n">
-        <v>1461.905708636216</v>
+        <v>1461.864377549981</v>
       </c>
       <c r="F13" t="n">
-        <v>29203</v>
+        <v>29174</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1766,16 +1766,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1457.440394984297</v>
+        <v>1455.983448832156</v>
       </c>
       <c r="D14" t="n">
-        <v>1450.858745882494</v>
+        <v>1449.463590089154</v>
       </c>
       <c r="E14" t="n">
-        <v>1464.0220440861</v>
+        <v>1462.503307575158</v>
       </c>
       <c r="F14" t="n">
-        <v>10239</v>
+        <v>10476</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1917,16 +1917,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1454.997373386936</v>
+        <v>1454.951683804795</v>
       </c>
       <c r="D15" t="n">
-        <v>1451.02490955859</v>
+        <v>1450.976425151739</v>
       </c>
       <c r="E15" t="n">
-        <v>1458.96983721528</v>
+        <v>1458.926942457851</v>
       </c>
       <c r="F15" t="n">
-        <v>54823</v>
+        <v>54767</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1984,68 +1984,148 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>mimo-v2.6-flash</t>
+          <t>gemma-4-31b</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1453.727153840523</v>
+        <v>1452.835259622734</v>
       </c>
       <c r="D16" t="n">
-        <v>1445.543146608404</v>
+        <v>1445.391511362457</v>
       </c>
       <c r="E16" t="n">
-        <v>1461.91116107264</v>
+        <v>1460.279007883011</v>
       </c>
       <c r="F16" t="n">
-        <v>5465</v>
+        <v>6133</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Xiaomi</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>31</v>
+      </c>
+      <c r="J16" t="n">
+        <v>31</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>dense</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr"/>
-      <c r="AB16" t="inlineStr"/>
-      <c r="AC16" t="inlineStr"/>
-      <c r="AD16" t="inlineStr"/>
-      <c r="AE16" t="inlineStr"/>
-      <c r="AF16" t="inlineStr"/>
-      <c r="AG16" t="inlineStr"/>
+          <t>name_parsing</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>62</v>
+      </c>
+      <c r="N16" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="O16" t="n">
+        <v>31</v>
+      </c>
+      <c r="P16" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="S16" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T16" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U16" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V16" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y16" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA16" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB16" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC16" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD16" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE16" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF16" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG16" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -2055,148 +2135,68 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>gemma-4-31b</t>
+          <t>mimo-v2.6-flash</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1452.725186989559</v>
+        <v>1451.782861723269</v>
       </c>
       <c r="D17" t="n">
-        <v>1445.280785843011</v>
+        <v>1443.941189608791</v>
       </c>
       <c r="E17" t="n">
-        <v>1460.169588136107</v>
+        <v>1459.624533837748</v>
       </c>
       <c r="F17" t="n">
-        <v>6137</v>
+        <v>6053</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Xiaomi</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>31</v>
-      </c>
-      <c r="J17" t="n">
-        <v>31</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>dense</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>name_parsing</t>
-        </is>
-      </c>
-      <c r="M17" t="n">
-        <v>62</v>
-      </c>
-      <c r="N17" t="n">
-        <v>77.5</v>
-      </c>
-      <c r="O17" t="n">
-        <v>31</v>
-      </c>
-      <c r="P17" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="R17" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="S17" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T17" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U17" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V17" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W17" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X17" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y17" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA17" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB17" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC17" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD17" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE17" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF17" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG17" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -2210,16 +2210,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1450.216689507568</v>
+        <v>1450.121849787226</v>
       </c>
       <c r="D18" t="n">
-        <v>1446.929149916141</v>
+        <v>1446.834361274673</v>
       </c>
       <c r="E18" t="n">
-        <v>1453.504229098995</v>
+        <v>1453.409338299778</v>
       </c>
       <c r="F18" t="n">
-        <v>74623</v>
+        <v>74565</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -2357,24 +2357,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>inkling</t>
+          <t>qwen3.5-397b-a17b</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1441.748598192381</v>
+        <v>1441.812667919804</v>
       </c>
       <c r="D19" t="n">
-        <v>1437.225364948475</v>
+        <v>1438.665343661678</v>
       </c>
       <c r="E19" t="n">
-        <v>1446.271831436289</v>
+        <v>1444.95999217793</v>
       </c>
       <c r="F19" t="n">
-        <v>34594</v>
+        <v>88660</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Thinky</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2383,10 +2383,10 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>975</v>
+        <v>397</v>
       </c>
       <c r="J19" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2395,26 +2395,26 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>aa_single_scrape</t>
+          <t>name_parsing</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>1950</v>
+        <v>794</v>
       </c>
       <c r="N19" t="n">
-        <v>2437.5</v>
+        <v>992.5</v>
       </c>
       <c r="O19" t="n">
-        <v>975</v>
+        <v>397</v>
       </c>
       <c r="P19" t="n">
-        <v>1218.8</v>
+        <v>496.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>487.5</v>
+        <v>198.5</v>
       </c>
       <c r="R19" t="n">
-        <v>609.4</v>
+        <v>248.1</v>
       </c>
       <c r="S19" s="5" t="inlineStr">
         <is>
@@ -2486,9 +2486,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AG19" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AG19" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
@@ -2508,148 +2508,68 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>qwen3.5-397b-a17b</t>
+          <t>glm-4.7</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1441.569858163239</v>
+        <v>1441.49975007789</v>
       </c>
       <c r="D20" t="n">
-        <v>1438.415460334742</v>
+        <v>1435.43833243339</v>
       </c>
       <c r="E20" t="n">
-        <v>1444.724255991736</v>
+        <v>1447.561167722389</v>
       </c>
       <c r="F20" t="n">
-        <v>88092</v>
+        <v>12228</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Z.ai</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>397</v>
-      </c>
-      <c r="J20" t="n">
-        <v>17</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>name_parsing</t>
-        </is>
-      </c>
-      <c r="M20" t="n">
-        <v>794</v>
-      </c>
-      <c r="N20" t="n">
-        <v>992.5</v>
-      </c>
-      <c r="O20" t="n">
-        <v>397</v>
-      </c>
-      <c r="P20" t="n">
-        <v>496.2</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>198.5</v>
-      </c>
-      <c r="R20" t="n">
-        <v>248.1</v>
-      </c>
-      <c r="S20" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T20" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U20" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V20" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W20" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X20" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y20" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z20" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA20" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB20" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC20" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD20" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AE20" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF20" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG20" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -2659,68 +2579,148 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>glm-4.7</t>
+          <t>inkling</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1441.527333291579</v>
+        <v>1441.375480290693</v>
       </c>
       <c r="D21" t="n">
-        <v>1435.463199494398</v>
+        <v>1436.872462583635</v>
       </c>
       <c r="E21" t="n">
-        <v>1447.591467088759</v>
+        <v>1445.87849799775</v>
       </c>
       <c r="F21" t="n">
-        <v>12219</v>
+        <v>35204</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Z.ai</t>
+          <t>Thinky</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>975</v>
+      </c>
+      <c r="J21" t="n">
+        <v>41</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
-      <c r="AA21" t="inlineStr"/>
-      <c r="AB21" t="inlineStr"/>
-      <c r="AC21" t="inlineStr"/>
-      <c r="AD21" t="inlineStr"/>
-      <c r="AE21" t="inlineStr"/>
-      <c r="AF21" t="inlineStr"/>
-      <c r="AG21" t="inlineStr"/>
+          <t>aa_single_scrape</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>1950</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2437.5</v>
+      </c>
+      <c r="O21" t="n">
+        <v>975</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1218.8</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>487.5</v>
+      </c>
+      <c r="R21" t="n">
+        <v>609.4</v>
+      </c>
+      <c r="S21" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T21" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U21" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V21" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W21" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X21" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y21" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z21" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA21" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB21" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC21" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD21" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE21" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF21" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG21" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -2734,16 +2734,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1439.738386572274</v>
+        <v>1440.055424093557</v>
       </c>
       <c r="D22" t="n">
-        <v>1435.784625596188</v>
+        <v>1436.111142899113</v>
       </c>
       <c r="E22" t="n">
-        <v>1443.69214754836</v>
+        <v>1443.999705288001</v>
       </c>
       <c r="F22" t="n">
-        <v>58171</v>
+        <v>58757</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2881,148 +2881,68 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>qwen3.8-27b</t>
+          <t>deepseek-v4-flash-high-preview</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1438.527970325345</v>
+        <v>1438.423647802235</v>
       </c>
       <c r="D23" t="n">
-        <v>1433.077908944736</v>
+        <v>1434.309732503248</v>
       </c>
       <c r="E23" t="n">
-        <v>1443.978031705955</v>
+        <v>1442.537563101221</v>
       </c>
       <c r="F23" t="n">
-        <v>17777</v>
+        <v>51648</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>27</v>
-      </c>
-      <c r="J23" t="n">
-        <v>27</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>dense</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>name_parsing</t>
-        </is>
-      </c>
-      <c r="M23" t="n">
-        <v>54</v>
-      </c>
-      <c r="N23" t="n">
-        <v>67.5</v>
-      </c>
-      <c r="O23" t="n">
-        <v>27</v>
-      </c>
-      <c r="P23" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="R23" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="S23" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T23" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U23" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V23" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W23" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X23" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y23" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z23" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA23" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB23" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC23" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD23" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE23" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF23" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG23" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -3032,68 +2952,148 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>deepseek-v4-flash-high-preview</t>
+          <t>qwen3.8-27b</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1438.477331717716</v>
+        <v>1437.699726423117</v>
       </c>
       <c r="D24" t="n">
-        <v>1434.364175827434</v>
+        <v>1432.284426086605</v>
       </c>
       <c r="E24" t="n">
-        <v>1442.590487607998</v>
+        <v>1443.115026759629</v>
       </c>
       <c r="F24" t="n">
-        <v>51691</v>
+        <v>18462</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>27</v>
+      </c>
+      <c r="J24" t="n">
+        <v>27</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>dense</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="inlineStr"/>
-      <c r="AB24" t="inlineStr"/>
-      <c r="AC24" t="inlineStr"/>
-      <c r="AD24" t="inlineStr"/>
-      <c r="AE24" t="inlineStr"/>
-      <c r="AF24" t="inlineStr"/>
-      <c r="AG24" t="inlineStr"/>
+          <t>name_parsing</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>54</v>
+      </c>
+      <c r="N24" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="O24" t="n">
+        <v>27</v>
+      </c>
+      <c r="P24" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="R24" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="S24" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T24" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U24" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V24" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W24" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X24" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y24" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z24" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA24" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB24" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC24" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD24" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE24" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF24" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG24" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -3107,16 +3107,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1437.492243548209</v>
+        <v>1437.453901668969</v>
       </c>
       <c r="D25" t="n">
-        <v>1430.050380624826</v>
+        <v>1430.00951430035</v>
       </c>
       <c r="E25" t="n">
-        <v>1444.934106471592</v>
+        <v>1444.898289037587</v>
       </c>
       <c r="F25" t="n">
-        <v>6083</v>
+        <v>6081</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -3258,16 +3258,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1435.884601459908</v>
+        <v>1436.019558281073</v>
       </c>
       <c r="D26" t="n">
-        <v>1431.839115630689</v>
+        <v>1431.973899917187</v>
       </c>
       <c r="E26" t="n">
-        <v>1439.930087289127</v>
+        <v>1440.065216644959</v>
       </c>
       <c r="F26" t="n">
-        <v>51869</v>
+        <v>51850</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -3409,16 +3409,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1433.739132510029</v>
+        <v>1433.605812533576</v>
       </c>
       <c r="D27" t="n">
-        <v>1429.507860766121</v>
+        <v>1429.373519290959</v>
       </c>
       <c r="E27" t="n">
-        <v>1437.970404253938</v>
+        <v>1437.838105776193</v>
       </c>
       <c r="F27" t="n">
-        <v>47292</v>
+        <v>47266</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -3480,16 +3480,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1430.504886477788</v>
+        <v>1430.558102339856</v>
       </c>
       <c r="D28" t="n">
-        <v>1423.992345581362</v>
+        <v>1424.046164052485</v>
       </c>
       <c r="E28" t="n">
-        <v>1437.017427374215</v>
+        <v>1437.070040627227</v>
       </c>
       <c r="F28" t="n">
-        <v>8355</v>
+        <v>8356</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -3631,16 +3631,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1430.043446718033</v>
+        <v>1430.076684063201</v>
       </c>
       <c r="D29" t="n">
-        <v>1426.948812484133</v>
+        <v>1426.982680329273</v>
       </c>
       <c r="E29" t="n">
-        <v>1433.138080951932</v>
+        <v>1433.17068779713</v>
       </c>
       <c r="F29" t="n">
-        <v>63225</v>
+        <v>63210</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -3782,13 +3782,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1426.93139319545</v>
+        <v>1426.927617154943</v>
       </c>
       <c r="D30" t="n">
-        <v>1420.518446848027</v>
+        <v>1420.516208704082</v>
       </c>
       <c r="E30" t="n">
-        <v>1433.344339542874</v>
+        <v>1433.339025605804</v>
       </c>
       <c r="F30" t="n">
         <v>11757</v>
@@ -3853,16 +3853,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1426.424051750329</v>
+        <v>1426.217526026591</v>
       </c>
       <c r="D31" t="n">
-        <v>1419.535993546036</v>
+        <v>1419.326064619545</v>
       </c>
       <c r="E31" t="n">
-        <v>1433.31210995462</v>
+        <v>1433.108987433637</v>
       </c>
       <c r="F31" t="n">
-        <v>11532</v>
+        <v>11515</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -4004,16 +4004,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1424.924915090035</v>
+        <v>1424.991657690778</v>
       </c>
       <c r="D32" t="n">
-        <v>1415.229433023199</v>
+        <v>1415.292280686214</v>
       </c>
       <c r="E32" t="n">
-        <v>1434.62039715687</v>
+        <v>1434.691034695343</v>
       </c>
       <c r="F32" t="n">
-        <v>3897</v>
+        <v>3893</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -4155,16 +4155,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1424.899244260691</v>
+        <v>1424.929628242865</v>
       </c>
       <c r="D33" t="n">
-        <v>1418.321775239341</v>
+        <v>1418.353743896235</v>
       </c>
       <c r="E33" t="n">
-        <v>1431.476713282041</v>
+        <v>1431.505512589495</v>
       </c>
       <c r="F33" t="n">
-        <v>8948</v>
+        <v>8947</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -4226,16 +4226,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1424.88463958302</v>
+        <v>1424.77342023501</v>
       </c>
       <c r="D34" t="n">
-        <v>1421.389557348873</v>
+        <v>1421.278574911297</v>
       </c>
       <c r="E34" t="n">
-        <v>1428.379721817166</v>
+        <v>1428.268265558724</v>
       </c>
       <c r="F34" t="n">
-        <v>48004</v>
+        <v>47999</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -4297,16 +4297,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1424.207107976129</v>
+        <v>1424.142362861242</v>
       </c>
       <c r="D35" t="n">
-        <v>1420.299184114695</v>
+        <v>1420.234221716797</v>
       </c>
       <c r="E35" t="n">
-        <v>1428.115031837564</v>
+        <v>1428.050504005688</v>
       </c>
       <c r="F35" t="n">
-        <v>35668</v>
+        <v>35662</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1422.63810922664</v>
+        <v>1422.742946224598</v>
       </c>
       <c r="D36" t="n">
-        <v>1419.05689958125</v>
+        <v>1419.162201285617</v>
       </c>
       <c r="E36" t="n">
-        <v>1426.219318872029</v>
+        <v>1426.323691163579</v>
       </c>
       <c r="F36" t="n">
-        <v>41966</v>
+        <v>41975</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -4439,16 +4439,16 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1422.364551154884</v>
+        <v>1422.399601713316</v>
       </c>
       <c r="D37" t="n">
-        <v>1419.807601048771</v>
+        <v>1419.842732395144</v>
       </c>
       <c r="E37" t="n">
-        <v>1424.921501260998</v>
+        <v>1424.956471031488</v>
       </c>
       <c r="F37" t="n">
-        <v>97808</v>
+        <v>97788</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -4590,16 +4590,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1422.027413572087</v>
+        <v>1422.064279260454</v>
       </c>
       <c r="D38" t="n">
-        <v>1415.63818303227</v>
+        <v>1415.676168685056</v>
       </c>
       <c r="E38" t="n">
-        <v>1428.416644111903</v>
+        <v>1428.452389835853</v>
       </c>
       <c r="F38" t="n">
-        <v>11943</v>
+        <v>11944</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -4661,16 +4661,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1421.588783462151</v>
+        <v>1421.636916430414</v>
       </c>
       <c r="D39" t="n">
-        <v>1415.895420047521</v>
+        <v>1415.942731846803</v>
       </c>
       <c r="E39" t="n">
-        <v>1427.28214687678</v>
+        <v>1427.331101014025</v>
       </c>
       <c r="F39" t="n">
-        <v>18060</v>
+        <v>18059</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -4732,16 +4732,16 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1418.632796184962</v>
+        <v>1418.693927213401</v>
       </c>
       <c r="D40" t="n">
-        <v>1412.096527854002</v>
+        <v>1412.156876037188</v>
       </c>
       <c r="E40" t="n">
-        <v>1425.169064515922</v>
+        <v>1425.230978389614</v>
       </c>
       <c r="F40" t="n">
-        <v>11539</v>
+        <v>11531</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -4883,16 +4883,16 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1418.176994107235</v>
+        <v>1418.228899511914</v>
       </c>
       <c r="D41" t="n">
-        <v>1413.268225982842</v>
+        <v>1413.320016703903</v>
       </c>
       <c r="E41" t="n">
-        <v>1423.085762231629</v>
+        <v>1423.137782319925</v>
       </c>
       <c r="F41" t="n">
-        <v>26967</v>
+        <v>26959</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -5030,20 +5030,20 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>deepseek-v3.1</t>
+          <t>deepseek-v3.1-terminus-thinking</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1417.161803158608</v>
+        <v>1417.209021514145</v>
       </c>
       <c r="D42" t="n">
-        <v>1411.092422280057</v>
+        <v>1407.075624540877</v>
       </c>
       <c r="E42" t="n">
-        <v>1423.231184037159</v>
+        <v>1427.342418487413</v>
       </c>
       <c r="F42" t="n">
-        <v>14540</v>
+        <v>3354</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -5101,20 +5101,20 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-terminus-thinking</t>
+          <t>deepseek-v3.1</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1416.927654322016</v>
+        <v>1417.145820248776</v>
       </c>
       <c r="D43" t="n">
-        <v>1406.799166716881</v>
+        <v>1411.078466364427</v>
       </c>
       <c r="E43" t="n">
-        <v>1427.056141927152</v>
+        <v>1423.213174133125</v>
       </c>
       <c r="F43" t="n">
-        <v>3357</v>
+        <v>14540</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -5176,16 +5176,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1416.082717859271</v>
+        <v>1416.097163110477</v>
       </c>
       <c r="D44" t="n">
-        <v>1411.78671457623</v>
+        <v>1411.799332527324</v>
       </c>
       <c r="E44" t="n">
-        <v>1420.378721142313</v>
+        <v>1420.394993693631</v>
       </c>
       <c r="F44" t="n">
-        <v>29666</v>
+        <v>29651</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -5327,16 +5327,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1416.001886592228</v>
+        <v>1415.931240112323</v>
       </c>
       <c r="D45" t="n">
-        <v>1409.324590646791</v>
+        <v>1409.254102978883</v>
       </c>
       <c r="E45" t="n">
-        <v>1422.679182537664</v>
+        <v>1422.608377245763</v>
       </c>
       <c r="F45" t="n">
-        <v>11413</v>
+        <v>11409</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -5398,16 +5398,16 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1414.920634971134</v>
+        <v>1414.980185450766</v>
       </c>
       <c r="D46" t="n">
-        <v>1411.495068497981</v>
+        <v>1411.560907662792</v>
       </c>
       <c r="E46" t="n">
-        <v>1418.346201444288</v>
+        <v>1418.39946323874</v>
       </c>
       <c r="F46" t="n">
-        <v>79403</v>
+        <v>79944</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -5469,16 +5469,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1414.719329220982</v>
+        <v>1414.83453642041</v>
       </c>
       <c r="D47" t="n">
-        <v>1404.992540263092</v>
+        <v>1405.10211190994</v>
       </c>
       <c r="E47" t="n">
-        <v>1424.446118178873</v>
+        <v>1424.566960930881</v>
       </c>
       <c r="F47" t="n">
-        <v>3602</v>
+        <v>3599</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -5540,16 +5540,16 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1413.71702688143</v>
+        <v>1413.887239408306</v>
       </c>
       <c r="D48" t="n">
-        <v>1410.814913463878</v>
+        <v>1410.987149099679</v>
       </c>
       <c r="E48" t="n">
-        <v>1416.619140298982</v>
+        <v>1416.787329716934</v>
       </c>
       <c r="F48" t="n">
-        <v>78986</v>
+        <v>79452</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -5691,16 +5691,16 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1413.393658132285</v>
+        <v>1413.425390030167</v>
       </c>
       <c r="D49" t="n">
-        <v>1406.84752602769</v>
+        <v>1406.875511990807</v>
       </c>
       <c r="E49" t="n">
-        <v>1419.93979023688</v>
+        <v>1419.975268069527</v>
       </c>
       <c r="F49" t="n">
-        <v>11250</v>
+        <v>11241</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -5842,16 +5842,16 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1411.283541364948</v>
+        <v>1411.27157240162</v>
       </c>
       <c r="D50" t="n">
-        <v>1406.342050636693</v>
+        <v>1406.329340438641</v>
       </c>
       <c r="E50" t="n">
-        <v>1416.225032093203</v>
+        <v>1416.213804364598</v>
       </c>
       <c r="F50" t="n">
-        <v>23668</v>
+        <v>23661</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -5993,16 +5993,16 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1408.934250793886</v>
+        <v>1408.831728156688</v>
       </c>
       <c r="D51" t="n">
-        <v>1401.513395538369</v>
+        <v>1401.414156106443</v>
       </c>
       <c r="E51" t="n">
-        <v>1416.355106049402</v>
+        <v>1416.249300206934</v>
       </c>
       <c r="F51" t="n">
-        <v>6871</v>
+        <v>6874</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1408.847189945266</v>
+        <v>1408.72409819639</v>
       </c>
       <c r="D52" t="n">
-        <v>1404.547032597415</v>
+        <v>1404.423416269354</v>
       </c>
       <c r="E52" t="n">
-        <v>1413.147347293117</v>
+        <v>1413.024780123425</v>
       </c>
       <c r="F52" t="n">
-        <v>28618</v>
+        <v>28612</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -6215,16 +6215,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1405.104088409852</v>
+        <v>1405.241270710841</v>
       </c>
       <c r="D53" t="n">
-        <v>1400.173688477651</v>
+        <v>1400.343917722984</v>
       </c>
       <c r="E53" t="n">
-        <v>1410.034488342053</v>
+        <v>1410.138623698699</v>
       </c>
       <c r="F53" t="n">
-        <v>26446</v>
+        <v>27070</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -6366,16 +6366,16 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1402.514885725651</v>
+        <v>1402.53451398059</v>
       </c>
       <c r="D54" t="n">
-        <v>1397.976702427165</v>
+        <v>1397.995990557387</v>
       </c>
       <c r="E54" t="n">
-        <v>1407.053069024138</v>
+        <v>1407.073037403793</v>
       </c>
       <c r="F54" t="n">
-        <v>37284</v>
+        <v>37279</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -6517,13 +6517,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1401.147784004097</v>
+        <v>1401.177191429132</v>
       </c>
       <c r="D55" t="n">
-        <v>1394.723036303906</v>
+        <v>1394.754334307371</v>
       </c>
       <c r="E55" t="n">
-        <v>1407.572531704287</v>
+        <v>1407.600048550892</v>
       </c>
       <c r="F55" t="n">
         <v>11123</v>
@@ -6668,16 +6668,16 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1400.029394812505</v>
+        <v>1399.992559008723</v>
       </c>
       <c r="D56" t="n">
-        <v>1393.442825219014</v>
+        <v>1393.404987817346</v>
       </c>
       <c r="E56" t="n">
-        <v>1406.615964405995</v>
+        <v>1406.580130200099</v>
       </c>
       <c r="F56" t="n">
-        <v>8776</v>
+        <v>8774</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -6819,16 +6819,16 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1398.917802883869</v>
+        <v>1398.986740127523</v>
       </c>
       <c r="D57" t="n">
-        <v>1394.129073157556</v>
+        <v>1394.198237430405</v>
       </c>
       <c r="E57" t="n">
-        <v>1403.706532610182</v>
+        <v>1403.775242824641</v>
       </c>
       <c r="F57" t="n">
-        <v>22607</v>
+        <v>22603</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -6970,13 +6970,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1398.131709342381</v>
+        <v>1398.117983968687</v>
       </c>
       <c r="D58" t="n">
-        <v>1393.236456623881</v>
+        <v>1393.222608958932</v>
       </c>
       <c r="E58" t="n">
-        <v>1403.026962060881</v>
+        <v>1403.013358978443</v>
       </c>
       <c r="F58" t="n">
         <v>18524</v>
@@ -7121,16 +7121,16 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1395.644493084921</v>
+        <v>1395.638607849424</v>
       </c>
       <c r="D59" t="n">
-        <v>1391.743584630641</v>
+        <v>1391.737618583955</v>
       </c>
       <c r="E59" t="n">
-        <v>1399.545401539201</v>
+        <v>1399.539597114893</v>
       </c>
       <c r="F59" t="n">
-        <v>44762</v>
+        <v>44758</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -7272,16 +7272,16 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1394.721573546292</v>
+        <v>1395.029963260086</v>
       </c>
       <c r="D60" t="n">
-        <v>1387.869769710979</v>
+        <v>1388.177289438941</v>
       </c>
       <c r="E60" t="n">
-        <v>1401.573377381606</v>
+        <v>1401.882637081232</v>
       </c>
       <c r="F60" t="n">
-        <v>7809</v>
+        <v>7805</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -7423,16 +7423,16 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1393.876292885215</v>
+        <v>1393.793394084286</v>
       </c>
       <c r="D61" t="n">
-        <v>1389.635684824487</v>
+        <v>1389.553018962186</v>
       </c>
       <c r="E61" t="n">
-        <v>1398.116900945943</v>
+        <v>1398.033769206386</v>
       </c>
       <c r="F61" t="n">
-        <v>30410</v>
+        <v>30408</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -7574,16 +7574,16 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1393.218901680072</v>
+        <v>1393.273766901803</v>
       </c>
       <c r="D62" t="n">
-        <v>1389.661129148547</v>
+        <v>1389.716290479776</v>
       </c>
       <c r="E62" t="n">
-        <v>1396.776674211597</v>
+        <v>1396.831243323829</v>
       </c>
       <c r="F62" t="n">
-        <v>60236</v>
+        <v>60207</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -7645,16 +7645,16 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1391.686220300875</v>
+        <v>1391.711623122026</v>
       </c>
       <c r="D63" t="n">
-        <v>1388.19753769919</v>
+        <v>1388.223175199253</v>
       </c>
       <c r="E63" t="n">
-        <v>1395.174902902559</v>
+        <v>1395.200071044799</v>
       </c>
       <c r="F63" t="n">
-        <v>48012</v>
+        <v>47998</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -7716,16 +7716,16 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1390.839111536408</v>
+        <v>1390.8451428342</v>
       </c>
       <c r="D64" t="n">
-        <v>1386.941984139183</v>
+        <v>1386.948707823527</v>
       </c>
       <c r="E64" t="n">
-        <v>1394.736238933634</v>
+        <v>1394.741577844872</v>
       </c>
       <c r="F64" t="n">
-        <v>42734</v>
+        <v>42730</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -7787,16 +7787,16 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1387.365681487454</v>
+        <v>1387.32104552345</v>
       </c>
       <c r="D65" t="n">
-        <v>1382.371457549832</v>
+        <v>1382.325913850224</v>
       </c>
       <c r="E65" t="n">
-        <v>1392.359905425076</v>
+        <v>1392.316177196677</v>
       </c>
       <c r="F65" t="n">
-        <v>25011</v>
+        <v>25006</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -7938,16 +7938,16 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1387.082562410915</v>
+        <v>1387.126002571981</v>
       </c>
       <c r="D66" t="n">
-        <v>1380.898526865866</v>
+        <v>1380.942552399045</v>
       </c>
       <c r="E66" t="n">
-        <v>1393.266597955964</v>
+        <v>1393.309452744918</v>
       </c>
       <c r="F66" t="n">
-        <v>11118</v>
+        <v>11115</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -8009,13 +8009,13 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1384.552537274528</v>
+        <v>1384.561240884782</v>
       </c>
       <c r="D67" t="n">
-        <v>1379.367489464706</v>
+        <v>1379.375909616568</v>
       </c>
       <c r="E67" t="n">
-        <v>1389.73758508435</v>
+        <v>1389.746572152996</v>
       </c>
       <c r="F67" t="n">
         <v>17187</v>
@@ -8080,16 +8080,16 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1382.776203902379</v>
+        <v>1382.65675988569</v>
       </c>
       <c r="D68" t="n">
-        <v>1377.857461885636</v>
+        <v>1377.737333386408</v>
       </c>
       <c r="E68" t="n">
-        <v>1387.694945919122</v>
+        <v>1387.576186384972</v>
       </c>
       <c r="F68" t="n">
-        <v>23182</v>
+        <v>23174</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -8231,13 +8231,13 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1378.904334248768</v>
+        <v>1378.670610924245</v>
       </c>
       <c r="D69" t="n">
-        <v>1367.724340989975</v>
+        <v>1367.489364818274</v>
       </c>
       <c r="E69" t="n">
-        <v>1390.08432750756</v>
+        <v>1389.851857030216</v>
       </c>
       <c r="F69" t="n">
         <v>2830</v>
@@ -8302,16 +8302,16 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1378.602728468169</v>
+        <v>1378.572343519039</v>
       </c>
       <c r="D70" t="n">
-        <v>1374.33733439781</v>
+        <v>1374.306697357198</v>
       </c>
       <c r="E70" t="n">
-        <v>1382.868122538527</v>
+        <v>1382.83798968088</v>
       </c>
       <c r="F70" t="n">
-        <v>31220</v>
+        <v>31201</v>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
@@ -8449,16 +8449,16 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1375.249838058633</v>
+        <v>1375.244302666996</v>
       </c>
       <c r="D71" t="n">
-        <v>1370.534232009159</v>
+        <v>1370.528059764902</v>
       </c>
       <c r="E71" t="n">
-        <v>1379.965444108106</v>
+        <v>1379.96054556909</v>
       </c>
       <c r="F71" t="n">
-        <v>25826</v>
+        <v>25825</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -8600,13 +8600,13 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1373.28095913468</v>
+        <v>1373.258648228139</v>
       </c>
       <c r="D72" t="n">
-        <v>1369.016695636827</v>
+        <v>1368.995211954967</v>
       </c>
       <c r="E72" t="n">
-        <v>1377.545222632533</v>
+        <v>1377.522084501312</v>
       </c>
       <c r="F72" t="n">
         <v>30454</v>
@@ -8671,16 +8671,16 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1369.379870939476</v>
+        <v>1369.353773968885</v>
       </c>
       <c r="D73" t="n">
-        <v>1363.496361363839</v>
+        <v>1363.469345867297</v>
       </c>
       <c r="E73" t="n">
-        <v>1375.263380515114</v>
+        <v>1375.238202070474</v>
       </c>
       <c r="F73" t="n">
-        <v>13382</v>
+        <v>13371</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -8822,16 +8822,16 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1367.397818654712</v>
+        <v>1367.300007066523</v>
       </c>
       <c r="D74" t="n">
-        <v>1362.795106651039</v>
+        <v>1362.696367355386</v>
       </c>
       <c r="E74" t="n">
-        <v>1372.000530658386</v>
+        <v>1371.90364677766</v>
       </c>
       <c r="F74" t="n">
-        <v>30281</v>
+        <v>30265</v>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
@@ -8969,16 +8969,16 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1365.398502518858</v>
+        <v>1365.391617962716</v>
       </c>
       <c r="D75" t="n">
-        <v>1361.687713255282</v>
+        <v>1361.680214713408</v>
       </c>
       <c r="E75" t="n">
-        <v>1369.109291782434</v>
+        <v>1369.103021212023</v>
       </c>
       <c r="F75" t="n">
-        <v>46437</v>
+        <v>46425</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -9120,16 +9120,16 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1364.814945454096</v>
+        <v>1364.865916947027</v>
       </c>
       <c r="D76" t="n">
-        <v>1359.089024918612</v>
+        <v>1359.139512192324</v>
       </c>
       <c r="E76" t="n">
-        <v>1370.54086598958</v>
+        <v>1370.59232170173</v>
       </c>
       <c r="F76" t="n">
-        <v>11979</v>
+        <v>11977</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -9191,16 +9191,16 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1364.007351445573</v>
+        <v>1363.942850248035</v>
       </c>
       <c r="D77" t="n">
-        <v>1359.702894260482</v>
+        <v>1359.638159630837</v>
       </c>
       <c r="E77" t="n">
-        <v>1368.311808630664</v>
+        <v>1368.247540865233</v>
       </c>
       <c r="F77" t="n">
-        <v>34048</v>
+        <v>34042</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -9262,16 +9262,16 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1360.527707348794</v>
+        <v>1360.460367387524</v>
       </c>
       <c r="D78" t="n">
-        <v>1353.396045122099</v>
+        <v>1353.326415308176</v>
       </c>
       <c r="E78" t="n">
-        <v>1367.659369575488</v>
+        <v>1367.594319466872</v>
       </c>
       <c r="F78" t="n">
-        <v>7861</v>
+        <v>7859</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -9413,13 +9413,13 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1358.449197654003</v>
+        <v>1358.437628619717</v>
       </c>
       <c r="D79" t="n">
-        <v>1353.690870778885</v>
+        <v>1353.679243697217</v>
       </c>
       <c r="E79" t="n">
-        <v>1363.207524529121</v>
+        <v>1363.196013542217</v>
       </c>
       <c r="F79" t="n">
         <v>21770</v>
@@ -9564,16 +9564,16 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1356.45653708856</v>
+        <v>1356.49558364836</v>
       </c>
       <c r="D80" t="n">
-        <v>1351.221118051274</v>
+        <v>1351.260268817022</v>
       </c>
       <c r="E80" t="n">
-        <v>1361.691956125846</v>
+        <v>1361.730898479698</v>
       </c>
       <c r="F80" t="n">
-        <v>17353</v>
+        <v>17348</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -9635,16 +9635,16 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1355.957579807005</v>
+        <v>1355.781338488142</v>
       </c>
       <c r="D81" t="n">
-        <v>1347.690443363504</v>
+        <v>1347.509743888398</v>
       </c>
       <c r="E81" t="n">
-        <v>1364.224716250506</v>
+        <v>1364.052933087886</v>
       </c>
       <c r="F81" t="n">
-        <v>5421</v>
+        <v>5417</v>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
@@ -9782,16 +9782,16 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1353.698415166401</v>
+        <v>1353.713189842364</v>
       </c>
       <c r="D82" t="n">
-        <v>1350.219380659513</v>
+        <v>1350.233630352496</v>
       </c>
       <c r="E82" t="n">
-        <v>1357.17744967329</v>
+        <v>1357.192749332233</v>
       </c>
       <c r="F82" t="n">
-        <v>55477</v>
+        <v>55467</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -9853,16 +9853,16 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1352.264341847894</v>
+        <v>1352.39406585147</v>
       </c>
       <c r="D83" t="n">
-        <v>1343.818644627783</v>
+        <v>1343.944182109022</v>
       </c>
       <c r="E83" t="n">
-        <v>1360.710039068005</v>
+        <v>1360.843949593917</v>
       </c>
       <c r="F83" t="n">
-        <v>4811</v>
+        <v>4807</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -9924,16 +9924,16 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1351.701828685937</v>
+        <v>1351.577517951259</v>
       </c>
       <c r="D84" t="n">
-        <v>1347.324857486818</v>
+        <v>1347.197819499163</v>
       </c>
       <c r="E84" t="n">
-        <v>1356.078799885056</v>
+        <v>1355.957216403356</v>
       </c>
       <c r="F84" t="n">
-        <v>30039</v>
+        <v>30018</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -10071,68 +10071,148 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>step-3</t>
+          <t>nvidia-nemotron-3.5-lightning-30b-a3b-nvfp4</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1349.393778453777</v>
+        <v>1349.509573329841</v>
       </c>
       <c r="D85" t="n">
-        <v>1341.865598512213</v>
+        <v>1343.475848619422</v>
       </c>
       <c r="E85" t="n">
-        <v>1356.92195839534</v>
+        <v>1355.543298040261</v>
       </c>
       <c r="F85" t="n">
-        <v>6272</v>
+        <v>14877</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>StepFun</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
+          <t>OpenMDW-1.1</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>30</v>
+      </c>
+      <c r="J85" t="n">
+        <v>3</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr"/>
-      <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr"/>
-      <c r="R85" t="inlineStr"/>
-      <c r="S85" t="inlineStr"/>
-      <c r="T85" t="inlineStr"/>
-      <c r="U85" t="inlineStr"/>
-      <c r="V85" t="inlineStr"/>
-      <c r="W85" t="inlineStr"/>
-      <c r="X85" t="inlineStr"/>
-      <c r="Y85" t="inlineStr"/>
-      <c r="Z85" t="inlineStr"/>
-      <c r="AA85" t="inlineStr"/>
-      <c r="AB85" t="inlineStr"/>
-      <c r="AC85" t="inlineStr"/>
-      <c r="AD85" t="inlineStr"/>
-      <c r="AE85" t="inlineStr"/>
-      <c r="AF85" t="inlineStr"/>
-      <c r="AG85" t="inlineStr"/>
+          <t>name_parsing</t>
+        </is>
+      </c>
+      <c r="M85" t="n">
+        <v>60</v>
+      </c>
+      <c r="N85" t="n">
+        <v>75</v>
+      </c>
+      <c r="O85" t="n">
+        <v>30</v>
+      </c>
+      <c r="P85" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>15</v>
+      </c>
+      <c r="R85" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="S85" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T85" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U85" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V85" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W85" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X85" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y85" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z85" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA85" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB85" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC85" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD85" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE85" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF85" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG85" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH85" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -10142,148 +10222,68 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>nvidia-nemotron-3.5-lightning-30b-a3b-nvfp4</t>
+          <t>step-3</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1348.638015425588</v>
+        <v>1349.395869032312</v>
       </c>
       <c r="D86" t="n">
-        <v>1342.531248179645</v>
+        <v>1341.864782153641</v>
       </c>
       <c r="E86" t="n">
-        <v>1354.744782671531</v>
+        <v>1356.926955910984</v>
       </c>
       <c r="F86" t="n">
-        <v>14326</v>
+        <v>6266</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>StepFun</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>OpenMDW-1.1</t>
-        </is>
-      </c>
-      <c r="I86" t="n">
-        <v>30</v>
-      </c>
-      <c r="J86" t="n">
-        <v>3</v>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
-          <t>name_parsing</t>
-        </is>
-      </c>
-      <c r="M86" t="n">
-        <v>60</v>
-      </c>
-      <c r="N86" t="n">
-        <v>75</v>
-      </c>
-      <c r="O86" t="n">
-        <v>30</v>
-      </c>
-      <c r="P86" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="Q86" t="n">
-        <v>15</v>
-      </c>
-      <c r="R86" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="S86" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T86" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U86" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V86" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W86" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X86" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y86" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z86" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA86" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB86" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC86" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD86" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE86" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF86" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG86" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr"/>
+      <c r="S86" t="inlineStr"/>
+      <c r="T86" t="inlineStr"/>
+      <c r="U86" t="inlineStr"/>
+      <c r="V86" t="inlineStr"/>
+      <c r="W86" t="inlineStr"/>
+      <c r="X86" t="inlineStr"/>
+      <c r="Y86" t="inlineStr"/>
+      <c r="Z86" t="inlineStr"/>
+      <c r="AA86" t="inlineStr"/>
+      <c r="AB86" t="inlineStr"/>
+      <c r="AC86" t="inlineStr"/>
+      <c r="AD86" t="inlineStr"/>
+      <c r="AE86" t="inlineStr"/>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="inlineStr"/>
       <c r="AH86" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -10297,13 +10297,13 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1347.63978619981</v>
+        <v>1347.622305137077</v>
       </c>
       <c r="D87" t="n">
-        <v>1335.959897927538</v>
+        <v>1335.943050366683</v>
       </c>
       <c r="E87" t="n">
-        <v>1359.319674472084</v>
+        <v>1359.301559907471</v>
       </c>
       <c r="F87" t="n">
         <v>2549</v>
@@ -10448,13 +10448,13 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1346.941718728933</v>
+        <v>1346.927857741671</v>
       </c>
       <c r="D88" t="n">
-        <v>1337.483550820804</v>
+        <v>1337.469985591327</v>
       </c>
       <c r="E88" t="n">
-        <v>1356.399886637062</v>
+        <v>1356.385729892014</v>
       </c>
       <c r="F88" t="n">
         <v>3926</v>
@@ -10599,16 +10599,16 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1343.790491861378</v>
+        <v>1343.783896577042</v>
       </c>
       <c r="D89" t="n">
-        <v>1336.479311392364</v>
+        <v>1336.470594818567</v>
       </c>
       <c r="E89" t="n">
-        <v>1351.101672330391</v>
+        <v>1351.097198335518</v>
       </c>
       <c r="F89" t="n">
-        <v>6889</v>
+        <v>6887</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -10670,16 +10670,16 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1343.23601620115</v>
+        <v>1343.36584929888</v>
       </c>
       <c r="D90" t="n">
-        <v>1335.477497952291</v>
+        <v>1335.607179368292</v>
       </c>
       <c r="E90" t="n">
-        <v>1350.994534450009</v>
+        <v>1351.124519229469</v>
       </c>
       <c r="F90" t="n">
-        <v>6819</v>
+        <v>6817</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -10821,13 +10821,13 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1342.90837339088</v>
+        <v>1342.897164861398</v>
       </c>
       <c r="D91" t="n">
-        <v>1332.887583633109</v>
+        <v>1332.876545425546</v>
       </c>
       <c r="E91" t="n">
-        <v>1352.929163148651</v>
+        <v>1352.917784297249</v>
       </c>
       <c r="F91" t="n">
         <v>3308</v>
@@ -10972,13 +10972,13 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1341.753768013428</v>
+        <v>1341.760404881006</v>
       </c>
       <c r="D92" t="n">
-        <v>1332.241683836977</v>
+        <v>1332.248569694422</v>
       </c>
       <c r="E92" t="n">
-        <v>1351.26585218988</v>
+        <v>1351.272240067591</v>
       </c>
       <c r="F92" t="n">
         <v>3829</v>
@@ -11123,16 +11123,16 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1339.754013372682</v>
+        <v>1339.550750915539</v>
       </c>
       <c r="D93" t="n">
-        <v>1329.294586317335</v>
+        <v>1329.066663270803</v>
       </c>
       <c r="E93" t="n">
-        <v>1350.213440428028</v>
+        <v>1350.034838560275</v>
       </c>
       <c r="F93" t="n">
-        <v>3416</v>
+        <v>3401</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -11274,16 +11274,16 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1335.887162152065</v>
+        <v>1335.761256700982</v>
       </c>
       <c r="D94" t="n">
-        <v>1331.418704307066</v>
+        <v>1331.293127086844</v>
       </c>
       <c r="E94" t="n">
-        <v>1340.355619997063</v>
+        <v>1340.22938631512</v>
       </c>
       <c r="F94" t="n">
-        <v>25084</v>
+        <v>25078</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -11425,13 +11425,13 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1335.350784796819</v>
+        <v>1335.36786147857</v>
       </c>
       <c r="D95" t="n">
-        <v>1331.619375269566</v>
+        <v>1331.636344097256</v>
       </c>
       <c r="E95" t="n">
-        <v>1339.082194324071</v>
+        <v>1339.099378859883</v>
       </c>
       <c r="F95" t="n">
         <v>41375</v>
@@ -11576,13 +11576,13 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1333.488510616226</v>
+        <v>1333.50272309109</v>
       </c>
       <c r="D96" t="n">
-        <v>1329.882089784069</v>
+        <v>1329.896416244613</v>
       </c>
       <c r="E96" t="n">
-        <v>1337.094931448383</v>
+        <v>1337.109029937566</v>
       </c>
       <c r="F96" t="n">
         <v>59656</v>
@@ -11727,16 +11727,16 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1329.149177354398</v>
+        <v>1329.193621212394</v>
       </c>
       <c r="D97" t="n">
-        <v>1323.00210756666</v>
+        <v>1323.0479856947</v>
       </c>
       <c r="E97" t="n">
-        <v>1335.296247142136</v>
+        <v>1335.339256730088</v>
       </c>
       <c r="F97" t="n">
-        <v>11794</v>
+        <v>11801</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -11878,13 +11878,13 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1327.817417702807</v>
+        <v>1327.794106135701</v>
       </c>
       <c r="D98" t="n">
-        <v>1315.682672489192</v>
+        <v>1315.660012823035</v>
       </c>
       <c r="E98" t="n">
-        <v>1339.952162916422</v>
+        <v>1339.928199448367</v>
       </c>
       <c r="F98" t="n">
         <v>2218</v>
@@ -12029,16 +12029,16 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1326.970503033269</v>
+        <v>1326.977863849166</v>
       </c>
       <c r="D99" t="n">
-        <v>1322.685239792983</v>
+        <v>1322.692349849318</v>
       </c>
       <c r="E99" t="n">
-        <v>1331.255766273555</v>
+        <v>1331.263377849013</v>
       </c>
       <c r="F99" t="n">
-        <v>39266</v>
+        <v>39262</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -12180,16 +12180,16 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1326.568297418625</v>
+        <v>1326.462985457504</v>
       </c>
       <c r="D100" t="n">
-        <v>1321.808821524116</v>
+        <v>1321.703680796824</v>
       </c>
       <c r="E100" t="n">
-        <v>1331.327773313134</v>
+        <v>1331.222290118184</v>
       </c>
       <c r="F100" t="n">
-        <v>26036</v>
+        <v>26037</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -12331,13 +12331,13 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1323.398766612131</v>
+        <v>1323.384603855063</v>
       </c>
       <c r="D101" t="n">
-        <v>1315.125148461245</v>
+        <v>1315.111215855622</v>
       </c>
       <c r="E101" t="n">
-        <v>1331.672384763016</v>
+        <v>1331.657991854504</v>
       </c>
       <c r="F101" t="n">
         <v>6795</v>
@@ -12402,16 +12402,16 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1322.614596574088</v>
+        <v>1322.584028382245</v>
       </c>
       <c r="D102" t="n">
-        <v>1315.313609654477</v>
+        <v>1315.281431544685</v>
       </c>
       <c r="E102" t="n">
-        <v>1329.915583493699</v>
+        <v>1329.886625219805</v>
       </c>
       <c r="F102" t="n">
-        <v>6934</v>
+        <v>6932</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -12473,13 +12473,13 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1321.855445026273</v>
+        <v>1321.764950535163</v>
       </c>
       <c r="D103" t="n">
-        <v>1300.659302405044</v>
+        <v>1300.572010467282</v>
       </c>
       <c r="E103" t="n">
-        <v>1343.051587647502</v>
+        <v>1342.957890603044</v>
       </c>
       <c r="F103" t="n">
         <v>818</v>
@@ -12624,16 +12624,16 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1321.58165610929</v>
+        <v>1321.638571622781</v>
       </c>
       <c r="D104" t="n">
-        <v>1316.8365391562</v>
+        <v>1316.894176724808</v>
       </c>
       <c r="E104" t="n">
-        <v>1326.326773062379</v>
+        <v>1326.382966520754</v>
       </c>
       <c r="F104" t="n">
-        <v>29668</v>
+        <v>29667</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -12775,13 +12775,13 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1318.089425765077</v>
+        <v>1318.084979923916</v>
       </c>
       <c r="D105" t="n">
-        <v>1312.385328424837</v>
+        <v>1312.381061635663</v>
       </c>
       <c r="E105" t="n">
-        <v>1323.793523105317</v>
+        <v>1323.788898212169</v>
       </c>
       <c r="F105" t="n">
         <v>16478</v>
@@ -12846,16 +12846,16 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1317.788321856259</v>
+        <v>1317.797560825658</v>
       </c>
       <c r="D106" t="n">
-        <v>1314.27865960886</v>
+        <v>1314.287170192333</v>
       </c>
       <c r="E106" t="n">
-        <v>1321.297984103657</v>
+        <v>1321.307951458983</v>
       </c>
       <c r="F106" t="n">
-        <v>54371</v>
+        <v>54366</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -12997,16 +12997,16 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1317.586336181587</v>
+        <v>1317.584094038728</v>
       </c>
       <c r="D107" t="n">
-        <v>1311.164885997544</v>
+        <v>1311.161501828368</v>
       </c>
       <c r="E107" t="n">
-        <v>1324.007786365631</v>
+        <v>1324.006686249088</v>
       </c>
       <c r="F107" t="n">
-        <v>10371</v>
+        <v>10368</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -13148,16 +13148,16 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1317.34354855468</v>
+        <v>1317.417745599214</v>
       </c>
       <c r="D108" t="n">
-        <v>1312.151781278129</v>
+        <v>1312.225565789352</v>
       </c>
       <c r="E108" t="n">
-        <v>1322.535315831231</v>
+        <v>1322.609925409078</v>
       </c>
       <c r="F108" t="n">
-        <v>22038</v>
+        <v>22042</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -13299,13 +13299,13 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1314.374079986559</v>
+        <v>1314.373014387154</v>
       </c>
       <c r="D109" t="n">
-        <v>1310.438986850528</v>
+        <v>1310.438075426826</v>
       </c>
       <c r="E109" t="n">
-        <v>1318.30917312259</v>
+        <v>1318.307953347482</v>
       </c>
       <c r="F109" t="n">
         <v>45459</v>
@@ -13450,13 +13450,13 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1314.153397072419</v>
+        <v>1314.144012356593</v>
       </c>
       <c r="D110" t="n">
-        <v>1309.586389242329</v>
+        <v>1309.576986013699</v>
       </c>
       <c r="E110" t="n">
-        <v>1318.720404902508</v>
+        <v>1318.711038699486</v>
       </c>
       <c r="F110" t="n">
         <v>24739</v>
@@ -13597,16 +13597,16 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1313.525399923312</v>
+        <v>1313.534004829241</v>
       </c>
       <c r="D111" t="n">
-        <v>1308.037076863434</v>
+        <v>1308.046485207478</v>
       </c>
       <c r="E111" t="n">
-        <v>1319.01372298319</v>
+        <v>1319.021524451004</v>
       </c>
       <c r="F111" t="n">
-        <v>15724</v>
+        <v>15722</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -13748,13 +13748,13 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1307.193014915279</v>
+        <v>1307.180088166303</v>
       </c>
       <c r="D112" t="n">
-        <v>1302.478973336676</v>
+        <v>1302.466201073729</v>
       </c>
       <c r="E112" t="n">
-        <v>1311.907056493883</v>
+        <v>1311.893975258877</v>
       </c>
       <c r="F112" t="n">
         <v>24572</v>
@@ -13819,13 +13819,13 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1306.605417251318</v>
+        <v>1306.592694099909</v>
       </c>
       <c r="D113" t="n">
-        <v>1300.929339296507</v>
+        <v>1300.916871056803</v>
       </c>
       <c r="E113" t="n">
-        <v>1312.281495206129</v>
+        <v>1312.268517143015</v>
       </c>
       <c r="F113" t="n">
         <v>19621</v>
@@ -13966,13 +13966,13 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1306.478628109015</v>
+        <v>1306.352310105346</v>
       </c>
       <c r="D114" t="n">
-        <v>1298.22632596132</v>
+        <v>1298.098944288148</v>
       </c>
       <c r="E114" t="n">
-        <v>1314.73093025671</v>
+        <v>1314.605675922543</v>
       </c>
       <c r="F114" t="n">
         <v>5811</v>
@@ -14117,13 +14117,13 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1305.537362219416</v>
+        <v>1305.536112701126</v>
       </c>
       <c r="D115" t="n">
-        <v>1301.081613969688</v>
+        <v>1301.080234217781</v>
       </c>
       <c r="E115" t="n">
-        <v>1309.993110469145</v>
+        <v>1309.991991184471</v>
       </c>
       <c r="F115" t="n">
         <v>28073</v>
@@ -14188,16 +14188,16 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1304.697817282826</v>
+        <v>1304.0675680601</v>
       </c>
       <c r="D116" t="n">
-        <v>1294.681778635902</v>
+        <v>1294.034737437274</v>
       </c>
       <c r="E116" t="n">
-        <v>1314.71385592975</v>
+        <v>1314.100398682927</v>
       </c>
       <c r="F116" t="n">
-        <v>4166</v>
+        <v>4161</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -14339,13 +14339,13 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1303.238264983027</v>
+        <v>1303.244346900854</v>
       </c>
       <c r="D117" t="n">
-        <v>1293.920506790486</v>
+        <v>1293.926814233014</v>
       </c>
       <c r="E117" t="n">
-        <v>1312.556023175568</v>
+        <v>1312.561879568695</v>
       </c>
       <c r="F117" t="n">
         <v>4171</v>
@@ -14490,16 +14490,16 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1303.080256468803</v>
+        <v>1303.117121515517</v>
       </c>
       <c r="D118" t="n">
-        <v>1298.530132923503</v>
+        <v>1298.566530601817</v>
       </c>
       <c r="E118" t="n">
-        <v>1307.630380014103</v>
+        <v>1307.667712429218</v>
       </c>
       <c r="F118" t="n">
-        <v>32556</v>
+        <v>32551</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -14641,13 +14641,13 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1302.858096991783</v>
+        <v>1302.849153314428</v>
       </c>
       <c r="D119" t="n">
-        <v>1298.769563628147</v>
+        <v>1298.760641517745</v>
       </c>
       <c r="E119" t="n">
-        <v>1306.946630355419</v>
+        <v>1306.93766511111</v>
       </c>
       <c r="F119" t="n">
         <v>39406</v>
@@ -14792,13 +14792,13 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1298.743514000223</v>
+        <v>1298.730329929532</v>
       </c>
       <c r="D120" t="n">
-        <v>1290.98028822052</v>
+        <v>1290.967383909811</v>
       </c>
       <c r="E120" t="n">
-        <v>1306.506739779927</v>
+        <v>1306.493275949254</v>
       </c>
       <c r="F120" t="n">
         <v>7140</v>
@@ -14943,13 +14943,13 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1293.321654520926</v>
+        <v>1293.318741333559</v>
       </c>
       <c r="D121" t="n">
-        <v>1289.57322392304</v>
+        <v>1289.570414415427</v>
       </c>
       <c r="E121" t="n">
-        <v>1297.070085118811</v>
+        <v>1297.06706825169</v>
       </c>
       <c r="F121" t="n">
         <v>55240</v>
@@ -15090,36 +15090,36 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>gemma-2-27b-it</t>
+          <t>granite-4.2-3b</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1289.44579585212</v>
+        <v>1289.522494910676</v>
       </c>
       <c r="D122" t="n">
-        <v>1286.048454251964</v>
+        <v>1277.91627908977</v>
       </c>
       <c r="E122" t="n">
-        <v>1292.843137452277</v>
+        <v>1301.128710731582</v>
       </c>
       <c r="F122" t="n">
-        <v>75754</v>
+        <v>3247</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Gemma license</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="J122" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
@@ -15132,22 +15132,22 @@
         </is>
       </c>
       <c r="M122" t="n">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="N122" t="n">
-        <v>67.5</v>
+        <v>7.5</v>
       </c>
       <c r="O122" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="P122" t="n">
-        <v>33.8</v>
+        <v>3.8</v>
       </c>
       <c r="Q122" t="n">
-        <v>13.5</v>
+        <v>1.5</v>
       </c>
       <c r="R122" t="n">
-        <v>16.9</v>
+        <v>1.9</v>
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
@@ -15241,64 +15241,148 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>jamba-1.5-large</t>
+          <t>gemma-2-27b-it</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1289.433482059348</v>
+        <v>1289.42769713196</v>
       </c>
       <c r="D123" t="n">
-        <v>1282.127621895249</v>
+        <v>1286.0303729711</v>
       </c>
       <c r="E123" t="n">
-        <v>1296.739342223447</v>
+        <v>1292.82502129282</v>
       </c>
       <c r="F123" t="n">
-        <v>8662</v>
-      </c>
-      <c r="G123" t="inlineStr"/>
+        <v>75754</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Jamba Open</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
+          <t>Gemma license</t>
+        </is>
+      </c>
+      <c r="I123" t="n">
+        <v>27</v>
+      </c>
+      <c r="J123" t="n">
+        <v>27</v>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>dense</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
-      <c r="O123" t="inlineStr"/>
-      <c r="P123" t="inlineStr"/>
-      <c r="Q123" t="inlineStr"/>
-      <c r="R123" t="inlineStr"/>
-      <c r="S123" t="inlineStr"/>
-      <c r="T123" t="inlineStr"/>
-      <c r="U123" t="inlineStr"/>
-      <c r="V123" t="inlineStr"/>
-      <c r="W123" t="inlineStr"/>
-      <c r="X123" t="inlineStr"/>
-      <c r="Y123" t="inlineStr"/>
-      <c r="Z123" t="inlineStr"/>
-      <c r="AA123" t="inlineStr"/>
-      <c r="AB123" t="inlineStr"/>
-      <c r="AC123" t="inlineStr"/>
-      <c r="AD123" t="inlineStr"/>
-      <c r="AE123" t="inlineStr"/>
-      <c r="AF123" t="inlineStr"/>
-      <c r="AG123" t="inlineStr"/>
+          <t>name_parsing</t>
+        </is>
+      </c>
+      <c r="M123" t="n">
+        <v>54</v>
+      </c>
+      <c r="N123" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="O123" t="n">
+        <v>27</v>
+      </c>
+      <c r="P123" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="R123" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="S123" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T123" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U123" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V123" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W123" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X123" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y123" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z123" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA123" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB123" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC123" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD123" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE123" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF123" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG123" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH123" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -15308,148 +15392,64 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>granite-4.2-3b</t>
+          <t>jamba-1.5-large</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1289.195559251609</v>
+        <v>1289.424524238361</v>
       </c>
       <c r="D124" t="n">
-        <v>1277.614050752003</v>
+        <v>1282.118979207166</v>
       </c>
       <c r="E124" t="n">
-        <v>1300.777067751214</v>
+        <v>1296.730069269556</v>
       </c>
       <c r="F124" t="n">
-        <v>3266</v>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>IBM</t>
-        </is>
-      </c>
+        <v>8662</v>
+      </c>
+      <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
-        </is>
-      </c>
-      <c r="I124" t="n">
-        <v>3</v>
-      </c>
-      <c r="J124" t="n">
-        <v>3</v>
-      </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>dense</t>
-        </is>
-      </c>
+          <t>Jamba Open</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr">
         <is>
-          <t>name_parsing</t>
-        </is>
-      </c>
-      <c r="M124" t="n">
-        <v>6</v>
-      </c>
-      <c r="N124" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O124" t="n">
-        <v>3</v>
-      </c>
-      <c r="P124" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Q124" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R124" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="S124" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T124" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U124" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V124" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W124" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X124" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y124" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z124" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA124" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB124" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC124" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD124" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE124" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF124" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG124" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr"/>
+      <c r="P124" t="inlineStr"/>
+      <c r="Q124" t="inlineStr"/>
+      <c r="R124" t="inlineStr"/>
+      <c r="S124" t="inlineStr"/>
+      <c r="T124" t="inlineStr"/>
+      <c r="U124" t="inlineStr"/>
+      <c r="V124" t="inlineStr"/>
+      <c r="W124" t="inlineStr"/>
+      <c r="X124" t="inlineStr"/>
+      <c r="Y124" t="inlineStr"/>
+      <c r="Z124" t="inlineStr"/>
+      <c r="AA124" t="inlineStr"/>
+      <c r="AB124" t="inlineStr"/>
+      <c r="AC124" t="inlineStr"/>
+      <c r="AD124" t="inlineStr"/>
+      <c r="AE124" t="inlineStr"/>
+      <c r="AF124" t="inlineStr"/>
+      <c r="AG124" t="inlineStr"/>
       <c r="AH124" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -15463,16 +15463,16 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1287.618860268671</v>
+        <v>1288.13289356819</v>
       </c>
       <c r="D125" t="n">
-        <v>1276.45584953181</v>
+        <v>1276.941956890217</v>
       </c>
       <c r="E125" t="n">
-        <v>1298.781871005531</v>
+        <v>1299.323830246162</v>
       </c>
       <c r="F125" t="n">
-        <v>3255</v>
+        <v>3237</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -15614,16 +15614,16 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1286.768820098388</v>
+        <v>1286.958823775603</v>
       </c>
       <c r="D126" t="n">
-        <v>1278.320532266788</v>
+        <v>1278.504912017922</v>
       </c>
       <c r="E126" t="n">
-        <v>1295.217107929989</v>
+        <v>1295.412735533285</v>
       </c>
       <c r="F126" t="n">
-        <v>5581</v>
+        <v>5576</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -15765,13 +15765,13 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1286.552312852134</v>
+        <v>1286.562353098289</v>
       </c>
       <c r="D127" t="n">
-        <v>1276.58571255348</v>
+        <v>1276.596220804974</v>
       </c>
       <c r="E127" t="n">
-        <v>1296.518913150787</v>
+        <v>1296.528485391603</v>
       </c>
       <c r="F127" t="n">
         <v>3749</v>
@@ -15916,13 +15916,13 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1286.465300433618</v>
+        <v>1286.448609685453</v>
       </c>
       <c r="D128" t="n">
-        <v>1279.190416432475</v>
+        <v>1279.173157834842</v>
       </c>
       <c r="E128" t="n">
-        <v>1293.740184434761</v>
+        <v>1293.724061536063</v>
       </c>
       <c r="F128" t="n">
         <v>8278</v>
@@ -16067,13 +16067,13 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1286.055811882577</v>
+        <v>1286.063810555537</v>
       </c>
       <c r="D129" t="n">
-        <v>1275.596397752076</v>
+        <v>1275.604880944859</v>
       </c>
       <c r="E129" t="n">
-        <v>1296.515226013077</v>
+        <v>1296.522740166215</v>
       </c>
       <c r="F129" t="n">
         <v>2846</v>
@@ -16218,13 +16218,13 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1280.367998734232</v>
+        <v>1280.346252379516</v>
       </c>
       <c r="D130" t="n">
-        <v>1273.509941818239</v>
+        <v>1273.48851888011</v>
       </c>
       <c r="E130" t="n">
-        <v>1287.226055650224</v>
+        <v>1287.203985878922</v>
       </c>
       <c r="F130" t="n">
         <v>10072</v>
@@ -16365,13 +16365,13 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1277.075573481362</v>
+        <v>1277.098749058932</v>
       </c>
       <c r="D131" t="n">
-        <v>1271.756008526501</v>
+        <v>1271.779651472364</v>
       </c>
       <c r="E131" t="n">
-        <v>1282.395138436223</v>
+        <v>1282.4178466455</v>
       </c>
       <c r="F131" t="n">
         <v>19659</v>
@@ -16516,13 +16516,13 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1276.498614867255</v>
+        <v>1276.504938680578</v>
       </c>
       <c r="D132" t="n">
-        <v>1272.911616348642</v>
+        <v>1272.918330680802</v>
       </c>
       <c r="E132" t="n">
-        <v>1280.085613385869</v>
+        <v>1280.091546680354</v>
       </c>
       <c r="F132" t="n">
         <v>156876</v>
@@ -16667,13 +16667,13 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1276.241659655763</v>
+        <v>1276.258892122072</v>
       </c>
       <c r="D133" t="n">
-        <v>1269.662513617844</v>
+        <v>1269.680021839597</v>
       </c>
       <c r="E133" t="n">
-        <v>1282.820805693682</v>
+        <v>1282.837762404546</v>
       </c>
       <c r="F133" t="n">
         <v>9866</v>
@@ -16818,13 +16818,13 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1274.376357995334</v>
+        <v>1274.374365475218</v>
       </c>
       <c r="D134" t="n">
-        <v>1268.455054055693</v>
+        <v>1268.453034976254</v>
       </c>
       <c r="E134" t="n">
-        <v>1280.297661934974</v>
+        <v>1280.295695974181</v>
       </c>
       <c r="F134" t="n">
         <v>14681</v>
@@ -16969,13 +16969,13 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1270.582770050619</v>
+        <v>1270.580978224246</v>
       </c>
       <c r="D135" t="n">
-        <v>1262.453592537177</v>
+        <v>1262.452082534718</v>
       </c>
       <c r="E135" t="n">
-        <v>1278.711947564061</v>
+        <v>1278.709873913773</v>
       </c>
       <c r="F135" t="n">
         <v>5432</v>
@@ -17120,13 +17120,13 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1267.208966085903</v>
+        <v>1267.208553138808</v>
       </c>
       <c r="D136" t="n">
-        <v>1262.308473492927</v>
+        <v>1262.308098316373</v>
       </c>
       <c r="E136" t="n">
-        <v>1272.109458678879</v>
+        <v>1272.109007961243</v>
       </c>
       <c r="F136" t="n">
         <v>27124</v>
@@ -17271,13 +17271,13 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1266.974374429908</v>
+        <v>1266.955393426152</v>
       </c>
       <c r="D137" t="n">
-        <v>1263.141950885822</v>
+        <v>1263.123001180984</v>
       </c>
       <c r="E137" t="n">
-        <v>1270.806797973994</v>
+        <v>1270.78778567132</v>
       </c>
       <c r="F137" t="n">
         <v>54611</v>
@@ -17422,13 +17422,13 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1265.328158708027</v>
+        <v>1265.32338831685</v>
       </c>
       <c r="D138" t="n">
-        <v>1259.053843776338</v>
+        <v>1259.049503047833</v>
       </c>
       <c r="E138" t="n">
-        <v>1271.602473639715</v>
+        <v>1271.597273585868</v>
       </c>
       <c r="F138" t="n">
         <v>15147</v>
@@ -17443,123 +17443,43 @@
           <t>DeepSeek License</t>
         </is>
       </c>
-      <c r="I138" t="n">
-        <v>236</v>
-      </c>
-      <c r="J138" t="n">
-        <v>21</v>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr">
         <is>
-          <t>aa_single_scrape</t>
-        </is>
-      </c>
-      <c r="M138" t="n">
-        <v>472</v>
-      </c>
-      <c r="N138" t="n">
-        <v>590</v>
-      </c>
-      <c r="O138" t="n">
-        <v>236</v>
-      </c>
-      <c r="P138" t="n">
-        <v>295</v>
-      </c>
-      <c r="Q138" t="n">
-        <v>118</v>
-      </c>
-      <c r="R138" t="n">
-        <v>147.5</v>
-      </c>
-      <c r="S138" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T138" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U138" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V138" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W138" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X138" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y138" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z138" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA138" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB138" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC138" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD138" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE138" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF138" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG138" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
+      <c r="O138" t="inlineStr"/>
+      <c r="P138" t="inlineStr"/>
+      <c r="Q138" t="inlineStr"/>
+      <c r="R138" t="inlineStr"/>
+      <c r="S138" t="inlineStr"/>
+      <c r="T138" t="inlineStr"/>
+      <c r="U138" t="inlineStr"/>
+      <c r="V138" t="inlineStr"/>
+      <c r="W138" t="inlineStr"/>
+      <c r="X138" t="inlineStr"/>
+      <c r="Y138" t="inlineStr"/>
+      <c r="Z138" t="inlineStr"/>
+      <c r="AA138" t="inlineStr"/>
+      <c r="AB138" t="inlineStr"/>
+      <c r="AC138" t="inlineStr"/>
+      <c r="AD138" t="inlineStr"/>
+      <c r="AE138" t="inlineStr"/>
+      <c r="AF138" t="inlineStr"/>
+      <c r="AG138" t="inlineStr"/>
       <c r="AH138" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -17573,13 +17493,13 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1261.76488088378</v>
+        <v>1261.778422810805</v>
       </c>
       <c r="D139" t="n">
-        <v>1256.816386948708</v>
+        <v>1256.830252051908</v>
       </c>
       <c r="E139" t="n">
-        <v>1266.713374818851</v>
+        <v>1266.726593569702</v>
       </c>
       <c r="F139" t="n">
         <v>37325</v>
@@ -17724,13 +17644,13 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1261.702582446025</v>
+        <v>1261.725252525771</v>
       </c>
       <c r="D140" t="n">
-        <v>1257.383814774923</v>
+        <v>1257.406965785593</v>
       </c>
       <c r="E140" t="n">
-        <v>1266.021350117127</v>
+        <v>1266.043539265949</v>
       </c>
       <c r="F140" t="n">
         <v>77554</v>
@@ -17795,13 +17715,13 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>1256.27072894919</v>
+        <v>1256.271010215897</v>
       </c>
       <c r="D141" t="n">
-        <v>1251.660164590519</v>
+        <v>1251.660350322239</v>
       </c>
       <c r="E141" t="n">
-        <v>1260.881293307861</v>
+        <v>1260.881670109555</v>
       </c>
       <c r="F141" t="n">
         <v>24126</v>
@@ -17946,13 +17866,13 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1251.63397879215</v>
+        <v>1251.646552959719</v>
       </c>
       <c r="D142" t="n">
-        <v>1240.85711829353</v>
+        <v>1240.870054185521</v>
       </c>
       <c r="E142" t="n">
-        <v>1262.410839290771</v>
+        <v>1262.423051733917</v>
       </c>
       <c r="F142" t="n">
         <v>3334</v>
@@ -18097,13 +18017,13 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>1250.355273553091</v>
+        <v>1250.371488195612</v>
       </c>
       <c r="D143" t="n">
-        <v>1243.751406986555</v>
+        <v>1243.767945729197</v>
       </c>
       <c r="E143" t="n">
-        <v>1256.959140119627</v>
+        <v>1256.975030662026</v>
       </c>
       <c r="F143" t="n">
         <v>10140</v>
@@ -18248,13 +18168,13 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>1239.750878820273</v>
+        <v>1239.74189556354</v>
       </c>
       <c r="D144" t="n">
-        <v>1232.524626953554</v>
+        <v>1232.516016144089</v>
       </c>
       <c r="E144" t="n">
-        <v>1246.977130686992</v>
+        <v>1246.967774982991</v>
       </c>
       <c r="F144" t="n">
         <v>8858</v>
@@ -18315,13 +18235,13 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1237.582301029211</v>
+        <v>1237.576477314295</v>
       </c>
       <c r="D145" t="n">
-        <v>1228.493514450835</v>
+        <v>1228.488150784239</v>
       </c>
       <c r="E145" t="n">
-        <v>1246.671087607587</v>
+        <v>1246.664803844352</v>
       </c>
       <c r="F145" t="n">
         <v>4781</v>
@@ -18466,13 +18386,13 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>1234.128338182251</v>
+        <v>1234.138241456109</v>
       </c>
       <c r="D146" t="n">
-        <v>1228.581819001509</v>
+        <v>1228.592238253344</v>
       </c>
       <c r="E146" t="n">
-        <v>1239.674857362992</v>
+        <v>1239.684244658874</v>
       </c>
       <c r="F146" t="n">
         <v>26195</v>
@@ -18617,13 +18537,13 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>1233.461069345032</v>
+        <v>1233.476897940968</v>
       </c>
       <c r="D147" t="n">
-        <v>1228.19397954118</v>
+        <v>1228.210370908478</v>
       </c>
       <c r="E147" t="n">
-        <v>1238.728159148884</v>
+        <v>1238.743424973458</v>
       </c>
       <c r="F147" t="n">
         <v>39302</v>
@@ -18768,13 +18688,13 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1229.517994684658</v>
+        <v>1229.538174750901</v>
       </c>
       <c r="D148" t="n">
-        <v>1224.96296587704</v>
+        <v>1224.983526550104</v>
       </c>
       <c r="E148" t="n">
-        <v>1234.073023492276</v>
+        <v>1234.092822951697</v>
       </c>
       <c r="F148" t="n">
         <v>51416</v>
@@ -18919,13 +18839,13 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1226.802948578299</v>
+        <v>1226.825645809424</v>
       </c>
       <c r="D149" t="n">
-        <v>1222.026040323814</v>
+        <v>1222.0492324151</v>
       </c>
       <c r="E149" t="n">
-        <v>1231.579856832783</v>
+        <v>1231.602059203747</v>
       </c>
       <c r="F149" t="n">
         <v>54036</v>
@@ -18990,13 +18910,13 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1223.564718458742</v>
+        <v>1223.575225024568</v>
       </c>
       <c r="D150" t="n">
-        <v>1219.827495339113</v>
+        <v>1219.838408276077</v>
       </c>
       <c r="E150" t="n">
-        <v>1227.301941578372</v>
+        <v>1227.312041773058</v>
       </c>
       <c r="F150" t="n">
         <v>104642</v>
@@ -19141,13 +19061,13 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1223.025510252321</v>
+        <v>1223.025260026554</v>
       </c>
       <c r="D151" t="n">
-        <v>1216.044746985433</v>
+        <v>1216.044626283644</v>
       </c>
       <c r="E151" t="n">
-        <v>1230.006273519208</v>
+        <v>1230.005893769464</v>
       </c>
       <c r="F151" t="n">
         <v>9818</v>
@@ -19292,13 +19212,13 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1220.464907149936</v>
+        <v>1220.469396268749</v>
       </c>
       <c r="D152" t="n">
-        <v>1209.792843206129</v>
+        <v>1209.797820389999</v>
       </c>
       <c r="E152" t="n">
-        <v>1231.136971093744</v>
+        <v>1231.140972147499</v>
       </c>
       <c r="F152" t="n">
         <v>2896</v>
@@ -19443,13 +19363,13 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>1212.941462953383</v>
+        <v>1212.962533775487</v>
       </c>
       <c r="D153" t="n">
-        <v>1202.166935704659</v>
+        <v>1202.188842078536</v>
       </c>
       <c r="E153" t="n">
-        <v>1223.715990202107</v>
+        <v>1223.736225472439</v>
       </c>
       <c r="F153" t="n">
         <v>4652</v>
@@ -19590,13 +19510,13 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1212.794617405299</v>
+        <v>1212.813106078924</v>
       </c>
       <c r="D154" t="n">
-        <v>1207.759691764107</v>
+        <v>1207.778638534456</v>
       </c>
       <c r="E154" t="n">
-        <v>1217.82954304649</v>
+        <v>1217.847573623392</v>
       </c>
       <c r="F154" t="n">
         <v>24146</v>
@@ -19737,13 +19657,13 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>1211.22625176179</v>
+        <v>1211.22008775016</v>
       </c>
       <c r="D155" t="n">
-        <v>1207.063811581746</v>
+        <v>1207.057773898704</v>
       </c>
       <c r="E155" t="n">
-        <v>1215.388691941834</v>
+        <v>1215.382401601615</v>
       </c>
       <c r="F155" t="n">
         <v>49605</v>
@@ -19888,13 +19808,13 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1208.436152876716</v>
+        <v>1208.456303687424</v>
       </c>
       <c r="D156" t="n">
-        <v>1197.343158490181</v>
+        <v>1197.364024590518</v>
       </c>
       <c r="E156" t="n">
-        <v>1219.529147263251</v>
+        <v>1219.54858278433</v>
       </c>
       <c r="F156" t="n">
         <v>3090</v>
@@ -20039,13 +19959,13 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1203.918817582605</v>
+        <v>1203.939515486712</v>
       </c>
       <c r="D157" t="n">
-        <v>1197.808545003663</v>
+        <v>1197.829761541376</v>
       </c>
       <c r="E157" t="n">
-        <v>1210.029090161547</v>
+        <v>1210.049269432047</v>
       </c>
       <c r="F157" t="n">
         <v>21741</v>
@@ -20190,13 +20110,13 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1200.065722025012</v>
+        <v>1200.047156476676</v>
       </c>
       <c r="D158" t="n">
-        <v>1195.959613882201</v>
+        <v>1195.94111196782</v>
       </c>
       <c r="E158" t="n">
-        <v>1204.171830167824</v>
+        <v>1204.153200985533</v>
       </c>
       <c r="F158" t="n">
         <v>46616</v>
@@ -20341,13 +20261,13 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>1197.834356247969</v>
+        <v>1197.856884713367</v>
       </c>
       <c r="D159" t="n">
-        <v>1192.674910214171</v>
+        <v>1192.697788916538</v>
       </c>
       <c r="E159" t="n">
-        <v>1202.993802281768</v>
+        <v>1203.015980510196</v>
       </c>
       <c r="F159" t="n">
         <v>25055</v>
@@ -20492,13 +20412,13 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1197.089928453988</v>
+        <v>1197.112658911012</v>
       </c>
       <c r="D160" t="n">
-        <v>1192.829432957213</v>
+        <v>1192.852708312139</v>
       </c>
       <c r="E160" t="n">
-        <v>1201.350423950764</v>
+        <v>1201.372609509886</v>
       </c>
       <c r="F160" t="n">
         <v>73503</v>
@@ -20643,13 +20563,13 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1195.44974080998</v>
+        <v>1195.465199280357</v>
       </c>
       <c r="D161" t="n">
-        <v>1189.34354503825</v>
+        <v>1189.359529124976</v>
       </c>
       <c r="E161" t="n">
-        <v>1201.555936581709</v>
+        <v>1201.570869435737</v>
       </c>
       <c r="F161" t="n">
         <v>32191</v>
@@ -20710,13 +20630,13 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1191.008284159787</v>
+        <v>1191.027429550588</v>
       </c>
       <c r="D162" t="n">
-        <v>1183.900731492628</v>
+        <v>1183.920488201132</v>
       </c>
       <c r="E162" t="n">
-        <v>1198.115836826946</v>
+        <v>1198.134370900044</v>
       </c>
       <c r="F162" t="n">
         <v>17839</v>
@@ -20861,13 +20781,13 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1190.706260891543</v>
+        <v>1190.721355126224</v>
       </c>
       <c r="D163" t="n">
-        <v>1183.522143371488</v>
+        <v>1183.537608739013</v>
       </c>
       <c r="E163" t="n">
-        <v>1197.890378411597</v>
+        <v>1197.905101513435</v>
       </c>
       <c r="F163" t="n">
         <v>9901</v>
@@ -21008,13 +20928,13 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>1184.864849036392</v>
+        <v>1184.880406235636</v>
       </c>
       <c r="D164" t="n">
-        <v>1173.402176695087</v>
+        <v>1173.418627259525</v>
       </c>
       <c r="E164" t="n">
-        <v>1196.327521377697</v>
+        <v>1196.342185211747</v>
       </c>
       <c r="F164" t="n">
         <v>4932</v>
@@ -21159,13 +21079,13 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>1184.662346344112</v>
+        <v>1184.68670013018</v>
       </c>
       <c r="D165" t="n">
-        <v>1175.242574862465</v>
+        <v>1175.267773464436</v>
       </c>
       <c r="E165" t="n">
-        <v>1194.082117825759</v>
+        <v>1194.105626795924</v>
       </c>
       <c r="F165" t="n">
         <v>8214</v>
@@ -21310,13 +21230,13 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1183.674983481226</v>
+        <v>1183.691474266126</v>
       </c>
       <c r="D166" t="n">
-        <v>1176.856685198581</v>
+        <v>1176.873766242435</v>
       </c>
       <c r="E166" t="n">
-        <v>1190.49328176387</v>
+        <v>1190.509182289817</v>
       </c>
       <c r="F166" t="n">
         <v>15483</v>
@@ -21457,13 +21377,13 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>1183.062099151682</v>
+        <v>1183.069719751941</v>
       </c>
       <c r="D167" t="n">
-        <v>1174.388763734478</v>
+        <v>1174.397000416579</v>
       </c>
       <c r="E167" t="n">
-        <v>1191.735434568885</v>
+        <v>1191.742439087303</v>
       </c>
       <c r="F167" t="n">
         <v>6638</v>
@@ -21608,13 +21528,13 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>1182.968104847911</v>
+        <v>1182.980710011684</v>
       </c>
       <c r="D168" t="n">
-        <v>1173.326470826978</v>
+        <v>1173.339909064116</v>
       </c>
       <c r="E168" t="n">
-        <v>1192.609738868845</v>
+        <v>1192.621510959252</v>
       </c>
       <c r="F168" t="n">
         <v>7968</v>
@@ -21675,13 +21595,13 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1182.662665851587</v>
+        <v>1182.681365645242</v>
       </c>
       <c r="D169" t="n">
-        <v>1174.681250621774</v>
+        <v>1174.700636894622</v>
       </c>
       <c r="E169" t="n">
-        <v>1190.644081081399</v>
+        <v>1190.662094395861</v>
       </c>
       <c r="F169" t="n">
         <v>12637</v>
@@ -21742,13 +21662,13 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>1182.531473340811</v>
+        <v>1182.506489579367</v>
       </c>
       <c r="D170" t="n">
-        <v>1176.466802355689</v>
+        <v>1176.442312457066</v>
       </c>
       <c r="E170" t="n">
-        <v>1188.596144325934</v>
+        <v>1188.570666701668</v>
       </c>
       <c r="F170" t="n">
         <v>23893</v>
@@ -21893,13 +21813,13 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1179.969810577241</v>
+        <v>1179.986795039114</v>
       </c>
       <c r="D171" t="n">
-        <v>1174.065831559653</v>
+        <v>1174.083340123296</v>
       </c>
       <c r="E171" t="n">
-        <v>1185.873789594829</v>
+        <v>1185.890249954931</v>
       </c>
       <c r="F171" t="n">
         <v>32832</v>
@@ -21960,13 +21880,13 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1178.792091409978</v>
+        <v>1178.8131472179</v>
       </c>
       <c r="D172" t="n">
-        <v>1167.611564467324</v>
+        <v>1167.633295799144</v>
       </c>
       <c r="E172" t="n">
-        <v>1189.972618352631</v>
+        <v>1189.992998636657</v>
       </c>
       <c r="F172" t="n">
         <v>3188</v>
@@ -22111,13 +22031,13 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>1177.587637589965</v>
+        <v>1177.616089329854</v>
       </c>
       <c r="D173" t="n">
-        <v>1167.797933627503</v>
+        <v>1167.827185338387</v>
       </c>
       <c r="E173" t="n">
-        <v>1187.377341552427</v>
+        <v>1187.404993321322</v>
       </c>
       <c r="F173" t="n">
         <v>6535</v>
@@ -22258,13 +22178,13 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>1175.87496596959</v>
+        <v>1175.889883914665</v>
       </c>
       <c r="D174" t="n">
-        <v>1165.48827601419</v>
+        <v>1165.504076333083</v>
       </c>
       <c r="E174" t="n">
-        <v>1186.261655924992</v>
+        <v>1186.275691496247</v>
       </c>
       <c r="F174" t="n">
         <v>5006</v>
@@ -22405,13 +22325,13 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>1172.844659584705</v>
+        <v>1172.86857167191</v>
       </c>
       <c r="D175" t="n">
-        <v>1166.658565087027</v>
+        <v>1166.683196577572</v>
       </c>
       <c r="E175" t="n">
-        <v>1179.030754082383</v>
+        <v>1179.053946766248</v>
       </c>
       <c r="F175" t="n">
         <v>22479</v>
@@ -22552,13 +22472,13 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>1171.007811226852</v>
+        <v>1171.027454330182</v>
       </c>
       <c r="D176" t="n">
-        <v>1165.097445181217</v>
+        <v>1165.117583283203</v>
       </c>
       <c r="E176" t="n">
-        <v>1176.918177272487</v>
+        <v>1176.937325377161</v>
       </c>
       <c r="F176" t="n">
         <v>17766</v>
@@ -22703,13 +22623,13 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>1170.860716945817</v>
+        <v>1170.90272013249</v>
       </c>
       <c r="D177" t="n">
-        <v>1163.467115001569</v>
+        <v>1163.509728074749</v>
       </c>
       <c r="E177" t="n">
-        <v>1178.254318890064</v>
+        <v>1178.295712190231</v>
       </c>
       <c r="F177" t="n">
         <v>16056</v>
@@ -22850,13 +22770,13 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>1170.546413377787</v>
+        <v>1170.575772318886</v>
       </c>
       <c r="D178" t="n">
-        <v>1165.061406344309</v>
+        <v>1165.09145151071</v>
       </c>
       <c r="E178" t="n">
-        <v>1176.031420411265</v>
+        <v>1176.060093127061</v>
       </c>
       <c r="F178" t="n">
         <v>38492</v>
@@ -23001,13 +22921,13 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>1167.324666474387</v>
+        <v>1167.352296747548</v>
       </c>
       <c r="D179" t="n">
-        <v>1159.273885590321</v>
+        <v>1159.302262497047</v>
       </c>
       <c r="E179" t="n">
-        <v>1175.375447358454</v>
+        <v>1175.40233099805</v>
       </c>
       <c r="F179" t="n">
         <v>10224</v>
@@ -23148,13 +23068,13 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>1166.729530784196</v>
+        <v>1166.739192878171</v>
       </c>
       <c r="D180" t="n">
-        <v>1159.026218385671</v>
+        <v>1159.036410776665</v>
       </c>
       <c r="E180" t="n">
-        <v>1174.43284318272</v>
+        <v>1174.441974979677</v>
       </c>
       <c r="F180" t="n">
         <v>7936</v>
@@ -23299,13 +23219,13 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>1164.315549620803</v>
+        <v>1164.343898882683</v>
       </c>
       <c r="D181" t="n">
-        <v>1152.424367152545</v>
+        <v>1152.45367839703</v>
       </c>
       <c r="E181" t="n">
-        <v>1176.206732089061</v>
+        <v>1176.234119368336</v>
       </c>
       <c r="F181" t="n">
         <v>3777</v>
@@ -23446,13 +23366,13 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>1156.577535814665</v>
+        <v>1156.591925945045</v>
       </c>
       <c r="D182" t="n">
-        <v>1148.196145746999</v>
+        <v>1148.211187273183</v>
       </c>
       <c r="E182" t="n">
-        <v>1164.958925882331</v>
+        <v>1164.972664616907</v>
       </c>
       <c r="F182" t="n">
         <v>6837</v>
@@ -23597,13 +23517,13 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>1154.6424766466</v>
+        <v>1154.66888494322</v>
       </c>
       <c r="D183" t="n">
-        <v>1142.069188459458</v>
+        <v>1142.09661067051</v>
       </c>
       <c r="E183" t="n">
-        <v>1167.215764833741</v>
+        <v>1167.241159215931</v>
       </c>
       <c r="F183" t="n">
         <v>3585</v>
@@ -23748,13 +23668,13 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>1154.184400362589</v>
+        <v>1154.223974073882</v>
       </c>
       <c r="D184" t="n">
-        <v>1142.706854093555</v>
+        <v>1142.747279796642</v>
       </c>
       <c r="E184" t="n">
-        <v>1165.661946631623</v>
+        <v>1165.700668351122</v>
       </c>
       <c r="F184" t="n">
         <v>3231</v>
@@ -23899,13 +23819,13 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>1152.352654720046</v>
+        <v>1152.374413805153</v>
       </c>
       <c r="D185" t="n">
-        <v>1139.216068681143</v>
+        <v>1139.239088280219</v>
       </c>
       <c r="E185" t="n">
-        <v>1165.489240758948</v>
+        <v>1165.509739330087</v>
       </c>
       <c r="F185" t="n">
         <v>4155</v>
@@ -24046,13 +23966,13 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>1152.194534223784</v>
+        <v>1152.215364672984</v>
       </c>
       <c r="D186" t="n">
-        <v>1136.912280528981</v>
+        <v>1136.93476536675</v>
       </c>
       <c r="E186" t="n">
-        <v>1167.476787918587</v>
+        <v>1167.495963979219</v>
       </c>
       <c r="F186" t="n">
         <v>1679</v>
@@ -24193,13 +24113,13 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>1150.675571858312</v>
+        <v>1150.69141916909</v>
       </c>
       <c r="D187" t="n">
-        <v>1138.466624156734</v>
+        <v>1138.483965051335</v>
       </c>
       <c r="E187" t="n">
-        <v>1162.884519559889</v>
+        <v>1162.898873286845</v>
       </c>
       <c r="F187" t="n">
         <v>2572</v>
@@ -24340,13 +24260,13 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>1149.442515749466</v>
+        <v>1149.463519500801</v>
       </c>
       <c r="D188" t="n">
-        <v>1140.245823359795</v>
+        <v>1140.267885628591</v>
       </c>
       <c r="E188" t="n">
-        <v>1158.639208139137</v>
+        <v>1158.659153373012</v>
       </c>
       <c r="F188" t="n">
         <v>7044</v>
@@ -24491,13 +24411,13 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>1149.311373265291</v>
+        <v>1149.337974797416</v>
       </c>
       <c r="D189" t="n">
-        <v>1142.670453943912</v>
+        <v>1142.697651044436</v>
       </c>
       <c r="E189" t="n">
-        <v>1155.952292586671</v>
+        <v>1155.978298550396</v>
       </c>
       <c r="F189" t="n">
         <v>19402</v>
@@ -24642,13 +24562,13 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>1148.04887111106</v>
+        <v>1148.057274130852</v>
       </c>
       <c r="D190" t="n">
-        <v>1131.038565206457</v>
+        <v>1131.048776234416</v>
       </c>
       <c r="E190" t="n">
-        <v>1165.059177015663</v>
+        <v>1165.065772027288</v>
       </c>
       <c r="F190" t="n">
         <v>1295</v>
@@ -24789,13 +24709,13 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>1143.766258408719</v>
+        <v>1143.788350888521</v>
       </c>
       <c r="D191" t="n">
-        <v>1133.891478578556</v>
+        <v>1133.914318789691</v>
       </c>
       <c r="E191" t="n">
-        <v>1153.641038238881</v>
+        <v>1153.66238298735</v>
       </c>
       <c r="F191" t="n">
         <v>4737</v>
@@ -24940,13 +24860,13 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>1143.052638541754</v>
+        <v>1143.070897709739</v>
       </c>
       <c r="D192" t="n">
-        <v>1136.615455246039</v>
+        <v>1136.634150869725</v>
       </c>
       <c r="E192" t="n">
-        <v>1149.489821837469</v>
+        <v>1149.507644549753</v>
       </c>
       <c r="F192" t="n">
         <v>12297</v>
@@ -25091,13 +25011,13 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>1141.491946414473</v>
+        <v>1141.506128128061</v>
       </c>
       <c r="D193" t="n">
-        <v>1134.810642372896</v>
+        <v>1134.825651166476</v>
       </c>
       <c r="E193" t="n">
-        <v>1148.173250456051</v>
+        <v>1148.186605089647</v>
       </c>
       <c r="F193" t="n">
         <v>19367</v>
@@ -25238,13 +25158,13 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>1141.326060298105</v>
+        <v>1141.354649909911</v>
       </c>
       <c r="D194" t="n">
-        <v>1134.614320625994</v>
+        <v>1134.643546413257</v>
       </c>
       <c r="E194" t="n">
-        <v>1148.037799970215</v>
+        <v>1148.065753406565</v>
       </c>
       <c r="F194" t="n">
         <v>19174</v>
@@ -25389,13 +25309,13 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>1139.286841383948</v>
+        <v>1139.297579686782</v>
       </c>
       <c r="D195" t="n">
-        <v>1128.366302421678</v>
+        <v>1128.378015978792</v>
       </c>
       <c r="E195" t="n">
-        <v>1150.207380346217</v>
+        <v>1150.217143394772</v>
       </c>
       <c r="F195" t="n">
         <v>4964</v>
@@ -25540,13 +25460,13 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>1137.685762950222</v>
+        <v>1137.668034791777</v>
       </c>
       <c r="D196" t="n">
-        <v>1128.216257664946</v>
+        <v>1128.199278461151</v>
       </c>
       <c r="E196" t="n">
-        <v>1147.155268235498</v>
+        <v>1147.136791122404</v>
       </c>
       <c r="F196" t="n">
         <v>8925</v>
@@ -25691,13 +25611,13 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>1136.775357677685</v>
+        <v>1136.797718774997</v>
       </c>
       <c r="D197" t="n">
-        <v>1127.903066255798</v>
+        <v>1127.926265117463</v>
       </c>
       <c r="E197" t="n">
-        <v>1145.647649099572</v>
+        <v>1145.669172432531</v>
       </c>
       <c r="F197" t="n">
         <v>7366</v>
@@ -25842,13 +25762,13 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>1130.728898204252</v>
+        <v>1130.755746927028</v>
       </c>
       <c r="D198" t="n">
-        <v>1121.918221258459</v>
+        <v>1121.945954202173</v>
       </c>
       <c r="E198" t="n">
-        <v>1139.539575150045</v>
+        <v>1139.565539651884</v>
       </c>
       <c r="F198" t="n">
         <v>11118</v>
@@ -25989,13 +25909,13 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>1129.755777217232</v>
+        <v>1129.771000591089</v>
       </c>
       <c r="D199" t="n">
-        <v>1122.341286039562</v>
+        <v>1122.35720385151</v>
       </c>
       <c r="E199" t="n">
-        <v>1137.170268394901</v>
+        <v>1137.184797330667</v>
       </c>
       <c r="F199" t="n">
         <v>20685</v>
@@ -26140,13 +26060,13 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>1128.025077648558</v>
+        <v>1128.051363070616</v>
       </c>
       <c r="D200" t="n">
-        <v>1121.633996814569</v>
+        <v>1121.660821762497</v>
       </c>
       <c r="E200" t="n">
-        <v>1134.416158482547</v>
+        <v>1134.441904378735</v>
       </c>
       <c r="F200" t="n">
         <v>20118</v>
@@ -26291,13 +26211,13 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>1127.425545361239</v>
+        <v>1127.443918051297</v>
       </c>
       <c r="D201" t="n">
-        <v>1115.370425891694</v>
+        <v>1115.390371550159</v>
       </c>
       <c r="E201" t="n">
-        <v>1139.480664830784</v>
+        <v>1139.497464552435</v>
       </c>
       <c r="F201" t="n">
         <v>2921</v>
@@ -26438,13 +26358,13 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>1126.860182148613</v>
+        <v>1126.882992031371</v>
       </c>
       <c r="D202" t="n">
-        <v>1111.307912970874</v>
+        <v>1111.332373274796</v>
       </c>
       <c r="E202" t="n">
-        <v>1142.412451326351</v>
+        <v>1142.433610787946</v>
       </c>
       <c r="F202" t="n">
         <v>1785</v>
@@ -26585,13 +26505,13 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>1121.535780602153</v>
+        <v>1121.550342372711</v>
       </c>
       <c r="D203" t="n">
-        <v>1110.5797475164</v>
+        <v>1110.595240727589</v>
       </c>
       <c r="E203" t="n">
-        <v>1132.491813687906</v>
+        <v>1132.505444017833</v>
       </c>
       <c r="F203" t="n">
         <v>5182</v>
@@ -26732,13 +26652,13 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>1119.10356035111</v>
+        <v>1119.11837001925</v>
       </c>
       <c r="D204" t="n">
-        <v>1101.01525599601</v>
+        <v>1101.032012932622</v>
       </c>
       <c r="E204" t="n">
-        <v>1137.191864706212</v>
+        <v>1137.204727105878</v>
       </c>
       <c r="F204" t="n">
         <v>1143</v>
@@ -26883,13 +26803,13 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>1116.610000983294</v>
+        <v>1116.588271680483</v>
       </c>
       <c r="D205" t="n">
-        <v>1108.891206176441</v>
+        <v>1108.870063272903</v>
       </c>
       <c r="E205" t="n">
-        <v>1124.328795790148</v>
+        <v>1124.306480088063</v>
       </c>
       <c r="F205" t="n">
         <v>10854</v>
@@ -27034,13 +26954,13 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>1115.232690681141</v>
+        <v>1115.247301605616</v>
       </c>
       <c r="D206" t="n">
-        <v>1106.126949981866</v>
+        <v>1106.142724442065</v>
       </c>
       <c r="E206" t="n">
-        <v>1124.338431380416</v>
+        <v>1124.351878769167</v>
       </c>
       <c r="F206" t="n">
         <v>6923</v>
@@ -27181,13 +27101,13 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>1114.625465481543</v>
+        <v>1114.63957317114</v>
       </c>
       <c r="D207" t="n">
-        <v>1100.283054245387</v>
+        <v>1100.298624640867</v>
       </c>
       <c r="E207" t="n">
-        <v>1128.967876717697</v>
+        <v>1128.980521701413</v>
       </c>
       <c r="F207" t="n">
         <v>2199</v>
@@ -27328,13 +27248,13 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>1111.060148797839</v>
+        <v>1111.07233691021</v>
       </c>
       <c r="D208" t="n">
-        <v>1103.179691053792</v>
+        <v>1103.19250347044</v>
       </c>
       <c r="E208" t="n">
-        <v>1118.940606541886</v>
+        <v>1118.95217034998</v>
       </c>
       <c r="F208" t="n">
         <v>8045</v>
@@ -27479,13 +27399,13 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>1110.286383880642</v>
+        <v>1110.298778853755</v>
       </c>
       <c r="D209" t="n">
-        <v>1101.023015851098</v>
+        <v>1101.03627688634</v>
       </c>
       <c r="E209" t="n">
-        <v>1119.549751910186</v>
+        <v>1119.56128082117</v>
       </c>
       <c r="F209" t="n">
         <v>8977</v>
@@ -27630,13 +27550,13 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>1107.820685873594</v>
+        <v>1107.854375958829</v>
       </c>
       <c r="D210" t="n">
-        <v>1100.781488140327</v>
+        <v>1100.815805174532</v>
       </c>
       <c r="E210" t="n">
-        <v>1114.85988360686</v>
+        <v>1114.892946743126</v>
       </c>
       <c r="F210" t="n">
         <v>14148</v>
@@ -27781,13 +27701,13 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>1093.602000063279</v>
+        <v>1093.583955448846</v>
       </c>
       <c r="D211" t="n">
-        <v>1082.143535487479</v>
+        <v>1082.126514124281</v>
       </c>
       <c r="E211" t="n">
-        <v>1105.060464639079</v>
+        <v>1105.041396773412</v>
       </c>
       <c r="F211" t="n">
         <v>4780</v>
@@ -27932,13 +27852,13 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>1091.062874621235</v>
+        <v>1091.07159923733</v>
       </c>
       <c r="D212" t="n">
-        <v>1081.745171111184</v>
+        <v>1081.754720783446</v>
       </c>
       <c r="E212" t="n">
-        <v>1100.380578131286</v>
+        <v>1100.388477691213</v>
       </c>
       <c r="F212" t="n">
         <v>7597</v>
@@ -28083,13 +28003,13 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>1073.531669739624</v>
+        <v>1073.568969986992</v>
       </c>
       <c r="D213" t="n">
-        <v>1062.397697904385</v>
+        <v>1062.436032521091</v>
       </c>
       <c r="E213" t="n">
-        <v>1084.665641574863</v>
+        <v>1084.701907452892</v>
       </c>
       <c r="F213" t="n">
         <v>6328</v>
@@ -28234,13 +28154,13 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>1070.846014158475</v>
+        <v>1070.864025141609</v>
       </c>
       <c r="D214" t="n">
-        <v>1061.022724284413</v>
+        <v>1061.042598224717</v>
       </c>
       <c r="E214" t="n">
-        <v>1080.669304032536</v>
+        <v>1080.685452058501</v>
       </c>
       <c r="F214" t="n">
         <v>6965</v>
@@ -28381,13 +28301,13 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>1070.14877529671</v>
+        <v>1070.134004768088</v>
       </c>
       <c r="D215" t="n">
-        <v>1058.754135565208</v>
+        <v>1058.741200069122</v>
       </c>
       <c r="E215" t="n">
-        <v>1081.543415028212</v>
+        <v>1081.526809467054</v>
       </c>
       <c r="F215" t="n">
         <v>5745</v>
@@ -28528,13 +28448,13 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>1067.624204258822</v>
+        <v>1067.624666533576</v>
       </c>
       <c r="D216" t="n">
-        <v>1052.479513644123</v>
+        <v>1052.482152283464</v>
       </c>
       <c r="E216" t="n">
-        <v>1082.768894873521</v>
+        <v>1082.767180783688</v>
       </c>
       <c r="F216" t="n">
         <v>1743</v>
@@ -28675,13 +28595,13 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>1063.362204026688</v>
+        <v>1063.364699681121</v>
       </c>
       <c r="D217" t="n">
-        <v>1051.448498347585</v>
+        <v>1051.452835302599</v>
       </c>
       <c r="E217" t="n">
-        <v>1075.275909705792</v>
+        <v>1075.276564059643</v>
       </c>
       <c r="F217" t="n">
         <v>3924</v>
@@ -28822,13 +28742,13 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>1056.49762436076</v>
+        <v>1056.511145632316</v>
       </c>
       <c r="D218" t="n">
-        <v>1044.864108157092</v>
+        <v>1044.878666831679</v>
       </c>
       <c r="E218" t="n">
-        <v>1068.131140564428</v>
+        <v>1068.143624432953</v>
       </c>
       <c r="F218" t="n">
         <v>4658</v>
@@ -28969,13 +28889,13 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>1042.25138564033</v>
+        <v>1042.262682731656</v>
       </c>
       <c r="D219" t="n">
-        <v>1030.924891505641</v>
+        <v>1030.938029741935</v>
       </c>
       <c r="E219" t="n">
-        <v>1053.57787977502</v>
+        <v>1053.587335721378</v>
       </c>
       <c r="F219" t="n">
         <v>4845</v>
@@ -29116,13 +29036,13 @@
         </is>
       </c>
       <c r="C220" t="n">
-        <v>1024.69443832352</v>
+        <v>1024.708133394474</v>
       </c>
       <c r="D220" t="n">
-        <v>1011.153272410936</v>
+        <v>1011.16845816492</v>
       </c>
       <c r="E220" t="n">
-        <v>1038.235604236104</v>
+        <v>1038.247808624028</v>
       </c>
       <c r="F220" t="n">
         <v>2658</v>
@@ -29263,13 +29183,13 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>1023.446857036427</v>
+        <v>1023.450000128857</v>
       </c>
       <c r="D221" t="n">
-        <v>1012.642381582216</v>
+        <v>1012.647417644738</v>
       </c>
       <c r="E221" t="n">
-        <v>1034.251332490637</v>
+        <v>1034.252582612976</v>
       </c>
       <c r="F221" t="n">
         <v>6310</v>
@@ -29410,13 +29330,13 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>995.741030667294</v>
+        <v>995.7618433901987</v>
       </c>
       <c r="D222" t="n">
-        <v>983.2408536434494</v>
+        <v>983.2636681582258</v>
       </c>
       <c r="E222" t="n">
-        <v>1008.241207691139</v>
+        <v>1008.260018622172</v>
       </c>
       <c r="F222" t="n">
         <v>4914</v>
@@ -29557,13 +29477,13 @@
         </is>
       </c>
       <c r="C223" t="n">
-        <v>992.4680063598643</v>
+        <v>992.4789855757126</v>
       </c>
       <c r="D223" t="n">
-        <v>980.1655265581131</v>
+        <v>980.178463778203</v>
       </c>
       <c r="E223" t="n">
-        <v>1004.770486161615</v>
+        <v>1004.779507373222</v>
       </c>
       <c r="F223" t="n">
         <v>4203</v>
@@ -29704,13 +29624,13 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>982.4067084039048</v>
+        <v>982.3976362191788</v>
       </c>
       <c r="D224" t="n">
-        <v>968.9657025469702</v>
+        <v>968.9591463641034</v>
       </c>
       <c r="E224" t="n">
-        <v>995.8477142608393</v>
+        <v>995.8361260742545</v>
       </c>
       <c r="F224" t="n">
         <v>3412</v>
@@ -29851,13 +29771,13 @@
         </is>
       </c>
       <c r="C225" t="n">
-        <v>975.0758191760643</v>
+        <v>975.0640371046704</v>
       </c>
       <c r="D225" t="n">
-        <v>959.3949693844793</v>
+        <v>959.3863965707224</v>
       </c>
       <c r="E225" t="n">
-        <v>990.7566689676493</v>
+        <v>990.7416776386183</v>
       </c>
       <c r="F225" t="n">
         <v>2391</v>
@@ -30002,13 +29922,13 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>953.1188426237578</v>
+        <v>953.136001015748</v>
       </c>
       <c r="D226" t="n">
-        <v>940.4833004033477</v>
+        <v>940.502915208808</v>
       </c>
       <c r="E226" t="n">
-        <v>965.754384844168</v>
+        <v>965.7690868226882</v>
       </c>
       <c r="F226" t="n">
         <v>3287</v>
@@ -30851,7 +30771,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>glm-5.3-flash</t>
+          <t>deepseek-v4.1-flash-max</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -30866,7 +30786,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>deepseek-v4.1-flash-max</t>
+          <t>glm-5.3-flash</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -31033,38 +30953,38 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>mimo-v2.6-flash</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+          <t>gemma-4-31b</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>31</v>
+      </c>
+      <c r="C16" t="n">
+        <v>31</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>dense</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>gemma-4-31b</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>31</v>
-      </c>
-      <c r="C17" t="n">
-        <v>31</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>dense</t>
-        </is>
-      </c>
+          <t>mimo-v2.6-flash</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -31094,14 +31014,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>inkling</t>
+          <t>qwen3.5-397b-a17b</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>975</v>
+        <v>397</v>
       </c>
       <c r="C19" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -31110,45 +31030,45 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>aa_single_scrape</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>qwen3.5-397b-a17b</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>397</v>
-      </c>
-      <c r="C20" t="n">
-        <v>17</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>glm-4.7</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>glm-4.7</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
+          <t>inkling</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>975</v>
+      </c>
+      <c r="C21" t="n">
+        <v>41</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>aa_single_scrape</t>
         </is>
       </c>
     </row>
@@ -31178,38 +31098,38 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>qwen3.8-27b</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>27</v>
-      </c>
-      <c r="C23" t="n">
-        <v>27</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>dense</t>
-        </is>
-      </c>
+          <t>deepseek-v4-flash-high-preview</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>deepseek-v4-flash-high-preview</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
+          <t>qwen3.8-27b</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>27</v>
+      </c>
+      <c r="C24" t="n">
+        <v>27</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>dense</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
@@ -31543,7 +31463,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>deepseek-v3.1</t>
+          <t>deepseek-v3.1-terminus-thinking</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -31558,7 +31478,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-terminus-thinking</t>
+          <t>deepseek-v3.1</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -32388,38 +32308,38 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>step-3</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr"/>
-      <c r="C85" t="inlineStr"/>
-      <c r="D85" t="inlineStr"/>
+          <t>nvidia-nemotron-3.5-lightning-30b-a3b-nvfp4</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>30</v>
+      </c>
+      <c r="C85" t="n">
+        <v>3</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>nvidia-nemotron-3.5-lightning-30b-a3b-nvfp4</t>
-        </is>
-      </c>
-      <c r="B86" t="n">
-        <v>30</v>
-      </c>
-      <c r="C86" t="n">
-        <v>3</v>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>step-3</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -33183,14 +33103,14 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>gemma-2-27b-it</t>
+          <t>granite-4.2-3b</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="C122" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -33206,38 +33126,38 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>jamba-1.5-large</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr"/>
-      <c r="C123" t="inlineStr"/>
-      <c r="D123" t="inlineStr"/>
+          <t>gemma-2-27b-it</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>27</v>
+      </c>
+      <c r="C123" t="n">
+        <v>27</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>dense</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>granite-4.2-3b</t>
-        </is>
-      </c>
-      <c r="B124" t="n">
-        <v>3</v>
-      </c>
-      <c r="C124" t="n">
-        <v>3</v>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>dense</t>
-        </is>
-      </c>
+          <t>jamba-1.5-large</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr"/>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -33546,20 +33466,12 @@
           <t>deepseek-coder-v2</t>
         </is>
       </c>
-      <c r="B138" t="n">
-        <v>236</v>
-      </c>
-      <c r="C138" t="n">
-        <v>21</v>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+      <c r="B138" t="inlineStr"/>
+      <c r="C138" t="inlineStr"/>
+      <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>aa_single_scrape</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>

--- a/arena_enrichment/output/arena_leaderboard_enriched.xlsx
+++ b/arena_enrichment/output/arena_leaderboard_enriched.xlsx
@@ -17443,43 +17443,123 @@
           <t>DeepSeek License</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
+      <c r="I138" t="n">
+        <v>236</v>
+      </c>
+      <c r="J138" t="n">
+        <v>21</v>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
-      <c r="O138" t="inlineStr"/>
-      <c r="P138" t="inlineStr"/>
-      <c r="Q138" t="inlineStr"/>
-      <c r="R138" t="inlineStr"/>
-      <c r="S138" t="inlineStr"/>
-      <c r="T138" t="inlineStr"/>
-      <c r="U138" t="inlineStr"/>
-      <c r="V138" t="inlineStr"/>
-      <c r="W138" t="inlineStr"/>
-      <c r="X138" t="inlineStr"/>
-      <c r="Y138" t="inlineStr"/>
-      <c r="Z138" t="inlineStr"/>
-      <c r="AA138" t="inlineStr"/>
-      <c r="AB138" t="inlineStr"/>
-      <c r="AC138" t="inlineStr"/>
-      <c r="AD138" t="inlineStr"/>
-      <c r="AE138" t="inlineStr"/>
-      <c r="AF138" t="inlineStr"/>
-      <c r="AG138" t="inlineStr"/>
+          <t>aa_single_scrape</t>
+        </is>
+      </c>
+      <c r="M138" t="n">
+        <v>472</v>
+      </c>
+      <c r="N138" t="n">
+        <v>590</v>
+      </c>
+      <c r="O138" t="n">
+        <v>236</v>
+      </c>
+      <c r="P138" t="n">
+        <v>295</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>118</v>
+      </c>
+      <c r="R138" t="n">
+        <v>147.5</v>
+      </c>
+      <c r="S138" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T138" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U138" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V138" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W138" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X138" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y138" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z138" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA138" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB138" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC138" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD138" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE138" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF138" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG138" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH138" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -33466,12 +33546,20 @@
           <t>deepseek-coder-v2</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr"/>
-      <c r="C138" t="inlineStr"/>
-      <c r="D138" t="inlineStr"/>
+      <c r="B138" t="n">
+        <v>236</v>
+      </c>
+      <c r="C138" t="n">
+        <v>21</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>aa_single_scrape</t>
         </is>
       </c>
     </row>

--- a/arena_enrichment/output/arena_leaderboard_enriched.xlsx
+++ b/arena_enrichment/output/arena_leaderboard_enriched.xlsx
@@ -674,16 +674,16 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1488.357698689695</v>
+        <v>1488.076952646026</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1483.586114955416</v>
+        <v>1483.38884168377</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1493.129282423974</v>
+        <v>1492.765063608281</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>28280</v>
+        <v>30351</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -745,16 +745,16 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1480.075697959219</v>
+        <v>1480.404198798028</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1470.671204204633</v>
+        <v>1471.023337093583</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1489.480191713805</v>
+        <v>1489.785060502473</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>4056</v>
+        <v>4069</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -816,16 +816,16 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1478.49856297707</v>
+        <v>1478.395227711814</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1472.940423691248</v>
+        <v>1472.992607478483</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1484.056702262892</v>
+        <v>1483.797847945144</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>17857</v>
+        <v>20049</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -887,16 +887,16 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1475.769482146397</v>
+        <v>1475.239278747727</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1471.469242460478</v>
+        <v>1470.988918136773</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1480.069721832316</v>
+        <v>1479.489639358682</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>45399</v>
+        <v>47521</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -954,24 +954,24 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>deepseek-v4.1-flash-max</t>
+          <t>glm-5.3-flash</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1474.440278165399</v>
+        <v>1474.573138007533</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1467.511746655351</v>
+        <v>1469.532872119089</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1481.368809675447</v>
+        <v>1479.613403895978</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>8728</v>
+        <v>27678</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Z.ai</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1025,24 +1025,24 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>glm-5.3-flash</t>
+          <t>deepseek-v4.1-flash-max</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1473.000490016389</v>
+        <v>1474.538972039915</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1467.657830534031</v>
+        <v>1468.014867762915</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1478.343149498747</v>
+        <v>1481.063076316914</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>22971</v>
+        <v>10872</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Z.ai</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1100,16 +1100,16 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1467.514738875952</v>
+        <v>1467.694298524061</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1463.894610214051</v>
+        <v>1464.116883332533</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1471.134867537853</v>
+        <v>1471.27171371559</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>70871</v>
+        <v>73197</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -1167,24 +1167,24 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>glm-5.1</t>
+          <t>deepseek-v4-pro-high-20260813</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1464.565468868514</v>
+        <v>1464.526542255673</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1460.882819739498</v>
+        <v>1457.912499596713</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1468.24811799753</v>
+        <v>1471.140584914632</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>58358</v>
+        <v>9815</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Z.ai</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1238,24 +1238,24 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro-high-20260813</t>
+          <t>glm-5.1</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1464.278528826575</v>
+        <v>1464.406289271268</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1457.651781275999</v>
+        <v>1460.771031364109</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1470.905276377151</v>
+        <v>1468.041547178427</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>9780</v>
+        <v>60592</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Z.ai</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1313,16 +1313,16 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1460.959439730511</v>
+        <v>1460.775493228967</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1456.528424830495</v>
+        <v>1456.350687506779</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1465.390454630528</v>
+        <v>1465.200298951155</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>39936</v>
+        <v>40066</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
@@ -1464,16 +1464,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1457.760968878053</v>
+        <v>1457.827631458692</v>
       </c>
       <c r="D12" t="n">
-        <v>1453.856104015234</v>
+        <v>1453.927877385534</v>
       </c>
       <c r="E12" t="n">
-        <v>1461.665833740871</v>
+        <v>1461.72738553185</v>
       </c>
       <c r="F12" t="n">
-        <v>57478</v>
+        <v>57657</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1615,16 +1615,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1457.611917586408</v>
+        <v>1457.518513492205</v>
       </c>
       <c r="D13" t="n">
-        <v>1453.359457622837</v>
+        <v>1453.275445588913</v>
       </c>
       <c r="E13" t="n">
-        <v>1461.864377549981</v>
+        <v>1461.761581395496</v>
       </c>
       <c r="F13" t="n">
-        <v>29174</v>
+        <v>29292</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1762,148 +1762,68 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hy3</t>
+          <t>deepseek-v4-pro-high-preview</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1455.983448832156</v>
+        <v>1454.769081210869</v>
       </c>
       <c r="D14" t="n">
-        <v>1449.463590089154</v>
+        <v>1450.806031225247</v>
       </c>
       <c r="E14" t="n">
-        <v>1462.503307575158</v>
+        <v>1458.73213119649</v>
       </c>
       <c r="F14" t="n">
-        <v>10476</v>
+        <v>54976</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tencent</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>299</v>
-      </c>
-      <c r="J14" t="n">
-        <v>21</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>aa_single_scrape</t>
-        </is>
-      </c>
-      <c r="M14" t="n">
-        <v>598</v>
-      </c>
-      <c r="N14" t="n">
-        <v>747.5</v>
-      </c>
-      <c r="O14" t="n">
-        <v>299</v>
-      </c>
-      <c r="P14" t="n">
-        <v>373.8</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>149.5</v>
-      </c>
-      <c r="R14" t="n">
-        <v>186.9</v>
-      </c>
-      <c r="S14" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T14" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U14" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V14" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W14" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y14" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z14" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA14" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB14" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC14" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD14" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AE14" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF14" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG14" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -1913,68 +1833,148 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro-high-preview</t>
+          <t>hy3</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1454.951683804795</v>
+        <v>1454.219963525435</v>
       </c>
       <c r="D15" t="n">
-        <v>1450.976425151739</v>
+        <v>1447.893596340846</v>
       </c>
       <c r="E15" t="n">
-        <v>1458.926942457851</v>
+        <v>1460.546330710023</v>
       </c>
       <c r="F15" t="n">
-        <v>54767</v>
+        <v>11284</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Tencent</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>299</v>
+      </c>
+      <c r="J15" t="n">
+        <v>21</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr"/>
-      <c r="AC15" t="inlineStr"/>
-      <c r="AD15" t="inlineStr"/>
-      <c r="AE15" t="inlineStr"/>
-      <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="inlineStr"/>
+          <t>aa_single_scrape</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>598</v>
+      </c>
+      <c r="N15" t="n">
+        <v>747.5</v>
+      </c>
+      <c r="O15" t="n">
+        <v>299</v>
+      </c>
+      <c r="P15" t="n">
+        <v>373.8</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>149.5</v>
+      </c>
+      <c r="R15" t="n">
+        <v>186.9</v>
+      </c>
+      <c r="S15" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T15" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U15" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V15" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W15" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X15" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y15" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z15" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA15" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB15" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC15" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD15" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE15" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF15" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG15" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -1988,16 +1988,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1452.835259622734</v>
+        <v>1452.374967275139</v>
       </c>
       <c r="D16" t="n">
-        <v>1445.391511362457</v>
+        <v>1444.935212236707</v>
       </c>
       <c r="E16" t="n">
-        <v>1460.279007883011</v>
+        <v>1459.814722313571</v>
       </c>
       <c r="F16" t="n">
-        <v>6133</v>
+        <v>6145</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -2139,16 +2139,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1451.782861723269</v>
+        <v>1450.653568047725</v>
       </c>
       <c r="D17" t="n">
-        <v>1443.941189608791</v>
+        <v>1443.575592053593</v>
       </c>
       <c r="E17" t="n">
-        <v>1459.624533837748</v>
+        <v>1457.731544041857</v>
       </c>
       <c r="F17" t="n">
-        <v>6053</v>
+        <v>8226</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -2210,16 +2210,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1450.121849787226</v>
+        <v>1450.089214430422</v>
       </c>
       <c r="D18" t="n">
-        <v>1446.834361274673</v>
+        <v>1446.808342953939</v>
       </c>
       <c r="E18" t="n">
-        <v>1453.409338299778</v>
+        <v>1453.370085906905</v>
       </c>
       <c r="F18" t="n">
-        <v>74565</v>
+        <v>74811</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -2361,16 +2361,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1441.812667919804</v>
+        <v>1441.746784599961</v>
       </c>
       <c r="D19" t="n">
-        <v>1438.665343661678</v>
+        <v>1438.629518509932</v>
       </c>
       <c r="E19" t="n">
-        <v>1444.95999217793</v>
+        <v>1444.86405068999</v>
       </c>
       <c r="F19" t="n">
-        <v>88660</v>
+        <v>91190</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -2512,16 +2512,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1441.49975007789</v>
+        <v>1441.15298195851</v>
       </c>
       <c r="D20" t="n">
-        <v>1435.43833243339</v>
+        <v>1435.098239459259</v>
       </c>
       <c r="E20" t="n">
-        <v>1447.561167722389</v>
+        <v>1447.207724457761</v>
       </c>
       <c r="F20" t="n">
-        <v>12228</v>
+        <v>12256</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -2583,16 +2583,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1441.375480290693</v>
+        <v>1440.994367729521</v>
       </c>
       <c r="D21" t="n">
-        <v>1436.872462583635</v>
+        <v>1436.590439163765</v>
       </c>
       <c r="E21" t="n">
-        <v>1445.87849799775</v>
+        <v>1445.398296295277</v>
       </c>
       <c r="F21" t="n">
-        <v>35204</v>
+        <v>37744</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -2734,16 +2734,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1440.055424093557</v>
+        <v>1440.460184695466</v>
       </c>
       <c r="D22" t="n">
-        <v>1436.111142899113</v>
+        <v>1436.56790990498</v>
       </c>
       <c r="E22" t="n">
-        <v>1443.999705288001</v>
+        <v>1444.352459485951</v>
       </c>
       <c r="F22" t="n">
-        <v>58757</v>
+        <v>61220</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2885,16 +2885,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1438.423647802235</v>
+        <v>1438.646538213572</v>
       </c>
       <c r="D23" t="n">
-        <v>1434.309732503248</v>
+        <v>1434.542437221376</v>
       </c>
       <c r="E23" t="n">
-        <v>1442.537563101221</v>
+        <v>1442.750639205768</v>
       </c>
       <c r="F23" t="n">
-        <v>51648</v>
+        <v>51859</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2956,16 +2956,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1437.699726423117</v>
+        <v>1438.095139707179</v>
       </c>
       <c r="D24" t="n">
-        <v>1432.284426086605</v>
+        <v>1432.821969651217</v>
       </c>
       <c r="E24" t="n">
-        <v>1443.115026759629</v>
+        <v>1443.368309763141</v>
       </c>
       <c r="F24" t="n">
-        <v>18462</v>
+        <v>20711</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -3107,16 +3107,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1437.453901668969</v>
+        <v>1437.618193427422</v>
       </c>
       <c r="D25" t="n">
-        <v>1430.00951430035</v>
+        <v>1430.176747803929</v>
       </c>
       <c r="E25" t="n">
-        <v>1444.898289037587</v>
+        <v>1445.059639050915</v>
       </c>
       <c r="F25" t="n">
-        <v>6081</v>
+        <v>6092</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -3258,16 +3258,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1436.019558281073</v>
+        <v>1436.014766830031</v>
       </c>
       <c r="D26" t="n">
-        <v>1431.973899917187</v>
+        <v>1431.979050786182</v>
       </c>
       <c r="E26" t="n">
-        <v>1440.065216644959</v>
+        <v>1440.050482873879</v>
       </c>
       <c r="F26" t="n">
-        <v>51850</v>
+        <v>52047</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -3409,16 +3409,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1433.605812533576</v>
+        <v>1433.682354635488</v>
       </c>
       <c r="D27" t="n">
-        <v>1429.373519290959</v>
+        <v>1429.457556697344</v>
       </c>
       <c r="E27" t="n">
-        <v>1437.838105776193</v>
+        <v>1437.907152573633</v>
       </c>
       <c r="F27" t="n">
-        <v>47266</v>
+        <v>47402</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -3480,16 +3480,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1430.558102339856</v>
+        <v>1430.378427137835</v>
       </c>
       <c r="D28" t="n">
-        <v>1424.046164052485</v>
+        <v>1423.872900248477</v>
       </c>
       <c r="E28" t="n">
-        <v>1437.070040627227</v>
+        <v>1436.883954027192</v>
       </c>
       <c r="F28" t="n">
-        <v>8356</v>
+        <v>8378</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -3631,16 +3631,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1430.076684063201</v>
+        <v>1430.096442457018</v>
       </c>
       <c r="D29" t="n">
-        <v>1426.982680329273</v>
+        <v>1427.007665404714</v>
       </c>
       <c r="E29" t="n">
-        <v>1433.17068779713</v>
+        <v>1433.185219509323</v>
       </c>
       <c r="F29" t="n">
-        <v>63210</v>
+        <v>63390</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -3782,16 +3782,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1426.927617154943</v>
+        <v>1426.35848178227</v>
       </c>
       <c r="D30" t="n">
-        <v>1420.516208704082</v>
+        <v>1419.960937872099</v>
       </c>
       <c r="E30" t="n">
-        <v>1433.339025605804</v>
+        <v>1432.756025692441</v>
       </c>
       <c r="F30" t="n">
-        <v>11757</v>
+        <v>11803</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -3853,16 +3853,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1426.217526026591</v>
+        <v>1426.085426097762</v>
       </c>
       <c r="D31" t="n">
-        <v>1419.326064619545</v>
+        <v>1419.204560895633</v>
       </c>
       <c r="E31" t="n">
-        <v>1433.108987433637</v>
+        <v>1432.96629129989</v>
       </c>
       <c r="F31" t="n">
-        <v>11515</v>
+        <v>11571</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -4000,148 +4000,68 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>muse-glimmer</t>
+          <t>deepseek-v3.2-exp-thinking</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1424.991657690778</v>
+        <v>1424.801370506729</v>
       </c>
       <c r="D32" t="n">
-        <v>1415.292280686214</v>
+        <v>1418.240669698635</v>
       </c>
       <c r="E32" t="n">
-        <v>1434.691034695343</v>
+        <v>1431.362071314823</v>
       </c>
       <c r="F32" t="n">
-        <v>3893</v>
+        <v>9008</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>30</v>
-      </c>
-      <c r="J32" t="n">
-        <v>30</v>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>dense</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>aa_single_scrape</t>
-        </is>
-      </c>
-      <c r="M32" t="n">
-        <v>60</v>
-      </c>
-      <c r="N32" t="n">
-        <v>75</v>
-      </c>
-      <c r="O32" t="n">
-        <v>30</v>
-      </c>
-      <c r="P32" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>15</v>
-      </c>
-      <c r="R32" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="S32" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T32" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U32" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V32" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W32" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X32" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y32" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z32" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA32" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB32" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC32" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD32" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE32" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF32" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG32" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr"/>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -4151,20 +4071,20 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>deepseek-v3.2-exp-thinking</t>
+          <t>deepseek-v3.2</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1424.929628242865</v>
+        <v>1424.794805351584</v>
       </c>
       <c r="D33" t="n">
-        <v>1418.353743896235</v>
+        <v>1421.303761030634</v>
       </c>
       <c r="E33" t="n">
-        <v>1431.505512589495</v>
+        <v>1428.285849672534</v>
       </c>
       <c r="F33" t="n">
-        <v>8947</v>
+        <v>48114</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -4222,68 +4142,148 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>deepseek-v3.2</t>
+          <t>muse-glimmer</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1424.77342023501</v>
+        <v>1424.502279455052</v>
       </c>
       <c r="D34" t="n">
-        <v>1421.278574911297</v>
+        <v>1414.812184754463</v>
       </c>
       <c r="E34" t="n">
-        <v>1428.268265558724</v>
+        <v>1434.192374155641</v>
       </c>
       <c r="F34" t="n">
-        <v>47999</v>
+        <v>3892</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>30</v>
+      </c>
+      <c r="J34" t="n">
+        <v>30</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>dense</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr"/>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr"/>
-      <c r="AA34" t="inlineStr"/>
-      <c r="AB34" t="inlineStr"/>
-      <c r="AC34" t="inlineStr"/>
-      <c r="AD34" t="inlineStr"/>
-      <c r="AE34" t="inlineStr"/>
-      <c r="AF34" t="inlineStr"/>
-      <c r="AG34" t="inlineStr"/>
+          <t>aa_single_scrape</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
+        <v>60</v>
+      </c>
+      <c r="N34" t="n">
+        <v>75</v>
+      </c>
+      <c r="O34" t="n">
+        <v>30</v>
+      </c>
+      <c r="P34" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>15</v>
+      </c>
+      <c r="R34" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="S34" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T34" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U34" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V34" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W34" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X34" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y34" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z34" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA34" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB34" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC34" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD34" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE34" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF34" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG34" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -4297,16 +4297,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1424.142362861242</v>
+        <v>1424.159146827059</v>
       </c>
       <c r="D35" t="n">
-        <v>1420.234221716797</v>
+        <v>1420.258902739121</v>
       </c>
       <c r="E35" t="n">
-        <v>1428.050504005688</v>
+        <v>1428.059390914997</v>
       </c>
       <c r="F35" t="n">
-        <v>35662</v>
+        <v>35828</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1422.742946224598</v>
+        <v>1422.630503501648</v>
       </c>
       <c r="D36" t="n">
-        <v>1419.162201285617</v>
+        <v>1419.055282475421</v>
       </c>
       <c r="E36" t="n">
-        <v>1426.323691163579</v>
+        <v>1426.205724527876</v>
       </c>
       <c r="F36" t="n">
-        <v>41975</v>
+        <v>42076</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -4439,16 +4439,16 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1422.399601713316</v>
+        <v>1422.257653067509</v>
       </c>
       <c r="D37" t="n">
-        <v>1419.842732395144</v>
+        <v>1419.707024483014</v>
       </c>
       <c r="E37" t="n">
-        <v>1424.956471031488</v>
+        <v>1424.808281652003</v>
       </c>
       <c r="F37" t="n">
-        <v>97788</v>
+        <v>98167</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -4590,16 +4590,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1422.064279260454</v>
+        <v>1421.433586838476</v>
       </c>
       <c r="D38" t="n">
-        <v>1415.676168685056</v>
+        <v>1415.05677694721</v>
       </c>
       <c r="E38" t="n">
-        <v>1428.452389835853</v>
+        <v>1427.810396729742</v>
       </c>
       <c r="F38" t="n">
-        <v>11944</v>
+        <v>11999</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -4661,16 +4661,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1421.636916430414</v>
+        <v>1421.394738052522</v>
       </c>
       <c r="D39" t="n">
-        <v>1415.942731846803</v>
+        <v>1415.714259863957</v>
       </c>
       <c r="E39" t="n">
-        <v>1427.331101014025</v>
+        <v>1427.075216241087</v>
       </c>
       <c r="F39" t="n">
-        <v>18059</v>
+        <v>18171</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -4732,16 +4732,16 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1418.693927213401</v>
+        <v>1418.463021459922</v>
       </c>
       <c r="D40" t="n">
-        <v>1412.156876037188</v>
+        <v>1411.939253922684</v>
       </c>
       <c r="E40" t="n">
-        <v>1425.230978389614</v>
+        <v>1424.986788997161</v>
       </c>
       <c r="F40" t="n">
-        <v>11531</v>
+        <v>11592</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -4883,16 +4883,16 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1418.228899511914</v>
+        <v>1417.736509068082</v>
       </c>
       <c r="D41" t="n">
-        <v>1413.320016703903</v>
+        <v>1412.843916623845</v>
       </c>
       <c r="E41" t="n">
-        <v>1423.137782319925</v>
+        <v>1422.629101512318</v>
       </c>
       <c r="F41" t="n">
-        <v>26959</v>
+        <v>27148</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -5030,20 +5030,20 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-terminus-thinking</t>
+          <t>deepseek-v3.1</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1417.209021514145</v>
+        <v>1417.179575350911</v>
       </c>
       <c r="D42" t="n">
-        <v>1407.075624540877</v>
+        <v>1411.118157410981</v>
       </c>
       <c r="E42" t="n">
-        <v>1427.342418487413</v>
+        <v>1423.24099329084</v>
       </c>
       <c r="F42" t="n">
-        <v>3354</v>
+        <v>14610</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -5101,68 +5101,148 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>deepseek-v3.1</t>
+          <t>qwen3.5-122b-a10b</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1417.145820248776</v>
+        <v>1416.280534166255</v>
       </c>
       <c r="D43" t="n">
-        <v>1411.078466364427</v>
+        <v>1411.992527091017</v>
       </c>
       <c r="E43" t="n">
-        <v>1423.213174133125</v>
+        <v>1420.568541241493</v>
       </c>
       <c r="F43" t="n">
-        <v>14540</v>
+        <v>29734</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>122</v>
+      </c>
+      <c r="J43" t="n">
+        <v>10</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr"/>
-      <c r="W43" t="inlineStr"/>
-      <c r="X43" t="inlineStr"/>
-      <c r="Y43" t="inlineStr"/>
-      <c r="Z43" t="inlineStr"/>
-      <c r="AA43" t="inlineStr"/>
-      <c r="AB43" t="inlineStr"/>
-      <c r="AC43" t="inlineStr"/>
-      <c r="AD43" t="inlineStr"/>
-      <c r="AE43" t="inlineStr"/>
-      <c r="AF43" t="inlineStr"/>
-      <c r="AG43" t="inlineStr"/>
+          <t>name_parsing</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
+        <v>244</v>
+      </c>
+      <c r="N43" t="n">
+        <v>305</v>
+      </c>
+      <c r="O43" t="n">
+        <v>122</v>
+      </c>
+      <c r="P43" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>61</v>
+      </c>
+      <c r="R43" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="S43" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T43" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U43" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V43" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W43" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X43" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y43" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z43" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA43" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB43" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC43" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD43" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE43" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF43" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG43" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>B200 SXM</t>
         </is>
       </c>
     </row>
@@ -5172,148 +5252,68 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>qwen3.5-122b-a10b</t>
+          <t>deepseek-v3.1-terminus-thinking</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1416.097163110477</v>
+        <v>1415.967630870797</v>
       </c>
       <c r="D44" t="n">
-        <v>1411.799332527324</v>
+        <v>1405.864287223406</v>
       </c>
       <c r="E44" t="n">
-        <v>1420.394993693631</v>
+        <v>1426.070974518188</v>
       </c>
       <c r="F44" t="n">
-        <v>29651</v>
+        <v>3377</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
-        </is>
-      </c>
-      <c r="I44" t="n">
-        <v>122</v>
-      </c>
-      <c r="J44" t="n">
-        <v>10</v>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>name_parsing</t>
-        </is>
-      </c>
-      <c r="M44" t="n">
-        <v>244</v>
-      </c>
-      <c r="N44" t="n">
-        <v>305</v>
-      </c>
-      <c r="O44" t="n">
-        <v>122</v>
-      </c>
-      <c r="P44" t="n">
-        <v>152.5</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>61</v>
-      </c>
-      <c r="R44" t="n">
-        <v>76.2</v>
-      </c>
-      <c r="S44" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T44" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U44" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V44" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W44" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X44" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y44" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z44" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA44" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB44" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC44" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD44" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE44" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF44" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG44" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr"/>
+      <c r="AC44" t="inlineStr"/>
+      <c r="AD44" t="inlineStr"/>
+      <c r="AE44" t="inlineStr"/>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="inlineStr"/>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>B200 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -5327,16 +5327,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1415.931240112323</v>
+        <v>1415.837581675816</v>
       </c>
       <c r="D45" t="n">
-        <v>1409.254102978883</v>
+        <v>1409.178639091479</v>
       </c>
       <c r="E45" t="n">
-        <v>1422.608377245763</v>
+        <v>1422.496524260152</v>
       </c>
       <c r="F45" t="n">
-        <v>11409</v>
+        <v>11458</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -5398,16 +5398,16 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1414.980185450766</v>
+        <v>1414.987764640942</v>
       </c>
       <c r="D46" t="n">
-        <v>1411.560907662792</v>
+        <v>1411.603038459481</v>
       </c>
       <c r="E46" t="n">
-        <v>1418.39946323874</v>
+        <v>1418.372490822403</v>
       </c>
       <c r="F46" t="n">
-        <v>79944</v>
+        <v>82436</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -5469,16 +5469,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1414.83453642041</v>
+        <v>1414.770444684517</v>
       </c>
       <c r="D47" t="n">
-        <v>1405.10211190994</v>
+        <v>1405.054777085932</v>
       </c>
       <c r="E47" t="n">
-        <v>1424.566960930881</v>
+        <v>1424.486112283103</v>
       </c>
       <c r="F47" t="n">
-        <v>3599</v>
+        <v>3609</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -5540,16 +5540,16 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1413.887239408306</v>
+        <v>1413.771654834484</v>
       </c>
       <c r="D48" t="n">
-        <v>1410.987149099679</v>
+        <v>1410.891604213389</v>
       </c>
       <c r="E48" t="n">
-        <v>1416.787329716934</v>
+        <v>1416.651705455579</v>
       </c>
       <c r="F48" t="n">
-        <v>79452</v>
+        <v>81759</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -5691,16 +5691,16 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1413.425390030167</v>
+        <v>1413.450319233152</v>
       </c>
       <c r="D49" t="n">
-        <v>1406.875511990807</v>
+        <v>1406.92802765197</v>
       </c>
       <c r="E49" t="n">
-        <v>1419.975268069527</v>
+        <v>1419.972610814335</v>
       </c>
       <c r="F49" t="n">
-        <v>11241</v>
+        <v>11325</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -5842,16 +5842,16 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1411.27157240162</v>
+        <v>1410.965192066163</v>
       </c>
       <c r="D50" t="n">
-        <v>1406.329340438641</v>
+        <v>1406.043270219937</v>
       </c>
       <c r="E50" t="n">
-        <v>1416.213804364598</v>
+        <v>1415.887113912389</v>
       </c>
       <c r="F50" t="n">
-        <v>23661</v>
+        <v>23803</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -5993,16 +5993,16 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1408.831728156688</v>
+        <v>1408.876451382</v>
       </c>
       <c r="D51" t="n">
-        <v>1401.414156106443</v>
+        <v>1401.469023473419</v>
       </c>
       <c r="E51" t="n">
-        <v>1416.249300206934</v>
+        <v>1416.28387929058</v>
       </c>
       <c r="F51" t="n">
-        <v>6874</v>
+        <v>6893</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1408.72409819639</v>
+        <v>1408.760406186229</v>
       </c>
       <c r="D52" t="n">
-        <v>1404.423416269354</v>
+        <v>1404.467472253218</v>
       </c>
       <c r="E52" t="n">
-        <v>1413.024780123425</v>
+        <v>1413.05334011924</v>
       </c>
       <c r="F52" t="n">
-        <v>28612</v>
+        <v>28677</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -6215,16 +6215,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1405.241270710841</v>
+        <v>1405.313516811711</v>
       </c>
       <c r="D53" t="n">
-        <v>1400.343917722984</v>
+        <v>1400.528219229474</v>
       </c>
       <c r="E53" t="n">
-        <v>1410.138623698699</v>
+        <v>1410.098814393947</v>
       </c>
       <c r="F53" t="n">
-        <v>27070</v>
+        <v>29528</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -6366,16 +6366,16 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1402.53451398059</v>
+        <v>1402.193791377557</v>
       </c>
       <c r="D54" t="n">
-        <v>1397.995990557387</v>
+        <v>1397.662928414309</v>
       </c>
       <c r="E54" t="n">
-        <v>1407.073037403793</v>
+        <v>1406.724654340805</v>
       </c>
       <c r="F54" t="n">
-        <v>37279</v>
+        <v>37497</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -6517,16 +6517,16 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1401.177191429132</v>
+        <v>1400.972711723199</v>
       </c>
       <c r="D55" t="n">
-        <v>1394.754334307371</v>
+        <v>1394.559195060767</v>
       </c>
       <c r="E55" t="n">
-        <v>1407.600048550892</v>
+        <v>1407.386228385632</v>
       </c>
       <c r="F55" t="n">
-        <v>11123</v>
+        <v>11174</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -6668,16 +6668,16 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1399.992559008723</v>
+        <v>1400.033776528542</v>
       </c>
       <c r="D56" t="n">
-        <v>1393.404987817346</v>
+        <v>1393.460513007756</v>
       </c>
       <c r="E56" t="n">
-        <v>1406.580130200099</v>
+        <v>1406.607040049329</v>
       </c>
       <c r="F56" t="n">
-        <v>8774</v>
+        <v>8822</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -6819,16 +6819,16 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1398.986740127523</v>
+        <v>1398.6580275354</v>
       </c>
       <c r="D57" t="n">
-        <v>1394.198237430405</v>
+        <v>1393.885251716407</v>
       </c>
       <c r="E57" t="n">
-        <v>1403.775242824641</v>
+        <v>1403.430803354393</v>
       </c>
       <c r="F57" t="n">
-        <v>22603</v>
+        <v>22763</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -6970,13 +6970,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1398.117983968687</v>
+        <v>1398.100721752383</v>
       </c>
       <c r="D58" t="n">
-        <v>1393.222608958932</v>
+        <v>1393.2057297304</v>
       </c>
       <c r="E58" t="n">
-        <v>1403.013358978443</v>
+        <v>1402.995713774367</v>
       </c>
       <c r="F58" t="n">
         <v>18524</v>
@@ -7121,16 +7121,16 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1395.638607849424</v>
+        <v>1395.193340110712</v>
       </c>
       <c r="D59" t="n">
-        <v>1391.737618583955</v>
+        <v>1391.302355731635</v>
       </c>
       <c r="E59" t="n">
-        <v>1399.539597114893</v>
+        <v>1399.08432448979</v>
       </c>
       <c r="F59" t="n">
-        <v>44758</v>
+        <v>44989</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -7272,16 +7272,16 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1395.029963260086</v>
+        <v>1394.714174126426</v>
       </c>
       <c r="D60" t="n">
-        <v>1388.177289438941</v>
+        <v>1387.889037102679</v>
       </c>
       <c r="E60" t="n">
-        <v>1401.882637081232</v>
+        <v>1401.539311150174</v>
       </c>
       <c r="F60" t="n">
-        <v>7805</v>
+        <v>7868</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -7423,16 +7423,16 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1393.793394084286</v>
+        <v>1393.835097211134</v>
       </c>
       <c r="D61" t="n">
-        <v>1389.553018962186</v>
+        <v>1389.604147316336</v>
       </c>
       <c r="E61" t="n">
-        <v>1398.033769206386</v>
+        <v>1398.066047105932</v>
       </c>
       <c r="F61" t="n">
-        <v>30408</v>
+        <v>30493</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -7574,16 +7574,16 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1393.273766901803</v>
+        <v>1393.198020429407</v>
       </c>
       <c r="D62" t="n">
-        <v>1389.716290479776</v>
+        <v>1389.645103877127</v>
       </c>
       <c r="E62" t="n">
-        <v>1396.831243323829</v>
+        <v>1396.750936981688</v>
       </c>
       <c r="F62" t="n">
-        <v>60207</v>
+        <v>60381</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -7645,16 +7645,16 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1391.711623122026</v>
+        <v>1391.624963388202</v>
       </c>
       <c r="D63" t="n">
-        <v>1388.223175199253</v>
+        <v>1388.141586285683</v>
       </c>
       <c r="E63" t="n">
-        <v>1395.200071044799</v>
+        <v>1395.108340490721</v>
       </c>
       <c r="F63" t="n">
-        <v>47998</v>
+        <v>48117</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -7716,16 +7716,16 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1390.8451428342</v>
+        <v>1390.885385061472</v>
       </c>
       <c r="D64" t="n">
-        <v>1386.948707823527</v>
+        <v>1386.997625666772</v>
       </c>
       <c r="E64" t="n">
-        <v>1394.741577844872</v>
+        <v>1394.773144456172</v>
       </c>
       <c r="F64" t="n">
-        <v>42730</v>
+        <v>42858</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -7787,16 +7787,16 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1387.32104552345</v>
+        <v>1387.51551147941</v>
       </c>
       <c r="D65" t="n">
-        <v>1382.325913850224</v>
+        <v>1382.540086428761</v>
       </c>
       <c r="E65" t="n">
-        <v>1392.316177196677</v>
+        <v>1392.49093653006</v>
       </c>
       <c r="F65" t="n">
-        <v>25006</v>
+        <v>25197</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -7938,16 +7938,16 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1387.126002571981</v>
+        <v>1386.348879086994</v>
       </c>
       <c r="D66" t="n">
-        <v>1380.942552399045</v>
+        <v>1380.177842607918</v>
       </c>
       <c r="E66" t="n">
-        <v>1393.309452744918</v>
+        <v>1392.51991556607</v>
       </c>
       <c r="F66" t="n">
-        <v>11115</v>
+        <v>11143</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -8009,16 +8009,16 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1384.561240884782</v>
+        <v>1384.633644150523</v>
       </c>
       <c r="D67" t="n">
-        <v>1379.375909616568</v>
+        <v>1379.458340997793</v>
       </c>
       <c r="E67" t="n">
-        <v>1389.746572152996</v>
+        <v>1389.808947303253</v>
       </c>
       <c r="F67" t="n">
-        <v>17187</v>
+        <v>17248</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -8080,16 +8080,16 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1382.65675988569</v>
+        <v>1382.404714441085</v>
       </c>
       <c r="D68" t="n">
-        <v>1377.737333386408</v>
+        <v>1377.501412598499</v>
       </c>
       <c r="E68" t="n">
-        <v>1387.576186384972</v>
+        <v>1387.308016283671</v>
       </c>
       <c r="F68" t="n">
-        <v>23174</v>
+        <v>23325</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -8231,16 +8231,16 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1378.670610924245</v>
+        <v>1378.739440642393</v>
       </c>
       <c r="D69" t="n">
-        <v>1367.489364818274</v>
+        <v>1367.567007342256</v>
       </c>
       <c r="E69" t="n">
-        <v>1389.851857030216</v>
+        <v>1389.911873942531</v>
       </c>
       <c r="F69" t="n">
-        <v>2830</v>
+        <v>2839</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -8302,16 +8302,16 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1378.572343519039</v>
+        <v>1378.695670162175</v>
       </c>
       <c r="D70" t="n">
-        <v>1374.306697357198</v>
+        <v>1374.437630835786</v>
       </c>
       <c r="E70" t="n">
-        <v>1382.83798968088</v>
+        <v>1382.953709488564</v>
       </c>
       <c r="F70" t="n">
-        <v>31201</v>
+        <v>31298</v>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
@@ -8449,16 +8449,16 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1375.244302666996</v>
+        <v>1374.968117831257</v>
       </c>
       <c r="D71" t="n">
-        <v>1370.528059764902</v>
+        <v>1370.260092933062</v>
       </c>
       <c r="E71" t="n">
-        <v>1379.96054556909</v>
+        <v>1379.676142729453</v>
       </c>
       <c r="F71" t="n">
-        <v>25825</v>
+        <v>25953</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -8600,16 +8600,16 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1373.258648228139</v>
+        <v>1373.118763406586</v>
       </c>
       <c r="D72" t="n">
-        <v>1368.995211954967</v>
+        <v>1368.865285518463</v>
       </c>
       <c r="E72" t="n">
-        <v>1377.522084501312</v>
+        <v>1377.372241294708</v>
       </c>
       <c r="F72" t="n">
-        <v>30454</v>
+        <v>30658</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -8671,16 +8671,16 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1369.353773968885</v>
+        <v>1369.289344820399</v>
       </c>
       <c r="D73" t="n">
-        <v>1363.469345867297</v>
+        <v>1363.430376175638</v>
       </c>
       <c r="E73" t="n">
-        <v>1375.238202070474</v>
+        <v>1375.148313465159</v>
       </c>
       <c r="F73" t="n">
-        <v>13371</v>
+        <v>13488</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -8822,16 +8822,16 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1367.300007066523</v>
+        <v>1367.258281518837</v>
       </c>
       <c r="D74" t="n">
-        <v>1362.696367355386</v>
+        <v>1362.664150229943</v>
       </c>
       <c r="E74" t="n">
-        <v>1371.90364677766</v>
+        <v>1371.852412807731</v>
       </c>
       <c r="F74" t="n">
-        <v>30265</v>
+        <v>30365</v>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
@@ -8969,16 +8969,16 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1365.391617962716</v>
+        <v>1365.407160367439</v>
       </c>
       <c r="D75" t="n">
-        <v>1361.680214713408</v>
+        <v>1361.704431907397</v>
       </c>
       <c r="E75" t="n">
-        <v>1369.103021212023</v>
+        <v>1369.109888827482</v>
       </c>
       <c r="F75" t="n">
-        <v>46425</v>
+        <v>46672</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -9120,16 +9120,16 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1364.865916947027</v>
+        <v>1364.678047797861</v>
       </c>
       <c r="D76" t="n">
-        <v>1359.139512192324</v>
+        <v>1358.963189076953</v>
       </c>
       <c r="E76" t="n">
-        <v>1370.59232170173</v>
+        <v>1370.392906518769</v>
       </c>
       <c r="F76" t="n">
-        <v>11977</v>
+        <v>12020</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -9191,16 +9191,16 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1363.942850248035</v>
+        <v>1363.768833190309</v>
       </c>
       <c r="D77" t="n">
-        <v>1359.638159630837</v>
+        <v>1359.477873572556</v>
       </c>
       <c r="E77" t="n">
-        <v>1368.247540865233</v>
+        <v>1368.059792808062</v>
       </c>
       <c r="F77" t="n">
-        <v>34042</v>
+        <v>34313</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -9262,16 +9262,16 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1360.460367387524</v>
+        <v>1360.31244234373</v>
       </c>
       <c r="D78" t="n">
-        <v>1353.326415308176</v>
+        <v>1353.184135401621</v>
       </c>
       <c r="E78" t="n">
-        <v>1367.594319466872</v>
+        <v>1367.440749285838</v>
       </c>
       <c r="F78" t="n">
-        <v>7859</v>
+        <v>7875</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -9413,13 +9413,13 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1358.437628619717</v>
+        <v>1358.433238362033</v>
       </c>
       <c r="D79" t="n">
-        <v>1353.679243697217</v>
+        <v>1353.675457552493</v>
       </c>
       <c r="E79" t="n">
-        <v>1363.196013542217</v>
+        <v>1363.191019171572</v>
       </c>
       <c r="F79" t="n">
         <v>21770</v>
@@ -9564,16 +9564,16 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1356.49558364836</v>
+        <v>1356.232892930213</v>
       </c>
       <c r="D80" t="n">
-        <v>1351.260268817022</v>
+        <v>1351.011349275132</v>
       </c>
       <c r="E80" t="n">
-        <v>1361.730898479698</v>
+        <v>1361.454436585295</v>
       </c>
       <c r="F80" t="n">
-        <v>17348</v>
+        <v>17466</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -9635,16 +9635,16 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1355.781338488142</v>
+        <v>1355.861688086077</v>
       </c>
       <c r="D81" t="n">
-        <v>1347.509743888398</v>
+        <v>1347.604540700712</v>
       </c>
       <c r="E81" t="n">
-        <v>1364.052933087886</v>
+        <v>1364.118835471442</v>
       </c>
       <c r="F81" t="n">
-        <v>5417</v>
+        <v>5435</v>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
@@ -9782,16 +9782,16 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1353.713189842364</v>
+        <v>1353.688072957493</v>
       </c>
       <c r="D82" t="n">
-        <v>1350.233630352496</v>
+        <v>1350.217612412707</v>
       </c>
       <c r="E82" t="n">
-        <v>1357.192749332233</v>
+        <v>1357.15853350228</v>
       </c>
       <c r="F82" t="n">
-        <v>55467</v>
+        <v>55769</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -9853,16 +9853,16 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1352.39406585147</v>
+        <v>1352.024965908695</v>
       </c>
       <c r="D83" t="n">
-        <v>1343.944182109022</v>
+        <v>1343.590329812661</v>
       </c>
       <c r="E83" t="n">
-        <v>1360.843949593917</v>
+        <v>1360.45960200473</v>
       </c>
       <c r="F83" t="n">
-        <v>4807</v>
+        <v>4824</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -9924,16 +9924,16 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1351.577517951259</v>
+        <v>1351.824252721032</v>
       </c>
       <c r="D84" t="n">
-        <v>1347.197819499163</v>
+        <v>1347.460018555976</v>
       </c>
       <c r="E84" t="n">
-        <v>1355.957216403356</v>
+        <v>1356.188486886089</v>
       </c>
       <c r="F84" t="n">
-        <v>30018</v>
+        <v>30218</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -10075,16 +10075,16 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1349.509573329841</v>
+        <v>1349.39589531772</v>
       </c>
       <c r="D85" t="n">
-        <v>1343.475848619422</v>
+        <v>1343.59292164096</v>
       </c>
       <c r="E85" t="n">
-        <v>1355.543298040261</v>
+        <v>1355.198868994481</v>
       </c>
       <c r="F85" t="n">
-        <v>14877</v>
+        <v>17120</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -10226,16 +10226,16 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1349.395869032312</v>
+        <v>1349.096931594353</v>
       </c>
       <c r="D86" t="n">
-        <v>1341.864782153641</v>
+        <v>1341.582966658337</v>
       </c>
       <c r="E86" t="n">
-        <v>1356.926955910984</v>
+        <v>1356.610896530369</v>
       </c>
       <c r="F86" t="n">
-        <v>6266</v>
+        <v>6292</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -10297,13 +10297,13 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1347.622305137077</v>
+        <v>1347.593079617044</v>
       </c>
       <c r="D87" t="n">
-        <v>1335.943050366683</v>
+        <v>1335.915320681713</v>
       </c>
       <c r="E87" t="n">
-        <v>1359.301559907471</v>
+        <v>1359.270838552375</v>
       </c>
       <c r="F87" t="n">
         <v>2549</v>
@@ -10448,13 +10448,13 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1346.927857741671</v>
+        <v>1346.878810149268</v>
       </c>
       <c r="D88" t="n">
-        <v>1337.469985591327</v>
+        <v>1337.421952724142</v>
       </c>
       <c r="E88" t="n">
-        <v>1356.385729892014</v>
+        <v>1356.335667574393</v>
       </c>
       <c r="F88" t="n">
         <v>3926</v>
@@ -10599,16 +10599,16 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1343.783896577042</v>
+        <v>1343.555100041403</v>
       </c>
       <c r="D89" t="n">
-        <v>1336.470594818567</v>
+        <v>1336.277400374531</v>
       </c>
       <c r="E89" t="n">
-        <v>1351.097198335518</v>
+        <v>1350.832799708275</v>
       </c>
       <c r="F89" t="n">
-        <v>6887</v>
+        <v>6951</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -10670,16 +10670,16 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1343.36584929888</v>
+        <v>1343.312168477375</v>
       </c>
       <c r="D90" t="n">
-        <v>1335.607179368292</v>
+        <v>1335.572545290405</v>
       </c>
       <c r="E90" t="n">
-        <v>1351.124519229469</v>
+        <v>1351.051791664345</v>
       </c>
       <c r="F90" t="n">
-        <v>6817</v>
+        <v>6860</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -10821,16 +10821,16 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1342.897164861398</v>
+        <v>1343.125340765463</v>
       </c>
       <c r="D91" t="n">
-        <v>1332.876545425546</v>
+        <v>1333.131722072919</v>
       </c>
       <c r="E91" t="n">
-        <v>1352.917784297249</v>
+        <v>1353.118959458007</v>
       </c>
       <c r="F91" t="n">
-        <v>3308</v>
+        <v>3327</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -10972,13 +10972,13 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1341.760404881006</v>
+        <v>1341.801295598512</v>
       </c>
       <c r="D92" t="n">
-        <v>1332.248569694422</v>
+        <v>1332.290470483739</v>
       </c>
       <c r="E92" t="n">
-        <v>1351.272240067591</v>
+        <v>1351.312120713286</v>
       </c>
       <c r="F92" t="n">
         <v>3829</v>
@@ -11123,16 +11123,16 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1339.550750915539</v>
+        <v>1339.667087241409</v>
       </c>
       <c r="D93" t="n">
-        <v>1329.066663270803</v>
+        <v>1329.196928727499</v>
       </c>
       <c r="E93" t="n">
-        <v>1350.034838560275</v>
+        <v>1350.137245755318</v>
       </c>
       <c r="F93" t="n">
-        <v>3401</v>
+        <v>3410</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -11274,16 +11274,16 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1335.761256700982</v>
+        <v>1335.652266054496</v>
       </c>
       <c r="D94" t="n">
-        <v>1331.293127086844</v>
+        <v>1331.191334392331</v>
       </c>
       <c r="E94" t="n">
-        <v>1340.22938631512</v>
+        <v>1340.113197716661</v>
       </c>
       <c r="F94" t="n">
-        <v>25078</v>
+        <v>25181</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -11425,13 +11425,13 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1335.36786147857</v>
+        <v>1335.411484884282</v>
       </c>
       <c r="D95" t="n">
-        <v>1331.636344097256</v>
+        <v>1331.680822238851</v>
       </c>
       <c r="E95" t="n">
-        <v>1339.099378859883</v>
+        <v>1339.142147529713</v>
       </c>
       <c r="F95" t="n">
         <v>41375</v>
@@ -11576,13 +11576,13 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1333.50272309109</v>
+        <v>1333.563182459957</v>
       </c>
       <c r="D96" t="n">
-        <v>1329.896416244613</v>
+        <v>1329.958151074828</v>
       </c>
       <c r="E96" t="n">
-        <v>1337.109029937566</v>
+        <v>1337.168213845087</v>
       </c>
       <c r="F96" t="n">
         <v>59656</v>
@@ -11727,16 +11727,16 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1329.193621212394</v>
+        <v>1329.269895972923</v>
       </c>
       <c r="D97" t="n">
-        <v>1323.0479856947</v>
+        <v>1323.129437934756</v>
       </c>
       <c r="E97" t="n">
-        <v>1335.339256730088</v>
+        <v>1335.41035401109</v>
       </c>
       <c r="F97" t="n">
-        <v>11801</v>
+        <v>11820</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -11878,13 +11878,13 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1327.794106135701</v>
+        <v>1327.77006623933</v>
       </c>
       <c r="D98" t="n">
-        <v>1315.660012823035</v>
+        <v>1315.637978067623</v>
       </c>
       <c r="E98" t="n">
-        <v>1339.928199448367</v>
+        <v>1339.902154411037</v>
       </c>
       <c r="F98" t="n">
         <v>2218</v>
@@ -12029,16 +12029,16 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1326.977863849166</v>
+        <v>1326.968363768185</v>
       </c>
       <c r="D99" t="n">
-        <v>1322.692349849318</v>
+        <v>1322.690594945479</v>
       </c>
       <c r="E99" t="n">
-        <v>1331.263377849013</v>
+        <v>1331.246132590891</v>
       </c>
       <c r="F99" t="n">
-        <v>39262</v>
+        <v>39453</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -12180,16 +12180,16 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1326.462985457504</v>
+        <v>1326.620633720609</v>
       </c>
       <c r="D100" t="n">
-        <v>1321.703680796824</v>
+        <v>1321.872522167025</v>
       </c>
       <c r="E100" t="n">
-        <v>1331.222290118184</v>
+        <v>1331.368745274194</v>
       </c>
       <c r="F100" t="n">
-        <v>26037</v>
+        <v>26160</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -12331,13 +12331,13 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1323.384603855063</v>
+        <v>1323.389119896954</v>
       </c>
       <c r="D101" t="n">
-        <v>1315.111215855622</v>
+        <v>1315.116694958672</v>
       </c>
       <c r="E101" t="n">
-        <v>1331.657991854504</v>
+        <v>1331.661544835236</v>
       </c>
       <c r="F101" t="n">
         <v>6795</v>
@@ -12402,16 +12402,16 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1322.584028382245</v>
+        <v>1322.758791852063</v>
       </c>
       <c r="D102" t="n">
-        <v>1315.281431544685</v>
+        <v>1315.484615750897</v>
       </c>
       <c r="E102" t="n">
-        <v>1329.886625219805</v>
+        <v>1330.032967953227</v>
       </c>
       <c r="F102" t="n">
-        <v>6932</v>
+        <v>6993</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -12473,16 +12473,16 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1321.764950535163</v>
+        <v>1322.025748525692</v>
       </c>
       <c r="D103" t="n">
-        <v>1300.572010467282</v>
+        <v>1300.919116036775</v>
       </c>
       <c r="E103" t="n">
-        <v>1342.957890603044</v>
+        <v>1343.132381014609</v>
       </c>
       <c r="F103" t="n">
-        <v>818</v>
+        <v>823</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -12624,16 +12624,16 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1321.638571622781</v>
+        <v>1321.52448891846</v>
       </c>
       <c r="D104" t="n">
-        <v>1316.894176724808</v>
+        <v>1316.788895596217</v>
       </c>
       <c r="E104" t="n">
-        <v>1326.382966520754</v>
+        <v>1326.260082240703</v>
       </c>
       <c r="F104" t="n">
-        <v>29667</v>
+        <v>29836</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -12775,13 +12775,13 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1318.084979923916</v>
+        <v>1318.101084000794</v>
       </c>
       <c r="D105" t="n">
-        <v>1312.381061635663</v>
+        <v>1312.39813224029</v>
       </c>
       <c r="E105" t="n">
-        <v>1323.788898212169</v>
+        <v>1323.804035761298</v>
       </c>
       <c r="F105" t="n">
         <v>16478</v>
@@ -12846,16 +12846,16 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1317.797560825658</v>
+        <v>1318.02455803514</v>
       </c>
       <c r="D106" t="n">
-        <v>1314.287170192333</v>
+        <v>1314.520875965425</v>
       </c>
       <c r="E106" t="n">
-        <v>1321.307951458983</v>
+        <v>1321.528240104855</v>
       </c>
       <c r="F106" t="n">
-        <v>54366</v>
+        <v>54504</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -12993,64 +12993,64 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>gpt-oss-20b</t>
+          <t>gemma-3n-e4b-it</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1317.584094038728</v>
+        <v>1317.51554658442</v>
       </c>
       <c r="D107" t="n">
-        <v>1311.161501828368</v>
+        <v>1312.333780627755</v>
       </c>
       <c r="E107" t="n">
-        <v>1324.006686249088</v>
+        <v>1322.697312541085</v>
       </c>
       <c r="F107" t="n">
-        <v>10368</v>
+        <v>22145</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>Gemma</t>
         </is>
       </c>
       <c r="I107" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="J107" t="n">
+        <v>4</v>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>aa_single_scrape</t>
+        </is>
+      </c>
+      <c r="M107" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="N107" t="n">
         <v>21</v>
       </c>
-      <c r="J107" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>override</t>
-        </is>
-      </c>
-      <c r="M107" t="n">
-        <v>42</v>
-      </c>
-      <c r="N107" t="n">
-        <v>52.5</v>
-      </c>
       <c r="O107" t="n">
-        <v>21</v>
+        <v>8.4</v>
       </c>
       <c r="P107" t="n">
-        <v>26.2</v>
+        <v>10.5</v>
       </c>
       <c r="Q107" t="n">
-        <v>10.5</v>
+        <v>4.2</v>
       </c>
       <c r="R107" t="n">
-        <v>13.1</v>
+        <v>5.2</v>
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
@@ -13144,36 +13144,36 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>gemma-3n-e4b-it</t>
+          <t>gpt-oss-20b</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1317.417745599214</v>
+        <v>1317.34874233002</v>
       </c>
       <c r="D108" t="n">
-        <v>1312.225565789352</v>
+        <v>1310.933910904282</v>
       </c>
       <c r="E108" t="n">
-        <v>1322.609925409078</v>
+        <v>1323.763573755758</v>
       </c>
       <c r="F108" t="n">
-        <v>22042</v>
+        <v>10418</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Gemma</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I108" t="n">
-        <v>8.4</v>
+        <v>21</v>
       </c>
       <c r="J108" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
@@ -13182,26 +13182,26 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>aa_single_scrape</t>
+          <t>override</t>
         </is>
       </c>
       <c r="M108" t="n">
-        <v>16.8</v>
+        <v>42</v>
       </c>
       <c r="N108" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="O108" t="n">
         <v>21</v>
       </c>
-      <c r="O108" t="n">
-        <v>8.4</v>
-      </c>
       <c r="P108" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="Q108" t="n">
         <v>10.5</v>
       </c>
-      <c r="Q108" t="n">
-        <v>4.2</v>
-      </c>
       <c r="R108" t="n">
-        <v>5.2</v>
+        <v>13.1</v>
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
@@ -13299,13 +13299,13 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1314.373014387154</v>
+        <v>1314.39631637599</v>
       </c>
       <c r="D109" t="n">
-        <v>1310.438075426826</v>
+        <v>1310.462529361907</v>
       </c>
       <c r="E109" t="n">
-        <v>1318.307953347482</v>
+        <v>1318.330103390074</v>
       </c>
       <c r="F109" t="n">
         <v>45459</v>
@@ -13450,13 +13450,13 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1314.144012356593</v>
+        <v>1314.152014517205</v>
       </c>
       <c r="D110" t="n">
-        <v>1309.576986013699</v>
+        <v>1309.585692051056</v>
       </c>
       <c r="E110" t="n">
-        <v>1318.711038699486</v>
+        <v>1318.718336983353</v>
       </c>
       <c r="F110" t="n">
         <v>24739</v>
@@ -13597,16 +13597,16 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1313.534004829241</v>
+        <v>1313.655815262937</v>
       </c>
       <c r="D111" t="n">
-        <v>1308.046485207478</v>
+        <v>1308.17789258603</v>
       </c>
       <c r="E111" t="n">
-        <v>1319.021524451004</v>
+        <v>1319.133737939844</v>
       </c>
       <c r="F111" t="n">
-        <v>15722</v>
+        <v>15779</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -13748,13 +13748,13 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1307.180088166303</v>
+        <v>1307.177160461887</v>
       </c>
       <c r="D112" t="n">
-        <v>1302.466201073729</v>
+        <v>1302.464268522681</v>
       </c>
       <c r="E112" t="n">
-        <v>1311.893975258877</v>
+        <v>1311.890052401092</v>
       </c>
       <c r="F112" t="n">
         <v>24572</v>
@@ -13819,13 +13819,13 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1306.592694099909</v>
+        <v>1306.626078078489</v>
       </c>
       <c r="D113" t="n">
-        <v>1300.916871056803</v>
+        <v>1300.951379691755</v>
       </c>
       <c r="E113" t="n">
-        <v>1312.268517143015</v>
+        <v>1312.300776465224</v>
       </c>
       <c r="F113" t="n">
         <v>19621</v>
@@ -13966,16 +13966,16 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1306.352310105346</v>
+        <v>1306.272199533137</v>
       </c>
       <c r="D114" t="n">
-        <v>1298.098944288148</v>
+        <v>1298.029125437992</v>
       </c>
       <c r="E114" t="n">
-        <v>1314.605675922543</v>
+        <v>1314.515273628281</v>
       </c>
       <c r="F114" t="n">
-        <v>5811</v>
+        <v>5830</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -14117,13 +14117,13 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1305.536112701126</v>
+        <v>1305.543944342693</v>
       </c>
       <c r="D115" t="n">
-        <v>1301.080234217781</v>
+        <v>1301.088581115976</v>
       </c>
       <c r="E115" t="n">
-        <v>1309.991991184471</v>
+        <v>1309.99930756941</v>
       </c>
       <c r="F115" t="n">
         <v>28073</v>
@@ -14188,16 +14188,16 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1304.0675680601</v>
+        <v>1304.023590137556</v>
       </c>
       <c r="D116" t="n">
-        <v>1294.034737437274</v>
+        <v>1294.02117886192</v>
       </c>
       <c r="E116" t="n">
-        <v>1314.100398682927</v>
+        <v>1314.026001413193</v>
       </c>
       <c r="F116" t="n">
-        <v>4161</v>
+        <v>4184</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -14339,13 +14339,13 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1303.244346900854</v>
+        <v>1303.28225024806</v>
       </c>
       <c r="D117" t="n">
-        <v>1293.926814233014</v>
+        <v>1293.965756709036</v>
       </c>
       <c r="E117" t="n">
-        <v>1312.561879568695</v>
+        <v>1312.598743787084</v>
       </c>
       <c r="F117" t="n">
         <v>4171</v>
@@ -14486,36 +14486,36 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>mistral-small-3.1-24b-instruct-2503</t>
+          <t>qwen2.5-72b-instruct</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1303.117121515517</v>
+        <v>1302.858187475445</v>
       </c>
       <c r="D118" t="n">
-        <v>1298.566530601817</v>
+        <v>1298.770526671143</v>
       </c>
       <c r="E118" t="n">
-        <v>1307.667712429218</v>
+        <v>1306.945848279747</v>
       </c>
       <c r="F118" t="n">
-        <v>32551</v>
+        <v>39406</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Mistral</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>Qwen</t>
         </is>
       </c>
       <c r="I118" t="n">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="J118" t="n">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
@@ -14528,26 +14528,26 @@
         </is>
       </c>
       <c r="M118" t="n">
-        <v>48</v>
+        <v>144</v>
       </c>
       <c r="N118" t="n">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="O118" t="n">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="P118" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="Q118" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="R118" t="n">
-        <v>15</v>
-      </c>
-      <c r="S118" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>45</v>
+      </c>
+      <c r="S118" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="T118" s="4" t="inlineStr">
@@ -14560,14 +14560,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V118" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W118" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="V118" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W118" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="X118" s="4" t="inlineStr">
@@ -14575,9 +14575,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y118" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="Y118" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="Z118" s="4" t="inlineStr">
@@ -14622,12 +14622,12 @@
       </c>
       <c r="AH118" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>B200 SXM</t>
         </is>
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>RTX PRO 6000</t>
         </is>
       </c>
     </row>
@@ -14637,36 +14637,36 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>qwen2.5-72b-instruct</t>
+          <t>mistral-small-3.1-24b-instruct-2503</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1302.849153314428</v>
+        <v>1302.844996161062</v>
       </c>
       <c r="D119" t="n">
-        <v>1298.760641517745</v>
+        <v>1298.304072434966</v>
       </c>
       <c r="E119" t="n">
-        <v>1306.93766511111</v>
+        <v>1307.385919887158</v>
       </c>
       <c r="F119" t="n">
-        <v>39406</v>
+        <v>32744</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Mistral</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Qwen</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I119" t="n">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="J119" t="n">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
@@ -14679,26 +14679,26 @@
         </is>
       </c>
       <c r="M119" t="n">
-        <v>144</v>
+        <v>48</v>
       </c>
       <c r="N119" t="n">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="O119" t="n">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="P119" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="Q119" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="R119" t="n">
-        <v>45</v>
-      </c>
-      <c r="S119" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>15</v>
+      </c>
+      <c r="S119" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="T119" s="4" t="inlineStr">
@@ -14711,14 +14711,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V119" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W119" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="V119" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W119" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="X119" s="4" t="inlineStr">
@@ -14726,9 +14726,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y119" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="Y119" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Z119" s="4" t="inlineStr">
@@ -14773,12 +14773,12 @@
       </c>
       <c r="AH119" t="inlineStr">
         <is>
-          <t>B200 SXM</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>RTX PRO 6000</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -14792,13 +14792,13 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1298.730329929532</v>
+        <v>1298.76669785577</v>
       </c>
       <c r="D120" t="n">
-        <v>1290.967383909811</v>
+        <v>1291.004775599771</v>
       </c>
       <c r="E120" t="n">
-        <v>1306.493275949254</v>
+        <v>1306.528620111769</v>
       </c>
       <c r="F120" t="n">
         <v>7140</v>
@@ -14943,13 +14943,13 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1293.318741333559</v>
+        <v>1293.363645727252</v>
       </c>
       <c r="D121" t="n">
-        <v>1289.570414415427</v>
+        <v>1289.61642431772</v>
       </c>
       <c r="E121" t="n">
-        <v>1297.06706825169</v>
+        <v>1297.110867136785</v>
       </c>
       <c r="F121" t="n">
         <v>55240</v>
@@ -15090,20 +15090,20 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>granite-4.2-3b</t>
+          <t>granite-4.2-8b</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1289.522494910676</v>
+        <v>1290.216976483155</v>
       </c>
       <c r="D122" t="n">
-        <v>1277.91627908977</v>
+        <v>1279.050833352174</v>
       </c>
       <c r="E122" t="n">
-        <v>1301.128710731582</v>
+        <v>1301.383119614135</v>
       </c>
       <c r="F122" t="n">
-        <v>3247</v>
+        <v>3253</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -15116,10 +15116,10 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J122" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
@@ -15132,22 +15132,22 @@
         </is>
       </c>
       <c r="M122" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="N122" t="n">
-        <v>7.5</v>
+        <v>20</v>
       </c>
       <c r="O122" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P122" t="n">
-        <v>3.8</v>
+        <v>10</v>
       </c>
       <c r="Q122" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="R122" t="n">
-        <v>1.9</v>
+        <v>5</v>
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
@@ -15241,36 +15241,36 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>gemma-2-27b-it</t>
+          <t>granite-4.2-3b</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1289.42769713196</v>
+        <v>1289.578936706166</v>
       </c>
       <c r="D123" t="n">
-        <v>1286.0303729711</v>
+        <v>1277.967466651478</v>
       </c>
       <c r="E123" t="n">
-        <v>1292.82502129282</v>
+        <v>1301.190406760853</v>
       </c>
       <c r="F123" t="n">
-        <v>75754</v>
+        <v>3251</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Gemma license</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I123" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="J123" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
@@ -15283,22 +15283,22 @@
         </is>
       </c>
       <c r="M123" t="n">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="N123" t="n">
-        <v>67.5</v>
+        <v>7.5</v>
       </c>
       <c r="O123" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="P123" t="n">
-        <v>33.8</v>
+        <v>3.8</v>
       </c>
       <c r="Q123" t="n">
-        <v>13.5</v>
+        <v>1.5</v>
       </c>
       <c r="R123" t="n">
-        <v>16.9</v>
+        <v>1.9</v>
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
@@ -15392,64 +15392,148 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>jamba-1.5-large</t>
+          <t>gemma-2-27b-it</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1289.424524238361</v>
+        <v>1289.447988295805</v>
       </c>
       <c r="D124" t="n">
-        <v>1282.118979207166</v>
+        <v>1286.051789237339</v>
       </c>
       <c r="E124" t="n">
-        <v>1296.730069269556</v>
+        <v>1292.844187354271</v>
       </c>
       <c r="F124" t="n">
-        <v>8662</v>
-      </c>
-      <c r="G124" t="inlineStr"/>
+        <v>75754</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Jamba Open</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
+          <t>Gemma license</t>
+        </is>
+      </c>
+      <c r="I124" t="n">
+        <v>27</v>
+      </c>
+      <c r="J124" t="n">
+        <v>27</v>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>dense</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
-      <c r="O124" t="inlineStr"/>
-      <c r="P124" t="inlineStr"/>
-      <c r="Q124" t="inlineStr"/>
-      <c r="R124" t="inlineStr"/>
-      <c r="S124" t="inlineStr"/>
-      <c r="T124" t="inlineStr"/>
-      <c r="U124" t="inlineStr"/>
-      <c r="V124" t="inlineStr"/>
-      <c r="W124" t="inlineStr"/>
-      <c r="X124" t="inlineStr"/>
-      <c r="Y124" t="inlineStr"/>
-      <c r="Z124" t="inlineStr"/>
-      <c r="AA124" t="inlineStr"/>
-      <c r="AB124" t="inlineStr"/>
-      <c r="AC124" t="inlineStr"/>
-      <c r="AD124" t="inlineStr"/>
-      <c r="AE124" t="inlineStr"/>
-      <c r="AF124" t="inlineStr"/>
-      <c r="AG124" t="inlineStr"/>
+          <t>name_parsing</t>
+        </is>
+      </c>
+      <c r="M124" t="n">
+        <v>54</v>
+      </c>
+      <c r="N124" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="O124" t="n">
+        <v>27</v>
+      </c>
+      <c r="P124" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="R124" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="S124" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T124" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U124" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V124" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W124" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X124" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y124" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z124" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA124" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB124" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC124" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD124" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE124" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF124" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG124" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH124" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -15459,148 +15543,64 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>granite-4.2-8b</t>
+          <t>jamba-1.5-large</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1288.13289356819</v>
+        <v>1289.42954591615</v>
       </c>
       <c r="D125" t="n">
-        <v>1276.941956890217</v>
+        <v>1282.125138211305</v>
       </c>
       <c r="E125" t="n">
-        <v>1299.323830246162</v>
+        <v>1296.733953620996</v>
       </c>
       <c r="F125" t="n">
-        <v>3237</v>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>IBM</t>
-        </is>
-      </c>
+        <v>8662</v>
+      </c>
+      <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
-        </is>
-      </c>
-      <c r="I125" t="n">
-        <v>8</v>
-      </c>
-      <c r="J125" t="n">
-        <v>8</v>
-      </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>dense</t>
-        </is>
-      </c>
+          <t>Jamba Open</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr">
         <is>
-          <t>name_parsing</t>
-        </is>
-      </c>
-      <c r="M125" t="n">
-        <v>16</v>
-      </c>
-      <c r="N125" t="n">
-        <v>20</v>
-      </c>
-      <c r="O125" t="n">
-        <v>8</v>
-      </c>
-      <c r="P125" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q125" t="n">
-        <v>4</v>
-      </c>
-      <c r="R125" t="n">
-        <v>5</v>
-      </c>
-      <c r="S125" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T125" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U125" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V125" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W125" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X125" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y125" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z125" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA125" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB125" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC125" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD125" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE125" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF125" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG125" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr"/>
+      <c r="P125" t="inlineStr"/>
+      <c r="Q125" t="inlineStr"/>
+      <c r="R125" t="inlineStr"/>
+      <c r="S125" t="inlineStr"/>
+      <c r="T125" t="inlineStr"/>
+      <c r="U125" t="inlineStr"/>
+      <c r="V125" t="inlineStr"/>
+      <c r="W125" t="inlineStr"/>
+      <c r="X125" t="inlineStr"/>
+      <c r="Y125" t="inlineStr"/>
+      <c r="Z125" t="inlineStr"/>
+      <c r="AA125" t="inlineStr"/>
+      <c r="AB125" t="inlineStr"/>
+      <c r="AC125" t="inlineStr"/>
+      <c r="AD125" t="inlineStr"/>
+      <c r="AE125" t="inlineStr"/>
+      <c r="AF125" t="inlineStr"/>
+      <c r="AG125" t="inlineStr"/>
       <c r="AH125" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI125" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -15614,16 +15614,16 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1286.958823775603</v>
+        <v>1287.249834797396</v>
       </c>
       <c r="D126" t="n">
-        <v>1278.504912017922</v>
+        <v>1278.851673219427</v>
       </c>
       <c r="E126" t="n">
-        <v>1295.412735533285</v>
+        <v>1295.647996375365</v>
       </c>
       <c r="F126" t="n">
-        <v>5576</v>
+        <v>5635</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -15761,36 +15761,36 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>llama-3.1-nemotron-51b-instruct</t>
+          <t>olmo-3.1-32b-think</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1286.562353098289</v>
+        <v>1286.813447310703</v>
       </c>
       <c r="D127" t="n">
-        <v>1276.596220804974</v>
+        <v>1279.551461348296</v>
       </c>
       <c r="E127" t="n">
-        <v>1296.528485391603</v>
+        <v>1294.07543327311</v>
       </c>
       <c r="F127" t="n">
-        <v>3749</v>
+        <v>8301</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Ai2</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Llama 3.1</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I127" t="n">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="J127" t="n">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
@@ -15803,26 +15803,26 @@
         </is>
       </c>
       <c r="M127" t="n">
-        <v>102</v>
+        <v>64</v>
       </c>
       <c r="N127" t="n">
-        <v>127.5</v>
+        <v>80</v>
       </c>
       <c r="O127" t="n">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="P127" t="n">
-        <v>63.8</v>
+        <v>40</v>
       </c>
       <c r="Q127" t="n">
-        <v>25.5</v>
+        <v>16</v>
       </c>
       <c r="R127" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="S127" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>20</v>
+      </c>
+      <c r="S127" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="T127" s="4" t="inlineStr">
@@ -15835,9 +15835,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V127" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="V127" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W127" s="4" t="inlineStr">
@@ -15897,7 +15897,7 @@
       </c>
       <c r="AH127" t="inlineStr">
         <is>
-          <t>H200 SXM</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI127" t="inlineStr">
@@ -15912,36 +15912,36 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>olmo-3.1-32b-think</t>
+          <t>llama-3.1-nemotron-51b-instruct</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1286.448609685453</v>
+        <v>1286.610035792815</v>
       </c>
       <c r="D128" t="n">
-        <v>1279.173157834842</v>
+        <v>1276.645294122894</v>
       </c>
       <c r="E128" t="n">
-        <v>1293.724061536063</v>
+        <v>1296.574777462735</v>
       </c>
       <c r="F128" t="n">
-        <v>8278</v>
+        <v>3749</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Ai2</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>Llama 3.1</t>
         </is>
       </c>
       <c r="I128" t="n">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="J128" t="n">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
@@ -15954,26 +15954,26 @@
         </is>
       </c>
       <c r="M128" t="n">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="N128" t="n">
-        <v>80</v>
+        <v>127.5</v>
       </c>
       <c r="O128" t="n">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="P128" t="n">
-        <v>40</v>
+        <v>63.8</v>
       </c>
       <c r="Q128" t="n">
-        <v>16</v>
+        <v>25.5</v>
       </c>
       <c r="R128" t="n">
-        <v>20</v>
-      </c>
-      <c r="S128" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>31.9</v>
+      </c>
+      <c r="S128" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="T128" s="4" t="inlineStr">
@@ -15986,9 +15986,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V128" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="V128" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="W128" s="4" t="inlineStr">
@@ -16048,7 +16048,7 @@
       </c>
       <c r="AH128" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>H200 SXM</t>
         </is>
       </c>
       <c r="AI128" t="inlineStr">
@@ -16067,13 +16067,13 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1286.063810555537</v>
+        <v>1286.119461395069</v>
       </c>
       <c r="D129" t="n">
-        <v>1275.604880944859</v>
+        <v>1275.661869263562</v>
       </c>
       <c r="E129" t="n">
-        <v>1296.522740166215</v>
+        <v>1296.577053526576</v>
       </c>
       <c r="F129" t="n">
         <v>2846</v>
@@ -16218,13 +16218,13 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1280.346252379516</v>
+        <v>1280.358558582015</v>
       </c>
       <c r="D130" t="n">
-        <v>1273.48851888011</v>
+        <v>1273.502051847493</v>
       </c>
       <c r="E130" t="n">
-        <v>1287.203985878922</v>
+        <v>1287.215065316537</v>
       </c>
       <c r="F130" t="n">
         <v>10072</v>
@@ -16365,13 +16365,13 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1277.098749058932</v>
+        <v>1277.159080299727</v>
       </c>
       <c r="D131" t="n">
-        <v>1271.779651472364</v>
+        <v>1271.841615376696</v>
       </c>
       <c r="E131" t="n">
-        <v>1282.4178466455</v>
+        <v>1282.476545222758</v>
       </c>
       <c r="F131" t="n">
         <v>19659</v>
@@ -16516,13 +16516,13 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1276.504938680578</v>
+        <v>1276.553306487852</v>
       </c>
       <c r="D132" t="n">
-        <v>1272.918330680802</v>
+        <v>1272.968430279146</v>
       </c>
       <c r="E132" t="n">
-        <v>1280.091546680354</v>
+        <v>1280.138182696557</v>
       </c>
       <c r="F132" t="n">
         <v>156876</v>
@@ -16667,13 +16667,13 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1276.258892122072</v>
+        <v>1276.312069635339</v>
       </c>
       <c r="D133" t="n">
-        <v>1269.680021839597</v>
+        <v>1269.734348581735</v>
       </c>
       <c r="E133" t="n">
-        <v>1282.837762404546</v>
+        <v>1282.889790688942</v>
       </c>
       <c r="F133" t="n">
         <v>9866</v>
@@ -16818,13 +16818,13 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1274.374365475218</v>
+        <v>1274.369451602471</v>
       </c>
       <c r="D134" t="n">
-        <v>1268.453034976254</v>
+        <v>1268.448705535433</v>
       </c>
       <c r="E134" t="n">
-        <v>1280.295695974181</v>
+        <v>1280.290197669509</v>
       </c>
       <c r="F134" t="n">
         <v>14681</v>
@@ -16969,13 +16969,13 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1270.580978224246</v>
+        <v>1270.606382614817</v>
       </c>
       <c r="D135" t="n">
-        <v>1262.452082534718</v>
+        <v>1262.478506548705</v>
       </c>
       <c r="E135" t="n">
-        <v>1278.709873913773</v>
+        <v>1278.73425868093</v>
       </c>
       <c r="F135" t="n">
         <v>5432</v>
@@ -17120,13 +17120,13 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1267.208553138808</v>
+        <v>1267.255037008777</v>
       </c>
       <c r="D136" t="n">
-        <v>1262.308098316373</v>
+        <v>1262.355410486415</v>
       </c>
       <c r="E136" t="n">
-        <v>1272.109007961243</v>
+        <v>1272.154663531139</v>
       </c>
       <c r="F136" t="n">
         <v>27124</v>
@@ -17271,13 +17271,13 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1266.955393426152</v>
+        <v>1266.973465248333</v>
       </c>
       <c r="D137" t="n">
-        <v>1263.123001180984</v>
+        <v>1263.142118946887</v>
       </c>
       <c r="E137" t="n">
-        <v>1270.78778567132</v>
+        <v>1270.804811549778</v>
       </c>
       <c r="F137" t="n">
         <v>54611</v>
@@ -17422,13 +17422,13 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1265.32338831685</v>
+        <v>1265.334270301796</v>
       </c>
       <c r="D138" t="n">
-        <v>1259.049503047833</v>
+        <v>1259.061856862598</v>
       </c>
       <c r="E138" t="n">
-        <v>1271.597273585868</v>
+        <v>1271.606683740994</v>
       </c>
       <c r="F138" t="n">
         <v>15147</v>
@@ -17573,13 +17573,13 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1261.778422810805</v>
+        <v>1261.817530853083</v>
       </c>
       <c r="D139" t="n">
-        <v>1256.830252051908</v>
+        <v>1256.870735072627</v>
       </c>
       <c r="E139" t="n">
-        <v>1266.726593569702</v>
+        <v>1266.764326633539</v>
       </c>
       <c r="F139" t="n">
         <v>37325</v>
@@ -17724,13 +17724,13 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1261.725252525771</v>
+        <v>1261.776442730933</v>
       </c>
       <c r="D140" t="n">
-        <v>1257.406965785593</v>
+        <v>1257.459984835166</v>
       </c>
       <c r="E140" t="n">
-        <v>1266.043539265949</v>
+        <v>1266.0929006267</v>
       </c>
       <c r="F140" t="n">
         <v>77554</v>
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>1256.271010215897</v>
+        <v>1256.280981094604</v>
       </c>
       <c r="D141" t="n">
-        <v>1251.660350322239</v>
+        <v>1251.670925645535</v>
       </c>
       <c r="E141" t="n">
-        <v>1260.881670109555</v>
+        <v>1260.891036543674</v>
       </c>
       <c r="F141" t="n">
         <v>24126</v>
@@ -17946,13 +17946,13 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1251.646552959719</v>
+        <v>1251.669031792788</v>
       </c>
       <c r="D142" t="n">
-        <v>1240.870054185521</v>
+        <v>1240.893945200454</v>
       </c>
       <c r="E142" t="n">
-        <v>1262.423051733917</v>
+        <v>1262.444118385122</v>
       </c>
       <c r="F142" t="n">
         <v>3334</v>
@@ -18097,13 +18097,13 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>1250.371488195612</v>
+        <v>1250.417391959581</v>
       </c>
       <c r="D143" t="n">
-        <v>1243.767945729197</v>
+        <v>1243.815112815472</v>
       </c>
       <c r="E143" t="n">
-        <v>1256.975030662026</v>
+        <v>1257.019671103689</v>
       </c>
       <c r="F143" t="n">
         <v>10140</v>
@@ -18248,13 +18248,13 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>1239.74189556354</v>
+        <v>1239.758947274614</v>
       </c>
       <c r="D144" t="n">
-        <v>1232.516016144089</v>
+        <v>1232.534337609302</v>
       </c>
       <c r="E144" t="n">
-        <v>1246.967774982991</v>
+        <v>1246.983556939925</v>
       </c>
       <c r="F144" t="n">
         <v>8858</v>
@@ -18315,13 +18315,13 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1237.576477314295</v>
+        <v>1237.592667757809</v>
       </c>
       <c r="D145" t="n">
-        <v>1228.488150784239</v>
+        <v>1228.505665212135</v>
       </c>
       <c r="E145" t="n">
-        <v>1246.664803844352</v>
+        <v>1246.679670303483</v>
       </c>
       <c r="F145" t="n">
         <v>4781</v>
@@ -18466,13 +18466,13 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>1234.138241456109</v>
+        <v>1234.174687243857</v>
       </c>
       <c r="D146" t="n">
-        <v>1228.592238253344</v>
+        <v>1228.630309047301</v>
       </c>
       <c r="E146" t="n">
-        <v>1239.684244658874</v>
+        <v>1239.719065440412</v>
       </c>
       <c r="F146" t="n">
         <v>26195</v>
@@ -18617,13 +18617,13 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>1233.476897940968</v>
+        <v>1233.521025311506</v>
       </c>
       <c r="D147" t="n">
-        <v>1228.210370908478</v>
+        <v>1228.25629553415</v>
       </c>
       <c r="E147" t="n">
-        <v>1238.743424973458</v>
+        <v>1238.785755088862</v>
       </c>
       <c r="F147" t="n">
         <v>39302</v>
@@ -18768,13 +18768,13 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1229.538174750901</v>
+        <v>1229.583164675144</v>
       </c>
       <c r="D148" t="n">
-        <v>1224.983526550104</v>
+        <v>1225.030130992563</v>
       </c>
       <c r="E148" t="n">
-        <v>1234.092822951697</v>
+        <v>1234.136198357725</v>
       </c>
       <c r="F148" t="n">
         <v>51416</v>
@@ -18919,13 +18919,13 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1226.825645809424</v>
+        <v>1226.873594606291</v>
       </c>
       <c r="D149" t="n">
-        <v>1222.0492324151</v>
+        <v>1222.098962722991</v>
       </c>
       <c r="E149" t="n">
-        <v>1231.602059203747</v>
+        <v>1231.648226489591</v>
       </c>
       <c r="F149" t="n">
         <v>54036</v>
@@ -18990,13 +18990,13 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1223.575225024568</v>
+        <v>1223.626774313489</v>
       </c>
       <c r="D150" t="n">
-        <v>1219.838408276077</v>
+        <v>1219.891701143035</v>
       </c>
       <c r="E150" t="n">
-        <v>1227.312041773058</v>
+        <v>1227.361847483942</v>
       </c>
       <c r="F150" t="n">
         <v>104642</v>
@@ -19141,13 +19141,13 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1223.025260026554</v>
+        <v>1223.074883855101</v>
       </c>
       <c r="D151" t="n">
-        <v>1216.044626283644</v>
+        <v>1216.09509690188</v>
       </c>
       <c r="E151" t="n">
-        <v>1230.005893769464</v>
+        <v>1230.054670808322</v>
       </c>
       <c r="F151" t="n">
         <v>9818</v>
@@ -19292,13 +19292,13 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1220.469396268749</v>
+        <v>1220.519477642192</v>
       </c>
       <c r="D152" t="n">
-        <v>1209.797820389999</v>
+        <v>1209.849312854154</v>
       </c>
       <c r="E152" t="n">
-        <v>1231.140972147499</v>
+        <v>1231.18964243023</v>
       </c>
       <c r="F152" t="n">
         <v>2896</v>
@@ -19443,13 +19443,13 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>1212.962533775487</v>
+        <v>1213.010015312354</v>
       </c>
       <c r="D153" t="n">
-        <v>1202.188842078536</v>
+        <v>1202.238392644843</v>
       </c>
       <c r="E153" t="n">
-        <v>1223.736225472439</v>
+        <v>1223.781637979865</v>
       </c>
       <c r="F153" t="n">
         <v>4652</v>
@@ -19590,13 +19590,13 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1212.813106078924</v>
+        <v>1212.86678253952</v>
       </c>
       <c r="D154" t="n">
-        <v>1207.778638534456</v>
+        <v>1207.83389519287</v>
       </c>
       <c r="E154" t="n">
-        <v>1217.847573623392</v>
+        <v>1217.899669886171</v>
       </c>
       <c r="F154" t="n">
         <v>24146</v>
@@ -19737,13 +19737,13 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>1211.22008775016</v>
+        <v>1211.251409545495</v>
       </c>
       <c r="D155" t="n">
-        <v>1207.057773898704</v>
+        <v>1207.090102365641</v>
       </c>
       <c r="E155" t="n">
-        <v>1215.382401601615</v>
+        <v>1215.41271672535</v>
       </c>
       <c r="F155" t="n">
         <v>49605</v>
@@ -19888,13 +19888,13 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1208.456303687424</v>
+        <v>1208.520002049767</v>
       </c>
       <c r="D156" t="n">
-        <v>1197.364024590518</v>
+        <v>1197.429555390333</v>
       </c>
       <c r="E156" t="n">
-        <v>1219.54858278433</v>
+        <v>1219.610448709202</v>
       </c>
       <c r="F156" t="n">
         <v>3090</v>
@@ -20039,13 +20039,13 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1203.939515486712</v>
+        <v>1203.987104397072</v>
       </c>
       <c r="D157" t="n">
-        <v>1197.829761541376</v>
+        <v>1197.878989017592</v>
       </c>
       <c r="E157" t="n">
-        <v>1210.049269432047</v>
+        <v>1210.095219776551</v>
       </c>
       <c r="F157" t="n">
         <v>21741</v>
@@ -20190,13 +20190,13 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1200.047156476676</v>
+        <v>1200.082324862897</v>
       </c>
       <c r="D158" t="n">
-        <v>1195.94111196782</v>
+        <v>1195.977350403531</v>
       </c>
       <c r="E158" t="n">
-        <v>1204.153200985533</v>
+        <v>1204.187299322264</v>
       </c>
       <c r="F158" t="n">
         <v>46616</v>
@@ -20341,13 +20341,13 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>1197.856884713367</v>
+        <v>1197.909170055806</v>
       </c>
       <c r="D159" t="n">
-        <v>1192.697788916538</v>
+        <v>1192.751511060209</v>
       </c>
       <c r="E159" t="n">
-        <v>1203.015980510196</v>
+        <v>1203.066829051403</v>
       </c>
       <c r="F159" t="n">
         <v>25055</v>
@@ -20492,13 +20492,13 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1197.112658911012</v>
+        <v>1197.161381139478</v>
       </c>
       <c r="D160" t="n">
-        <v>1192.852708312139</v>
+        <v>1192.903402580381</v>
       </c>
       <c r="E160" t="n">
-        <v>1201.372609509886</v>
+        <v>1201.419359698575</v>
       </c>
       <c r="F160" t="n">
         <v>73503</v>
@@ -20643,13 +20643,13 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1195.465199280357</v>
+        <v>1195.49973393297</v>
       </c>
       <c r="D161" t="n">
-        <v>1189.359529124976</v>
+        <v>1189.395744893988</v>
       </c>
       <c r="E161" t="n">
-        <v>1201.570869435737</v>
+        <v>1201.603722971951</v>
       </c>
       <c r="F161" t="n">
         <v>32191</v>
@@ -20710,13 +20710,13 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1191.027429550588</v>
+        <v>1191.07817906747</v>
       </c>
       <c r="D162" t="n">
-        <v>1183.920488201132</v>
+        <v>1183.973000812676</v>
       </c>
       <c r="E162" t="n">
-        <v>1198.134370900044</v>
+        <v>1198.183357322264</v>
       </c>
       <c r="F162" t="n">
         <v>17839</v>
@@ -20861,13 +20861,13 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1190.721355126224</v>
+        <v>1190.78520986817</v>
       </c>
       <c r="D163" t="n">
-        <v>1183.537608739013</v>
+        <v>1183.602804380142</v>
       </c>
       <c r="E163" t="n">
-        <v>1197.905101513435</v>
+        <v>1197.967615356198</v>
       </c>
       <c r="F163" t="n">
         <v>9901</v>
@@ -21008,13 +21008,13 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>1184.880406235636</v>
+        <v>1184.912127305348</v>
       </c>
       <c r="D164" t="n">
-        <v>1173.418627259525</v>
+        <v>1173.452504961609</v>
       </c>
       <c r="E164" t="n">
-        <v>1196.342185211747</v>
+        <v>1196.371749649087</v>
       </c>
       <c r="F164" t="n">
         <v>4932</v>
@@ -21159,13 +21159,13 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>1184.68670013018</v>
+        <v>1184.740200449117</v>
       </c>
       <c r="D165" t="n">
-        <v>1175.267773464436</v>
+        <v>1175.323398033449</v>
       </c>
       <c r="E165" t="n">
-        <v>1194.105626795924</v>
+        <v>1194.157002864785</v>
       </c>
       <c r="F165" t="n">
         <v>8214</v>
@@ -21310,13 +21310,13 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1183.691474266126</v>
+        <v>1183.741812034325</v>
       </c>
       <c r="D166" t="n">
-        <v>1176.873766242435</v>
+        <v>1176.925784966907</v>
       </c>
       <c r="E166" t="n">
-        <v>1190.509182289817</v>
+        <v>1190.557839101743</v>
       </c>
       <c r="F166" t="n">
         <v>15483</v>
@@ -21457,13 +21457,13 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>1183.069719751941</v>
+        <v>1183.098732727753</v>
       </c>
       <c r="D167" t="n">
-        <v>1174.397000416579</v>
+        <v>1174.427832133942</v>
       </c>
       <c r="E167" t="n">
-        <v>1191.742439087303</v>
+        <v>1191.769633321564</v>
       </c>
       <c r="F167" t="n">
         <v>6638</v>
@@ -21608,13 +21608,13 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>1182.980710011684</v>
+        <v>1183.007755668613</v>
       </c>
       <c r="D168" t="n">
-        <v>1173.339909064116</v>
+        <v>1173.369031040362</v>
       </c>
       <c r="E168" t="n">
-        <v>1192.621510959252</v>
+        <v>1192.646480296865</v>
       </c>
       <c r="F168" t="n">
         <v>7968</v>
@@ -21675,13 +21675,13 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1182.681365645242</v>
+        <v>1182.722731161721</v>
       </c>
       <c r="D169" t="n">
-        <v>1174.700636894622</v>
+        <v>1174.743876851052</v>
       </c>
       <c r="E169" t="n">
-        <v>1190.662094395861</v>
+        <v>1190.70158547239</v>
       </c>
       <c r="F169" t="n">
         <v>12637</v>
@@ -21742,13 +21742,13 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>1182.506489579367</v>
+        <v>1182.504007884267</v>
       </c>
       <c r="D170" t="n">
-        <v>1176.442312457066</v>
+        <v>1176.441498825942</v>
       </c>
       <c r="E170" t="n">
-        <v>1188.570666701668</v>
+        <v>1188.566516942592</v>
       </c>
       <c r="F170" t="n">
         <v>23893</v>
@@ -21893,13 +21893,13 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1179.986795039114</v>
+        <v>1180.024183861937</v>
       </c>
       <c r="D171" t="n">
-        <v>1174.083340123296</v>
+        <v>1174.122432014771</v>
       </c>
       <c r="E171" t="n">
-        <v>1185.890249954931</v>
+        <v>1185.925935709103</v>
       </c>
       <c r="F171" t="n">
         <v>32832</v>
@@ -21960,13 +21960,13 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1178.8131472179</v>
+        <v>1178.884561571042</v>
       </c>
       <c r="D172" t="n">
-        <v>1167.633295799144</v>
+        <v>1167.706586901553</v>
       </c>
       <c r="E172" t="n">
-        <v>1189.992998636657</v>
+        <v>1190.062536240532</v>
       </c>
       <c r="F172" t="n">
         <v>3188</v>
@@ -22111,13 +22111,13 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>1177.616089329854</v>
+        <v>1177.676170064263</v>
       </c>
       <c r="D173" t="n">
-        <v>1167.827185338387</v>
+        <v>1167.889283745029</v>
       </c>
       <c r="E173" t="n">
-        <v>1187.404993321322</v>
+        <v>1187.463056383497</v>
       </c>
       <c r="F173" t="n">
         <v>6535</v>
@@ -22258,13 +22258,13 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>1175.889883914665</v>
+        <v>1175.92282754203</v>
       </c>
       <c r="D174" t="n">
-        <v>1165.504076333083</v>
+        <v>1165.53917816652</v>
       </c>
       <c r="E174" t="n">
-        <v>1186.275691496247</v>
+        <v>1186.306476917539</v>
       </c>
       <c r="F174" t="n">
         <v>5006</v>
@@ -22405,13 +22405,13 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>1172.86857167191</v>
+        <v>1172.920896515775</v>
       </c>
       <c r="D175" t="n">
-        <v>1166.683196577572</v>
+        <v>1166.737567541781</v>
       </c>
       <c r="E175" t="n">
-        <v>1179.053946766248</v>
+        <v>1179.104225489769</v>
       </c>
       <c r="F175" t="n">
         <v>22479</v>
@@ -22552,13 +22552,13 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>1171.027454330182</v>
+        <v>1171.076399113687</v>
       </c>
       <c r="D176" t="n">
-        <v>1165.117583283203</v>
+        <v>1165.168139998825</v>
       </c>
       <c r="E176" t="n">
-        <v>1176.937325377161</v>
+        <v>1176.984658228549</v>
       </c>
       <c r="F176" t="n">
         <v>17766</v>
@@ -22703,13 +22703,13 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>1170.90272013249</v>
+        <v>1171.000274622691</v>
       </c>
       <c r="D177" t="n">
-        <v>1163.509728074749</v>
+        <v>1163.609105015326</v>
       </c>
       <c r="E177" t="n">
-        <v>1178.295712190231</v>
+        <v>1178.391444230056</v>
       </c>
       <c r="F177" t="n">
         <v>16056</v>
@@ -22850,13 +22850,13 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>1170.575772318886</v>
+        <v>1170.645428827034</v>
       </c>
       <c r="D178" t="n">
-        <v>1165.09145151071</v>
+        <v>1165.163119877561</v>
       </c>
       <c r="E178" t="n">
-        <v>1176.060093127061</v>
+        <v>1176.127737776507</v>
       </c>
       <c r="F178" t="n">
         <v>38492</v>
@@ -23001,13 +23001,13 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>1167.352296747548</v>
+        <v>1167.413584107437</v>
       </c>
       <c r="D179" t="n">
-        <v>1159.302262497047</v>
+        <v>1159.365547908964</v>
       </c>
       <c r="E179" t="n">
-        <v>1175.40233099805</v>
+        <v>1175.461620305909</v>
       </c>
       <c r="F179" t="n">
         <v>10224</v>
@@ -23148,13 +23148,13 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>1166.739192878171</v>
+        <v>1166.783332504956</v>
       </c>
       <c r="D180" t="n">
-        <v>1159.036410776665</v>
+        <v>1159.082053631871</v>
       </c>
       <c r="E180" t="n">
-        <v>1174.441974979677</v>
+        <v>1174.484611378041</v>
       </c>
       <c r="F180" t="n">
         <v>7936</v>
@@ -23299,13 +23299,13 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>1164.343898882683</v>
+        <v>1164.410970612149</v>
       </c>
       <c r="D181" t="n">
-        <v>1152.45367839703</v>
+        <v>1152.523033161836</v>
       </c>
       <c r="E181" t="n">
-        <v>1176.234119368336</v>
+        <v>1176.298908062461</v>
       </c>
       <c r="F181" t="n">
         <v>3777</v>
@@ -23446,13 +23446,13 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>1156.591925945045</v>
+        <v>1156.633208217194</v>
       </c>
       <c r="D182" t="n">
-        <v>1148.211187273183</v>
+        <v>1148.254392192315</v>
       </c>
       <c r="E182" t="n">
-        <v>1164.972664616907</v>
+        <v>1165.012024242073</v>
       </c>
       <c r="F182" t="n">
         <v>6837</v>
@@ -23597,13 +23597,13 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>1154.66888494322</v>
+        <v>1154.718382304435</v>
       </c>
       <c r="D183" t="n">
-        <v>1142.09661067051</v>
+        <v>1142.148503384554</v>
       </c>
       <c r="E183" t="n">
-        <v>1167.241159215931</v>
+        <v>1167.288261224316</v>
       </c>
       <c r="F183" t="n">
         <v>3585</v>
@@ -23748,13 +23748,13 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>1154.223974073882</v>
+        <v>1154.332935078334</v>
       </c>
       <c r="D184" t="n">
-        <v>1142.747279796642</v>
+        <v>1142.858318018465</v>
       </c>
       <c r="E184" t="n">
-        <v>1165.700668351122</v>
+        <v>1165.807552138202</v>
       </c>
       <c r="F184" t="n">
         <v>3231</v>
@@ -23899,13 +23899,13 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>1152.374413805153</v>
+        <v>1152.418270256552</v>
       </c>
       <c r="D185" t="n">
-        <v>1139.239088280219</v>
+        <v>1139.285820082545</v>
       </c>
       <c r="E185" t="n">
-        <v>1165.509739330087</v>
+        <v>1165.55072043056</v>
       </c>
       <c r="F185" t="n">
         <v>4155</v>
@@ -24046,13 +24046,13 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>1152.215364672984</v>
+        <v>1152.261078770421</v>
       </c>
       <c r="D186" t="n">
-        <v>1136.93476536675</v>
+        <v>1136.984219701136</v>
       </c>
       <c r="E186" t="n">
-        <v>1167.495963979219</v>
+        <v>1167.537937839706</v>
       </c>
       <c r="F186" t="n">
         <v>1679</v>
@@ -24193,13 +24193,13 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>1150.69141916909</v>
+        <v>1150.724481338786</v>
       </c>
       <c r="D187" t="n">
-        <v>1138.483965051335</v>
+        <v>1138.520382072628</v>
       </c>
       <c r="E187" t="n">
-        <v>1162.898873286845</v>
+        <v>1162.928580604944</v>
       </c>
       <c r="F187" t="n">
         <v>2572</v>
@@ -24340,13 +24340,13 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>1149.463519500801</v>
+        <v>1149.508507221554</v>
       </c>
       <c r="D188" t="n">
-        <v>1140.267885628591</v>
+        <v>1140.315425897636</v>
       </c>
       <c r="E188" t="n">
-        <v>1158.659153373012</v>
+        <v>1158.701588545472</v>
       </c>
       <c r="F188" t="n">
         <v>7044</v>
@@ -24491,13 +24491,13 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>1149.337974797416</v>
+        <v>1149.39597365394</v>
       </c>
       <c r="D189" t="n">
-        <v>1142.697651044436</v>
+        <v>1142.757412245208</v>
       </c>
       <c r="E189" t="n">
-        <v>1155.978298550396</v>
+        <v>1156.034535062672</v>
       </c>
       <c r="F189" t="n">
         <v>19402</v>
@@ -24642,13 +24642,13 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>1148.057274130852</v>
+        <v>1148.074565917073</v>
       </c>
       <c r="D190" t="n">
-        <v>1131.048776234416</v>
+        <v>1131.070088588212</v>
       </c>
       <c r="E190" t="n">
-        <v>1165.065772027288</v>
+        <v>1165.079043245935</v>
       </c>
       <c r="F190" t="n">
         <v>1295</v>
@@ -24789,13 +24789,13 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>1143.788350888521</v>
+        <v>1143.845996577317</v>
       </c>
       <c r="D191" t="n">
-        <v>1133.914318789691</v>
+        <v>1133.973882532601</v>
       </c>
       <c r="E191" t="n">
-        <v>1153.66238298735</v>
+        <v>1153.718110622032</v>
       </c>
       <c r="F191" t="n">
         <v>4737</v>
@@ -24940,13 +24940,13 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>1143.070897709739</v>
+        <v>1143.116990954994</v>
       </c>
       <c r="D192" t="n">
-        <v>1136.634150869725</v>
+        <v>1136.681733326911</v>
       </c>
       <c r="E192" t="n">
-        <v>1149.507644549753</v>
+        <v>1149.552248583076</v>
       </c>
       <c r="F192" t="n">
         <v>12297</v>
@@ -25091,13 +25091,13 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>1141.506128128061</v>
+        <v>1141.534848370228</v>
       </c>
       <c r="D193" t="n">
-        <v>1134.825651166476</v>
+        <v>1134.856588411879</v>
       </c>
       <c r="E193" t="n">
-        <v>1148.186605089647</v>
+        <v>1148.213108328577</v>
       </c>
       <c r="F193" t="n">
         <v>19367</v>
@@ -25238,13 +25238,13 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>1141.354649909911</v>
+        <v>1141.423792947119</v>
       </c>
       <c r="D194" t="n">
-        <v>1134.643546413257</v>
+        <v>1134.714459799777</v>
       </c>
       <c r="E194" t="n">
-        <v>1148.065753406565</v>
+        <v>1148.13312609446</v>
       </c>
       <c r="F194" t="n">
         <v>19174</v>
@@ -25389,13 +25389,13 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>1139.297579686782</v>
+        <v>1139.318108555044</v>
       </c>
       <c r="D195" t="n">
-        <v>1128.378015978792</v>
+        <v>1128.400870244383</v>
       </c>
       <c r="E195" t="n">
-        <v>1150.217143394772</v>
+        <v>1150.235346865704</v>
       </c>
       <c r="F195" t="n">
         <v>4964</v>
@@ -25540,13 +25540,13 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>1137.668034791777</v>
+        <v>1137.671935026667</v>
       </c>
       <c r="D196" t="n">
-        <v>1128.199278461151</v>
+        <v>1128.205142501026</v>
       </c>
       <c r="E196" t="n">
-        <v>1147.136791122404</v>
+        <v>1147.138727552308</v>
       </c>
       <c r="F196" t="n">
         <v>8925</v>
@@ -25691,13 +25691,13 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>1136.797718774997</v>
+        <v>1136.846932559639</v>
       </c>
       <c r="D197" t="n">
-        <v>1127.926265117463</v>
+        <v>1127.977602650871</v>
       </c>
       <c r="E197" t="n">
-        <v>1145.669172432531</v>
+        <v>1145.716262468406</v>
       </c>
       <c r="F197" t="n">
         <v>7366</v>
@@ -25842,13 +25842,13 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>1130.755746927028</v>
+        <v>1130.811551696537</v>
       </c>
       <c r="D198" t="n">
-        <v>1121.945954202173</v>
+        <v>1122.003972377587</v>
       </c>
       <c r="E198" t="n">
-        <v>1139.565539651884</v>
+        <v>1139.619131015486</v>
       </c>
       <c r="F198" t="n">
         <v>11118</v>
@@ -25989,13 +25989,13 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>1129.771000591089</v>
+        <v>1129.807328695872</v>
       </c>
       <c r="D199" t="n">
-        <v>1122.35720385151</v>
+        <v>1122.395469494099</v>
       </c>
       <c r="E199" t="n">
-        <v>1137.184797330667</v>
+        <v>1137.219187897646</v>
       </c>
       <c r="F199" t="n">
         <v>20685</v>
@@ -26140,13 +26140,13 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>1128.051363070616</v>
+        <v>1128.111661535967</v>
       </c>
       <c r="D200" t="n">
-        <v>1121.660821762497</v>
+        <v>1121.722757589427</v>
       </c>
       <c r="E200" t="n">
-        <v>1134.441904378735</v>
+        <v>1134.500565482507</v>
       </c>
       <c r="F200" t="n">
         <v>20118</v>
@@ -26291,13 +26291,13 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>1127.443918051297</v>
+        <v>1127.479566396374</v>
       </c>
       <c r="D201" t="n">
-        <v>1115.390371550159</v>
+        <v>1115.429528375787</v>
       </c>
       <c r="E201" t="n">
-        <v>1139.497464552435</v>
+        <v>1139.529604416961</v>
       </c>
       <c r="F201" t="n">
         <v>2921</v>
@@ -26438,13 +26438,13 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>1126.882992031371</v>
+        <v>1126.9291322708</v>
       </c>
       <c r="D202" t="n">
-        <v>1111.332373274796</v>
+        <v>1111.382197258206</v>
       </c>
       <c r="E202" t="n">
-        <v>1142.433610787946</v>
+        <v>1142.476067283392</v>
       </c>
       <c r="F202" t="n">
         <v>1785</v>
@@ -26585,13 +26585,13 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>1121.550342372711</v>
+        <v>1121.581081823224</v>
       </c>
       <c r="D203" t="n">
-        <v>1110.595240727589</v>
+        <v>1110.628230543668</v>
       </c>
       <c r="E203" t="n">
-        <v>1132.505444017833</v>
+        <v>1132.533933102781</v>
       </c>
       <c r="F203" t="n">
         <v>5182</v>
@@ -26732,13 +26732,13 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>1119.11837001925</v>
+        <v>1119.166006630958</v>
       </c>
       <c r="D204" t="n">
-        <v>1101.032012932622</v>
+        <v>1101.083892260423</v>
       </c>
       <c r="E204" t="n">
-        <v>1137.204727105878</v>
+        <v>1137.248121001493</v>
       </c>
       <c r="F204" t="n">
         <v>1143</v>
@@ -26883,13 +26883,13 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>1116.588271680483</v>
+        <v>1116.594520052223</v>
       </c>
       <c r="D205" t="n">
-        <v>1108.870063272903</v>
+        <v>1108.878041699289</v>
       </c>
       <c r="E205" t="n">
-        <v>1124.306480088063</v>
+        <v>1124.310998405157</v>
       </c>
       <c r="F205" t="n">
         <v>10854</v>
@@ -27034,13 +27034,13 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>1115.247301605616</v>
+        <v>1115.276766985227</v>
       </c>
       <c r="D206" t="n">
-        <v>1106.142724442065</v>
+        <v>1106.174950898874</v>
       </c>
       <c r="E206" t="n">
-        <v>1124.351878769167</v>
+        <v>1124.37858307158</v>
       </c>
       <c r="F206" t="n">
         <v>6923</v>
@@ -27181,13 +27181,13 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>1114.63957317114</v>
+        <v>1114.684844082725</v>
       </c>
       <c r="D207" t="n">
-        <v>1100.298624640867</v>
+        <v>1100.347268485597</v>
       </c>
       <c r="E207" t="n">
-        <v>1128.980521701413</v>
+        <v>1129.022419679854</v>
       </c>
       <c r="F207" t="n">
         <v>2199</v>
@@ -27328,13 +27328,13 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>1111.07233691021</v>
+        <v>1111.116598456527</v>
       </c>
       <c r="D208" t="n">
-        <v>1103.19250347044</v>
+        <v>1103.238483013187</v>
       </c>
       <c r="E208" t="n">
-        <v>1118.95217034998</v>
+        <v>1118.994713899866</v>
       </c>
       <c r="F208" t="n">
         <v>8045</v>
@@ -27479,13 +27479,13 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>1110.298778853755</v>
+        <v>1110.324123567318</v>
       </c>
       <c r="D209" t="n">
-        <v>1101.03627688634</v>
+        <v>1101.063789404209</v>
       </c>
       <c r="E209" t="n">
-        <v>1119.56128082117</v>
+        <v>1119.584457730428</v>
       </c>
       <c r="F209" t="n">
         <v>8977</v>
@@ -27630,13 +27630,13 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>1107.854375958829</v>
+        <v>1107.931015910331</v>
       </c>
       <c r="D210" t="n">
-        <v>1100.815805174532</v>
+        <v>1100.894211262731</v>
       </c>
       <c r="E210" t="n">
-        <v>1114.892946743126</v>
+        <v>1114.967820557931</v>
       </c>
       <c r="F210" t="n">
         <v>14148</v>
@@ -27781,13 +27781,13 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>1093.583955448846</v>
+        <v>1093.586092234318</v>
       </c>
       <c r="D211" t="n">
-        <v>1082.126514124281</v>
+        <v>1082.131119642866</v>
       </c>
       <c r="E211" t="n">
-        <v>1105.041396773412</v>
+        <v>1105.041064825771</v>
       </c>
       <c r="F211" t="n">
         <v>4780</v>
@@ -27932,13 +27932,13 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>1091.07159923733</v>
+        <v>1091.088241320796</v>
       </c>
       <c r="D212" t="n">
-        <v>1081.754720783446</v>
+        <v>1081.773446739254</v>
       </c>
       <c r="E212" t="n">
-        <v>1100.388477691213</v>
+        <v>1100.403035902337</v>
       </c>
       <c r="F212" t="n">
         <v>7597</v>
@@ -28083,13 +28083,13 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>1073.568969986992</v>
+        <v>1073.650889079105</v>
       </c>
       <c r="D213" t="n">
-        <v>1062.436032521091</v>
+        <v>1062.520502410783</v>
       </c>
       <c r="E213" t="n">
-        <v>1084.701907452892</v>
+        <v>1084.781275747426</v>
       </c>
       <c r="F213" t="n">
         <v>6328</v>
@@ -28234,13 +28234,13 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>1070.864025141609</v>
+        <v>1070.899979170712</v>
       </c>
       <c r="D214" t="n">
-        <v>1061.042598224717</v>
+        <v>1061.082731731523</v>
       </c>
       <c r="E214" t="n">
-        <v>1080.685452058501</v>
+        <v>1080.717226609901</v>
       </c>
       <c r="F214" t="n">
         <v>6965</v>
@@ -28381,13 +28381,13 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>1070.134004768088</v>
+        <v>1070.101284387255</v>
       </c>
       <c r="D215" t="n">
-        <v>1058.741200069122</v>
+        <v>1058.71255583073</v>
       </c>
       <c r="E215" t="n">
-        <v>1081.526809467054</v>
+        <v>1081.49001294378</v>
       </c>
       <c r="F215" t="n">
         <v>5745</v>
@@ -28528,13 +28528,13 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>1067.624666533576</v>
+        <v>1067.624670294893</v>
       </c>
       <c r="D216" t="n">
-        <v>1052.482152283464</v>
+        <v>1052.486905750884</v>
       </c>
       <c r="E216" t="n">
-        <v>1082.767180783688</v>
+        <v>1082.762434838902</v>
       </c>
       <c r="F216" t="n">
         <v>1743</v>
@@ -28675,13 +28675,13 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>1063.364699681121</v>
+        <v>1063.369238360916</v>
       </c>
       <c r="D217" t="n">
-        <v>1051.452835302599</v>
+        <v>1051.461416717826</v>
       </c>
       <c r="E217" t="n">
-        <v>1075.276564059643</v>
+        <v>1075.277060004007</v>
       </c>
       <c r="F217" t="n">
         <v>3924</v>
@@ -28822,13 +28822,13 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>1056.511145632316</v>
+        <v>1056.536507961287</v>
       </c>
       <c r="D218" t="n">
-        <v>1044.878666831679</v>
+        <v>1044.906491526109</v>
       </c>
       <c r="E218" t="n">
-        <v>1068.143624432953</v>
+        <v>1068.166524396464</v>
       </c>
       <c r="F218" t="n">
         <v>4658</v>
@@ -28969,13 +28969,13 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>1042.262682731656</v>
+        <v>1042.28574062834</v>
       </c>
       <c r="D219" t="n">
-        <v>1030.938029741935</v>
+        <v>1030.965164873791</v>
       </c>
       <c r="E219" t="n">
-        <v>1053.587335721378</v>
+        <v>1053.606316382889</v>
       </c>
       <c r="F219" t="n">
         <v>4845</v>
@@ -29116,13 +29116,13 @@
         </is>
       </c>
       <c r="C220" t="n">
-        <v>1024.708133394474</v>
+        <v>1024.734889497263</v>
       </c>
       <c r="D220" t="n">
-        <v>1011.16845816492</v>
+        <v>1011.198530060076</v>
       </c>
       <c r="E220" t="n">
-        <v>1038.247808624028</v>
+        <v>1038.271248934452</v>
       </c>
       <c r="F220" t="n">
         <v>2658</v>
@@ -29263,13 +29263,13 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>1023.450000128857</v>
+        <v>1023.454015097337</v>
       </c>
       <c r="D221" t="n">
-        <v>1012.647417644738</v>
+        <v>1012.655627852093</v>
       </c>
       <c r="E221" t="n">
-        <v>1034.252582612976</v>
+        <v>1034.252402342581</v>
       </c>
       <c r="F221" t="n">
         <v>6310</v>
@@ -29410,13 +29410,13 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>995.7618433901987</v>
+        <v>995.8029648280213</v>
       </c>
       <c r="D222" t="n">
-        <v>983.2636681582258</v>
+        <v>983.3091568473337</v>
       </c>
       <c r="E222" t="n">
-        <v>1008.260018622172</v>
+        <v>1008.296772808709</v>
       </c>
       <c r="F222" t="n">
         <v>4914</v>
@@ -29557,13 +29557,13 @@
         </is>
       </c>
       <c r="C223" t="n">
-        <v>992.4789855757126</v>
+        <v>992.5030939561772</v>
       </c>
       <c r="D223" t="n">
-        <v>980.178463778203</v>
+        <v>980.2068736695239</v>
       </c>
       <c r="E223" t="n">
-        <v>1004.779507373222</v>
+        <v>1004.799314242831</v>
       </c>
       <c r="F223" t="n">
         <v>4203</v>
@@ -29704,13 +29704,13 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>982.3976362191788</v>
+        <v>982.3750269259182</v>
       </c>
       <c r="D224" t="n">
-        <v>968.9591463641034</v>
+        <v>968.9419979418211</v>
       </c>
       <c r="E224" t="n">
-        <v>995.8361260742545</v>
+        <v>995.8080559100151</v>
       </c>
       <c r="F224" t="n">
         <v>3412</v>
@@ -29851,13 +29851,13 @@
         </is>
       </c>
       <c r="C225" t="n">
-        <v>975.0640371046704</v>
+        <v>975.0386311413082</v>
       </c>
       <c r="D225" t="n">
-        <v>959.3863965707224</v>
+        <v>959.3678169475826</v>
       </c>
       <c r="E225" t="n">
-        <v>990.7416776386183</v>
+        <v>990.7094453350337</v>
       </c>
       <c r="F225" t="n">
         <v>2391</v>
@@ -30002,13 +30002,13 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>953.136001015748</v>
+        <v>953.1687355209536</v>
       </c>
       <c r="D226" t="n">
-        <v>940.502915208808</v>
+        <v>940.5409653587996</v>
       </c>
       <c r="E226" t="n">
-        <v>965.7690868226882</v>
+        <v>965.7965056831076</v>
       </c>
       <c r="F226" t="n">
         <v>3287</v>
@@ -30851,7 +30851,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>deepseek-v4.1-flash-max</t>
+          <t>glm-5.3-flash</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -30866,7 +30866,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>glm-5.3-flash</t>
+          <t>deepseek-v4.1-flash-max</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -30896,7 +30896,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>glm-5.1</t>
+          <t>deepseek-v4-pro-high-20260813</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -30911,7 +30911,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro-high-20260813</t>
+          <t>glm-5.1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -30995,38 +30995,38 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>hy3</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>299</v>
-      </c>
-      <c r="C14" t="n">
-        <v>21</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>deepseek-v4-pro-high-preview</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>aa_single_scrape</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro-high-preview</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+          <t>hy3</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>299</v>
+      </c>
+      <c r="C15" t="n">
+        <v>21</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>aa_single_scrape</t>
         </is>
       </c>
     </row>
@@ -31361,30 +31361,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>muse-glimmer</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>30</v>
-      </c>
-      <c r="C32" t="n">
-        <v>30</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>dense</t>
-        </is>
-      </c>
+          <t>deepseek-v3.2-exp-thinking</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>aa_single_scrape</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>deepseek-v3.2-exp-thinking</t>
+          <t>deepseek-v3.2</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -31399,15 +31391,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>deepseek-v3.2</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
+          <t>muse-glimmer</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>30</v>
+      </c>
+      <c r="C34" t="n">
+        <v>30</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>dense</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>aa_single_scrape</t>
         </is>
       </c>
     </row>
@@ -31543,7 +31543,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-terminus-thinking</t>
+          <t>deepseek-v3.1</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -31558,38 +31558,38 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>deepseek-v3.1</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
+          <t>qwen3.5-122b-a10b</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>122</v>
+      </c>
+      <c r="C43" t="n">
+        <v>10</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>qwen3.5-122b-a10b</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>122</v>
-      </c>
-      <c r="C44" t="n">
-        <v>10</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>deepseek-v3.1-terminus-thinking</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -32854,14 +32854,14 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>gpt-oss-20b</t>
+          <t>gemma-3n-e4b-it</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>21</v>
+        <v>8.4</v>
       </c>
       <c r="C107" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -32870,21 +32870,21 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>aa_single_scrape</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>gemma-3n-e4b-it</t>
+          <t>gpt-oss-20b</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>8.4</v>
+        <v>21</v>
       </c>
       <c r="C108" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -32893,7 +32893,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>aa_single_scrape</t>
+          <t>override</t>
         </is>
       </c>
     </row>
@@ -33091,14 +33091,14 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>mistral-small-3.1-24b-instruct-2503</t>
+          <t>qwen2.5-72b-instruct</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="C118" t="n">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -33114,14 +33114,14 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>qwen2.5-72b-instruct</t>
+          <t>mistral-small-3.1-24b-instruct-2503</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="C119" t="n">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -33183,14 +33183,14 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>granite-4.2-3b</t>
+          <t>granite-4.2-8b</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C122" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -33206,14 +33206,14 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>gemma-2-27b-it</t>
+          <t>granite-4.2-3b</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="C123" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -33229,38 +33229,38 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>jamba-1.5-large</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr"/>
-      <c r="C124" t="inlineStr"/>
-      <c r="D124" t="inlineStr"/>
+          <t>gemma-2-27b-it</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>27</v>
+      </c>
+      <c r="C124" t="n">
+        <v>27</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>dense</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>granite-4.2-8b</t>
-        </is>
-      </c>
-      <c r="B125" t="n">
-        <v>8</v>
-      </c>
-      <c r="C125" t="n">
-        <v>8</v>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>dense</t>
-        </is>
-      </c>
+          <t>jamba-1.5-large</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr"/>
+      <c r="C125" t="inlineStr"/>
+      <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -33290,14 +33290,14 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>llama-3.1-nemotron-51b-instruct</t>
+          <t>olmo-3.1-32b-think</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="C127" t="n">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -33313,14 +33313,14 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>olmo-3.1-32b-think</t>
+          <t>llama-3.1-nemotron-51b-instruct</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="C128" t="n">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
